--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FA9B08-323D-4013-A62E-287D8C61B49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF064698-A154-4B25-BE65-5FA2D3540356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
@@ -860,7 +860,7 @@
         <v>414000</v>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1775265.6417320003</v>
@@ -869,22 +869,22 @@
         <v>2337972.5216000001</v>
       </c>
       <c r="H2">
-        <v>9999999</v>
-      </c>
-      <c r="I2" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1052044.8400000001</v>
       </c>
       <c r="K2">
-        <v>1673707.7000000002</v>
+        <v>1673707.7</v>
       </c>
       <c r="L2">
-        <v>9999999</v>
-      </c>
-      <c r="M2" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
       <c r="N2">
         <v>90210</v>
@@ -913,7 +913,7 @@
         <v>414000</v>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1722922.372057667</v>
@@ -922,10 +922,10 @@
         <v>2318026.381866667</v>
       </c>
       <c r="H3">
-        <v>9999999</v>
-      </c>
-      <c r="I3" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1042480.7960000001</v>
@@ -934,10 +934,10 @@
         <v>1660955.6413333334</v>
       </c>
       <c r="L3">
-        <v>9999999</v>
-      </c>
-      <c r="M3" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
       </c>
       <c r="N3">
         <v>88856.85</v>
@@ -966,7 +966,7 @@
         <v>414000</v>
       </c>
       <c r="E4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1670579.1023833335</v>
@@ -975,10 +975,10 @@
         <v>2298080.2421333333</v>
       </c>
       <c r="H4">
-        <v>9999999</v>
-      </c>
-      <c r="I4" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1032916.7520000001</v>
@@ -987,10 +987,10 @@
         <v>1648203.5826666667</v>
       </c>
       <c r="L4">
-        <v>9999999</v>
-      </c>
-      <c r="M4" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
       </c>
       <c r="N4">
         <v>87523</v>
@@ -1019,7 +1019,7 @@
         <v>414000</v>
       </c>
       <c r="E5">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>1618235.832709</v>
@@ -1028,10 +1028,10 @@
         <v>2278134.1023999997</v>
       </c>
       <c r="H5">
-        <v>9999999</v>
-      </c>
-      <c r="I5" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1023352.708</v>
@@ -1040,10 +1040,10 @@
         <v>1635451.524</v>
       </c>
       <c r="L5">
-        <v>9999999</v>
-      </c>
-      <c r="M5" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
       <c r="N5">
         <v>86209.15</v>
@@ -1072,7 +1072,7 @@
         <v>414000</v>
       </c>
       <c r="E6">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>1565892.5630346665</v>
@@ -1081,10 +1081,10 @@
         <v>2258187.9626666661</v>
       </c>
       <c r="H6">
-        <v>9999999</v>
-      </c>
-      <c r="I6" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
       </c>
       <c r="J6">
         <v>1013788.6639999999</v>
@@ -1093,10 +1093,10 @@
         <v>1622699.4653333335</v>
       </c>
       <c r="L6">
-        <v>9999999</v>
-      </c>
-      <c r="M6" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
       </c>
       <c r="N6">
         <v>84915.01</v>
@@ -1125,7 +1125,7 @@
         <v>414000</v>
       </c>
       <c r="E7">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>1513549.293360333</v>
@@ -1134,10 +1134,10 @@
         <v>2238241.8229333302</v>
       </c>
       <c r="H7">
-        <v>9999999</v>
-      </c>
-      <c r="I7" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
       </c>
       <c r="J7">
         <v>1004224.62</v>
@@ -1146,10 +1146,10 @@
         <v>1609947.4066666667</v>
       </c>
       <c r="L7">
-        <v>9999999</v>
-      </c>
-      <c r="M7" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
       </c>
       <c r="N7">
         <v>83640.289999999994</v>
@@ -1178,7 +1178,7 @@
         <v>414000</v>
       </c>
       <c r="E8">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>1461206.0236859999</v>
@@ -1187,10 +1187,10 @@
         <v>2218295.6831999999</v>
       </c>
       <c r="H8">
-        <v>9999999</v>
-      </c>
-      <c r="I8" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
       </c>
       <c r="J8">
         <v>994660.57600000012</v>
@@ -1199,10 +1199,10 @@
         <v>1597195.3480000002</v>
       </c>
       <c r="L8">
-        <v>9999999</v>
-      </c>
-      <c r="M8" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
       </c>
       <c r="N8">
         <v>82384.69</v>
@@ -1231,7 +1231,7 @@
         <v>414000</v>
       </c>
       <c r="E9">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>1444015.15599508</v>
@@ -1240,10 +1240,10 @@
         <v>2205259.4561600001</v>
       </c>
       <c r="H9">
-        <v>9999999</v>
-      </c>
-      <c r="I9" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
       </c>
       <c r="J9">
         <v>992747.76720000012</v>
@@ -1252,10 +1252,10 @@
         <v>1594326.1348000003</v>
       </c>
       <c r="L9">
-        <v>9999999</v>
-      </c>
-      <c r="M9" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
       </c>
       <c r="N9">
         <v>81147.92</v>
@@ -1284,7 +1284,7 @@
         <v>414000</v>
       </c>
       <c r="E10">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>1426824.2883041599</v>
@@ -1293,10 +1293,10 @@
         <v>2192223.2291199998</v>
       </c>
       <c r="H10">
-        <v>9999999</v>
-      </c>
-      <c r="I10" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
       </c>
       <c r="J10">
         <v>990834.9584</v>
@@ -1305,10 +1305,10 @@
         <v>1591456.9216000002</v>
       </c>
       <c r="L10">
-        <v>9999999</v>
-      </c>
-      <c r="M10" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
       </c>
       <c r="N10">
         <v>79929.7</v>
@@ -1337,7 +1337,7 @@
         <v>414000</v>
       </c>
       <c r="E11">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>1409633.42061324</v>
@@ -1346,10 +1346,10 @@
         <v>2179187.0020799995</v>
       </c>
       <c r="H11">
-        <v>9999999</v>
-      </c>
-      <c r="I11" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
       </c>
       <c r="J11">
         <v>988922.1496</v>
@@ -1358,10 +1358,10 @@
         <v>1588587.7084000004</v>
       </c>
       <c r="L11">
-        <v>9999999</v>
-      </c>
-      <c r="M11" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
       </c>
       <c r="N11">
         <v>78729.759999999995</v>
@@ -1390,7 +1390,7 @@
         <v>414000</v>
       </c>
       <c r="E12">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>1392442.5529223196</v>
@@ -1399,10 +1399,10 @@
         <v>2166150.7750399997</v>
       </c>
       <c r="H12">
-        <v>9999999</v>
-      </c>
-      <c r="I12" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
       </c>
       <c r="J12">
         <v>987009.34079999989</v>
@@ -1411,10 +1411,10 @@
         <v>1585718.4952000002</v>
       </c>
       <c r="L12">
-        <v>9999999</v>
-      </c>
-      <c r="M12" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
       </c>
       <c r="N12">
         <v>77547.820000000007</v>
@@ -1443,7 +1443,7 @@
         <v>414000</v>
       </c>
       <c r="E13">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>1375251.6852313997</v>
@@ -1452,10 +1452,10 @@
         <v>2153114.5479999995</v>
       </c>
       <c r="H13">
-        <v>9999999</v>
-      </c>
-      <c r="I13" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
       </c>
       <c r="J13">
         <v>985096.53199999989</v>
@@ -1464,10 +1464,10 @@
         <v>1582849.2820000004</v>
       </c>
       <c r="L13">
-        <v>9999999</v>
-      </c>
-      <c r="M13" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
       </c>
       <c r="N13">
         <v>76383.600000000006</v>
@@ -1496,7 +1496,7 @@
         <v>414000</v>
       </c>
       <c r="E14">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>1358060.8175404796</v>
@@ -1505,10 +1505,10 @@
         <v>2140078.3209599997</v>
       </c>
       <c r="H14">
-        <v>9999999</v>
-      </c>
-      <c r="I14" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
       </c>
       <c r="J14">
         <v>983183.72319999977</v>
@@ -1517,10 +1517,10 @@
         <v>1579980.0688000005</v>
       </c>
       <c r="L14">
-        <v>9999999</v>
-      </c>
-      <c r="M14" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
       </c>
       <c r="N14">
         <v>75236.84</v>
@@ -1549,7 +1549,7 @@
         <v>414000</v>
       </c>
       <c r="E15">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>1340869.9498495597</v>
@@ -1558,10 +1558,10 @@
         <v>2127042.0939199994</v>
       </c>
       <c r="H15">
-        <v>9999999</v>
-      </c>
-      <c r="I15" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
       </c>
       <c r="J15">
         <v>981270.91439999978</v>
@@ -1570,10 +1570,10 @@
         <v>1577110.8556000004</v>
       </c>
       <c r="L15">
-        <v>9999999</v>
-      </c>
-      <c r="M15" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
       </c>
       <c r="N15">
         <v>74107.289999999994</v>
@@ -1602,7 +1602,7 @@
         <v>414000</v>
       </c>
       <c r="E16">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>1323679.0821586396</v>
@@ -1611,10 +1611,10 @@
         <v>2114005.8668799992</v>
       </c>
       <c r="H16">
-        <v>9999999</v>
-      </c>
-      <c r="I16" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
       </c>
       <c r="J16">
         <v>979358.10559999966</v>
@@ -1623,10 +1623,10 @@
         <v>1574241.6424000005</v>
       </c>
       <c r="L16">
-        <v>9999999</v>
-      </c>
-      <c r="M16" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
       </c>
       <c r="N16">
         <v>72994.679999999993</v>
@@ -1655,7 +1655,7 @@
         <v>414000</v>
       </c>
       <c r="E17">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <v>1306488.2144677194</v>
@@ -1664,10 +1664,10 @@
         <v>2100969.6398399994</v>
       </c>
       <c r="H17">
-        <v>9999999</v>
-      </c>
-      <c r="I17" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
       </c>
       <c r="J17">
         <v>977445.29679999966</v>
@@ -1676,10 +1676,10 @@
         <v>1571372.4292000004</v>
       </c>
       <c r="L17">
-        <v>9999999</v>
-      </c>
-      <c r="M17" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
       </c>
       <c r="N17">
         <v>71898.759999999995</v>
@@ -1708,7 +1708,7 @@
         <v>414000</v>
       </c>
       <c r="E18">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>1288027.7959324</v>
@@ -1717,10 +1717,10 @@
         <v>2087933.4128</v>
       </c>
       <c r="H18">
-        <v>9999999</v>
-      </c>
-      <c r="I18" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
       </c>
       <c r="J18">
         <v>975532.48799999955</v>
@@ -1729,10 +1729,10 @@
         <v>1568503.2160000005</v>
       </c>
       <c r="L18">
-        <v>9999999</v>
-      </c>
-      <c r="M18" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
       </c>
       <c r="N18">
         <v>70819.28</v>
@@ -1761,7 +1761,7 @@
         <v>414000</v>
       </c>
       <c r="E19">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>1288154.7510168403</v>
@@ -1770,10 +1770,10 @@
         <v>2076927.41784</v>
       </c>
       <c r="H19">
-        <v>9999999</v>
-      </c>
-      <c r="I19" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
       </c>
       <c r="J19">
         <v>973619.67919999966</v>
@@ -1782,10 +1782,10 @@
         <v>1565634.0028000006</v>
       </c>
       <c r="L19">
-        <v>9999999</v>
-      </c>
-      <c r="M19" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
       </c>
       <c r="N19">
         <v>69755.990000000005</v>
@@ -1814,7 +1814,7 @@
         <v>414000</v>
       </c>
       <c r="E20">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <v>1288281.7061012802</v>
@@ -1823,10 +1823,10 @@
         <v>2065921.4228800002</v>
       </c>
       <c r="H20">
-        <v>9999999</v>
-      </c>
-      <c r="I20" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
       </c>
       <c r="J20">
         <v>971706.87039999955</v>
@@ -1835,10 +1835,10 @@
         <v>1562764.7896000005</v>
       </c>
       <c r="L20">
-        <v>9999999</v>
-      </c>
-      <c r="M20" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
       </c>
       <c r="N20">
         <v>68708.649999999994</v>
@@ -1867,7 +1867,7 @@
         <v>414000</v>
       </c>
       <c r="E21">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <v>1288408.6611857202</v>
@@ -1876,10 +1876,10 @@
         <v>2054915.4279200002</v>
       </c>
       <c r="H21">
-        <v>9999999</v>
-      </c>
-      <c r="I21" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
       </c>
       <c r="J21">
         <v>969794.06159999955</v>
@@ -1888,10 +1888,10 @@
         <v>1559895.5764000006</v>
       </c>
       <c r="L21">
-        <v>9999999</v>
-      </c>
-      <c r="M21" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
       </c>
       <c r="N21">
         <v>67677.02</v>
@@ -1920,7 +1920,7 @@
         <v>414000</v>
       </c>
       <c r="E22">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <v>1288535.6162701603</v>
@@ -1929,10 +1929,10 @@
         <v>2043909.4329600004</v>
       </c>
       <c r="H22">
-        <v>9999999</v>
-      </c>
-      <c r="I22" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
       </c>
       <c r="J22">
         <v>967881.25279999943</v>
@@ -1941,10 +1941,10 @@
         <v>1557026.3632000005</v>
       </c>
       <c r="L22">
-        <v>9999999</v>
-      </c>
-      <c r="M22" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
       </c>
       <c r="N22">
         <v>66660.86</v>
@@ -1973,7 +1973,7 @@
         <v>414000</v>
       </c>
       <c r="E23">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>1288662.5713546001</v>
@@ -1982,10 +1982,10 @@
         <v>2032903.4380000005</v>
       </c>
       <c r="H23">
-        <v>9999999</v>
-      </c>
-      <c r="I23" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
       </c>
       <c r="J23">
         <v>965968.44399999944</v>
@@ -1994,10 +1994,10 @@
         <v>1554157.1500000006</v>
       </c>
       <c r="L23">
-        <v>9999999</v>
-      </c>
-      <c r="M23" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
       </c>
       <c r="N23">
         <v>65659.95</v>
@@ -2026,7 +2026,7 @@
         <v>414000</v>
       </c>
       <c r="E24">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>1288789.5264390404</v>
@@ -2035,10 +2035,10 @@
         <v>2021897.4430400007</v>
       </c>
       <c r="H24">
-        <v>9999999</v>
-      </c>
-      <c r="I24" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
       </c>
       <c r="J24">
         <v>964055.63519999932</v>
@@ -2047,10 +2047,10 @@
         <v>1551287.9368000007</v>
       </c>
       <c r="L24">
-        <v>9999999</v>
-      </c>
-      <c r="M24" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
       </c>
       <c r="N24">
         <v>64674.05</v>
@@ -2079,7 +2079,7 @@
         <v>414000</v>
       </c>
       <c r="E25">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>1288916.4815234803</v>
@@ -2088,10 +2088,10 @@
         <v>2010891.4480800009</v>
       </c>
       <c r="H25">
-        <v>9999999</v>
-      </c>
-      <c r="I25" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
       </c>
       <c r="J25">
         <v>962142.82639999932</v>
@@ -2100,10 +2100,10 @@
         <v>1548418.7236000006</v>
       </c>
       <c r="L25">
-        <v>9999999</v>
-      </c>
-      <c r="M25" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
       </c>
       <c r="N25">
         <v>63702.94</v>
@@ -2132,7 +2132,7 @@
         <v>414000</v>
       </c>
       <c r="E26">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1289043.4366079206</v>
@@ -2141,10 +2141,10 @@
         <v>1999885.4531200009</v>
       </c>
       <c r="H26">
-        <v>9999999</v>
-      </c>
-      <c r="I26" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
       </c>
       <c r="J26">
         <v>960230.01759999921</v>
@@ -2153,10 +2153,10 @@
         <v>1545549.5104000007</v>
       </c>
       <c r="L26">
-        <v>9999999</v>
-      </c>
-      <c r="M26" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
       </c>
       <c r="N26">
         <v>62746.400000000001</v>
@@ -2185,7 +2185,7 @@
         <v>414000</v>
       </c>
       <c r="E27">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>1289170.3916923604</v>
@@ -2194,10 +2194,10 @@
         <v>1988879.4581600011</v>
       </c>
       <c r="H27">
-        <v>9999999</v>
-      </c>
-      <c r="I27" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
       </c>
       <c r="J27">
         <v>958317.20879999921</v>
@@ -2206,10 +2206,10 @@
         <v>1542680.2972000006</v>
       </c>
       <c r="L27">
-        <v>9999999</v>
-      </c>
-      <c r="M27" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
       </c>
       <c r="N27">
         <v>61804.2</v>
@@ -2238,7 +2238,7 @@
         <v>414000</v>
       </c>
       <c r="E28">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>1289297.3467768</v>
@@ -2247,10 +2247,10 @@
         <v>1977873.4631999999</v>
       </c>
       <c r="H28">
-        <v>9999999</v>
-      </c>
-      <c r="I28" s="5">
-        <v>11000</v>
+        <v>2380000</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
       </c>
       <c r="J28">
         <v>956404.40000000026</v>
@@ -2259,10 +2259,10 @@
         <v>1539811.0840000003</v>
       </c>
       <c r="L28">
-        <v>9999999</v>
-      </c>
-      <c r="M28" s="5">
-        <v>11000</v>
+        <v>1700000</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
       </c>
       <c r="N28">
         <v>60876.14</v>
@@ -9050,7 +9050,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E3" s="5">
         <v>0.25</v>
@@ -9059,25 +9059,25 @@
         <v>0</v>
       </c>
       <c r="G3" s="6">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="J3" s="5">
-        <v>8.5999999999999993E-2</v>
+      <c r="J3" s="6">
+        <v>0.2</v>
       </c>
       <c r="K3" s="5">
         <v>0.8</v>
       </c>
       <c r="L3" s="5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N3" s="5">
         <v>5</v>
@@ -9094,8 +9094,8 @@
       <c r="R3" s="6">
         <v>0.85</v>
       </c>
-      <c r="S3" s="5">
-        <v>8.5999999999999993E-2</v>
+      <c r="S3" s="6">
+        <v>0.2</v>
       </c>
       <c r="T3" s="5">
         <v>25000</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E4" s="5">
         <v>0.25</v>
@@ -9138,23 +9138,23 @@
       <c r="F4" s="5">
         <v>0</v>
       </c>
-      <c r="G4" s="7">
-        <v>24000</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
+      <c r="G4" s="6">
+        <v>23000</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="J4" s="5">
-        <v>8.5999999999999993E-2</v>
+      <c r="J4" s="6">
+        <v>0.2</v>
       </c>
       <c r="K4" s="5">
         <v>0.8</v>
       </c>
       <c r="L4" s="5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M4" s="5">
         <v>20</v>
@@ -9171,11 +9171,11 @@
       <c r="Q4" s="6">
         <v>10000</v>
       </c>
-      <c r="R4" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="S4" s="5">
-        <v>8.5999999999999993E-2</v>
+      <c r="R4" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="S4" s="6">
+        <v>0.2</v>
       </c>
       <c r="T4" s="5">
         <v>25000</v>
@@ -9234,7 +9234,7 @@
         <v>0.8</v>
       </c>
       <c r="L5" s="5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M5">
         <v>30</v>
@@ -10323,7 +10323,7 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C2">
         <v>26250</v>
@@ -10340,7 +10340,7 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C3">
         <v>26250</v>
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C4">
         <v>26250</v>
@@ -10374,7 +10374,7 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C5">
         <v>26250</v>
@@ -10391,7 +10391,7 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C6">
         <v>26250</v>
@@ -10408,7 +10408,7 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C7">
         <v>26250</v>
@@ -10425,7 +10425,7 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C8">
         <v>26250</v>
@@ -10442,7 +10442,7 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C9">
         <v>26250</v>
@@ -10459,7 +10459,7 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C10">
         <v>26250</v>
@@ -10476,7 +10476,7 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C11">
         <v>26250</v>
@@ -10493,7 +10493,7 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C12">
         <v>26250</v>
@@ -10510,7 +10510,7 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C13">
         <v>26250</v>
@@ -10527,7 +10527,7 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C14">
         <v>26250</v>
@@ -10544,7 +10544,7 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C15">
         <v>26250</v>
@@ -10561,7 +10561,7 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C16">
         <v>26250</v>
@@ -10578,7 +10578,7 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>74200</v>
+        <v>70000</v>
       </c>
       <c r="C17">
         <v>26250</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F7FBD-CA77-4252-8E4F-5DD69389CF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B845115B-BB82-49DB-B75B-FF27A4EBAF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -395,7 +395,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,6 +441,12 @@
       <color rgb="FF648C1A"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2445,6 +2451,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9161,7 +9168,7 @@
         <v>0.38879999999999998</v>
       </c>
       <c r="K2" s="5">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="L2" s="5">
         <v>0.2</v>
@@ -9244,7 +9251,7 @@
         <v>0.2</v>
       </c>
       <c r="K3" s="5">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="L3" s="5">
         <v>0.2</v>
@@ -9327,7 +9334,7 @@
         <v>0.2</v>
       </c>
       <c r="K4" s="5">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="L4" s="5">
         <v>0.2</v>
@@ -9410,7 +9417,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" s="5">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="L5" s="5">
         <v>0.2</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B845115B-BB82-49DB-B75B-FF27A4EBAF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA2D59B-8BB7-4815-BB60-5AF9193FB5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -10521,7 +10521,7 @@
         <v>36915</v>
       </c>
       <c r="E2">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -10538,7 +10538,7 @@
         <v>36915</v>
       </c>
       <c r="E3">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -10555,7 +10555,7 @@
         <v>36915</v>
       </c>
       <c r="E4">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -10572,7 +10572,7 @@
         <v>36915</v>
       </c>
       <c r="E5">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -10589,7 +10589,7 @@
         <v>36915</v>
       </c>
       <c r="E6">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -10606,7 +10606,7 @@
         <v>36915</v>
       </c>
       <c r="E7">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -10623,7 +10623,7 @@
         <v>21800</v>
       </c>
       <c r="E8">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -10640,7 +10640,7 @@
         <v>21800</v>
       </c>
       <c r="E9">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -10657,7 +10657,7 @@
         <v>21800</v>
       </c>
       <c r="E10">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -10674,7 +10674,7 @@
         <v>21800</v>
       </c>
       <c r="E11">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -10691,7 +10691,7 @@
         <v>21800</v>
       </c>
       <c r="E12">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -10708,7 +10708,7 @@
         <v>21800</v>
       </c>
       <c r="E13">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -10725,7 +10725,7 @@
         <v>21800</v>
       </c>
       <c r="E14">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -10742,7 +10742,7 @@
         <v>21800</v>
       </c>
       <c r="E15">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -10759,7 +10759,7 @@
         <v>21800</v>
       </c>
       <c r="E16">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -10776,7 +10776,7 @@
         <v>21800</v>
       </c>
       <c r="E17">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -10793,7 +10793,7 @@
         <v>21800</v>
       </c>
       <c r="E18">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -10810,7 +10810,7 @@
         <v>21800</v>
       </c>
       <c r="E19">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -10827,7 +10827,7 @@
         <v>21800</v>
       </c>
       <c r="E20">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -10844,7 +10844,7 @@
         <v>21800</v>
       </c>
       <c r="E21">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -10861,7 +10861,7 @@
         <v>21800</v>
       </c>
       <c r="E22">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -10878,7 +10878,7 @@
         <v>21800</v>
       </c>
       <c r="E23">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -10895,7 +10895,7 @@
         <v>21800</v>
       </c>
       <c r="E24">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -10912,7 +10912,7 @@
         <v>21800</v>
       </c>
       <c r="E25">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -10929,7 +10929,7 @@
         <v>21800</v>
       </c>
       <c r="E26">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -10946,7 +10946,7 @@
         <v>21800</v>
       </c>
       <c r="E27">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -10963,7 +10963,7 @@
         <v>21800</v>
       </c>
       <c r="E28">
-        <v>9999999999</v>
+        <v>999999</v>
       </c>
     </row>
   </sheetData>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7503729A-C057-4E46-ADEE-6887F65A1064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A0B217-3077-4B04-8989-9088753CD6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -544,7 +544,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -562,7 +562,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -10513,13 +10512,13 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>65.5</v>
-      </c>
-      <c r="C2" s="9">
-        <v>2.1</v>
-      </c>
-      <c r="D2" s="9">
-        <v>15.28</v>
+        <v>65500</v>
+      </c>
+      <c r="C2">
+        <v>2100</v>
+      </c>
+      <c r="D2">
+        <v>15280</v>
       </c>
       <c r="E2">
         <v>999999</v>
@@ -10531,13 +10530,13 @@
       </c>
       <c r="B3">
         <f>SUM(B2*1.04)</f>
-        <v>68.12</v>
-      </c>
-      <c r="C3" s="9">
-        <v>2.1</v>
-      </c>
-      <c r="D3" s="9">
-        <v>15.28</v>
+        <v>68120</v>
+      </c>
+      <c r="C3">
+        <v>2100</v>
+      </c>
+      <c r="D3">
+        <v>15280</v>
       </c>
       <c r="E3">
         <v>999999</v>
@@ -10549,13 +10548,13 @@
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B9" si="0">SUM(B3*1.04)</f>
-        <v>70.844800000000006</v>
-      </c>
-      <c r="C4" s="9">
-        <v>3.96</v>
-      </c>
-      <c r="D4" s="9">
-        <v>15.85</v>
+        <v>70844.800000000003</v>
+      </c>
+      <c r="C4">
+        <v>3960</v>
+      </c>
+      <c r="D4">
+        <v>15850</v>
       </c>
       <c r="E4">
         <v>999999</v>
@@ -10567,13 +10566,13 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>73.678592000000009</v>
-      </c>
-      <c r="C5" s="9">
-        <v>3.42</v>
-      </c>
-      <c r="D5" s="9">
-        <v>18.7</v>
+        <v>73678.592000000004</v>
+      </c>
+      <c r="C5">
+        <v>3420</v>
+      </c>
+      <c r="D5">
+        <v>18700</v>
       </c>
       <c r="E5">
         <v>999999</v>
@@ -10585,13 +10584,13 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>76.625735680000005</v>
-      </c>
-      <c r="C6" s="9">
-        <v>4.99</v>
-      </c>
-      <c r="D6" s="9">
-        <v>20.440000000000001</v>
+        <v>76625.735680000013</v>
+      </c>
+      <c r="C6">
+        <v>4990</v>
+      </c>
+      <c r="D6">
+        <v>20440</v>
       </c>
       <c r="E6">
         <v>999999</v>
@@ -10603,13 +10602,13 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>79.690765107200008</v>
-      </c>
-      <c r="C7" s="9">
-        <v>6.41</v>
-      </c>
-      <c r="D7" s="9">
-        <v>20.9</v>
+        <v>79690.765107200015</v>
+      </c>
+      <c r="C7">
+        <v>6410</v>
+      </c>
+      <c r="D7">
+        <v>20900</v>
       </c>
       <c r="E7">
         <v>999999</v>
@@ -10621,13 +10620,13 @@
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>82.878395711488011</v>
-      </c>
-      <c r="C8" s="9">
-        <v>6.31</v>
-      </c>
-      <c r="D8" s="9">
-        <v>21.8</v>
+        <v>82878.395711488018</v>
+      </c>
+      <c r="C8">
+        <v>6310</v>
+      </c>
+      <c r="D8">
+        <v>21800</v>
       </c>
       <c r="E8">
         <v>999999</v>
@@ -10638,15 +10637,15 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C9">
         <f>SUM(C8*1.2465)</f>
-        <v>7.8654149999999987</v>
+        <v>7865.415</v>
       </c>
       <c r="D9">
         <f>SUM(D8*1.0626)</f>
-        <v>23.164680000000001</v>
+        <v>23164.68</v>
       </c>
       <c r="E9">
         <v>999999</v>
@@ -10657,15 +10656,15 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C10">
         <f t="shared" ref="C10:C12" si="1">SUM(C9*1.2465)</f>
-        <v>9.8042397974999975</v>
+        <v>9804.2397975000003</v>
       </c>
       <c r="D10">
         <f t="shared" ref="D10:D13" si="2">SUM(D9*1.0626)</f>
-        <v>24.614788967999999</v>
+        <v>24614.788968000001</v>
       </c>
       <c r="E10">
         <v>999999</v>
@@ -10676,15 +10675,15 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>12.220984907583746</v>
+        <v>12220.98490758375</v>
       </c>
       <c r="D11">
         <f t="shared" si="2"/>
-        <v>26.155674757396799</v>
+        <v>26155.674757396802</v>
       </c>
       <c r="E11">
         <v>999999</v>
@@ -10695,15 +10694,15 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>15.233457687303138</v>
+        <v>15233.457687303144</v>
       </c>
       <c r="D12">
         <f t="shared" si="2"/>
-        <v>27.793019997209839</v>
+        <v>27793.019997209842</v>
       </c>
       <c r="E12">
         <v>999999</v>
@@ -10714,15 +10713,15 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C13">
         <f>SUM(C12*1.2465)</f>
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D13">
         <f t="shared" si="2"/>
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E13">
         <v>999999</v>
@@ -10733,13 +10732,13 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C14">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D14">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E14">
         <v>999999</v>
@@ -10750,13 +10749,13 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C15">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D15">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E15">
         <v>999999</v>
@@ -10767,13 +10766,13 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C16">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D16">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E16">
         <v>999999</v>
@@ -10784,13 +10783,13 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C17">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D17">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E17">
         <v>999999</v>
@@ -10801,13 +10800,13 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C18">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D18">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E18">
         <v>999999</v>
@@ -10818,13 +10817,13 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C19">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D19">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E19">
         <v>999999</v>
@@ -10835,13 +10834,13 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C20">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D20">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E20">
         <v>999999</v>
@@ -10852,13 +10851,13 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C21">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D21">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E21">
         <v>999999</v>
@@ -10869,13 +10868,13 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C22">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D22">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E22">
         <v>999999</v>
@@ -10886,13 +10885,13 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C23">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D23">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E23">
         <v>999999</v>
@@ -10903,13 +10902,13 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C24">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D24">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E24">
         <v>999999</v>
@@ -10920,13 +10919,13 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C25">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D25">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E25">
         <v>999999</v>
@@ -10937,13 +10936,13 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C26">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D26">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E26">
         <v>999999</v>
@@ -10954,13 +10953,13 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C27">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D27">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E27">
         <v>999999</v>
@@ -10971,13 +10970,13 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>82.878395711488011</v>
+        <v>82878.395711488018</v>
       </c>
       <c r="C28">
-        <v>18.98850500722336</v>
+        <v>18988.505007223368</v>
       </c>
       <c r="D28">
-        <v>29.532863049035175</v>
+        <v>29532.863049035179</v>
       </c>
       <c r="E28">
         <v>999999</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerald\Desktop\urbsextension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76775CF2-2FE5-492A-BD98-4162FA4A53CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C09D9B4-4F64-4E34-98C5-550EE28DFFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-7545" windowWidth="16440" windowHeight="28440" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="dcr" sheetId="6" r:id="rId6"/>
     <sheet name="stocklvl" sheetId="7" r:id="rId7"/>
     <sheet name="installable_capacity" sheetId="3" r:id="rId8"/>
+    <sheet name="lng_block" sheetId="13" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="124">
   <si>
     <t>Value</t>
   </si>
@@ -385,6 +386,36 @@
   </si>
   <si>
     <t>308 477,99</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>limit</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>Other Europe</t>
+  </si>
+  <si>
+    <t>Other Africa</t>
+  </si>
+  <si>
+    <t>Trinidad &amp; Tobago</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Other Americas</t>
   </si>
 </sst>
 </file>
@@ -449,7 +480,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,6 +514,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,7 +581,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -565,6 +602,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -909,9 +947,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31FF74EF-7037-4139-88AF-F295C305C1F7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -919,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -927,7 +965,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -935,7 +973,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -951,25 +989,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185AF38-42FD-4CFF-B287-2FCFFF6C6EF3}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="37.33203125" customWidth="1"/>
-    <col min="5" max="5" width="29.88671875" customWidth="1"/>
-    <col min="6" max="6" width="39.88671875" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" customWidth="1"/>
-    <col min="9" max="9" width="22.5546875" customWidth="1"/>
-    <col min="10" max="10" width="24.109375" customWidth="1"/>
-    <col min="11" max="11" width="27.6640625" customWidth="1"/>
-    <col min="12" max="12" width="22.88671875" customWidth="1"/>
-    <col min="13" max="13" width="20.109375" customWidth="1"/>
-    <col min="15" max="15" width="32.77734375" customWidth="1"/>
-    <col min="16" max="16" width="35.21875" customWidth="1"/>
-    <col min="17" max="17" width="31.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="37.28515625" customWidth="1"/>
+    <col min="5" max="5" width="29.85546875" customWidth="1"/>
+    <col min="6" max="6" width="39.85546875" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="24.140625" customWidth="1"/>
+    <col min="11" max="11" width="27.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" customWidth="1"/>
+    <col min="15" max="15" width="32.7109375" customWidth="1"/>
+    <col min="16" max="16" width="35.28515625" customWidth="1"/>
+    <col min="17" max="17" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1022,7 +1060,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -1075,7 +1113,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1128,7 +1166,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -1181,7 +1219,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -1234,7 +1272,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -1287,7 +1325,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -1340,7 +1378,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -1393,7 +1431,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -1446,7 +1484,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -1499,7 +1537,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -1552,7 +1590,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -1605,7 +1643,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -1658,7 +1696,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -1711,7 +1749,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -1764,7 +1802,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -1817,7 +1855,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -1870,7 +1908,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -1923,7 +1961,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -1976,7 +2014,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -2029,7 +2067,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -2082,7 +2120,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -2135,7 +2173,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -2188,7 +2226,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -2241,7 +2279,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -2294,7 +2332,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -2347,7 +2385,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -2400,7 +2438,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -2462,64 +2500,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0D039F-A3AA-471E-A6A2-F25F8348E84D}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
   </sheetData>
@@ -2530,12 +2568,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6341E4C-4AB4-44A4-8119-B6BB3BEB6E84}">
   <dimension ref="A1:F325"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -2555,7 +2593,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2575,7 +2613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2595,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2615,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2635,7 +2673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2655,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2675,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2695,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2715,7 +2753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2735,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2755,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2775,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2795,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1</v>
       </c>
@@ -2815,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2835,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
@@ -2855,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>4</v>
       </c>
@@ -2875,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5</v>
       </c>
@@ -2895,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6</v>
       </c>
@@ -2915,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>7</v>
       </c>
@@ -2935,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>8</v>
       </c>
@@ -2955,7 +2993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9</v>
       </c>
@@ -2975,7 +3013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>10</v>
       </c>
@@ -2995,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>11</v>
       </c>
@@ -3015,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>12</v>
       </c>
@@ -3035,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
@@ -3055,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2</v>
       </c>
@@ -3075,7 +3113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3095,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -3115,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>5</v>
       </c>
@@ -3135,7 +3173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>6</v>
       </c>
@@ -3155,7 +3193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3175,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>8</v>
       </c>
@@ -3195,7 +3233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9</v>
       </c>
@@ -3215,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>10</v>
       </c>
@@ -3235,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>11</v>
       </c>
@@ -3255,7 +3293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>12</v>
       </c>
@@ -3275,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1</v>
       </c>
@@ -3295,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2</v>
       </c>
@@ -3315,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3335,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3355,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5</v>
       </c>
@@ -3375,7 +3413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>6</v>
       </c>
@@ -3395,7 +3433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>7</v>
       </c>
@@ -3415,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3435,7 +3473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3455,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>10</v>
       </c>
@@ -3475,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>11</v>
       </c>
@@ -3495,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>12</v>
       </c>
@@ -3515,7 +3553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1</v>
       </c>
@@ -3535,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2</v>
       </c>
@@ -3555,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>3</v>
       </c>
@@ -3575,7 +3613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3595,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>5</v>
       </c>
@@ -3615,7 +3653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>6</v>
       </c>
@@ -3635,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>7</v>
       </c>
@@ -3655,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>8</v>
       </c>
@@ -3675,7 +3713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>9</v>
       </c>
@@ -3695,7 +3733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10</v>
       </c>
@@ -3715,7 +3753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>11</v>
       </c>
@@ -3735,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>12</v>
       </c>
@@ -3755,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1</v>
       </c>
@@ -3775,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2</v>
       </c>
@@ -3795,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>3</v>
       </c>
@@ -3815,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>4</v>
       </c>
@@ -3835,7 +3873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>5</v>
       </c>
@@ -3855,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>6</v>
       </c>
@@ -3875,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>7</v>
       </c>
@@ -3895,7 +3933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>8</v>
       </c>
@@ -3915,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>9</v>
       </c>
@@ -3935,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>10</v>
       </c>
@@ -3955,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>11</v>
       </c>
@@ -3975,7 +4013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>12</v>
       </c>
@@ -3995,7 +4033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1</v>
       </c>
@@ -4015,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2</v>
       </c>
@@ -4035,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>3</v>
       </c>
@@ -4055,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>4</v>
       </c>
@@ -4075,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>5</v>
       </c>
@@ -4095,7 +4133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>6</v>
       </c>
@@ -4115,7 +4153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>7</v>
       </c>
@@ -4135,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>8</v>
       </c>
@@ -4155,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>9</v>
       </c>
@@ -4175,7 +4213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>10</v>
       </c>
@@ -4195,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>11</v>
       </c>
@@ -4215,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>12</v>
       </c>
@@ -4235,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1</v>
       </c>
@@ -4255,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2</v>
       </c>
@@ -4275,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>3</v>
       </c>
@@ -4295,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>4</v>
       </c>
@@ -4315,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>5</v>
       </c>
@@ -4335,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>6</v>
       </c>
@@ -4355,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>7</v>
       </c>
@@ -4375,7 +4413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>8</v>
       </c>
@@ -4395,7 +4433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>9</v>
       </c>
@@ -4415,7 +4453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>10</v>
       </c>
@@ -4435,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>11</v>
       </c>
@@ -4455,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4475,7 +4513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1</v>
       </c>
@@ -4495,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2</v>
       </c>
@@ -4515,7 +4553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>3</v>
       </c>
@@ -4535,7 +4573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>4</v>
       </c>
@@ -4555,7 +4593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>5</v>
       </c>
@@ -4575,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>6</v>
       </c>
@@ -4595,7 +4633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>7</v>
       </c>
@@ -4615,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>8</v>
       </c>
@@ -4635,7 +4673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>9</v>
       </c>
@@ -4655,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>10</v>
       </c>
@@ -4675,7 +4713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>11</v>
       </c>
@@ -4695,7 +4733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>12</v>
       </c>
@@ -4715,7 +4753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1</v>
       </c>
@@ -4735,7 +4773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2</v>
       </c>
@@ -4755,7 +4793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>3</v>
       </c>
@@ -4775,7 +4813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>4</v>
       </c>
@@ -4795,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>5</v>
       </c>
@@ -4815,7 +4853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>6</v>
       </c>
@@ -4835,7 +4873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>7</v>
       </c>
@@ -4855,7 +4893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>8</v>
       </c>
@@ -4875,7 +4913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>9</v>
       </c>
@@ -4895,7 +4933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>10</v>
       </c>
@@ -4915,7 +4953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>11</v>
       </c>
@@ -4935,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>12</v>
       </c>
@@ -4955,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1</v>
       </c>
@@ -4975,7 +5013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2</v>
       </c>
@@ -4995,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>3</v>
       </c>
@@ -5015,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>4</v>
       </c>
@@ -5035,7 +5073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>5</v>
       </c>
@@ -5055,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>6</v>
       </c>
@@ -5075,7 +5113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>7</v>
       </c>
@@ -5095,7 +5133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>8</v>
       </c>
@@ -5115,7 +5153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>9</v>
       </c>
@@ -5135,7 +5173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>10</v>
       </c>
@@ -5155,7 +5193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>11</v>
       </c>
@@ -5175,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>12</v>
       </c>
@@ -5195,7 +5233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>1</v>
       </c>
@@ -5215,7 +5253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2</v>
       </c>
@@ -5235,7 +5273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>3</v>
       </c>
@@ -5255,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>4</v>
       </c>
@@ -5275,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>5</v>
       </c>
@@ -5295,7 +5333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>6</v>
       </c>
@@ -5315,7 +5353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>7</v>
       </c>
@@ -5335,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>8</v>
       </c>
@@ -5355,7 +5393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>9</v>
       </c>
@@ -5375,7 +5413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>10</v>
       </c>
@@ -5395,7 +5433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>11</v>
       </c>
@@ -5415,7 +5453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>12</v>
       </c>
@@ -5435,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1</v>
       </c>
@@ -5455,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2</v>
       </c>
@@ -5475,7 +5513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>3</v>
       </c>
@@ -5495,7 +5533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>4</v>
       </c>
@@ -5515,7 +5553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>5</v>
       </c>
@@ -5535,7 +5573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>6</v>
       </c>
@@ -5555,7 +5593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>7</v>
       </c>
@@ -5575,7 +5613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>8</v>
       </c>
@@ -5595,7 +5633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>9</v>
       </c>
@@ -5615,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>10</v>
       </c>
@@ -5635,7 +5673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>11</v>
       </c>
@@ -5655,7 +5693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>12</v>
       </c>
@@ -5675,7 +5713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1</v>
       </c>
@@ -5695,7 +5733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2</v>
       </c>
@@ -5715,7 +5753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>3</v>
       </c>
@@ -5735,7 +5773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>4</v>
       </c>
@@ -5755,7 +5793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>5</v>
       </c>
@@ -5775,7 +5813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>6</v>
       </c>
@@ -5795,7 +5833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>7</v>
       </c>
@@ -5815,7 +5853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>8</v>
       </c>
@@ -5835,7 +5873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>9</v>
       </c>
@@ -5855,7 +5893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>10</v>
       </c>
@@ -5875,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>11</v>
       </c>
@@ -5895,7 +5933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>12</v>
       </c>
@@ -5915,7 +5953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>1</v>
       </c>
@@ -5935,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2</v>
       </c>
@@ -5955,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>3</v>
       </c>
@@ -5975,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>4</v>
       </c>
@@ -5995,7 +6033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>5</v>
       </c>
@@ -6015,7 +6053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>6</v>
       </c>
@@ -6035,7 +6073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>7</v>
       </c>
@@ -6055,7 +6093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>8</v>
       </c>
@@ -6075,7 +6113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>9</v>
       </c>
@@ -6095,7 +6133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>10</v>
       </c>
@@ -6115,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>11</v>
       </c>
@@ -6135,7 +6173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>12</v>
       </c>
@@ -6155,7 +6193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1</v>
       </c>
@@ -6175,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2</v>
       </c>
@@ -6195,7 +6233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>3</v>
       </c>
@@ -6215,7 +6253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>4</v>
       </c>
@@ -6235,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>5</v>
       </c>
@@ -6255,7 +6293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>6</v>
       </c>
@@ -6275,7 +6313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>7</v>
       </c>
@@ -6295,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>8</v>
       </c>
@@ -6315,7 +6353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>9</v>
       </c>
@@ -6335,7 +6373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>10</v>
       </c>
@@ -6355,7 +6393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>11</v>
       </c>
@@ -6375,7 +6413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>12</v>
       </c>
@@ -6395,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1</v>
       </c>
@@ -6415,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2</v>
       </c>
@@ -6435,7 +6473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>3</v>
       </c>
@@ -6455,7 +6493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>4</v>
       </c>
@@ -6475,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>5</v>
       </c>
@@ -6495,7 +6533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>6</v>
       </c>
@@ -6515,7 +6553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>7</v>
       </c>
@@ -6535,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>8</v>
       </c>
@@ -6555,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>9</v>
       </c>
@@ -6575,7 +6613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>10</v>
       </c>
@@ -6595,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>11</v>
       </c>
@@ -6615,7 +6653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>12</v>
       </c>
@@ -6635,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1</v>
       </c>
@@ -6655,7 +6693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2</v>
       </c>
@@ -6675,7 +6713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>3</v>
       </c>
@@ -6695,7 +6733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>4</v>
       </c>
@@ -6715,7 +6753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>5</v>
       </c>
@@ -6735,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>6</v>
       </c>
@@ -6755,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>7</v>
       </c>
@@ -6775,7 +6813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>8</v>
       </c>
@@ -6795,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>9</v>
       </c>
@@ -6815,7 +6853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>10</v>
       </c>
@@ -6835,7 +6873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>11</v>
       </c>
@@ -6855,7 +6893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>12</v>
       </c>
@@ -6875,7 +6913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1</v>
       </c>
@@ -6895,7 +6933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2</v>
       </c>
@@ -6915,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>3</v>
       </c>
@@ -6935,7 +6973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>4</v>
       </c>
@@ -6955,7 +6993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>5</v>
       </c>
@@ -6975,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>6</v>
       </c>
@@ -6995,7 +7033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>7</v>
       </c>
@@ -7015,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>8</v>
       </c>
@@ -7035,7 +7073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>9</v>
       </c>
@@ -7055,7 +7093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>10</v>
       </c>
@@ -7075,7 +7113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>11</v>
       </c>
@@ -7095,7 +7133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>12</v>
       </c>
@@ -7115,7 +7153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1</v>
       </c>
@@ -7135,7 +7173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2</v>
       </c>
@@ -7155,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>3</v>
       </c>
@@ -7175,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>4</v>
       </c>
@@ -7195,7 +7233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>5</v>
       </c>
@@ -7215,7 +7253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>6</v>
       </c>
@@ -7235,7 +7273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>7</v>
       </c>
@@ -7255,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>8</v>
       </c>
@@ -7275,7 +7313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>9</v>
       </c>
@@ -7295,7 +7333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>10</v>
       </c>
@@ -7315,7 +7353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>11</v>
       </c>
@@ -7335,7 +7373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>12</v>
       </c>
@@ -7355,7 +7393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1</v>
       </c>
@@ -7375,7 +7413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2</v>
       </c>
@@ -7395,7 +7433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>3</v>
       </c>
@@ -7415,7 +7453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>4</v>
       </c>
@@ -7435,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>5</v>
       </c>
@@ -7455,7 +7493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>6</v>
       </c>
@@ -7475,7 +7513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>7</v>
       </c>
@@ -7495,7 +7533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>8</v>
       </c>
@@ -7515,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>9</v>
       </c>
@@ -7535,7 +7573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>10</v>
       </c>
@@ -7555,7 +7593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>11</v>
       </c>
@@ -7575,7 +7613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>12</v>
       </c>
@@ -7595,7 +7633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1</v>
       </c>
@@ -7615,7 +7653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2</v>
       </c>
@@ -7635,7 +7673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>3</v>
       </c>
@@ -7655,7 +7693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>4</v>
       </c>
@@ -7675,7 +7713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>5</v>
       </c>
@@ -7695,7 +7733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>6</v>
       </c>
@@ -7715,7 +7753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>7</v>
       </c>
@@ -7735,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>8</v>
       </c>
@@ -7755,7 +7793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>9</v>
       </c>
@@ -7775,7 +7813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>10</v>
       </c>
@@ -7795,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>11</v>
       </c>
@@ -7815,7 +7853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>12</v>
       </c>
@@ -7835,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>1</v>
       </c>
@@ -7855,7 +7893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2</v>
       </c>
@@ -7875,7 +7913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>3</v>
       </c>
@@ -7895,7 +7933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>4</v>
       </c>
@@ -7915,7 +7953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>5</v>
       </c>
@@ -7935,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>6</v>
       </c>
@@ -7955,7 +7993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>7</v>
       </c>
@@ -7975,7 +8013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>8</v>
       </c>
@@ -7995,7 +8033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>9</v>
       </c>
@@ -8015,7 +8053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>10</v>
       </c>
@@ -8035,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>11</v>
       </c>
@@ -8055,7 +8093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>12</v>
       </c>
@@ -8075,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1</v>
       </c>
@@ -8095,7 +8133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>2</v>
       </c>
@@ -8115,7 +8153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>3</v>
       </c>
@@ -8135,7 +8173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>4</v>
       </c>
@@ -8155,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>5</v>
       </c>
@@ -8175,7 +8213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>6</v>
       </c>
@@ -8195,7 +8233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>7</v>
       </c>
@@ -8215,7 +8253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>8</v>
       </c>
@@ -8235,7 +8273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>9</v>
       </c>
@@ -8255,7 +8293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>10</v>
       </c>
@@ -8275,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>11</v>
       </c>
@@ -8295,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>12</v>
       </c>
@@ -8315,7 +8353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>1</v>
       </c>
@@ -8335,7 +8373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>2</v>
       </c>
@@ -8355,7 +8393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>3</v>
       </c>
@@ -8375,7 +8413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>4</v>
       </c>
@@ -8395,7 +8433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>5</v>
       </c>
@@ -8415,7 +8453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>6</v>
       </c>
@@ -8435,7 +8473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>7</v>
       </c>
@@ -8455,7 +8493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>8</v>
       </c>
@@ -8475,7 +8513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>9</v>
       </c>
@@ -8495,7 +8533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>10</v>
       </c>
@@ -8515,7 +8553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>11</v>
       </c>
@@ -8535,7 +8573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>12</v>
       </c>
@@ -8555,7 +8593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>1</v>
       </c>
@@ -8575,7 +8613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>2</v>
       </c>
@@ -8595,7 +8633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>3</v>
       </c>
@@ -8615,7 +8653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>4</v>
       </c>
@@ -8635,7 +8673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>5</v>
       </c>
@@ -8655,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>6</v>
       </c>
@@ -8675,7 +8713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>7</v>
       </c>
@@ -8695,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>8</v>
       </c>
@@ -8715,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>9</v>
       </c>
@@ -8735,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>10</v>
       </c>
@@ -8755,7 +8793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>11</v>
       </c>
@@ -8775,7 +8813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>12</v>
       </c>
@@ -8795,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>1</v>
       </c>
@@ -8815,7 +8853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>2</v>
       </c>
@@ -8835,7 +8873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>3</v>
       </c>
@@ -8855,7 +8893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>4</v>
       </c>
@@ -8875,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>5</v>
       </c>
@@ -8895,7 +8933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>6</v>
       </c>
@@ -8915,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>7</v>
       </c>
@@ -8935,7 +8973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>8</v>
       </c>
@@ -8955,7 +8993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>9</v>
       </c>
@@ -8975,7 +9013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>10</v>
       </c>
@@ -8995,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>11</v>
       </c>
@@ -9015,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>12</v>
       </c>
@@ -9043,20 +9081,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71493739-45C2-4A8D-9266-24BB3FC8F4DB}">
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" customWidth="1"/>
-    <col min="20" max="20" width="20.5546875" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="14" max="14" width="20.140625" customWidth="1"/>
+    <col min="20" max="20" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
@@ -9139,7 +9177,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -9222,7 +9260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -9305,7 +9343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -9388,7 +9426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
@@ -9471,43 +9509,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
     </row>
   </sheetData>
@@ -9519,9 +9557,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69FD329D-454B-4A8C-B502-49D79ABB4242}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -9538,7 +9576,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -9555,7 +9593,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -9572,7 +9610,7 @@
         <v>2.2200000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -9589,7 +9627,7 @@
         <v>2.4400000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -9606,7 +9644,7 @@
         <v>2.6599999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -9623,7 +9661,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -9640,7 +9678,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -9657,7 +9695,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -9674,7 +9712,7 @@
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -9691,7 +9729,7 @@
         <v>3.7600000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -9708,7 +9746,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -9725,7 +9763,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -9742,7 +9780,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -9759,7 +9797,7 @@
         <v>4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -9776,7 +9814,7 @@
         <v>4.6399999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -9793,7 +9831,7 @@
         <v>4.8599999999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -9810,7 +9848,7 @@
         <v>5.0799999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -9827,7 +9865,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -9844,7 +9882,7 @@
         <v>5.5199999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -9861,7 +9899,7 @@
         <v>5.74E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -9878,7 +9916,7 @@
         <v>5.96E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -9895,7 +9933,7 @@
         <v>6.1800000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -9912,7 +9950,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -9929,7 +9967,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -9946,7 +9984,7 @@
         <v>6.8400000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -9963,7 +10001,7 @@
         <v>7.0599999999999996E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -9980,7 +10018,7 @@
         <v>7.2800000000000004E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10005,9 +10043,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1143316B-9FC2-4B52-982D-1F4DD6859A8E}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10024,7 +10062,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10041,7 +10079,7 @@
         <v>26229.707720000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10058,7 +10096,7 @@
         <v>26589.174669999997</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10075,7 +10113,7 @@
         <v>60431.69513</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10092,7 +10130,7 @@
         <v>95314.195130000007</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10109,7 +10147,7 @@
         <v>130196.6951</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10126,7 +10164,7 @@
         <v>165780.465</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10143,7 +10181,7 @@
         <v>179750.54879999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10160,7 +10198,7 @@
         <v>195610.7611</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10177,7 +10215,7 @@
         <v>196499.72339999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10194,7 +10232,7 @@
         <v>198853.9976</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10211,7 +10249,7 @@
         <v>202089.00579999998</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10228,7 +10266,7 @@
         <v>164077.8836</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10245,7 +10283,7 @@
         <v>126654.49769999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10262,7 +10300,7 @@
         <v>90701.344779999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10279,7 +10317,7 @@
         <v>57298.538379999998</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10296,7 +10334,7 @@
         <v>40938.322699999997</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10313,7 +10351,7 @@
         <v>30788.296410000003</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10330,7 +10368,7 @@
         <v>28368.054080000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10347,7 +10385,7 @@
         <v>31250.81408</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10364,7 +10402,7 @@
         <v>34011.350160000002</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10381,7 +10419,7 @@
         <v>35066.675019999995</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10398,7 +10436,7 @@
         <v>33453.543590000001</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10415,7 +10453,7 @@
         <v>25310.301890000002</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10432,7 +10470,7 @@
         <v>11877.08452</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10449,7 +10487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10466,7 +10504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10491,9 +10529,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790A601-26C3-4DCA-97B6-9342C547A4A0}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10510,7 +10548,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10527,7 +10565,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10545,7 +10583,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10563,7 +10601,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10581,7 +10619,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10599,7 +10637,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10617,7 +10655,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10635,7 +10673,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10654,7 +10692,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10673,7 +10711,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10692,7 +10730,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10711,7 +10749,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10730,7 +10768,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10747,7 +10785,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10764,7 +10802,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10781,7 +10819,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10798,7 +10836,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10815,7 +10853,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10832,7 +10870,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10849,7 +10887,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10866,7 +10904,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10883,7 +10921,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10900,7 +10938,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10917,7 +10955,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10934,7 +10972,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10951,7 +10989,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10968,7 +11006,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10983,6 +11021,139 @@
       </c>
       <c r="E28">
         <v>999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>138105619</v>
+      </c>
+      <c r="C2">
+        <v>15.87</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>471381508</v>
+      </c>
+      <c r="C3">
+        <v>28.56</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>27736037</v>
+      </c>
+      <c r="C4">
+        <v>29.18</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>61588793</v>
+      </c>
+      <c r="C5">
+        <v>30.15</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>144907263</v>
+      </c>
+      <c r="C6">
+        <v>33.33</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>471381508</v>
+      </c>
+      <c r="C7">
+        <v>39.69</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>98828156</v>
+      </c>
+      <c r="C8">
+        <v>43.14</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>999999999999</v>
+      </c>
+      <c r="C9">
+        <v>79.319999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerald\Desktop\urbsextension\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C09D9B4-4F64-4E34-98C5-550EE28DFFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F918984-D2CD-4EB7-B7E0-942DB386408D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-7545" windowWidth="16440" windowHeight="28440" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -947,9 +947,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31FF74EF-7037-4139-88AF-F295C305C1F7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -957,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -965,7 +965,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -973,7 +973,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -989,25 +989,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185AF38-42FD-4CFF-B287-2FCFFF6C6EF3}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="4" width="37.28515625" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" customWidth="1"/>
-    <col min="6" max="6" width="39.85546875" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" customWidth="1"/>
-    <col min="10" max="10" width="24.140625" customWidth="1"/>
-    <col min="11" max="11" width="27.7109375" customWidth="1"/>
-    <col min="12" max="12" width="22.85546875" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" customWidth="1"/>
-    <col min="15" max="15" width="32.7109375" customWidth="1"/>
-    <col min="16" max="16" width="35.28515625" customWidth="1"/>
-    <col min="17" max="17" width="31.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" customWidth="1"/>
+    <col min="6" max="6" width="39.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="22.5546875" customWidth="1"/>
+    <col min="10" max="10" width="24.109375" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" customWidth="1"/>
+    <col min="12" max="12" width="22.88671875" customWidth="1"/>
+    <col min="13" max="13" width="20.109375" customWidth="1"/>
+    <col min="15" max="15" width="32.6640625" customWidth="1"/>
+    <col min="16" max="16" width="35.33203125" customWidth="1"/>
+    <col min="17" max="17" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -2500,64 +2500,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0D039F-A3AA-471E-A6A2-F25F8348E84D}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
     </row>
   </sheetData>
@@ -2568,12 +2568,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6341E4C-4AB4-44A4-8119-B6BB3BEB6E84}">
   <dimension ref="A1:F325"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>5</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>6</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>7</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>8</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>9</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>10</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>11</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>12</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>4</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>5</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>6</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>8</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>9</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>10</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>11</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>12</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>5</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>6</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>7</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>10</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>11</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>12</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>3</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>5</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>6</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>7</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>8</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>9</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>10</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>11</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>12</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>3</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>4</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>5</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>6</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>7</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>8</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>9</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>10</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>11</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>12</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>3</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>4</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>5</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>6</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>7</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>8</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>9</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>10</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>11</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>12</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>2</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>3</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>4</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>5</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>6</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>7</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>8</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>9</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>10</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>11</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>3</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>4</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>5</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>6</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>7</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>8</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>9</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>10</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>11</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>12</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>3</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>4</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>5</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>6</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>7</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>8</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>9</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>10</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>11</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>12</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>1</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>3</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>4</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>5</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>6</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>7</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>8</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>9</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>10</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>11</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>12</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>1</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>2</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>3</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>4</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>5</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>6</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>7</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>8</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>9</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>10</v>
       </c>
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>11</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>12</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>1</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>2</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>3</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>4</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>5</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>6</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>7</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>8</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>9</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>10</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>11</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>12</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>1</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>2</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>3</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>4</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>5</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>6</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>7</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>8</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>9</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>10</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>11</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>12</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>1</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>2</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>3</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>4</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>5</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>6</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>7</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>8</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>9</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>10</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>11</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>12</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>1</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>2</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>3</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>4</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>5</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>6</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>7</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>8</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>9</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>10</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>11</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>12</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>1</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>2</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>3</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>4</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>5</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>6</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>7</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>8</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>9</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>10</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>11</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>12</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>1</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>2</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>3</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>4</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>5</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>6</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>7</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>8</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>9</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>10</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>11</v>
       </c>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>12</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>1</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>2</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>3</v>
       </c>
@@ -6973,7 +6973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>4</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>5</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>6</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>7</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>8</v>
       </c>
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>9</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>10</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>11</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>12</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>1</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>2</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>3</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>4</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>5</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>6</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>7</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>8</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>9</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>10</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>11</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>12</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>1</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>2</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>3</v>
       </c>
@@ -7453,7 +7453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>4</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>5</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>6</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>7</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>8</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>9</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>10</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>11</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>12</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>1</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>2</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>3</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>4</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>5</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>6</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>7</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>8</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>9</v>
       </c>
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>10</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>11</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>12</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>1</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>2</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>3</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>4</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>5</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>6</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>7</v>
       </c>
@@ -8013,7 +8013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>8</v>
       </c>
@@ -8033,7 +8033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>9</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>10</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>11</v>
       </c>
@@ -8093,7 +8093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>12</v>
       </c>
@@ -8113,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>1</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>2</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>3</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>4</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>5</v>
       </c>
@@ -8213,7 +8213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>6</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>7</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>8</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>9</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>10</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>11</v>
       </c>
@@ -8333,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>12</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>1</v>
       </c>
@@ -8373,7 +8373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>2</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>3</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>4</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>5</v>
       </c>
@@ -8453,7 +8453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>6</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>7</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>8</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>9</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>10</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>11</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>12</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>1</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>2</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>3</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>4</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>5</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>6</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>7</v>
       </c>
@@ -8733,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>8</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>9</v>
       </c>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>10</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>11</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>12</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>1</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>2</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>3</v>
       </c>
@@ -8893,7 +8893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>4</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>5</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>6</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>7</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>8</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>9</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>10</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>11</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>12</v>
       </c>
@@ -9081,20 +9081,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71493739-45C2-4A8D-9266-24BB3FC8F4DB}">
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" customWidth="1"/>
-    <col min="20" max="20" width="20.5703125" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" customWidth="1"/>
+    <col min="20" max="20" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -9426,7 +9426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
@@ -9509,43 +9509,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
     </row>
   </sheetData>
@@ -9557,9 +9557,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69FD329D-454B-4A8C-B502-49D79ABB4242}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -9610,7 +9610,7 @@
         <v>2.2200000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -9627,7 +9627,7 @@
         <v>2.4400000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -9644,7 +9644,7 @@
         <v>2.6599999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -9661,7 +9661,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -9695,7 +9695,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>3.7600000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>4.6399999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -9831,7 +9831,7 @@
         <v>4.8599999999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>5.0799999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>5.5199999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -9899,7 +9899,7 @@
         <v>5.74E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>5.96E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>6.1800000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -9950,7 +9950,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>6.8400000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>7.0599999999999996E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10018,7 +10018,7 @@
         <v>7.2800000000000004E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10043,9 +10043,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1143316B-9FC2-4B52-982D-1F4DD6859A8E}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>26229.707720000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10096,7 +10096,7 @@
         <v>26589.174669999997</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10113,7 +10113,7 @@
         <v>60431.69513</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>95314.195130000007</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>130196.6951</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>165780.465</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>179750.54879999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>195610.7611</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>196499.72339999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>198853.9976</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>202089.00579999998</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>164077.8836</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>126654.49769999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>90701.344779999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>57298.538379999998</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>40938.322699999997</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10351,7 +10351,7 @@
         <v>30788.296410000003</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>28368.054080000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>31250.81408</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10402,7 +10402,7 @@
         <v>34011.350160000002</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>35066.675019999995</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10436,7 +10436,7 @@
         <v>33453.543590000001</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>25310.301890000002</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>11877.08452</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10529,9 +10529,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790A601-26C3-4DCA-97B6-9342C547A4A0}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10565,7 +10565,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10601,7 +10601,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10619,7 +10619,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10655,7 +10655,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10711,7 +10711,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10730,7 +10730,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10819,7 +10819,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10887,7 +10887,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -11031,12 +11031,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>114</v>
       </c>
@@ -11047,7 +11047,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -11055,13 +11055,13 @@
         <v>138105619</v>
       </c>
       <c r="C2">
-        <v>15.87</v>
+        <v>1000</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -11069,13 +11069,13 @@
         <v>471381508</v>
       </c>
       <c r="C3">
-        <v>28.56</v>
+        <v>1000</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -11083,13 +11083,13 @@
         <v>27736037</v>
       </c>
       <c r="C4">
-        <v>29.18</v>
+        <v>1000</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -11097,13 +11097,13 @@
         <v>61588793</v>
       </c>
       <c r="C5">
-        <v>30.15</v>
+        <v>1000</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -11111,13 +11111,13 @@
         <v>144907263</v>
       </c>
       <c r="C6">
-        <v>33.33</v>
+        <v>1000</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -11125,13 +11125,13 @@
         <v>471381508</v>
       </c>
       <c r="C7">
-        <v>39.69</v>
+        <v>1000</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -11139,13 +11139,13 @@
         <v>98828156</v>
       </c>
       <c r="C8">
-        <v>43.14</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -11153,7 +11153,7 @@
         <v>999999999999</v>
       </c>
       <c r="C9">
-        <v>79.319999999999993</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1294A14-454B-4C12-A610-4EBC208C09E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242CF2B7-D5E0-4759-9FC3-53FB16E4A55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -11058,7 +11058,7 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11202,7 +11202,7 @@
       <c r="B9">
         <v>2321122320</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>23.61</v>
       </c>
       <c r="D9">
@@ -11219,7 +11219,7 @@
       <c r="B10">
         <v>633033360</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>25.71</v>
       </c>
       <c r="D10">
@@ -11236,7 +11236,7 @@
       <c r="B11">
         <v>453673908.00000006</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11">
         <v>27.37</v>
       </c>
       <c r="D11">
@@ -11253,7 +11253,7 @@
       <c r="B12">
         <v>397755961.20000005</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12">
         <v>27.66</v>
       </c>
       <c r="D12">
@@ -11270,7 +11270,7 @@
       <c r="B13">
         <v>1477077840.0000002</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13">
         <v>34.409999999999997</v>
       </c>
       <c r="D13">
@@ -11287,7 +11287,7 @@
       <c r="B14">
         <v>220506620.40000001</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14">
         <v>34.409999999999997</v>
       </c>
       <c r="D14">

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B802C3-58CC-41DB-9A14-CDBF4AD62AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4527232-E70C-4408-BA96-E521B1020982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="lng_block" sheetId="13" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">lng_block!$C$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">lng_block!$C$1:$C$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
   <si>
     <t>Value</t>
   </si>
@@ -229,168 +229,6 @@
     <t>total_facility_cap_initial</t>
   </si>
   <si>
-    <t>280 439,83</t>
-  </si>
-  <si>
-    <t>274 754,91</t>
-  </si>
-  <si>
-    <t>269 179,44</t>
-  </si>
-  <si>
-    <t>263 711,78</t>
-  </si>
-  <si>
-    <t>258 350,32</t>
-  </si>
-  <si>
-    <t>253 093,46</t>
-  </si>
-  <si>
-    <t>247 939,65</t>
-  </si>
-  <si>
-    <t>242 887,37</t>
-  </si>
-  <si>
-    <t>237 935,10</t>
-  </si>
-  <si>
-    <t>233 081,40</t>
-  </si>
-  <si>
-    <t>228 324,82</t>
-  </si>
-  <si>
-    <t>223 663,91</t>
-  </si>
-  <si>
-    <t>219 097,32</t>
-  </si>
-  <si>
-    <t>214 623,65</t>
-  </si>
-  <si>
-    <t>210 241,60</t>
-  </si>
-  <si>
-    <t>205 949,84</t>
-  </si>
-  <si>
-    <t>201 747,12</t>
-  </si>
-  <si>
-    <t>197 632,19</t>
-  </si>
-  <si>
-    <t>193 603,83</t>
-  </si>
-  <si>
-    <t>189 660,87</t>
-  </si>
-  <si>
-    <t>185 802,14</t>
-  </si>
-  <si>
-    <t>182 026,51</t>
-  </si>
-  <si>
-    <t>178 332,87</t>
-  </si>
-  <si>
-    <t>174 720,11</t>
-  </si>
-  <si>
-    <t>171 187,17</t>
-  </si>
-  <si>
-    <t>167 732,98</t>
-  </si>
-  <si>
-    <t>164 356,52</t>
-  </si>
-  <si>
-    <t>527 469,86</t>
-  </si>
-  <si>
-    <t>516 785,56</t>
-  </si>
-  <si>
-    <t>506 302,50</t>
-  </si>
-  <si>
-    <t>496 017,89</t>
-  </si>
-  <si>
-    <t>485 929,01</t>
-  </si>
-  <si>
-    <t>476 033,18</t>
-  </si>
-  <si>
-    <t>466 327,80</t>
-  </si>
-  <si>
-    <t>456 810,30</t>
-  </si>
-  <si>
-    <t>447 478,16</t>
-  </si>
-  <si>
-    <t>438 328,91</t>
-  </si>
-  <si>
-    <t>429 360,14</t>
-  </si>
-  <si>
-    <t>420 569,49</t>
-  </si>
-  <si>
-    <t>411 954,65</t>
-  </si>
-  <si>
-    <t>403 513,36</t>
-  </si>
-  <si>
-    <t>395 243,39</t>
-  </si>
-  <si>
-    <t>387 142,59</t>
-  </si>
-  <si>
-    <t>379 208,83</t>
-  </si>
-  <si>
-    <t>371 440,05</t>
-  </si>
-  <si>
-    <t>363 834,24</t>
-  </si>
-  <si>
-    <t>356 389,41</t>
-  </si>
-  <si>
-    <t>349 103,66</t>
-  </si>
-  <si>
-    <t>341 975,10</t>
-  </si>
-  <si>
-    <t>334 991,90</t>
-  </si>
-  <si>
-    <t>328 152,29</t>
-  </si>
-  <si>
-    <t>321 454,54</t>
-  </si>
-  <si>
-    <t>314 897,00</t>
-  </si>
-  <si>
-    <t>308 477,99</t>
-  </si>
-  <si>
     <t>block</t>
   </si>
   <si>
@@ -400,49 +238,7 @@
     <t>price</t>
   </si>
   <si>
-    <t>Algeria</t>
-  </si>
-  <si>
-    <t>Other Europe</t>
-  </si>
-  <si>
-    <t>Other Africa</t>
-  </si>
-  <si>
-    <t>Trinidad &amp; Tobago</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>Other Americas</t>
-  </si>
-  <si>
     <t>emissions</t>
-  </si>
-  <si>
-    <t>dummy block</t>
-  </si>
-  <si>
-    <t>Qatar</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Malaysia</t>
-  </si>
-  <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
-    <t>Oman</t>
-  </si>
-  <si>
-    <t>Other Asia Pacific</t>
-  </si>
-  <si>
-    <t>Other ME</t>
   </si>
   <si>
     <t>oandm_EU27_solarPV</t>
@@ -456,6 +252,15 @@
   <si>
     <t>oandm_EU27_Batteries</t>
   </si>
+  <si>
+    <t>Net Zero Demand</t>
+  </si>
+  <si>
+    <t>New Momentum Demand</t>
+  </si>
+  <si>
+    <t>What the heck Demand</t>
+  </si>
 </sst>
 </file>
 
@@ -465,7 +270,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,12 +323,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -564,12 +363,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBF1DE"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -601,6 +400,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -626,7 +434,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -647,9 +455,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -1071,7 +879,7 @@
         <v>37</v>
       </c>
       <c r="F1" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="G1" t="s">
         <v>28</v>
@@ -1086,7 +894,7 @@
         <v>38</v>
       </c>
       <c r="K1" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="L1" t="s">
         <v>43</v>
@@ -1101,7 +909,7 @@
         <v>46</v>
       </c>
       <c r="P1" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="Q1" t="s">
         <v>52</v>
@@ -1116,7 +924,7 @@
         <v>55</v>
       </c>
       <c r="U1" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
@@ -1168,11 +976,11 @@
       <c r="P2">
         <v>17386.633918245541</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>87</v>
+      <c r="Q2">
+        <v>280439.83</v>
+      </c>
+      <c r="R2">
+        <v>527469.86</v>
       </c>
       <c r="S2" s="8">
         <v>489061.86</v>
@@ -1233,11 +1041,11 @@
       <c r="P3">
         <v>17386.633918245541</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>88</v>
+      <c r="Q3">
+        <v>274754.90999999997</v>
+      </c>
+      <c r="R3">
+        <v>516785.56</v>
       </c>
       <c r="S3" s="8">
         <v>489061.86</v>
@@ -1298,11 +1106,11 @@
       <c r="P4">
         <v>17386.633918245541</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>89</v>
+      <c r="Q4">
+        <v>269179.44</v>
+      </c>
+      <c r="R4">
+        <v>506302.5</v>
       </c>
       <c r="S4" s="8">
         <v>489061.86</v>
@@ -1363,11 +1171,11 @@
       <c r="P5">
         <v>17386.633918245541</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>90</v>
+      <c r="Q5">
+        <v>263711.78000000003</v>
+      </c>
+      <c r="R5">
+        <v>496017.89</v>
       </c>
       <c r="S5" s="8">
         <v>489061.86</v>
@@ -1428,11 +1236,11 @@
       <c r="P6">
         <v>17386.633918245541</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>91</v>
+      <c r="Q6">
+        <v>258350.32</v>
+      </c>
+      <c r="R6">
+        <v>485929.01</v>
       </c>
       <c r="S6" s="8">
         <v>489061.86</v>
@@ -1493,11 +1301,11 @@
       <c r="P7">
         <v>17386.633918245541</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>92</v>
+      <c r="Q7">
+        <v>253093.46</v>
+      </c>
+      <c r="R7">
+        <v>476033.18</v>
       </c>
       <c r="S7" s="8">
         <v>489061.86</v>
@@ -1558,11 +1366,11 @@
       <c r="P8">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>93</v>
+      <c r="Q8">
+        <v>247939.65</v>
+      </c>
+      <c r="R8">
+        <v>466327.8</v>
       </c>
       <c r="S8" s="8">
         <v>489061.86</v>
@@ -1623,11 +1431,11 @@
       <c r="P9">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>94</v>
+      <c r="Q9">
+        <v>242887.37</v>
+      </c>
+      <c r="R9">
+        <v>456810.3</v>
       </c>
       <c r="S9" s="8">
         <v>489061.86</v>
@@ -1688,11 +1496,11 @@
       <c r="P10">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>95</v>
+      <c r="Q10">
+        <v>237935.1</v>
+      </c>
+      <c r="R10">
+        <v>447478.16</v>
       </c>
       <c r="S10" s="8">
         <v>489061.86</v>
@@ -1753,11 +1561,11 @@
       <c r="P11">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>96</v>
+      <c r="Q11">
+        <v>233081.4</v>
+      </c>
+      <c r="R11">
+        <v>438328.91</v>
       </c>
       <c r="S11" s="8">
         <v>489061.86</v>
@@ -1818,11 +1626,11 @@
       <c r="P12">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>97</v>
+      <c r="Q12">
+        <v>228324.82</v>
+      </c>
+      <c r="R12">
+        <v>429360.14</v>
       </c>
       <c r="S12" s="8">
         <v>489061.86</v>
@@ -1883,11 +1691,11 @@
       <c r="P13">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>98</v>
+      <c r="Q13">
+        <v>223663.91</v>
+      </c>
+      <c r="R13">
+        <v>420569.49</v>
       </c>
       <c r="S13" s="8">
         <v>489061.86</v>
@@ -1948,11 +1756,11 @@
       <c r="P14">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>99</v>
+      <c r="Q14">
+        <v>219097.32</v>
+      </c>
+      <c r="R14">
+        <v>411954.65</v>
       </c>
       <c r="S14" s="8">
         <v>489061.86</v>
@@ -2013,11 +1821,11 @@
       <c r="P15">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>100</v>
+      <c r="Q15">
+        <v>214623.65</v>
+      </c>
+      <c r="R15">
+        <v>403513.36</v>
       </c>
       <c r="S15" s="8">
         <v>489061.86</v>
@@ -2078,11 +1886,11 @@
       <c r="P16">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>101</v>
+      <c r="Q16">
+        <v>210241.6</v>
+      </c>
+      <c r="R16">
+        <v>395243.39</v>
       </c>
       <c r="S16" s="8">
         <v>489061.86</v>
@@ -2143,11 +1951,11 @@
       <c r="P17">
         <v>16662.667964091612</v>
       </c>
-      <c r="Q17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>102</v>
+      <c r="Q17">
+        <v>205949.84</v>
+      </c>
+      <c r="R17">
+        <v>387142.59</v>
       </c>
       <c r="S17" s="8">
         <v>489061.86</v>
@@ -2208,11 +2016,11 @@
       <c r="P18">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>103</v>
+      <c r="Q18">
+        <v>201747.12</v>
+      </c>
+      <c r="R18">
+        <v>379208.83</v>
       </c>
       <c r="S18" s="8">
         <v>489061.86</v>
@@ -2273,11 +2081,11 @@
       <c r="P19">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>104</v>
+      <c r="Q19">
+        <v>197632.19</v>
+      </c>
+      <c r="R19">
+        <v>371440.05</v>
       </c>
       <c r="S19" s="8">
         <v>489061.86</v>
@@ -2338,11 +2146,11 @@
       <c r="P20">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>105</v>
+      <c r="Q20">
+        <v>193603.83</v>
+      </c>
+      <c r="R20">
+        <v>363834.24</v>
       </c>
       <c r="S20" s="8">
         <v>489061.86</v>
@@ -2403,11 +2211,11 @@
       <c r="P21">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>106</v>
+      <c r="Q21">
+        <v>189660.87</v>
+      </c>
+      <c r="R21">
+        <v>356389.41</v>
       </c>
       <c r="S21" s="8">
         <v>489061.86</v>
@@ -2468,11 +2276,11 @@
       <c r="P22">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>107</v>
+      <c r="Q22">
+        <v>185802.14</v>
+      </c>
+      <c r="R22">
+        <v>349103.66</v>
       </c>
       <c r="S22" s="8">
         <v>489061.86</v>
@@ -2533,11 +2341,11 @@
       <c r="P23">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>108</v>
+      <c r="Q23">
+        <v>182026.51</v>
+      </c>
+      <c r="R23">
+        <v>341975.1</v>
       </c>
       <c r="S23" s="8">
         <v>489061.86</v>
@@ -2598,11 +2406,11 @@
       <c r="P24">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>109</v>
+      <c r="Q24">
+        <v>178332.87</v>
+      </c>
+      <c r="R24">
+        <v>334991.90000000002</v>
       </c>
       <c r="S24" s="8">
         <v>489061.86</v>
@@ -2663,11 +2471,11 @@
       <c r="P25">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>110</v>
+      <c r="Q25">
+        <v>174720.11</v>
+      </c>
+      <c r="R25">
+        <v>328152.28999999998</v>
       </c>
       <c r="S25" s="8">
         <v>489061.86</v>
@@ -2728,11 +2536,11 @@
       <c r="P26">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>111</v>
+      <c r="Q26">
+        <v>171187.17</v>
+      </c>
+      <c r="R26">
+        <v>321454.53999999998</v>
       </c>
       <c r="S26" s="8">
         <v>489061.86</v>
@@ -2793,11 +2601,11 @@
       <c r="P27">
         <v>15965.364846295015</v>
       </c>
-      <c r="Q27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>112</v>
+      <c r="Q27">
+        <v>167732.98000000001</v>
+      </c>
+      <c r="R27">
+        <v>314897</v>
       </c>
       <c r="S27" s="8">
         <v>489061.86</v>
@@ -2858,11 +2666,11 @@
       <c r="P28">
         <v>15602.06928231802</v>
       </c>
-      <c r="Q28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>113</v>
+      <c r="Q28">
+        <v>164356.51999999999</v>
+      </c>
+      <c r="R28">
+        <v>308477.99</v>
       </c>
       <c r="S28" s="8">
         <v>489061.86</v>
@@ -10953,7 +10761,6 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <f>SUM(B2*1.04)</f>
         <v>68120</v>
       </c>
       <c r="C3">
@@ -10971,7 +10778,6 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B8" si="0">SUM(B3*1.04)</f>
         <v>70844.800000000003</v>
       </c>
       <c r="C4">
@@ -10989,7 +10795,6 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <f t="shared" si="0"/>
         <v>73678.592000000004</v>
       </c>
       <c r="C5">
@@ -11007,7 +10812,6 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <f t="shared" si="0"/>
         <v>76625.735680000013</v>
       </c>
       <c r="C6">
@@ -11025,8 +10829,7 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <f t="shared" si="0"/>
-        <v>79690.765107200015</v>
+        <v>79690.765107200001</v>
       </c>
       <c r="C7">
         <v>6410</v>
@@ -11043,7 +10846,6 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <f t="shared" si="0"/>
         <v>82878.395711488018</v>
       </c>
       <c r="C8">
@@ -11152,7 +10954,7 @@
         <v>20887.355507945696</v>
       </c>
       <c r="D14">
-        <v>29532.863049035175</v>
+        <v>31009.506201486936</v>
       </c>
       <c r="E14">
         <v>999999</v>
@@ -11169,7 +10971,7 @@
         <v>22976.091058740265</v>
       </c>
       <c r="D15">
-        <v>29532.863049035175</v>
+        <v>32559.981511561284</v>
       </c>
       <c r="E15">
         <v>999999</v>
@@ -11186,7 +10988,7 @@
         <v>25273.700164614293</v>
       </c>
       <c r="D16">
-        <v>29532.863049035175</v>
+        <v>34187.980587139347</v>
       </c>
       <c r="E16">
         <v>999999</v>
@@ -11203,7 +11005,7 @@
         <v>27801.070181075727</v>
       </c>
       <c r="D17">
-        <v>29532.863049035175</v>
+        <v>35897.379616496313</v>
       </c>
       <c r="E17">
         <v>999999</v>
@@ -11220,7 +11022,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D18">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E18">
         <v>999999</v>
@@ -11237,7 +11039,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D19">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E19">
         <v>999999</v>
@@ -11254,7 +11056,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D20">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E20">
         <v>999999</v>
@@ -11271,7 +11073,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D21">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E21">
         <v>999999</v>
@@ -11288,7 +11090,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D22">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E22">
         <v>999999</v>
@@ -11305,7 +11107,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D23">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E23">
         <v>999999</v>
@@ -11322,7 +11124,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D24">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E24">
         <v>999999</v>
@@ -11339,7 +11141,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D25">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E25">
         <v>999999</v>
@@ -11356,7 +11158,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D26">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E26">
         <v>999999</v>
@@ -11373,7 +11175,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D27">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E27">
         <v>999999</v>
@@ -11390,7 +11192,7 @@
         <v>30581.177199183301</v>
       </c>
       <c r="D28">
-        <v>30581.177199183301</v>
+        <v>37692.24859732113</v>
       </c>
       <c r="E28">
         <v>999999</v>
@@ -11403,263 +11205,76 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
     <col min="5" max="5" width="25.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" t="s">
-        <v>123</v>
+        <v>62</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>211011120.00000003</v>
+      <c r="B2" s="8">
+        <v>286654747.94721401</v>
       </c>
       <c r="C2" s="8">
-        <v>9.61</v>
-      </c>
-      <c r="D2">
+        <v>29.19</v>
+      </c>
+      <c r="D2" s="12">
         <v>6.9372000000000003E-2</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2126230105.0000002</v>
+      <c r="B3" s="8">
+        <v>1109104864.5590901</v>
       </c>
       <c r="C3" s="8">
-        <v>13.66</v>
-      </c>
-      <c r="D3">
+        <v>42.69</v>
+      </c>
+      <c r="D3" s="12">
         <v>4.9157999999999993E-2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>81239281.200000003</v>
+      <c r="B4" s="8">
+        <v>293070999999.70697</v>
       </c>
       <c r="C4" s="8">
-        <v>15.66</v>
-      </c>
-      <c r="D4">
+        <v>94.17</v>
+      </c>
+      <c r="D4" s="12">
         <v>4.4639999999999999E-2</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>167331818.16000003</v>
-      </c>
-      <c r="C5" s="8">
-        <v>17.489999999999998</v>
-      </c>
-      <c r="D5">
-        <v>4.4639999999999999E-2</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>90734781.600000009</v>
-      </c>
-      <c r="C6" s="8">
-        <v>18.18</v>
-      </c>
-      <c r="D6">
-        <v>4.6440000000000002E-2</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1055055600.0000001</v>
-      </c>
-      <c r="C7" s="8">
-        <v>18.87</v>
-      </c>
-      <c r="D7">
-        <v>4.4639999999999999E-2</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>179359452.00000003</v>
-      </c>
-      <c r="C8" s="8">
-        <v>20.09</v>
-      </c>
-      <c r="D8">
-        <v>4.0806000000000002E-2</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2321122320</v>
-      </c>
-      <c r="C9" s="8">
-        <v>23.61</v>
-      </c>
-      <c r="D9">
-        <v>0.19746</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>633033360</v>
-      </c>
-      <c r="C10" s="8">
-        <v>25.71</v>
-      </c>
-      <c r="D10">
-        <v>5.1839999999999997E-2</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>453673908.00000006</v>
-      </c>
-      <c r="C11" s="8">
-        <v>27.37</v>
-      </c>
-      <c r="D11">
-        <v>5.7239999999999999E-2</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>397755961.20000005</v>
-      </c>
-      <c r="C12" s="8">
-        <v>27.66</v>
-      </c>
-      <c r="D12">
-        <v>5.7239999999999999E-2</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>1477077840.0000002</v>
-      </c>
-      <c r="C13" s="8">
-        <v>34.409999999999997</v>
-      </c>
-      <c r="D13">
-        <v>3.9239999999999997E-2</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>220506620.40000001</v>
-      </c>
-      <c r="C14" s="8">
-        <v>34.409999999999997</v>
-      </c>
-      <c r="D14">
-        <v>5.7239999999999999E-2</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>99999999999</v>
-      </c>
-      <c r="C15" s="8">
-        <v>1000</v>
-      </c>
-      <c r="D15">
-        <v>0.19746</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>124</v>
+      <c r="E4" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4527232-E70C-4408-BA96-E521B1020982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E8F9F3-0BF6-4B0F-8696-ACA83E9A43F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -11231,7 +11231,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <v>286654747.94721401</v>
+        <v>270613611.10000002</v>
       </c>
       <c r="C2" s="8">
         <v>29.19</v>
@@ -11248,7 +11248,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8">
-        <v>1109104864.5590901</v>
+        <v>1047284444.4400001</v>
       </c>
       <c r="C3" s="8">
         <v>42.69</v>
@@ -11265,10 +11265,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8">
-        <v>293070999999.70697</v>
+        <v>2930833333.3299999</v>
       </c>
       <c r="C4" s="8">
-        <v>94.17</v>
+        <v>150</v>
       </c>
       <c r="D4" s="12">
         <v>4.4639999999999999E-2</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E8F9F3-0BF6-4B0F-8696-ACA83E9A43F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAB626C-FF8B-49DC-9212-F08D6DF01308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -21,10 +21,10 @@
     <sheet name="dcr" sheetId="6" r:id="rId6"/>
     <sheet name="stocklvl" sheetId="7" r:id="rId7"/>
     <sheet name="installable_capacity" sheetId="3" r:id="rId8"/>
-    <sheet name="lng_block" sheetId="13" r:id="rId9"/>
+    <sheet name="gas_block" sheetId="13" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">lng_block!$C$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$C$1:$C$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="73">
   <si>
     <t>Value</t>
   </si>
@@ -253,13 +253,19 @@
     <t>oandm_EU27_Batteries</t>
   </si>
   <si>
-    <t>Net Zero Demand</t>
+    <t>stf</t>
   </si>
   <si>
-    <t>New Momentum Demand</t>
+    <t>pipegas</t>
   </si>
   <si>
-    <t>What the heck Demand</t>
+    <t>NZ_LNG</t>
+  </si>
+  <si>
+    <t>NM_LNG</t>
+  </si>
+  <si>
+    <t>WTF_LNG</t>
   </si>
 </sst>
 </file>
@@ -401,11 +407,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -434,7 +446,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -455,9 +467,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -471,7 +491,28 @@
     <cellStyle name="N_Table1_Header" xfId="6" xr:uid="{5B945886-E1B9-4000-BFBC-F4E856A0CA51}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -9372,8 +9413,8 @@
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6">
-        <v>260000</v>
+      <c r="B2" s="11">
+        <v>304000</v>
       </c>
       <c r="C2" s="6">
         <v>40000</v>
@@ -11205,79 +11246,1419 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.5546875" customWidth="1"/>
     <col min="5" max="5" width="25.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="13">
         <v>270613611.10000002</v>
       </c>
-      <c r="C2" s="8">
+      <c r="D2" s="13">
         <v>29.19</v>
       </c>
-      <c r="D2" s="12">
+      <c r="G2" s="10">
         <v>6.9372000000000003E-2</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="13">
         <v>1047284444.4400001</v>
       </c>
-      <c r="C3" s="8">
+      <c r="D3" s="13">
         <v>42.69</v>
       </c>
-      <c r="D3" s="12">
+      <c r="G3" s="10">
         <v>4.9157999999999993E-2</v>
       </c>
-      <c r="E3" s="10" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D4" s="13">
+        <v>150</v>
+      </c>
+      <c r="G4" s="10">
+        <v>4.4639999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="12"/>
+      <c r="B5" s="14" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8">
+      <c r="C5" s="13">
+        <v>319200000</v>
+      </c>
+      <c r="D5" s="13">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D6" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D7" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="13">
         <v>2930833333.3299999</v>
       </c>
-      <c r="C4" s="8">
+      <c r="D8" s="13">
         <v>150</v>
       </c>
-      <c r="D4" s="12">
-        <v>4.4639999999999999E-2</v>
-      </c>
-      <c r="E4" s="11" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="13">
+        <v>306266016</v>
+      </c>
+      <c r="D9" s="13">
+        <v>22.545000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="C10" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D10" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D11" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D12" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="13">
+        <v>293856117.03167999</v>
+      </c>
+      <c r="D13" s="13">
+        <v>22.41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
+        <v>2027</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D14" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D15" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="12"/>
+      <c r="B16" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D16" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="12"/>
+      <c r="B17" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="13">
+        <v>281949067.16955632</v>
+      </c>
+      <c r="D17" s="13">
+        <v>22.274999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
+        <v>2028</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D18" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="12"/>
+      <c r="B19" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D19" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="12"/>
+      <c r="B20" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D20" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="13">
+        <v>270524490.96784592</v>
+      </c>
+      <c r="D21" s="13">
+        <v>22.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
+        <v>2029</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D22" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="12"/>
+      <c r="B23" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D23" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="12"/>
+      <c r="B24" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D24" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="12"/>
+      <c r="B25" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="13">
+        <v>259562838.5938288</v>
+      </c>
+      <c r="D25" s="13">
+        <v>22.004999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
+        <v>2030</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D26" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="12"/>
+      <c r="B27" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D27" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="12"/>
+      <c r="B28" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D28" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="12"/>
+      <c r="B29" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="13">
+        <v>249045352.37400681</v>
+      </c>
+      <c r="D29" s="13">
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="12">
+        <v>2031</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D30" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="12"/>
+      <c r="B31" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D31" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="12"/>
+      <c r="B32" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D32" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="12"/>
+      <c r="B33" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="13">
+        <v>238954034.69581211</v>
+      </c>
+      <c r="D33" s="13">
+        <v>21.734999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="12">
+        <v>2032</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D34" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="12"/>
+      <c r="B35" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D35" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="12"/>
+      <c r="B36" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D36" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="12"/>
+      <c r="B37" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="13">
+        <v>229271617.20993781</v>
+      </c>
+      <c r="D37" s="13">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="12">
+        <v>2033</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D38" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="12"/>
+      <c r="B39" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D39" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="12"/>
+      <c r="B40" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D40" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="12"/>
+      <c r="B41" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="13">
+        <v>219981531.2805911</v>
+      </c>
+      <c r="D41" s="13">
+        <v>21.465</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="12">
+        <v>2034</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D42" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="12"/>
+      <c r="B43" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D43" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="12"/>
+      <c r="B44" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D44" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="12"/>
+      <c r="B45" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="13">
+        <v>211067879.63310149</v>
+      </c>
+      <c r="D45" s="13">
+        <v>21.33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="12">
+        <v>2035</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D46" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="12"/>
+      <c r="B47" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D47" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="12"/>
+      <c r="B48" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D48" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="12"/>
+      <c r="B49" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="13">
+        <v>202515409.1503683</v>
+      </c>
+      <c r="D49" s="13">
+        <v>21.195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="12">
+        <v>2036</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D50" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="12"/>
+      <c r="B51" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D51" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="12"/>
+      <c r="B52" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D52" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="12"/>
+      <c r="B53" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="13">
+        <v>194309484.77159539</v>
+      </c>
+      <c r="D53" s="13">
+        <v>21.06</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="12">
+        <v>2037</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D54" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="12"/>
+      <c r="B55" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D55" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="12"/>
+      <c r="B56" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D56" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="12"/>
+      <c r="B57" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="13">
+        <v>186436064.4486503</v>
+      </c>
+      <c r="D57" s="13">
+        <v>20.925000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="12">
+        <v>2038</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D58" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="12"/>
+      <c r="B59" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D59" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="12"/>
+      <c r="B60" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D60" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="12"/>
+      <c r="B61" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="13">
+        <v>178881675.11719099</v>
+      </c>
+      <c r="D61" s="13">
+        <v>20.79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="12">
+        <v>2039</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D62" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="12"/>
+      <c r="B63" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D63" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="12"/>
+      <c r="B64" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D64" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="12"/>
+      <c r="B65" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="13">
+        <v>171633389.64144239</v>
+      </c>
+      <c r="D65" s="13">
+        <v>20.655000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="12">
+        <v>2040</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D66" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="12"/>
+      <c r="B67" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D67" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="12"/>
+      <c r="B68" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D68" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="12"/>
+      <c r="B69" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="13">
+        <v>164678804.6931712</v>
+      </c>
+      <c r="D69" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="12">
+        <v>2041</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D70" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="12"/>
+      <c r="B71" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D71" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="12"/>
+      <c r="B72" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D72" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="12"/>
+      <c r="B73" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73" s="13">
+        <v>158006019.52700391</v>
+      </c>
+      <c r="D73" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="12">
+        <v>2042</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C74" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D74" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="12"/>
+      <c r="B75" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D75" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="12"/>
+      <c r="B76" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D76" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="12"/>
+      <c r="B77" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C77" s="13">
+        <v>151603615.61576971</v>
+      </c>
+      <c r="D77" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="12">
+        <v>2043</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C78" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D78" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="12"/>
+      <c r="B79" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D79" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="12"/>
+      <c r="B80" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C80" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D80" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="12"/>
+      <c r="B81" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C81" s="13">
+        <v>145460637.11101869</v>
+      </c>
+      <c r="D81" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="12">
+        <v>2044</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C82" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D82" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="12"/>
+      <c r="B83" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C83" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D83" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="12"/>
+      <c r="B84" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C84" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D84" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="12"/>
+      <c r="B85" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C85" s="13">
+        <v>139566572.0952802</v>
+      </c>
+      <c r="D85" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="12">
+        <v>2045</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C86" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D86" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="12"/>
+      <c r="B87" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C87" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D87" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="12"/>
+      <c r="B88" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C88" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D88" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="12"/>
+      <c r="B89" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C89" s="13">
+        <v>133911334.5939794</v>
+      </c>
+      <c r="D89" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="12">
+        <v>2046</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C90" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D90" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="12"/>
+      <c r="B91" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C91" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D91" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="12"/>
+      <c r="B92" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C92" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D92" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="12"/>
+      <c r="B93" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C93" s="13">
+        <v>128485247.3162314</v>
+      </c>
+      <c r="D93" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="12">
+        <v>2047</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C94" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D94" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="12"/>
+      <c r="B95" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C95" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D95" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="12"/>
+      <c r="B96" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C96" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D96" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="12"/>
+      <c r="B97" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C97" s="13">
+        <v>123279025.09497771</v>
+      </c>
+      <c r="D97" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="12">
+        <v>2048</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C98" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D98" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="12"/>
+      <c r="B99" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C99" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D99" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="12"/>
+      <c r="B100" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C100" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D100" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="12"/>
+      <c r="B101" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C101" s="13">
+        <v>118283758.9981292</v>
+      </c>
+      <c r="D101" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="12">
+        <v>2049</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D102" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="12"/>
+      <c r="B103" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D103" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="12"/>
+      <c r="B104" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C104" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D104" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="12"/>
+      <c r="B105" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C105" s="13">
+        <v>113490901.083525</v>
+      </c>
+      <c r="D105" s="13">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="12">
+        <v>2050</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C106" s="13">
+        <v>270613611.10000002</v>
+      </c>
+      <c r="D106" s="13">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="12"/>
+      <c r="B107" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" s="13">
+        <v>1047284444.4400001</v>
+      </c>
+      <c r="D107" s="13">
+        <v>42.69</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="12"/>
+      <c r="B108" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C108" s="13">
+        <v>2930833333.3299999</v>
+      </c>
+      <c r="D108" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="12"/>
+      <c r="B109" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C109" s="13">
+        <v>108892249.7716206</v>
+      </c>
+      <c r="D109" s="13">
+        <v>20.52</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A98:A101"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3966CB-6233-4861-A1AB-524FA1662BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE77B3D-C3B4-4E0C-AFC1-23B6CEAF6A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -9413,10 +9413,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="6">
-        <v>0.24030000000000001</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="J2" s="6">
-        <v>0.38879999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="K2" s="5">
         <v>0.8</v>
@@ -9495,7 +9495,7 @@
       <c r="H3" s="5">
         <v>0</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="6">
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="J3" s="6">
@@ -9578,7 +9578,7 @@
       <c r="H4" s="5">
         <v>0</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="6">
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="J4" s="6">
@@ -9662,7 +9662,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="6">
-        <v>0.27439999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="J5" s="6">
         <v>0.3</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE77B3D-C3B4-4E0C-AFC1-23B6CEAF6A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F3767D-D283-4351-B8AB-5CB928985F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -11228,7 +11228,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -11276,6 +11277,7 @@
       <c r="D3">
         <v>42.69</v>
       </c>
+      <c r="E3" s="2"/>
       <c r="G3" s="10">
         <v>4.9157999999999993E-2</v>
       </c>
@@ -11301,7 +11303,7 @@
         <v>69</v>
       </c>
       <c r="C5" s="2">
-        <v>532000000</v>
+        <v>484006334</v>
       </c>
       <c r="D5">
         <v>22.68</v>
@@ -11351,7 +11353,8 @@
         <v>69</v>
       </c>
       <c r="C9" s="2">
-        <v>510132160</v>
+        <f>SUM(C5*(1-0.04052))</f>
+        <v>464394397.34631997</v>
       </c>
       <c r="D9">
         <v>22.545000000000002</v>
@@ -11401,7 +11404,8 @@
         <v>69</v>
       </c>
       <c r="C13" s="2">
-        <v>489197947</v>
+        <f>SUM(C9*(1-0.04052))</f>
+        <v>445577136.36584711</v>
       </c>
       <c r="D13">
         <v>22.41</v>
@@ -11451,7 +11455,8 @@
         <v>69</v>
       </c>
       <c r="C17" s="2">
-        <v>469163758</v>
+        <f>SUM(C13*(1-0.04052))</f>
+        <v>427522350.80030298</v>
       </c>
       <c r="D17">
         <v>22.274999999999999</v>
@@ -11501,7 +11506,8 @@
         <v>69</v>
       </c>
       <c r="C21" s="2">
-        <v>449997786</v>
+        <f>SUM(C17*(1-0.04052))</f>
+        <v>410199145.14587468</v>
       </c>
       <c r="D21">
         <v>22.14</v>
@@ -11551,7 +11557,8 @@
         <v>69</v>
       </c>
       <c r="C25" s="2">
-        <v>431671839</v>
+        <f>SUM(C21*(1-0.04052))</f>
+        <v>393577875.78456384</v>
       </c>
       <c r="D25">
         <v>22.004999999999999</v>
@@ -11601,7 +11608,8 @@
         <v>69</v>
       </c>
       <c r="C29" s="2">
-        <v>414151522</v>
+        <f>SUM(C25*(1-0.04052))</f>
+        <v>377630100.25777334</v>
       </c>
       <c r="D29">
         <v>21.87</v>
@@ -11651,7 +11659,8 @@
         <v>69</v>
       </c>
       <c r="C33" s="2">
-        <v>397404638</v>
+        <f>SUM(C29*(1-0.04052))</f>
+        <v>362328528.59532839</v>
       </c>
       <c r="D33">
         <v>21.734999999999999</v>
@@ -11701,7 +11710,8 @@
         <v>69</v>
       </c>
       <c r="C37" s="2">
-        <v>381406956</v>
+        <f>SUM(C33*(1-0.04052))</f>
+        <v>347646976.61664569</v>
       </c>
       <c r="D37">
         <v>21.6</v>
@@ -11751,7 +11761,8 @@
         <v>69</v>
       </c>
       <c r="C41" s="2">
-        <v>366136021</v>
+        <f>SUM(C37*(1-0.04052))</f>
+        <v>333560321.12413919</v>
       </c>
       <c r="D41">
         <v>21.465</v>
@@ -11801,7 +11812,8 @@
         <v>69</v>
       </c>
       <c r="C45" s="2">
-        <v>351566712</v>
+        <f>SUM(C41*(1-0.04052))</f>
+        <v>320044456.91218907</v>
       </c>
       <c r="D45">
         <v>21.33</v>
@@ -11851,7 +11863,8 @@
         <v>69</v>
       </c>
       <c r="C49" s="2">
-        <v>337680248</v>
+        <f>SUM(C45*(1-0.04052))</f>
+        <v>307076255.51810718</v>
       </c>
       <c r="D49">
         <v>21.195</v>
@@ -11901,7 +11914,8 @@
         <v>69</v>
       </c>
       <c r="C53" s="2">
-        <v>324452734</v>
+        <f>SUM(C49*(1-0.04052))</f>
+        <v>294633525.64451349</v>
       </c>
       <c r="D53">
         <v>21.06</v>
@@ -11951,7 +11965,8 @@
         <v>69</v>
       </c>
       <c r="C57" s="2">
-        <v>311864566</v>
+        <f>SUM(C53*(1-0.04052))</f>
+        <v>282694975.1853978</v>
       </c>
       <c r="D57">
         <v>20.925000000000001</v>
@@ -12001,7 +12016,8 @@
         <v>69</v>
       </c>
       <c r="C61" s="2">
-        <v>299896970</v>
+        <f>SUM(C57*(1-0.04052))</f>
+        <v>271240174.79088551</v>
       </c>
       <c r="D61">
         <v>20.79</v>
@@ -12051,7 +12067,8 @@
         <v>69</v>
       </c>
       <c r="C65" s="2">
-        <v>288530884</v>
+        <f>SUM(C61*(1-0.04052))</f>
+        <v>260249522.90835881</v>
       </c>
       <c r="D65">
         <v>20.655000000000001</v>
@@ -12101,7 +12118,8 @@
         <v>69</v>
       </c>
       <c r="C69" s="2">
-        <v>277748804</v>
+        <f>SUM(C65*(1-0.04052))</f>
+        <v>249704212.24011213</v>
       </c>
       <c r="D69">
         <v>20.52</v>
@@ -12151,7 +12169,8 @@
         <v>69</v>
       </c>
       <c r="C73" s="2">
-        <v>267535969</v>
+        <f>SUM(C69*(1-0.04052))</f>
+        <v>239586197.56014279</v>
       </c>
       <c r="D73">
         <v>20.52</v>
@@ -12201,7 +12220,8 @@
         <v>69</v>
       </c>
       <c r="C77" s="2">
-        <v>257872875</v>
+        <f>SUM(C73*(1-0.04052))</f>
+        <v>229878164.83500579</v>
       </c>
       <c r="D77">
         <v>20.52</v>
@@ -12251,7 +12271,8 @@
         <v>69</v>
       </c>
       <c r="C81" s="2">
-        <v>248744486</v>
+        <f>SUM(C77*(1-0.04052))</f>
+        <v>220563501.59589136</v>
       </c>
       <c r="D81">
         <v>20.52</v>
@@ -12301,7 +12322,8 @@
         <v>69</v>
       </c>
       <c r="C85" s="2">
-        <v>240136226</v>
+        <f>SUM(C81*(1-0.04052))</f>
+        <v>211626268.51122585</v>
       </c>
       <c r="D85">
         <v>20.52</v>
@@ -12351,7 +12373,8 @@
         <v>69</v>
       </c>
       <c r="C89" s="2">
-        <v>232032192</v>
+        <f>SUM(C85*(1-0.04052))</f>
+        <v>203051172.11115098</v>
       </c>
       <c r="D89">
         <v>20.52</v>
@@ -12401,7 +12424,8 @@
         <v>69</v>
       </c>
       <c r="C93" s="2">
-        <v>224418473</v>
+        <f>SUM(C89*(1-0.04052))</f>
+        <v>194823538.61720714</v>
       </c>
       <c r="D93">
         <v>20.52</v>
@@ -12451,7 +12475,8 @@
         <v>69</v>
       </c>
       <c r="C97" s="2">
-        <v>217272367</v>
+        <f>SUM(C93*(1-0.04052))</f>
+        <v>186929288.8324379</v>
       </c>
       <c r="D97">
         <v>20.52</v>
@@ -12501,7 +12526,8 @@
         <v>69</v>
       </c>
       <c r="C101" s="2">
-        <v>210579168</v>
+        <f>SUM(C97*(1-0.04052))</f>
+        <v>179354914.04894751</v>
       </c>
       <c r="D101">
         <v>20.52</v>
@@ -12551,7 +12577,8 @@
         <v>69</v>
       </c>
       <c r="C105" s="2">
-        <v>204325995</v>
+        <f>SUM(C101*(1-0.04052))</f>
+        <v>172087452.93168417</v>
       </c>
       <c r="D105">
         <v>20.52</v>
@@ -12601,7 +12628,8 @@
         <v>69</v>
       </c>
       <c r="C109" s="2">
-        <v>198500000</v>
+        <f>SUM(C105*(1-0.04052))</f>
+        <v>165114469.33889231</v>
       </c>
       <c r="D109">
         <v>20.52</v>
@@ -12610,6 +12638,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -12617,26 +12665,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F3767D-D283-4351-B8AB-5CB928985F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC3AB8D-448B-4BC5-89B4-998695B2552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -821,9 +821,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31FF74EF-7037-4139-88AF-F295C305C1F7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -839,7 +839,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -847,7 +847,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -863,25 +863,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185AF38-42FD-4CFF-B287-2FCFFF6C6EF3}">
   <dimension ref="A1:U28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="5" width="37.33203125" customWidth="1"/>
-    <col min="6" max="6" width="29.88671875" customWidth="1"/>
-    <col min="7" max="7" width="39.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" customWidth="1"/>
-    <col min="10" max="11" width="22.5546875" customWidth="1"/>
-    <col min="12" max="12" width="24.109375" customWidth="1"/>
-    <col min="13" max="13" width="27.6640625" customWidth="1"/>
-    <col min="14" max="14" width="22.88671875" customWidth="1"/>
-    <col min="15" max="16" width="20.109375" customWidth="1"/>
-    <col min="18" max="18" width="32.6640625" customWidth="1"/>
-    <col min="19" max="19" width="35.33203125" customWidth="1"/>
-    <col min="20" max="20" width="31.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="5" width="37.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="7" max="7" width="39.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="10" max="11" width="22.5703125" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" customWidth="1"/>
+    <col min="13" max="13" width="27.7109375" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" customWidth="1"/>
+    <col min="15" max="16" width="20.140625" customWidth="1"/>
+    <col min="18" max="18" width="32.7109375" customWidth="1"/>
+    <col min="19" max="19" width="35.28515625" customWidth="1"/>
+    <col min="20" max="20" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -946,7 +946,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -957,7 +957,7 @@
         <v>303600</v>
       </c>
       <c r="D2" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E2" s="8">
         <v>1000</v>
@@ -972,7 +972,7 @@
         <v>2337972.5216000001</v>
       </c>
       <c r="I2" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J2" s="8">
         <v>1000</v>
@@ -987,7 +987,7 @@
         <v>1673707.7</v>
       </c>
       <c r="N2" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O2">
         <v>1000</v>
@@ -1002,7 +1002,7 @@
         <v>527469.86</v>
       </c>
       <c r="S2" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T2">
         <v>1000</v>
@@ -1011,7 +1011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>299045.40000000002</v>
       </c>
       <c r="D3" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E3" s="8">
         <v>1000</v>
@@ -1037,7 +1037,7 @@
         <v>2318026.381866667</v>
       </c>
       <c r="I3" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J3" s="8">
         <v>1000</v>
@@ -1052,7 +1052,7 @@
         <v>1660955.6413333334</v>
       </c>
       <c r="N3" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O3">
         <v>1000</v>
@@ -1067,7 +1067,7 @@
         <v>516785.56</v>
       </c>
       <c r="S3" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T3">
         <v>1000</v>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>294559.71899999998</v>
       </c>
       <c r="D4" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E4" s="8">
         <v>1000</v>
@@ -1102,7 +1102,7 @@
         <v>2298080.2421333333</v>
       </c>
       <c r="I4" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J4" s="8">
         <v>1000</v>
@@ -1117,7 +1117,7 @@
         <v>1648203.5826666667</v>
       </c>
       <c r="N4" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O4">
         <v>1000</v>
@@ -1132,7 +1132,7 @@
         <v>506302.5</v>
       </c>
       <c r="S4" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T4">
         <v>1000</v>
@@ -1141,7 +1141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>290141.32319999998</v>
       </c>
       <c r="D5" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E5" s="8">
         <v>1000</v>
@@ -1167,7 +1167,7 @@
         <v>2278134.1023999997</v>
       </c>
       <c r="I5" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J5" s="8">
         <v>1000</v>
@@ -1182,7 +1182,7 @@
         <v>1635451.524</v>
       </c>
       <c r="N5" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O5">
         <v>1000</v>
@@ -1197,7 +1197,7 @@
         <v>496017.89</v>
       </c>
       <c r="S5" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T5">
         <v>1000</v>
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>285788.2034</v>
       </c>
       <c r="D6" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E6" s="8">
         <v>1000</v>
@@ -1232,7 +1232,7 @@
         <v>2258187.9626666661</v>
       </c>
       <c r="I6" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J6" s="8">
         <v>1000</v>
@@ -1247,7 +1247,7 @@
         <v>1622699.4653333335</v>
       </c>
       <c r="N6" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O6">
         <v>1000</v>
@@ -1262,7 +1262,7 @@
         <v>485929.01</v>
       </c>
       <c r="S6" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T6">
         <v>1000</v>
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>281498.4804</v>
       </c>
       <c r="D7" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E7" s="8">
         <v>1000</v>
@@ -1297,7 +1297,7 @@
         <v>2238241.8229333302</v>
       </c>
       <c r="I7" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J7" s="8">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>1609947.4066666667</v>
       </c>
       <c r="N7" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O7">
         <v>1000</v>
@@ -1327,7 +1327,7 @@
         <v>476033.18</v>
       </c>
       <c r="S7" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T7">
         <v>1000</v>
@@ -1336,7 +1336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>277270.34419999999</v>
       </c>
       <c r="D8" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E8" s="8">
         <v>1000</v>
@@ -1362,7 +1362,7 @@
         <v>2218295.6831999999</v>
       </c>
       <c r="I8" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J8" s="8">
         <v>1000</v>
@@ -1377,7 +1377,7 @@
         <v>1597195.3480000002</v>
       </c>
       <c r="N8" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O8">
         <v>1000</v>
@@ -1392,7 +1392,7 @@
         <v>466327.8</v>
       </c>
       <c r="S8" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T8">
         <v>1000</v>
@@ -1401,7 +1401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>273102.28909999999</v>
       </c>
       <c r="D9" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E9" s="8">
         <v>1000</v>
@@ -1427,7 +1427,7 @@
         <v>2205259.4561600001</v>
       </c>
       <c r="I9" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J9" s="8">
         <v>1000</v>
@@ -1442,7 +1442,7 @@
         <v>1594326.1348000003</v>
       </c>
       <c r="N9" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O9">
         <v>1000</v>
@@ -1457,7 +1457,7 @@
         <v>456810.3</v>
       </c>
       <c r="S9" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T9">
         <v>1000</v>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>268993.2548</v>
       </c>
       <c r="D10" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E10" s="8">
         <v>1000</v>
@@ -1492,7 +1492,7 @@
         <v>2192223.2291199998</v>
       </c>
       <c r="I10" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J10" s="8">
         <v>1000</v>
@@ -1507,7 +1507,7 @@
         <v>1591456.9216000002</v>
       </c>
       <c r="N10" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O10">
         <v>1000</v>
@@ -1522,7 +1522,7 @@
         <v>447478.16</v>
       </c>
       <c r="S10" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T10">
         <v>1000</v>
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>264942.41499999998</v>
       </c>
       <c r="D11" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E11" s="8">
         <v>1000</v>
@@ -1557,7 +1557,7 @@
         <v>2179187.0020799995</v>
       </c>
       <c r="I11" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J11" s="8">
         <v>1000</v>
@@ -1572,7 +1572,7 @@
         <v>1588587.7084000004</v>
       </c>
       <c r="N11" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O11">
         <v>1000</v>
@@ -1587,7 +1587,7 @@
         <v>438328.91</v>
       </c>
       <c r="S11" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T11">
         <v>1000</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>260948.7948</v>
       </c>
       <c r="D12" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E12" s="8">
         <v>1000</v>
@@ -1622,7 +1622,7 @@
         <v>2166150.7750399997</v>
       </c>
       <c r="I12" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J12" s="8">
         <v>1000</v>
@@ -1637,7 +1637,7 @@
         <v>1585718.4952000002</v>
       </c>
       <c r="N12" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O12">
         <v>1000</v>
@@ -1652,7 +1652,7 @@
         <v>429360.14</v>
       </c>
       <c r="S12" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T12">
         <v>1000</v>
@@ -1661,7 +1661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>257011.4613</v>
       </c>
       <c r="D13" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E13" s="8">
         <v>1000</v>
@@ -1687,7 +1687,7 @@
         <v>2153114.5479999995</v>
       </c>
       <c r="I13" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J13" s="8">
         <v>1000</v>
@@ -1702,7 +1702,7 @@
         <v>1582849.2820000004</v>
       </c>
       <c r="N13" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O13">
         <v>1000</v>
@@ -1717,7 +1717,7 @@
         <v>420569.49</v>
       </c>
       <c r="S13" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T13">
         <v>1000</v>
@@ -1726,7 +1726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>253129.39139999999</v>
       </c>
       <c r="D14" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E14" s="8">
         <v>1000</v>
@@ -1752,7 +1752,7 @@
         <v>2140078.3209599997</v>
       </c>
       <c r="I14" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J14" s="8">
         <v>1000</v>
@@ -1767,7 +1767,7 @@
         <v>1579980.0688000005</v>
       </c>
       <c r="N14" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O14">
         <v>1000</v>
@@ -1782,7 +1782,7 @@
         <v>411954.65</v>
       </c>
       <c r="S14" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T14">
         <v>1000</v>
@@ -1791,7 +1791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>249301.63759999999</v>
       </c>
       <c r="D15" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E15" s="8">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>2127042.0939199994</v>
       </c>
       <c r="I15" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J15" s="8">
         <v>1000</v>
@@ -1832,7 +1832,7 @@
         <v>1577110.8556000004</v>
       </c>
       <c r="N15" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O15">
         <v>1000</v>
@@ -1847,7 +1847,7 @@
         <v>403513.36</v>
       </c>
       <c r="S15" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T15">
         <v>1000</v>
@@ -1856,7 +1856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>245527.30809999999</v>
       </c>
       <c r="D16" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E16" s="8">
         <v>1000</v>
@@ -1882,7 +1882,7 @@
         <v>2114005.8668799992</v>
       </c>
       <c r="I16" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J16" s="8">
         <v>1000</v>
@@ -1897,7 +1897,7 @@
         <v>1574241.6424000005</v>
       </c>
       <c r="N16" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O16">
         <v>1000</v>
@@ -1912,7 +1912,7 @@
         <v>395243.39</v>
       </c>
       <c r="S16" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T16">
         <v>1000</v>
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>241805.39859999999</v>
       </c>
       <c r="D17" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E17" s="8">
         <v>1000</v>
@@ -1947,7 +1947,7 @@
         <v>2100969.6398399994</v>
       </c>
       <c r="I17" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J17" s="8">
         <v>1000</v>
@@ -1962,7 +1962,7 @@
         <v>1571372.4292000004</v>
       </c>
       <c r="N17" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O17">
         <v>1000</v>
@@ -1977,7 +1977,7 @@
         <v>387142.59</v>
       </c>
       <c r="S17" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T17">
         <v>1000</v>
@@ -1986,7 +1986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>238134.9901</v>
       </c>
       <c r="D18" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E18" s="8">
         <v>1000</v>
@@ -2012,7 +2012,7 @@
         <v>2087933.4128</v>
       </c>
       <c r="I18" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J18" s="8">
         <v>1000</v>
@@ -2027,7 +2027,7 @@
         <v>1568503.2160000005</v>
       </c>
       <c r="N18" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O18">
         <v>1000</v>
@@ -2042,7 +2042,7 @@
         <v>379208.83</v>
       </c>
       <c r="S18" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T18">
         <v>1000</v>
@@ -2051,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>234515.065</v>
       </c>
       <c r="D19" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E19" s="8">
         <v>1000</v>
@@ -2077,7 +2077,7 @@
         <v>2076927.41784</v>
       </c>
       <c r="I19" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J19" s="8">
         <v>1000</v>
@@ -2092,7 +2092,7 @@
         <v>1565634.0028000006</v>
       </c>
       <c r="N19" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O19">
         <v>1000</v>
@@ -2107,7 +2107,7 @@
         <v>371440.05</v>
       </c>
       <c r="S19" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T19">
         <v>1000</v>
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>230944.68799999999</v>
       </c>
       <c r="D20" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E20" s="8">
         <v>1000</v>
@@ -2142,7 +2142,7 @@
         <v>2065921.4228800002</v>
       </c>
       <c r="I20" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J20" s="8">
         <v>1000</v>
@@ -2157,7 +2157,7 @@
         <v>1562764.7896000005</v>
       </c>
       <c r="N20" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O20">
         <v>1000</v>
@@ -2172,7 +2172,7 @@
         <v>363834.24</v>
       </c>
       <c r="S20" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T20">
         <v>1000</v>
@@ -2181,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>227422.96530000001</v>
       </c>
       <c r="D21" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E21" s="8">
         <v>1000</v>
@@ -2207,7 +2207,7 @@
         <v>2054915.4279200002</v>
       </c>
       <c r="I21" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J21" s="8">
         <v>1000</v>
@@ -2222,7 +2222,7 @@
         <v>1559895.5764000006</v>
       </c>
       <c r="N21" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O21">
         <v>1000</v>
@@ -2237,7 +2237,7 @@
         <v>356389.41</v>
       </c>
       <c r="S21" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T21">
         <v>1000</v>
@@ -2246,7 +2246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>223948.88099999999</v>
       </c>
       <c r="D22" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E22" s="8">
         <v>1000</v>
@@ -2272,7 +2272,7 @@
         <v>2043909.4329600004</v>
       </c>
       <c r="I22" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J22" s="8">
         <v>1000</v>
@@ -2287,7 +2287,7 @@
         <v>1557026.3632000005</v>
       </c>
       <c r="N22" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O22">
         <v>1000</v>
@@ -2302,7 +2302,7 @@
         <v>349103.66</v>
       </c>
       <c r="S22" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T22">
         <v>1000</v>
@@ -2311,7 +2311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>220521.46350000001</v>
       </c>
       <c r="D23" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E23" s="8">
         <v>1000</v>
@@ -2337,7 +2337,7 @@
         <v>2032903.4380000005</v>
       </c>
       <c r="I23" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J23" s="8">
         <v>1000</v>
@@ -2352,7 +2352,7 @@
         <v>1554157.1500000006</v>
       </c>
       <c r="N23" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O23">
         <v>1000</v>
@@ -2367,7 +2367,7 @@
         <v>341975.1</v>
       </c>
       <c r="S23" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T23">
         <v>1000</v>
@@ -2376,7 +2376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>217139.74350000001</v>
       </c>
       <c r="D24" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E24" s="8">
         <v>1000</v>
@@ -2402,7 +2402,7 @@
         <v>2021897.4430400007</v>
       </c>
       <c r="I24" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J24" s="8">
         <v>1000</v>
@@ -2417,7 +2417,7 @@
         <v>1551287.9368000007</v>
       </c>
       <c r="N24" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O24">
         <v>1000</v>
@@ -2432,7 +2432,7 @@
         <v>334991.90000000002</v>
       </c>
       <c r="S24" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T24">
         <v>1000</v>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>213802.75769999999</v>
       </c>
       <c r="D25" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E25" s="8">
         <v>1000</v>
@@ -2467,7 +2467,7 @@
         <v>2010891.4480800009</v>
       </c>
       <c r="I25" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J25" s="8">
         <v>1000</v>
@@ -2482,7 +2482,7 @@
         <v>1548418.7236000006</v>
       </c>
       <c r="N25" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O25">
         <v>1000</v>
@@ -2497,7 +2497,7 @@
         <v>328152.28999999998</v>
       </c>
       <c r="S25" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T25">
         <v>1000</v>
@@ -2506,7 +2506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>210509.61679999999</v>
       </c>
       <c r="D26" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E26" s="8">
         <v>1000</v>
@@ -2532,7 +2532,7 @@
         <v>1999885.4531200009</v>
       </c>
       <c r="I26" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J26" s="8">
         <v>1000</v>
@@ -2547,7 +2547,7 @@
         <v>1545549.5104000007</v>
       </c>
       <c r="N26" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O26">
         <v>1000</v>
@@ -2562,7 +2562,7 @@
         <v>321454.53999999998</v>
       </c>
       <c r="S26" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T26">
         <v>1000</v>
@@ -2571,7 +2571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>207259.3126</v>
       </c>
       <c r="D27" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E27" s="8">
         <v>1000</v>
@@ -2597,7 +2597,7 @@
         <v>1988879.4581600011</v>
       </c>
       <c r="I27" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J27" s="8">
         <v>1000</v>
@@ -2612,7 +2612,7 @@
         <v>1542680.2972000006</v>
       </c>
       <c r="N27" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O27">
         <v>1000</v>
@@ -2627,7 +2627,7 @@
         <v>314897</v>
       </c>
       <c r="S27" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T27">
         <v>1000</v>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>204050.9535</v>
       </c>
       <c r="D28" s="8">
-        <v>227700</v>
+        <v>257700</v>
       </c>
       <c r="E28" s="8">
         <v>1000</v>
@@ -2662,7 +2662,7 @@
         <v>1977873.4631999999</v>
       </c>
       <c r="I28" s="8">
-        <v>1646946.1610000001</v>
+        <v>1996946.1610000001</v>
       </c>
       <c r="J28" s="8">
         <v>1000</v>
@@ -2677,7 +2677,7 @@
         <v>1539811.0840000003</v>
       </c>
       <c r="N28" s="8">
-        <v>1093231.041</v>
+        <v>1143231.041</v>
       </c>
       <c r="O28">
         <v>1000</v>
@@ -2692,7 +2692,7 @@
         <v>308477.99</v>
       </c>
       <c r="S28" s="8">
-        <v>489061.86</v>
+        <v>519061.86</v>
       </c>
       <c r="T28">
         <v>1000</v>
@@ -2710,64 +2710,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0D039F-A3AA-471E-A6A2-F25F8348E84D}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
   </sheetData>
@@ -2778,12 +2778,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6341E4C-4AB4-44A4-8119-B6BB3BEB6E84}">
   <dimension ref="A1:F325"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>4</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>7</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>8</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>10</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>11</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>12</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>5</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>6</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>8</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>10</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>11</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>12</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>6</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>7</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>10</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>11</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>12</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>3</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>5</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>6</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>7</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>8</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>9</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>11</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>12</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>3</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>4</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>5</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>6</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>7</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>8</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>9</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>10</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>11</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>12</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>3</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>4</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>5</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>6</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>7</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>8</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>9</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>10</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>11</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>12</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>3</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>4</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>5</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>6</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>7</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>8</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>9</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>10</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>11</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>3</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>4</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>5</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>6</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>7</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>8</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>9</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>10</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>11</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>12</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>3</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>4</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>5</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>6</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>7</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>8</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>9</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>10</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>11</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>12</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>3</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>4</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>5</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>6</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>7</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>8</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>9</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>10</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>11</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>12</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>1</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>3</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>4</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>5</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>6</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>7</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>8</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>9</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>10</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>11</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>12</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>3</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>4</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>5</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>6</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>7</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>8</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>9</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>10</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>11</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>12</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>3</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>4</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>5</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>6</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>7</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>8</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>9</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>10</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>11</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>12</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>1</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2</v>
       </c>
@@ -6203,7 +6203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>3</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>4</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>5</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>6</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>7</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>8</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>9</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>10</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>11</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>12</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1</v>
       </c>
@@ -6423,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>3</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>4</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>5</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>6</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>7</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>8</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>9</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>10</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>11</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>12</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>3</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>4</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>5</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>6</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>7</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>8</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>9</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>10</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>11</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>12</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>3</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>4</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>5</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>6</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>7</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>8</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>9</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>10</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>11</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>12</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>3</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>4</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>5</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>6</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>7</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>8</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>9</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>10</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>11</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>12</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2</v>
       </c>
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>3</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>4</v>
       </c>
@@ -7443,7 +7443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>5</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>6</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>7</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>8</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>9</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>10</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>11</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>12</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>3</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>4</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>5</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>6</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>7</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>8</v>
       </c>
@@ -7763,7 +7763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>9</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>10</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>11</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>12</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2</v>
       </c>
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>3</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>4</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>5</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>6</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>7</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>8</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>9</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>10</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>11</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>12</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>1</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>3</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>4</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>5</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>6</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>7</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>8</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>9</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>10</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>11</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>12</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>2</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>3</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>4</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>5</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>6</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>7</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>8</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>9</v>
       </c>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>10</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>11</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>12</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>1</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>2</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>3</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>4</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>5</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>6</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>7</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>8</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>9</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>10</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>11</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>12</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>1</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>2</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>3</v>
       </c>
@@ -8863,7 +8863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>4</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>5</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>6</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>7</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>8</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>9</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>10</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>11</v>
       </c>
@@ -9023,7 +9023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>12</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>1</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>2</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>3</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>4</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>5</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>6</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>7</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>8</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>9</v>
       </c>
@@ -9223,7 +9223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>10</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>11</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>12</v>
       </c>
@@ -9291,20 +9291,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71493739-45C2-4A8D-9266-24BB3FC8F4DB}">
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" customWidth="1"/>
-    <col min="20" max="20" width="20.5546875" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="14" max="14" width="20.140625" customWidth="1"/>
+    <col min="20" max="20" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
@@ -9719,43 +9719,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
     </row>
   </sheetData>
@@ -9767,9 +9767,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69FD329D-454B-4A8C-B502-49D79ABB4242}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -9803,7 +9803,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -9820,7 +9820,7 @@
         <v>2.2200000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>2.4400000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>2.6599999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -9905,7 +9905,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>3.7600000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -9990,7 +9990,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10007,7 +10007,7 @@
         <v>4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10024,7 +10024,7 @@
         <v>4.6399999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10041,7 +10041,7 @@
         <v>4.8599999999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10058,7 +10058,7 @@
         <v>5.0799999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>5.5199999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>5.74E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>5.96E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>6.1800000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10160,7 +10160,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10177,7 +10177,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>6.8400000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>7.0599999999999996E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10228,7 +10228,7 @@
         <v>7.2800000000000004E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10253,9 +10253,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1143316B-9FC2-4B52-982D-1F4DD6859A8E}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10289,7 +10289,7 @@
         <v>26229.707720000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>26589.174669999997</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>60431.69513</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>95314.195130000007</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10357,7 +10357,7 @@
         <v>130196.6951</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>165780.465</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10391,7 +10391,7 @@
         <v>179750.54879999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>195610.7611</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>196499.72339999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>198853.9976</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>202089.00579999998</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10476,7 +10476,7 @@
         <v>164077.8836</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>126654.49769999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>90701.344779999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>57298.538379999998</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>40938.322699999997</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10561,7 +10561,7 @@
         <v>30788.296410000003</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10578,7 +10578,7 @@
         <v>28368.054080000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>31250.81408</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10612,7 +10612,7 @@
         <v>34011.350160000002</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>35066.675019999995</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>33453.543590000001</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10663,7 +10663,7 @@
         <v>25310.301890000002</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>11877.08452</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10739,9 +10739,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790A601-26C3-4DCA-97B6-9342C547A4A0}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10775,7 +10775,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10843,7 +10843,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10928,7 +10928,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10979,7 +10979,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10996,7 +10996,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -11013,7 +11013,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -11047,7 +11047,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -11098,7 +11098,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -11115,7 +11115,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -11200,7 +11200,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -11225,14 +11225,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}">
   <dimension ref="A1:G109"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" customWidth="1"/>
-    <col min="5" max="5" width="8.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>68</v>
       </c>
@@ -11249,7 +11249,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>2024</v>
       </c>
@@ -11266,7 +11266,7 @@
         <v>6.9372000000000003E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
       <c r="B3" s="12" t="s">
         <v>71</v>
@@ -11282,7 +11282,7 @@
         <v>4.9157999999999993E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="12" t="s">
         <v>72</v>
@@ -11297,7 +11297,7 @@
         <v>4.4639999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="B5" s="12" t="s">
         <v>69</v>
@@ -11309,7 +11309,7 @@
         <v>22.68</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>2025</v>
       </c>
@@ -11323,7 +11323,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="12" t="s">
         <v>71</v>
@@ -11335,7 +11335,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="12" t="s">
         <v>72</v>
@@ -11347,7 +11347,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="12" t="s">
         <v>69</v>
@@ -11360,7 +11360,7 @@
         <v>22.545000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>2026</v>
       </c>
@@ -11374,7 +11374,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="12" t="s">
         <v>71</v>
@@ -11386,7 +11386,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="12" t="s">
         <v>72</v>
@@ -11398,7 +11398,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="12" t="s">
         <v>69</v>
@@ -11411,7 +11411,7 @@
         <v>22.41</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>2027</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="12" t="s">
         <v>71</v>
@@ -11437,7 +11437,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="12" t="s">
         <v>72</v>
@@ -11449,7 +11449,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="12" t="s">
         <v>69</v>
@@ -11462,7 +11462,7 @@
         <v>22.274999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>2028</v>
       </c>
@@ -11476,7 +11476,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="12" t="s">
         <v>71</v>
@@ -11488,7 +11488,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="12" t="s">
         <v>72</v>
@@ -11500,7 +11500,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="12" t="s">
         <v>69</v>
@@ -11513,7 +11513,7 @@
         <v>22.14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>2029</v>
       </c>
@@ -11527,7 +11527,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="12" t="s">
         <v>71</v>
@@ -11539,7 +11539,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="12" t="s">
         <v>72</v>
@@ -11551,7 +11551,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="12" t="s">
         <v>69</v>
@@ -11564,7 +11564,7 @@
         <v>22.004999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>2030</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="12" t="s">
         <v>71</v>
@@ -11590,7 +11590,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="12" t="s">
         <v>72</v>
@@ -11602,7 +11602,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="12" t="s">
         <v>69</v>
@@ -11615,7 +11615,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
         <v>2031</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
       <c r="B31" s="12" t="s">
         <v>71</v>
@@ -11641,7 +11641,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="12" t="s">
         <v>72</v>
@@ -11653,7 +11653,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="12" t="s">
         <v>69</v>
@@ -11666,7 +11666,7 @@
         <v>21.734999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <v>2032</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="12" t="s">
         <v>71</v>
@@ -11692,7 +11692,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="12" t="s">
         <v>72</v>
@@ -11704,7 +11704,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="12" t="s">
         <v>69</v>
@@ -11717,7 +11717,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="13">
         <v>2033</v>
       </c>
@@ -11731,7 +11731,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="12" t="s">
         <v>71</v>
@@ -11743,7 +11743,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="12" t="s">
         <v>72</v>
@@ -11755,7 +11755,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="12" t="s">
         <v>69</v>
@@ -11768,7 +11768,7 @@
         <v>21.465</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <v>2034</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="12" t="s">
         <v>71</v>
@@ -11794,7 +11794,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="12" t="s">
         <v>72</v>
@@ -11806,7 +11806,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="13"/>
       <c r="B45" s="12" t="s">
         <v>69</v>
@@ -11819,7 +11819,7 @@
         <v>21.33</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="13">
         <v>2035</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>
       <c r="B47" s="12" t="s">
         <v>71</v>
@@ -11845,7 +11845,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="12" t="s">
         <v>72</v>
@@ -11857,7 +11857,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
       <c r="B49" s="12" t="s">
         <v>69</v>
@@ -11870,7 +11870,7 @@
         <v>21.195</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
         <v>2036</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="12" t="s">
         <v>71</v>
@@ -11896,7 +11896,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
       <c r="B52" s="12" t="s">
         <v>72</v>
@@ -11908,7 +11908,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="13"/>
       <c r="B53" s="12" t="s">
         <v>69</v>
@@ -11921,7 +11921,7 @@
         <v>21.06</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="13">
         <v>2037</v>
       </c>
@@ -11935,7 +11935,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="13"/>
       <c r="B55" s="12" t="s">
         <v>71</v>
@@ -11947,7 +11947,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="13"/>
       <c r="B56" s="12" t="s">
         <v>72</v>
@@ -11959,7 +11959,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
       <c r="B57" s="12" t="s">
         <v>69</v>
@@ -11972,7 +11972,7 @@
         <v>20.925000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="13">
         <v>2038</v>
       </c>
@@ -11986,7 +11986,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="13"/>
       <c r="B59" s="12" t="s">
         <v>71</v>
@@ -11998,7 +11998,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="13"/>
       <c r="B60" s="12" t="s">
         <v>72</v>
@@ -12010,7 +12010,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="13"/>
       <c r="B61" s="12" t="s">
         <v>69</v>
@@ -12023,7 +12023,7 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="13">
         <v>2039</v>
       </c>
@@ -12037,7 +12037,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="13"/>
       <c r="B63" s="12" t="s">
         <v>71</v>
@@ -12049,7 +12049,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="13"/>
       <c r="B64" s="12" t="s">
         <v>72</v>
@@ -12061,7 +12061,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="13"/>
       <c r="B65" s="12" t="s">
         <v>69</v>
@@ -12074,7 +12074,7 @@
         <v>20.655000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="13">
         <v>2040</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="13"/>
       <c r="B67" s="12" t="s">
         <v>71</v>
@@ -12100,7 +12100,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="13"/>
       <c r="B68" s="12" t="s">
         <v>72</v>
@@ -12112,7 +12112,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="13"/>
       <c r="B69" s="12" t="s">
         <v>69</v>
@@ -12125,7 +12125,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="13">
         <v>2041</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="13"/>
       <c r="B71" s="12" t="s">
         <v>71</v>
@@ -12151,7 +12151,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="13"/>
       <c r="B72" s="12" t="s">
         <v>72</v>
@@ -12163,7 +12163,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="13"/>
       <c r="B73" s="12" t="s">
         <v>69</v>
@@ -12176,7 +12176,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="13">
         <v>2042</v>
       </c>
@@ -12190,7 +12190,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="13"/>
       <c r="B75" s="12" t="s">
         <v>71</v>
@@ -12202,7 +12202,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="13"/>
       <c r="B76" s="12" t="s">
         <v>72</v>
@@ -12214,7 +12214,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="13"/>
       <c r="B77" s="12" t="s">
         <v>69</v>
@@ -12227,7 +12227,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="13">
         <v>2043</v>
       </c>
@@ -12241,7 +12241,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="13"/>
       <c r="B79" s="12" t="s">
         <v>71</v>
@@ -12253,7 +12253,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="13"/>
       <c r="B80" s="12" t="s">
         <v>72</v>
@@ -12265,7 +12265,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="13"/>
       <c r="B81" s="12" t="s">
         <v>69</v>
@@ -12278,7 +12278,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="13">
         <v>2044</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="13"/>
       <c r="B83" s="12" t="s">
         <v>71</v>
@@ -12304,7 +12304,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="13"/>
       <c r="B84" s="12" t="s">
         <v>72</v>
@@ -12316,7 +12316,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" s="12" t="s">
         <v>69</v>
@@ -12329,7 +12329,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="13">
         <v>2045</v>
       </c>
@@ -12343,7 +12343,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="13"/>
       <c r="B87" s="12" t="s">
         <v>71</v>
@@ -12355,7 +12355,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="13"/>
       <c r="B88" s="12" t="s">
         <v>72</v>
@@ -12367,7 +12367,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="13"/>
       <c r="B89" s="12" t="s">
         <v>69</v>
@@ -12380,7 +12380,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="13">
         <v>2046</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="13"/>
       <c r="B91" s="12" t="s">
         <v>71</v>
@@ -12406,7 +12406,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="13"/>
       <c r="B92" s="12" t="s">
         <v>72</v>
@@ -12418,7 +12418,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="13"/>
       <c r="B93" s="12" t="s">
         <v>69</v>
@@ -12431,7 +12431,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="13">
         <v>2047</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="13"/>
       <c r="B95" s="12" t="s">
         <v>71</v>
@@ -12457,7 +12457,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="13"/>
       <c r="B96" s="12" t="s">
         <v>72</v>
@@ -12469,7 +12469,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="13"/>
       <c r="B97" s="12" t="s">
         <v>69</v>
@@ -12482,7 +12482,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="13">
         <v>2048</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
       <c r="B99" s="12" t="s">
         <v>71</v>
@@ -12508,7 +12508,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="13"/>
       <c r="B100" s="12" t="s">
         <v>72</v>
@@ -12520,7 +12520,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="13"/>
       <c r="B101" s="12" t="s">
         <v>69</v>
@@ -12533,7 +12533,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="13">
         <v>2049</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="13"/>
       <c r="B103" s="12" t="s">
         <v>71</v>
@@ -12559,7 +12559,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="13"/>
       <c r="B104" s="12" t="s">
         <v>72</v>
@@ -12571,7 +12571,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="13"/>
       <c r="B105" s="12" t="s">
         <v>69</v>
@@ -12584,7 +12584,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="13">
         <v>2050</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="13"/>
       <c r="B107" s="12" t="s">
         <v>71</v>
@@ -12610,7 +12610,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="13"/>
       <c r="B108" s="12" t="s">
         <v>72</v>
@@ -12622,7 +12622,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="13"/>
       <c r="B109" s="12" t="s">
         <v>69</v>
@@ -12638,26 +12638,6 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -12665,6 +12645,26 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89486067-0CA3-4462-89DC-4E65E91C57C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67065" yWindow="-5580" windowWidth="38670" windowHeight="21150" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="67230" yWindow="-4800" windowWidth="13830" windowHeight="7035" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -9419,7 +9419,7 @@
         <v>0.2</v>
       </c>
       <c r="K2" s="5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L2" s="5">
         <v>0.8</v>
@@ -9502,7 +9502,7 @@
         <v>0.2</v>
       </c>
       <c r="K3" s="5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L3" s="5">
         <v>0.8</v>
@@ -9585,7 +9585,7 @@
         <v>0.2</v>
       </c>
       <c r="K4" s="5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L4" s="5">
         <v>0.8</v>
@@ -9668,7 +9668,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" s="5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="5">
         <v>0.8</v>
@@ -12638,26 +12638,6 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -12665,6 +12645,26 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F8DECA5-D051-4C44-8AE6-0B1E7095FB46}"/>
   <bookViews>
-    <workbookView xWindow="67230" yWindow="-4800" windowWidth="13830" windowHeight="7035" activeTab="4" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView minimized="1" xWindow="735" yWindow="735" windowWidth="28800" windowHeight="15345" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="72">
   <si>
     <t>Value</t>
   </si>
@@ -238,9 +238,6 @@
     <t>price</t>
   </si>
   <si>
-    <t>emissions</t>
-  </si>
-  <si>
     <t>oandm_EU27_solarPV</t>
   </si>
   <si>
@@ -330,7 +327,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,12 +361,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +437,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -467,7 +458,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -821,9 +811,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31FF74EF-7037-4139-88AF-F295C305C1F7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -831,7 +821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -839,7 +829,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -847,7 +837,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -863,25 +853,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185AF38-42FD-4CFF-B287-2FCFFF6C6EF3}">
   <dimension ref="A1:U28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="5" width="37.33203125" customWidth="1"/>
-    <col min="6" max="6" width="29.88671875" customWidth="1"/>
-    <col min="7" max="7" width="39.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" customWidth="1"/>
-    <col min="10" max="11" width="22.5546875" customWidth="1"/>
-    <col min="12" max="12" width="24.109375" customWidth="1"/>
-    <col min="13" max="13" width="27.6640625" customWidth="1"/>
-    <col min="14" max="14" width="22.88671875" customWidth="1"/>
-    <col min="15" max="16" width="20.109375" customWidth="1"/>
-    <col min="18" max="18" width="32.6640625" customWidth="1"/>
-    <col min="19" max="19" width="35.33203125" customWidth="1"/>
-    <col min="20" max="20" width="31.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="5" width="37.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="7" max="7" width="39.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="10" max="11" width="22.5703125" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" customWidth="1"/>
+    <col min="13" max="13" width="27.7109375" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" customWidth="1"/>
+    <col min="15" max="16" width="20.140625" customWidth="1"/>
+    <col min="18" max="18" width="32.7109375" customWidth="1"/>
+    <col min="19" max="19" width="35.28515625" customWidth="1"/>
+    <col min="20" max="20" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -898,7 +888,7 @@
         <v>37</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G1" t="s">
         <v>28</v>
@@ -913,7 +903,7 @@
         <v>38</v>
       </c>
       <c r="K1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L1" t="s">
         <v>43</v>
@@ -928,7 +918,7 @@
         <v>46</v>
       </c>
       <c r="P1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q1" t="s">
         <v>52</v>
@@ -943,10 +933,10 @@
         <v>55</v>
       </c>
       <c r="U1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -1011,7 +1001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1076,7 +1066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -1141,7 +1131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -1206,7 +1196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -1271,7 +1261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -1336,7 +1326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -1401,7 +1391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -1466,7 +1456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -1531,7 +1521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -1596,7 +1586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -1661,7 +1651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -1726,7 +1716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -1791,7 +1781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -1856,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -1921,7 +1911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -1986,7 +1976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -2051,7 +2041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -2116,7 +2106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -2181,7 +2171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -2246,7 +2236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -2311,7 +2301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -2376,7 +2366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -2441,7 +2431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -2506,7 +2496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -2571,7 +2561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -2636,7 +2626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -2710,64 +2700,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0D039F-A3AA-471E-A6A2-F25F8348E84D}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
   </sheetData>
@@ -2778,12 +2768,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6341E4C-4AB4-44A4-8119-B6BB3BEB6E84}">
   <dimension ref="A1:F325"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -2803,7 +2793,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2823,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2843,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2863,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2883,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2903,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2923,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2943,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2963,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2983,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3003,7 +2993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3023,7 +3013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3043,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1</v>
       </c>
@@ -3063,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3083,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
@@ -3103,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>4</v>
       </c>
@@ -3123,7 +3113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5</v>
       </c>
@@ -3143,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6</v>
       </c>
@@ -3163,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>7</v>
       </c>
@@ -3183,7 +3173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>8</v>
       </c>
@@ -3203,7 +3193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9</v>
       </c>
@@ -3223,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>10</v>
       </c>
@@ -3243,7 +3233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>11</v>
       </c>
@@ -3263,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>12</v>
       </c>
@@ -3283,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
@@ -3303,7 +3293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2</v>
       </c>
@@ -3323,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3343,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -3363,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>5</v>
       </c>
@@ -3383,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>6</v>
       </c>
@@ -3403,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3423,7 +3413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>8</v>
       </c>
@@ -3443,7 +3433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9</v>
       </c>
@@ -3463,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>10</v>
       </c>
@@ -3483,7 +3473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>11</v>
       </c>
@@ -3503,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>12</v>
       </c>
@@ -3523,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1</v>
       </c>
@@ -3543,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2</v>
       </c>
@@ -3563,7 +3553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3583,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3603,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5</v>
       </c>
@@ -3623,7 +3613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>6</v>
       </c>
@@ -3643,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>7</v>
       </c>
@@ -3663,7 +3653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3683,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3703,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>10</v>
       </c>
@@ -3723,7 +3713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>11</v>
       </c>
@@ -3743,7 +3733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>12</v>
       </c>
@@ -3763,7 +3753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1</v>
       </c>
@@ -3783,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2</v>
       </c>
@@ -3803,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>3</v>
       </c>
@@ -3823,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3843,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>5</v>
       </c>
@@ -3863,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>6</v>
       </c>
@@ -3883,7 +3873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>7</v>
       </c>
@@ -3903,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>8</v>
       </c>
@@ -3923,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>9</v>
       </c>
@@ -3943,7 +3933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10</v>
       </c>
@@ -3963,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>11</v>
       </c>
@@ -3983,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>12</v>
       </c>
@@ -4003,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1</v>
       </c>
@@ -4023,7 +4013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2</v>
       </c>
@@ -4043,7 +4033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>3</v>
       </c>
@@ -4063,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>4</v>
       </c>
@@ -4083,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>5</v>
       </c>
@@ -4103,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>6</v>
       </c>
@@ -4123,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>7</v>
       </c>
@@ -4143,7 +4133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>8</v>
       </c>
@@ -4163,7 +4153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>9</v>
       </c>
@@ -4183,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>10</v>
       </c>
@@ -4203,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>11</v>
       </c>
@@ -4223,7 +4213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>12</v>
       </c>
@@ -4243,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1</v>
       </c>
@@ -4263,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2</v>
       </c>
@@ -4283,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>3</v>
       </c>
@@ -4303,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>4</v>
       </c>
@@ -4323,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>5</v>
       </c>
@@ -4343,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>6</v>
       </c>
@@ -4363,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>7</v>
       </c>
@@ -4383,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>8</v>
       </c>
@@ -4403,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>9</v>
       </c>
@@ -4423,7 +4413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>10</v>
       </c>
@@ -4443,7 +4433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>11</v>
       </c>
@@ -4463,7 +4453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>12</v>
       </c>
@@ -4483,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1</v>
       </c>
@@ -4503,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2</v>
       </c>
@@ -4523,7 +4513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>3</v>
       </c>
@@ -4543,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>4</v>
       </c>
@@ -4563,7 +4553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>5</v>
       </c>
@@ -4583,7 +4573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>6</v>
       </c>
@@ -4603,7 +4593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>7</v>
       </c>
@@ -4623,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>8</v>
       </c>
@@ -4643,7 +4633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>9</v>
       </c>
@@ -4663,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>10</v>
       </c>
@@ -4683,7 +4673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>11</v>
       </c>
@@ -4703,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4723,7 +4713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1</v>
       </c>
@@ -4743,7 +4733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2</v>
       </c>
@@ -4763,7 +4753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>3</v>
       </c>
@@ -4783,7 +4773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>4</v>
       </c>
@@ -4803,7 +4793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>5</v>
       </c>
@@ -4823,7 +4813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>6</v>
       </c>
@@ -4843,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>7</v>
       </c>
@@ -4863,7 +4853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>8</v>
       </c>
@@ -4883,7 +4873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>9</v>
       </c>
@@ -4903,7 +4893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>10</v>
       </c>
@@ -4923,7 +4913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>11</v>
       </c>
@@ -4943,7 +4933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>12</v>
       </c>
@@ -4963,7 +4953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1</v>
       </c>
@@ -4983,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2</v>
       </c>
@@ -5003,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>3</v>
       </c>
@@ -5023,7 +5013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>4</v>
       </c>
@@ -5043,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>5</v>
       </c>
@@ -5063,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>6</v>
       </c>
@@ -5083,7 +5073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>7</v>
       </c>
@@ -5103,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>8</v>
       </c>
@@ -5123,7 +5113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>9</v>
       </c>
@@ -5143,7 +5133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>10</v>
       </c>
@@ -5163,7 +5153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>11</v>
       </c>
@@ -5183,7 +5173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>12</v>
       </c>
@@ -5203,7 +5193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1</v>
       </c>
@@ -5223,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2</v>
       </c>
@@ -5243,7 +5233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>3</v>
       </c>
@@ -5263,7 +5253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>4</v>
       </c>
@@ -5283,7 +5273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>5</v>
       </c>
@@ -5303,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>6</v>
       </c>
@@ -5323,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>7</v>
       </c>
@@ -5343,7 +5333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>8</v>
       </c>
@@ -5363,7 +5353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>9</v>
       </c>
@@ -5383,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>10</v>
       </c>
@@ -5403,7 +5393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>11</v>
       </c>
@@ -5423,7 +5413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>12</v>
       </c>
@@ -5443,7 +5433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>1</v>
       </c>
@@ -5463,7 +5453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2</v>
       </c>
@@ -5483,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>3</v>
       </c>
@@ -5503,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>4</v>
       </c>
@@ -5523,7 +5513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>5</v>
       </c>
@@ -5543,7 +5533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>6</v>
       </c>
@@ -5563,7 +5553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>7</v>
       </c>
@@ -5583,7 +5573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>8</v>
       </c>
@@ -5603,7 +5593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>9</v>
       </c>
@@ -5623,7 +5613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>10</v>
       </c>
@@ -5643,7 +5633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>11</v>
       </c>
@@ -5663,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>12</v>
       </c>
@@ -5683,7 +5673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1</v>
       </c>
@@ -5703,7 +5693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2</v>
       </c>
@@ -5723,7 +5713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>3</v>
       </c>
@@ -5743,7 +5733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>4</v>
       </c>
@@ -5763,7 +5753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>5</v>
       </c>
@@ -5783,7 +5773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>6</v>
       </c>
@@ -5803,7 +5793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>7</v>
       </c>
@@ -5823,7 +5813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>8</v>
       </c>
@@ -5843,7 +5833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>9</v>
       </c>
@@ -5863,7 +5853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>10</v>
       </c>
@@ -5883,7 +5873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>11</v>
       </c>
@@ -5903,7 +5893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>12</v>
       </c>
@@ -5923,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1</v>
       </c>
@@ -5943,7 +5933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2</v>
       </c>
@@ -5963,7 +5953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>3</v>
       </c>
@@ -5983,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>4</v>
       </c>
@@ -6003,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>5</v>
       </c>
@@ -6023,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>6</v>
       </c>
@@ -6043,7 +6033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>7</v>
       </c>
@@ -6063,7 +6053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>8</v>
       </c>
@@ -6083,7 +6073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>9</v>
       </c>
@@ -6103,7 +6093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>10</v>
       </c>
@@ -6123,7 +6113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>11</v>
       </c>
@@ -6143,7 +6133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>12</v>
       </c>
@@ -6163,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>1</v>
       </c>
@@ -6183,7 +6173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2</v>
       </c>
@@ -6203,7 +6193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>3</v>
       </c>
@@ -6223,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>4</v>
       </c>
@@ -6243,7 +6233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>5</v>
       </c>
@@ -6263,7 +6253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>6</v>
       </c>
@@ -6283,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>7</v>
       </c>
@@ -6303,7 +6293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>8</v>
       </c>
@@ -6323,7 +6313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>9</v>
       </c>
@@ -6343,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>10</v>
       </c>
@@ -6363,7 +6353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>11</v>
       </c>
@@ -6383,7 +6373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>12</v>
       </c>
@@ -6403,7 +6393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1</v>
       </c>
@@ -6423,7 +6413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2</v>
       </c>
@@ -6443,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>3</v>
       </c>
@@ -6463,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>4</v>
       </c>
@@ -6483,7 +6473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>5</v>
       </c>
@@ -6503,7 +6493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>6</v>
       </c>
@@ -6523,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>7</v>
       </c>
@@ -6543,7 +6533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>8</v>
       </c>
@@ -6563,7 +6553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>9</v>
       </c>
@@ -6583,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>10</v>
       </c>
@@ -6603,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>11</v>
       </c>
@@ -6623,7 +6613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>12</v>
       </c>
@@ -6643,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1</v>
       </c>
@@ -6663,7 +6653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2</v>
       </c>
@@ -6683,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>3</v>
       </c>
@@ -6703,7 +6693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>4</v>
       </c>
@@ -6723,7 +6713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>5</v>
       </c>
@@ -6743,7 +6733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>6</v>
       </c>
@@ -6763,7 +6753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>7</v>
       </c>
@@ -6783,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>8</v>
       </c>
@@ -6803,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>9</v>
       </c>
@@ -6823,7 +6813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>10</v>
       </c>
@@ -6843,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>11</v>
       </c>
@@ -6863,7 +6853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>12</v>
       </c>
@@ -6883,7 +6873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1</v>
       </c>
@@ -6903,7 +6893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2</v>
       </c>
@@ -6923,7 +6913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>3</v>
       </c>
@@ -6943,7 +6933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>4</v>
       </c>
@@ -6963,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>5</v>
       </c>
@@ -6983,7 +6973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>6</v>
       </c>
@@ -7003,7 +6993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>7</v>
       </c>
@@ -7023,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>8</v>
       </c>
@@ -7043,7 +7033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>9</v>
       </c>
@@ -7063,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>10</v>
       </c>
@@ -7083,7 +7073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>11</v>
       </c>
@@ -7103,7 +7093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>12</v>
       </c>
@@ -7123,7 +7113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1</v>
       </c>
@@ -7143,7 +7133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2</v>
       </c>
@@ -7163,7 +7153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>3</v>
       </c>
@@ -7183,7 +7173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>4</v>
       </c>
@@ -7203,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>5</v>
       </c>
@@ -7223,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>6</v>
       </c>
@@ -7243,7 +7233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>7</v>
       </c>
@@ -7263,7 +7253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>8</v>
       </c>
@@ -7283,7 +7273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>9</v>
       </c>
@@ -7303,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>10</v>
       </c>
@@ -7323,7 +7313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>11</v>
       </c>
@@ -7343,7 +7333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>12</v>
       </c>
@@ -7363,7 +7353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1</v>
       </c>
@@ -7383,7 +7373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2</v>
       </c>
@@ -7403,7 +7393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>3</v>
       </c>
@@ -7423,7 +7413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>4</v>
       </c>
@@ -7443,7 +7433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>5</v>
       </c>
@@ -7463,7 +7453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>6</v>
       </c>
@@ -7483,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>7</v>
       </c>
@@ -7503,7 +7493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>8</v>
       </c>
@@ -7523,7 +7513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>9</v>
       </c>
@@ -7543,7 +7533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>10</v>
       </c>
@@ -7563,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>11</v>
       </c>
@@ -7583,7 +7573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>12</v>
       </c>
@@ -7603,7 +7593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1</v>
       </c>
@@ -7623,7 +7613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2</v>
       </c>
@@ -7643,7 +7633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>3</v>
       </c>
@@ -7663,7 +7653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>4</v>
       </c>
@@ -7683,7 +7673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>5</v>
       </c>
@@ -7703,7 +7693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>6</v>
       </c>
@@ -7723,7 +7713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>7</v>
       </c>
@@ -7743,7 +7733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>8</v>
       </c>
@@ -7763,7 +7753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>9</v>
       </c>
@@ -7783,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>10</v>
       </c>
@@ -7803,7 +7793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>11</v>
       </c>
@@ -7823,7 +7813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>12</v>
       </c>
@@ -7843,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1</v>
       </c>
@@ -7863,7 +7853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2</v>
       </c>
@@ -7883,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>3</v>
       </c>
@@ -7903,7 +7893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>4</v>
       </c>
@@ -7923,7 +7913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>5</v>
       </c>
@@ -7943,7 +7933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>6</v>
       </c>
@@ -7963,7 +7953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>7</v>
       </c>
@@ -7983,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>8</v>
       </c>
@@ -8003,7 +7993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>9</v>
       </c>
@@ -8023,7 +8013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>10</v>
       </c>
@@ -8043,7 +8033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>11</v>
       </c>
@@ -8063,7 +8053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>12</v>
       </c>
@@ -8083,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>1</v>
       </c>
@@ -8103,7 +8093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2</v>
       </c>
@@ -8123,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>3</v>
       </c>
@@ -8143,7 +8133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>4</v>
       </c>
@@ -8163,7 +8153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>5</v>
       </c>
@@ -8183,7 +8173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>6</v>
       </c>
@@ -8203,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>7</v>
       </c>
@@ -8223,7 +8213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>8</v>
       </c>
@@ -8243,7 +8233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>9</v>
       </c>
@@ -8263,7 +8253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>10</v>
       </c>
@@ -8283,7 +8273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>11</v>
       </c>
@@ -8303,7 +8293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>12</v>
       </c>
@@ -8323,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1</v>
       </c>
@@ -8343,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>2</v>
       </c>
@@ -8363,7 +8353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>3</v>
       </c>
@@ -8383,7 +8373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>4</v>
       </c>
@@ -8403,7 +8393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>5</v>
       </c>
@@ -8423,7 +8413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>6</v>
       </c>
@@ -8443,7 +8433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>7</v>
       </c>
@@ -8463,7 +8453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>8</v>
       </c>
@@ -8483,7 +8473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>9</v>
       </c>
@@ -8503,7 +8493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>10</v>
       </c>
@@ -8523,7 +8513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>11</v>
       </c>
@@ -8543,7 +8533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>12</v>
       </c>
@@ -8563,7 +8553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>1</v>
       </c>
@@ -8583,7 +8573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>2</v>
       </c>
@@ -8603,7 +8593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>3</v>
       </c>
@@ -8623,7 +8613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>4</v>
       </c>
@@ -8643,7 +8633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>5</v>
       </c>
@@ -8663,7 +8653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>6</v>
       </c>
@@ -8683,7 +8673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>7</v>
       </c>
@@ -8703,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>8</v>
       </c>
@@ -8723,7 +8713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>9</v>
       </c>
@@ -8743,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>10</v>
       </c>
@@ -8763,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>11</v>
       </c>
@@ -8783,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>12</v>
       </c>
@@ -8803,7 +8793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>1</v>
       </c>
@@ -8823,7 +8813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>2</v>
       </c>
@@ -8843,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>3</v>
       </c>
@@ -8863,7 +8853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>4</v>
       </c>
@@ -8883,7 +8873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>5</v>
       </c>
@@ -8903,7 +8893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>6</v>
       </c>
@@ -8923,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>7</v>
       </c>
@@ -8943,7 +8933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>8</v>
       </c>
@@ -8963,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>9</v>
       </c>
@@ -8983,7 +8973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>10</v>
       </c>
@@ -9003,7 +8993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>11</v>
       </c>
@@ -9023,7 +9013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>12</v>
       </c>
@@ -9043,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>1</v>
       </c>
@@ -9063,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>2</v>
       </c>
@@ -9083,7 +9073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>3</v>
       </c>
@@ -9103,7 +9093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>4</v>
       </c>
@@ -9123,7 +9113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>5</v>
       </c>
@@ -9143,7 +9133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>6</v>
       </c>
@@ -9163,7 +9153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>7</v>
       </c>
@@ -9183,7 +9173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>8</v>
       </c>
@@ -9203,7 +9193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>9</v>
       </c>
@@ -9223,7 +9213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>10</v>
       </c>
@@ -9243,7 +9233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>11</v>
       </c>
@@ -9263,7 +9253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>12</v>
       </c>
@@ -9291,20 +9281,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71493739-45C2-4A8D-9266-24BB3FC8F4DB}">
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" customWidth="1"/>
-    <col min="20" max="20" width="20.5546875" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="14" max="14" width="20.140625" customWidth="1"/>
+    <col min="20" max="20" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
@@ -9387,11 +9377,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>211115</v>
       </c>
       <c r="C2" s="6">
@@ -9470,7 +9460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -9553,7 +9543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -9636,7 +9626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
@@ -9719,43 +9709,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
     </row>
   </sheetData>
@@ -9767,9 +9757,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69FD329D-454B-4A8C-B502-49D79ABB4242}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -9786,7 +9776,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -9803,7 +9793,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -9820,7 +9810,7 @@
         <v>2.2200000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -9837,7 +9827,7 @@
         <v>2.4400000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -9854,7 +9844,7 @@
         <v>2.6599999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -9871,7 +9861,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -9888,7 +9878,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -9905,7 +9895,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -9922,7 +9912,7 @@
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -9939,7 +9929,7 @@
         <v>3.7600000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -9956,7 +9946,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -9973,7 +9963,7 @@
         <v>3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -9990,7 +9980,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10007,7 +9997,7 @@
         <v>4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10024,7 +10014,7 @@
         <v>4.6399999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10041,7 +10031,7 @@
         <v>4.8599999999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10058,7 +10048,7 @@
         <v>5.0799999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10075,7 +10065,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10092,7 +10082,7 @@
         <v>5.5199999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10109,7 +10099,7 @@
         <v>5.74E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10126,7 +10116,7 @@
         <v>5.96E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10143,7 +10133,7 @@
         <v>6.1800000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10160,7 +10150,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10177,7 +10167,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10194,7 +10184,7 @@
         <v>6.8400000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10211,7 +10201,7 @@
         <v>7.0599999999999996E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10228,7 +10218,7 @@
         <v>7.2800000000000004E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10253,9 +10243,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1143316B-9FC2-4B52-982D-1F4DD6859A8E}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10272,7 +10262,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10289,7 +10279,7 @@
         <v>26229.707720000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10306,7 +10296,7 @@
         <v>26589.174669999997</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10323,7 +10313,7 @@
         <v>60431.69513</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10340,7 +10330,7 @@
         <v>95314.195130000007</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10357,7 +10347,7 @@
         <v>130196.6951</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10374,7 +10364,7 @@
         <v>165780.465</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10391,7 +10381,7 @@
         <v>179750.54879999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10408,7 +10398,7 @@
         <v>195610.7611</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10425,7 +10415,7 @@
         <v>196499.72339999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10442,7 +10432,7 @@
         <v>198853.9976</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10459,7 +10449,7 @@
         <v>202089.00579999998</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10476,7 +10466,7 @@
         <v>164077.8836</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10493,7 +10483,7 @@
         <v>126654.49769999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10510,7 +10500,7 @@
         <v>90701.344779999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -10527,7 +10517,7 @@
         <v>57298.538379999998</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -10544,7 +10534,7 @@
         <v>40938.322699999997</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -10561,7 +10551,7 @@
         <v>30788.296410000003</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -10578,7 +10568,7 @@
         <v>28368.054080000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -10595,7 +10585,7 @@
         <v>31250.81408</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -10612,7 +10602,7 @@
         <v>34011.350160000002</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -10629,7 +10619,7 @@
         <v>35066.675019999995</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -10646,7 +10636,7 @@
         <v>33453.543590000001</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -10663,7 +10653,7 @@
         <v>25310.301890000002</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -10680,7 +10670,7 @@
         <v>11877.08452</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -10697,7 +10687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -10714,7 +10704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -10739,9 +10729,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790A601-26C3-4DCA-97B6-9342C547A4A0}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -10758,7 +10748,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -10775,7 +10765,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -10792,7 +10782,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -10809,7 +10799,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -10826,7 +10816,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -10843,7 +10833,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -10860,7 +10850,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -10877,7 +10867,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -10894,7 +10884,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -10911,7 +10901,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -10928,7 +10918,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -10945,7 +10935,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -10962,7 +10952,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -10979,7 +10969,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -10996,7 +10986,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -11013,7 +11003,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -11030,7 +11020,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -11047,7 +11037,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -11064,7 +11054,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -11081,7 +11071,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -11098,7 +11088,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -11115,7 +11105,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -11132,7 +11122,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -11149,7 +11139,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -11166,7 +11156,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -11183,7 +11173,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -11200,7 +11190,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -11224,37 +11214,34 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}">
-  <dimension ref="A1:G109"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E109"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="12" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
         <v>2024</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>70</v>
+      <c r="B2" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C2" s="2">
         <v>270613611.10000002</v>
@@ -11262,14 +11249,11 @@
       <c r="D2">
         <v>29.19</v>
       </c>
-      <c r="G2" s="10">
-        <v>6.9372000000000003E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="12" t="s">
-        <v>71</v>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C3" s="2">
         <v>1047284444</v>
@@ -11278,14 +11262,11 @@
         <v>42.69</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="G3" s="10">
-        <v>4.9157999999999993E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="12" t="s">
-        <v>72</v>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>2930833333</v>
@@ -11293,14 +11274,11 @@
       <c r="D4">
         <v>150</v>
       </c>
-      <c r="G4" s="10">
-        <v>4.4639999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="12" t="s">
-        <v>69</v>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C5" s="2">
         <v>484006334</v>
@@ -11309,12 +11287,12 @@
         <v>22.68</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="13">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
         <v>2025</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>70</v>
+      <c r="B6" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C6" s="2">
         <v>270613611.10000002</v>
@@ -11323,10 +11301,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="12" t="s">
-        <v>71</v>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C7" s="2">
         <v>1047284444</v>
@@ -11335,10 +11313,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="12" t="s">
-        <v>72</v>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>2930833333</v>
@@ -11347,10 +11325,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="12" t="s">
-        <v>69</v>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C9" s="2">
         <f>SUM(C5*(1-0.04052))</f>
@@ -11360,12 +11338,12 @@
         <v>22.545000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
         <v>2026</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>70</v>
+      <c r="B10" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C10" s="2">
         <v>270613611.10000002</v>
@@ -11374,10 +11352,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="12" t="s">
-        <v>71</v>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C11" s="2">
         <v>1047284444</v>
@@ -11386,10 +11364,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="12" t="s">
-        <v>72</v>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>2930833333</v>
@@ -11398,10 +11376,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="12" t="s">
-        <v>69</v>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="12"/>
+      <c r="B13" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C13" s="2">
         <f>SUM(C9*(1-0.04052))</f>
@@ -11411,12 +11389,12 @@
         <v>22.41</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
         <v>2027</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>70</v>
+      <c r="B14" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C14" s="2">
         <v>270613611.10000002</v>
@@ -11425,10 +11403,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="12" t="s">
-        <v>71</v>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C15" s="2">
         <v>1047284444</v>
@@ -11437,10 +11415,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="12" t="s">
-        <v>72</v>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>2930833333</v>
@@ -11449,10 +11427,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="12" t="s">
-        <v>69</v>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C17" s="2">
         <f>SUM(C13*(1-0.04052))</f>
@@ -11462,12 +11440,12 @@
         <v>22.274999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
         <v>2028</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>70</v>
+      <c r="B18" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C18" s="2">
         <v>270613611.10000002</v>
@@ -11476,10 +11454,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="12" t="s">
-        <v>71</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C19" s="2">
         <v>1047284444</v>
@@ -11488,10 +11466,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="12" t="s">
-        <v>72</v>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C20" s="2">
         <v>2930833333</v>
@@ -11500,10 +11478,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="12" t="s">
-        <v>69</v>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C21" s="2">
         <f>SUM(C17*(1-0.04052))</f>
@@ -11513,12 +11491,12 @@
         <v>22.14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
         <v>2029</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>70</v>
+      <c r="B22" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C22" s="2">
         <v>270613611.10000002</v>
@@ -11527,10 +11505,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="12" t="s">
-        <v>71</v>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C23" s="2">
         <v>1047284444</v>
@@ -11539,10 +11517,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="12" t="s">
-        <v>72</v>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>2930833333</v>
@@ -11551,10 +11529,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="12" t="s">
-        <v>69</v>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C25" s="2">
         <f>SUM(C21*(1-0.04052))</f>
@@ -11564,12 +11542,12 @@
         <v>22.004999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="13">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
         <v>2030</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>70</v>
+      <c r="B26" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C26" s="2">
         <v>270613611.10000002</v>
@@ -11578,10 +11556,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="12" t="s">
-        <v>71</v>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="12"/>
+      <c r="B27" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C27" s="2">
         <v>1047284444</v>
@@ -11590,10 +11568,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="12" t="s">
-        <v>72</v>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="12"/>
+      <c r="B28" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C28" s="2">
         <v>2930833333</v>
@@ -11602,10 +11580,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="12" t="s">
-        <v>69</v>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C29" s="2">
         <f>SUM(C25*(1-0.04052))</f>
@@ -11615,12 +11593,12 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
         <v>2031</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>70</v>
+      <c r="B30" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C30" s="2">
         <v>270613611.10000002</v>
@@ -11629,10 +11607,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="12" t="s">
-        <v>71</v>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C31" s="2">
         <v>1047284444</v>
@@ -11641,10 +11619,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="12" t="s">
-        <v>72</v>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>2930833333</v>
@@ -11653,10 +11631,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="12" t="s">
-        <v>69</v>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C33" s="2">
         <f>SUM(C29*(1-0.04052))</f>
@@ -11666,12 +11644,12 @@
         <v>21.734999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
         <v>2032</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>70</v>
+      <c r="B34" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C34" s="2">
         <v>270613611.10000002</v>
@@ -11680,10 +11658,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="12" t="s">
-        <v>71</v>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="12"/>
+      <c r="B35" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C35" s="2">
         <v>1047284444</v>
@@ -11692,10 +11670,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="12" t="s">
-        <v>72</v>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
+      <c r="B36" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>2930833333</v>
@@ -11704,10 +11682,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="12" t="s">
-        <v>69</v>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="12"/>
+      <c r="B37" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C37" s="2">
         <f>SUM(C33*(1-0.04052))</f>
@@ -11717,12 +11695,12 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="13">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
         <v>2033</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>70</v>
+      <c r="B38" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C38" s="2">
         <v>270613611.10000002</v>
@@ -11731,10 +11709,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="12" t="s">
-        <v>71</v>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C39" s="2">
         <v>1047284444</v>
@@ -11743,10 +11721,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="12" t="s">
-        <v>72</v>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="12"/>
+      <c r="B40" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C40" s="2">
         <v>2930833333</v>
@@ -11755,10 +11733,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="12" t="s">
-        <v>69</v>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+      <c r="B41" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C41" s="2">
         <f>SUM(C37*(1-0.04052))</f>
@@ -11768,12 +11746,12 @@
         <v>21.465</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="13">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
         <v>2034</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>70</v>
+      <c r="B42" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C42" s="2">
         <v>270613611.10000002</v>
@@ -11782,10 +11760,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="12" t="s">
-        <v>71</v>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+      <c r="B43" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C43" s="2">
         <v>1047284444</v>
@@ -11794,10 +11772,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="12" t="s">
-        <v>72</v>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="12"/>
+      <c r="B44" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C44" s="2">
         <v>2930833333</v>
@@ -11806,10 +11784,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="12" t="s">
-        <v>69</v>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C45" s="2">
         <f>SUM(C41*(1-0.04052))</f>
@@ -11819,12 +11797,12 @@
         <v>21.33</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="13">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
         <v>2035</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>70</v>
+      <c r="B46" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C46" s="2">
         <v>270613611.10000002</v>
@@ -11833,10 +11811,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="12" t="s">
-        <v>71</v>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+      <c r="B47" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C47" s="2">
         <v>1047284444</v>
@@ -11845,10 +11823,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="12" t="s">
-        <v>72</v>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="12"/>
+      <c r="B48" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C48" s="2">
         <v>2930833333</v>
@@ -11857,10 +11835,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="12" t="s">
-        <v>69</v>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="12"/>
+      <c r="B49" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C49" s="2">
         <f>SUM(C45*(1-0.04052))</f>
@@ -11870,12 +11848,12 @@
         <v>21.195</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="13">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
         <v>2036</v>
       </c>
-      <c r="B50" s="12" t="s">
-        <v>70</v>
+      <c r="B50" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C50" s="2">
         <v>270613611.10000002</v>
@@ -11884,10 +11862,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="12" t="s">
-        <v>71</v>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="12"/>
+      <c r="B51" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C51" s="2">
         <v>1047284444</v>
@@ -11896,10 +11874,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="12" t="s">
-        <v>72</v>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="12"/>
+      <c r="B52" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>2930833333</v>
@@ -11908,10 +11886,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="12" t="s">
-        <v>69</v>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="12"/>
+      <c r="B53" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C53" s="2">
         <f>SUM(C49*(1-0.04052))</f>
@@ -11921,12 +11899,12 @@
         <v>21.06</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="13">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
         <v>2037</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>70</v>
+      <c r="B54" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C54" s="2">
         <v>270613611.10000002</v>
@@ -11935,10 +11913,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="12" t="s">
-        <v>71</v>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="12"/>
+      <c r="B55" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C55" s="2">
         <v>1047284444</v>
@@ -11947,10 +11925,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="12" t="s">
-        <v>72</v>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="12"/>
+      <c r="B56" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>2930833333</v>
@@ -11959,10 +11937,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="12" t="s">
-        <v>69</v>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="12"/>
+      <c r="B57" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C57" s="2">
         <f>SUM(C53*(1-0.04052))</f>
@@ -11972,12 +11950,12 @@
         <v>20.925000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="13">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
         <v>2038</v>
       </c>
-      <c r="B58" s="12" t="s">
-        <v>70</v>
+      <c r="B58" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C58" s="2">
         <v>270613611.10000002</v>
@@ -11986,10 +11964,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="12" t="s">
-        <v>71</v>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="12"/>
+      <c r="B59" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C59" s="2">
         <v>1047284444</v>
@@ -11998,10 +11976,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="12" t="s">
-        <v>72</v>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="12"/>
+      <c r="B60" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C60" s="2">
         <v>2930833333</v>
@@ -12010,10 +11988,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="12" t="s">
-        <v>69</v>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="12"/>
+      <c r="B61" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C61" s="2">
         <f>SUM(C57*(1-0.04052))</f>
@@ -12023,12 +12001,12 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="13">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
         <v>2039</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>70</v>
+      <c r="B62" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C62" s="2">
         <v>270613611.10000002</v>
@@ -12037,10 +12015,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="12" t="s">
-        <v>71</v>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="12"/>
+      <c r="B63" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C63" s="2">
         <v>1047284444</v>
@@ -12049,10 +12027,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="12" t="s">
-        <v>72</v>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="12"/>
+      <c r="B64" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C64" s="2">
         <v>2930833333</v>
@@ -12061,10 +12039,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="12" t="s">
-        <v>69</v>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="12"/>
+      <c r="B65" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C65" s="2">
         <f>SUM(C61*(1-0.04052))</f>
@@ -12074,12 +12052,12 @@
         <v>20.655000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="13">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
         <v>2040</v>
       </c>
-      <c r="B66" s="12" t="s">
-        <v>70</v>
+      <c r="B66" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C66" s="2">
         <v>270613611.10000002</v>
@@ -12088,10 +12066,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="12" t="s">
-        <v>71</v>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="12"/>
+      <c r="B67" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C67" s="2">
         <v>1047284444</v>
@@ -12100,10 +12078,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="12" t="s">
-        <v>72</v>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="12"/>
+      <c r="B68" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C68" s="2">
         <v>2930833333</v>
@@ -12112,10 +12090,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="12" t="s">
-        <v>69</v>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="12"/>
+      <c r="B69" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C69" s="2">
         <f>SUM(C65*(1-0.04052))</f>
@@ -12125,12 +12103,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="13">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
         <v>2041</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>70</v>
+      <c r="B70" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C70" s="2">
         <v>270613611.10000002</v>
@@ -12139,10 +12117,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="12" t="s">
-        <v>71</v>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="12"/>
+      <c r="B71" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C71" s="2">
         <v>1047284444</v>
@@ -12151,10 +12129,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="12" t="s">
-        <v>72</v>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="12"/>
+      <c r="B72" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C72" s="2">
         <v>2930833333</v>
@@ -12163,10 +12141,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="12" t="s">
-        <v>69</v>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="12"/>
+      <c r="B73" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C73" s="2">
         <f>SUM(C69*(1-0.04052))</f>
@@ -12176,12 +12154,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="13">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
         <v>2042</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>70</v>
+      <c r="B74" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C74" s="2">
         <v>270613611.10000002</v>
@@ -12190,10 +12168,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="12" t="s">
-        <v>71</v>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="12"/>
+      <c r="B75" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C75" s="2">
         <v>1047284444</v>
@@ -12202,10 +12180,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="12" t="s">
-        <v>72</v>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="12"/>
+      <c r="B76" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C76" s="2">
         <v>2930833333</v>
@@ -12214,10 +12192,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="12" t="s">
-        <v>69</v>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="12"/>
+      <c r="B77" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C77" s="2">
         <f>SUM(C73*(1-0.04052))</f>
@@ -12227,12 +12205,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="13">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
         <v>2043</v>
       </c>
-      <c r="B78" s="12" t="s">
-        <v>70</v>
+      <c r="B78" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C78" s="2">
         <v>270613611.10000002</v>
@@ -12241,10 +12219,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="12" t="s">
-        <v>71</v>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="12"/>
+      <c r="B79" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C79" s="2">
         <v>1047284444</v>
@@ -12253,10 +12231,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="13"/>
-      <c r="B80" s="12" t="s">
-        <v>72</v>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="12"/>
+      <c r="B80" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C80" s="2">
         <v>2930833333</v>
@@ -12265,10 +12243,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="13"/>
-      <c r="B81" s="12" t="s">
-        <v>69</v>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="12"/>
+      <c r="B81" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C81" s="2">
         <f>SUM(C77*(1-0.04052))</f>
@@ -12278,12 +12256,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="13">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
         <v>2044</v>
       </c>
-      <c r="B82" s="12" t="s">
-        <v>70</v>
+      <c r="B82" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C82" s="2">
         <v>270613611.10000002</v>
@@ -12292,10 +12270,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="13"/>
-      <c r="B83" s="12" t="s">
-        <v>71</v>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="12"/>
+      <c r="B83" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C83" s="2">
         <v>1047284444</v>
@@ -12304,10 +12282,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="13"/>
-      <c r="B84" s="12" t="s">
-        <v>72</v>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="12"/>
+      <c r="B84" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C84" s="2">
         <v>2930833333</v>
@@ -12316,10 +12294,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="13"/>
-      <c r="B85" s="12" t="s">
-        <v>69</v>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="12"/>
+      <c r="B85" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C85" s="2">
         <f>SUM(C81*(1-0.04052))</f>
@@ -12329,12 +12307,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="13">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
         <v>2045</v>
       </c>
-      <c r="B86" s="12" t="s">
-        <v>70</v>
+      <c r="B86" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C86" s="2">
         <v>270613611.10000002</v>
@@ -12343,10 +12321,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="13"/>
-      <c r="B87" s="12" t="s">
-        <v>71</v>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="12"/>
+      <c r="B87" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C87" s="2">
         <v>1047284444</v>
@@ -12355,10 +12333,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="13"/>
-      <c r="B88" s="12" t="s">
-        <v>72</v>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="12"/>
+      <c r="B88" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C88" s="2">
         <v>2930833333</v>
@@ -12367,10 +12345,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="13"/>
-      <c r="B89" s="12" t="s">
-        <v>69</v>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="12"/>
+      <c r="B89" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C89" s="2">
         <f>SUM(C85*(1-0.04052))</f>
@@ -12380,12 +12358,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="13">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
         <v>2046</v>
       </c>
-      <c r="B90" s="12" t="s">
-        <v>70</v>
+      <c r="B90" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C90" s="2">
         <v>270613611.10000002</v>
@@ -12394,10 +12372,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="13"/>
-      <c r="B91" s="12" t="s">
-        <v>71</v>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="12"/>
+      <c r="B91" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C91" s="2">
         <v>1047284444</v>
@@ -12406,10 +12384,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="13"/>
-      <c r="B92" s="12" t="s">
-        <v>72</v>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="12"/>
+      <c r="B92" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C92" s="2">
         <v>2930833333</v>
@@ -12418,10 +12396,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="13"/>
-      <c r="B93" s="12" t="s">
-        <v>69</v>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="12"/>
+      <c r="B93" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C93" s="2">
         <f>SUM(C89*(1-0.04052))</f>
@@ -12431,12 +12409,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="13">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
         <v>2047</v>
       </c>
-      <c r="B94" s="12" t="s">
-        <v>70</v>
+      <c r="B94" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C94" s="2">
         <v>270613611.10000002</v>
@@ -12445,10 +12423,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="13"/>
-      <c r="B95" s="12" t="s">
-        <v>71</v>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="12"/>
+      <c r="B95" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C95" s="2">
         <v>1047284444</v>
@@ -12457,10 +12435,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="13"/>
-      <c r="B96" s="12" t="s">
-        <v>72</v>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="12"/>
+      <c r="B96" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C96" s="2">
         <v>2930833333</v>
@@ -12469,10 +12447,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="13"/>
-      <c r="B97" s="12" t="s">
-        <v>69</v>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="12"/>
+      <c r="B97" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C97" s="2">
         <f>SUM(C93*(1-0.04052))</f>
@@ -12482,12 +12460,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="13">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
         <v>2048</v>
       </c>
-      <c r="B98" s="12" t="s">
-        <v>70</v>
+      <c r="B98" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C98" s="2">
         <v>270613611.10000002</v>
@@ -12496,10 +12474,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="13"/>
-      <c r="B99" s="12" t="s">
-        <v>71</v>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="12"/>
+      <c r="B99" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C99" s="2">
         <v>1047284444</v>
@@ -12508,10 +12486,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="13"/>
-      <c r="B100" s="12" t="s">
-        <v>72</v>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="12"/>
+      <c r="B100" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C100" s="2">
         <v>2930833333</v>
@@ -12520,10 +12498,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="13"/>
-      <c r="B101" s="12" t="s">
-        <v>69</v>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="12"/>
+      <c r="B101" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C101" s="2">
         <f>SUM(C97*(1-0.04052))</f>
@@ -12533,12 +12511,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="13">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
         <v>2049</v>
       </c>
-      <c r="B102" s="12" t="s">
-        <v>70</v>
+      <c r="B102" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C102" s="2">
         <v>270613611.10000002</v>
@@ -12547,10 +12525,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="13"/>
-      <c r="B103" s="12" t="s">
-        <v>71</v>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="12"/>
+      <c r="B103" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C103" s="2">
         <v>1047284444</v>
@@ -12559,10 +12537,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="13"/>
-      <c r="B104" s="12" t="s">
-        <v>72</v>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="12"/>
+      <c r="B104" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C104" s="2">
         <v>2930833333</v>
@@ -12571,10 +12549,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="13"/>
-      <c r="B105" s="12" t="s">
-        <v>69</v>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="12"/>
+      <c r="B105" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C105" s="2">
         <f>SUM(C101*(1-0.04052))</f>
@@ -12584,12 +12562,12 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="13">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
         <v>2050</v>
       </c>
-      <c r="B106" s="12" t="s">
-        <v>70</v>
+      <c r="B106" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C106" s="2">
         <v>270613611.10000002</v>
@@ -12598,10 +12576,10 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="13"/>
-      <c r="B107" s="12" t="s">
-        <v>71</v>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="12"/>
+      <c r="B107" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C107" s="2">
         <v>1047284444</v>
@@ -12610,10 +12588,10 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="13"/>
-      <c r="B108" s="12" t="s">
-        <v>72</v>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="12"/>
+      <c r="B108" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C108" s="2">
         <v>2930833333</v>
@@ -12622,10 +12600,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="13"/>
-      <c r="B109" s="12" t="s">
-        <v>69</v>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="12"/>
+      <c r="B109" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C109" s="2">
         <f>SUM(C105*(1-0.04052))</f>
@@ -12638,6 +12616,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -12645,26 +12643,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F8DECA5-D051-4C44-8AE6-0B1E7095FB46}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AD15F06-E503-4891-AF71-B5AEAB14D995}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="735" yWindow="735" windowWidth="28800" windowHeight="15345" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="6" activeTab="11" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -22,6 +22,11 @@
     <sheet name="stocklvl" sheetId="7" r:id="rId7"/>
     <sheet name="installable_capacity" sheetId="3" r:id="rId8"/>
     <sheet name="gas_block" sheetId="13" r:id="rId9"/>
+    <sheet name="Tech_Stage_Specs" sheetId="14" r:id="rId10"/>
+    <sheet name="Materieal_Intensity" sheetId="15" r:id="rId11"/>
+    <sheet name="Material_Market" sheetId="17" r:id="rId12"/>
+    <sheet name="Component_Map" sheetId="18" r:id="rId13"/>
+    <sheet name="Cost_Data" sheetId="16" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
@@ -47,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="157">
   <si>
     <t>Value</t>
   </si>
@@ -263,6 +268,261 @@
   </si>
   <si>
     <t>WTF_LNG</t>
+  </si>
+  <si>
+    <t>build_time_lag</t>
+  </si>
+  <si>
+    <t>energy_needs</t>
+  </si>
+  <si>
+    <t>is_final_stage</t>
+  </si>
+  <si>
+    <t>solarPV</t>
+  </si>
+  <si>
+    <t>windon</t>
+  </si>
+  <si>
+    <t>windoff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note </t>
+  </si>
+  <si>
+    <t>finished</t>
+  </si>
+  <si>
+    <t>host</t>
+  </si>
+  <si>
+    <t>unique</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Ingot</t>
+  </si>
+  <si>
+    <t>Silicon</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Glass</t>
+  </si>
+  <si>
+    <t>40.0</t>
+  </si>
+  <si>
+    <t>38.0</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Aluminum</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Blade</t>
+  </si>
+  <si>
+    <t>Composite</t>
+  </si>
+  <si>
+    <t>12.0</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Tower</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>150.0</t>
+  </si>
+  <si>
+    <t>Nacelle</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>RareEarth</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Batteries</t>
+  </si>
+  <si>
+    <t>Lithium</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>Cobalt</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>wndon</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Wafer</t>
+  </si>
+  <si>
+    <t>80.0</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>120.0</t>
+  </si>
+  <si>
+    <t>70.0</t>
+  </si>
+  <si>
+    <t>60.0</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>90.0</t>
+  </si>
+  <si>
+    <t>Assembly</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>200.0</t>
+  </si>
+  <si>
+    <t>250.0</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>Pack</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>Cons_Tech</t>
+  </si>
+  <si>
+    <t>Cons_Stage</t>
+  </si>
+  <si>
+    <t>Input_Tech</t>
+  </si>
+  <si>
+    <t>Input_Stage</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>rec_efficiency</t>
+  </si>
+  <si>
+    <t>intensity</t>
+  </si>
+  <si>
+    <t>scrap_content</t>
+  </si>
+  <si>
+    <t>mining_cost</t>
+  </si>
+  <si>
+    <t>import_cost</t>
+  </si>
+  <si>
+    <t>mining_limit</t>
+  </si>
+  <si>
+    <t>capex_base</t>
+  </si>
+  <si>
+    <t>opex_var_base</t>
+  </si>
+  <si>
+    <t>import_cost_part</t>
+  </si>
+  <si>
+    <t>init_cap</t>
   </si>
 </sst>
 </file>
@@ -491,6 +751,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -850,6 +1114,1292 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C0D52F-0ADA-4AC5-8A50-4699398C8904}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>150</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>80</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA1A697-84AA-4F97-BE70-81695B57512E}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BB5A9E-0DE2-4C9D-A6F4-EBF765E41A9E}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2">
+        <v>1000000</v>
+      </c>
+      <c r="D2">
+        <v>1800</v>
+      </c>
+      <c r="E2">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3">
+        <v>5000</v>
+      </c>
+      <c r="D3">
+        <v>650000</v>
+      </c>
+      <c r="E3">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4">
+        <v>5000000</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2024</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5">
+        <v>2000000</v>
+      </c>
+      <c r="D5">
+        <v>2000</v>
+      </c>
+      <c r="E5">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6">
+        <v>500000</v>
+      </c>
+      <c r="D6">
+        <v>3000</v>
+      </c>
+      <c r="E6">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7">
+        <v>10000000</v>
+      </c>
+      <c r="D7">
+        <v>600</v>
+      </c>
+      <c r="E7">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8">
+        <v>800000</v>
+      </c>
+      <c r="D8">
+        <v>8000</v>
+      </c>
+      <c r="E8">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2024</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>20000</v>
+      </c>
+      <c r="D9">
+        <v>40000</v>
+      </c>
+      <c r="E9">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10">
+        <v>150000</v>
+      </c>
+      <c r="D10">
+        <v>15000</v>
+      </c>
+      <c r="E10">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2024</v>
+      </c>
+      <c r="B11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11">
+        <v>50000</v>
+      </c>
+      <c r="D11">
+        <v>30000</v>
+      </c>
+      <c r="E11">
+        <v>35000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{996B2112-D2EE-4E9F-B294-4222E881A3C9}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE844EE-882F-4833-8B87-00A8BB665263}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2024</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2024</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2024</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2024</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185AF38-42FD-4CFF-B287-2FCFFF6C6EF3}">
   <dimension ref="A1:U28"/>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AD15F06-E503-4891-AF71-B5AEAB14D995}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A20A2E7-1617-4C82-9341-AEA66E3C0C5A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="6" activeTab="11" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="14" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -23,10 +23,11 @@
     <sheet name="installable_capacity" sheetId="3" r:id="rId8"/>
     <sheet name="gas_block" sheetId="13" r:id="rId9"/>
     <sheet name="Tech_Stage_Specs" sheetId="14" r:id="rId10"/>
-    <sheet name="Materieal_Intensity" sheetId="15" r:id="rId11"/>
+    <sheet name="Material_Intensity" sheetId="15" r:id="rId11"/>
     <sheet name="Material_Market" sheetId="17" r:id="rId12"/>
     <sheet name="Component_Map" sheetId="18" r:id="rId13"/>
     <sheet name="Cost_Data" sheetId="16" r:id="rId14"/>
+    <sheet name="Import_Cost_Stage" sheetId="19" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="167">
   <si>
     <t>Value</t>
   </si>
@@ -411,9 +412,6 @@
     <t>0.2</t>
   </si>
   <si>
-    <t>wndon</t>
-  </si>
-  <si>
     <t>Year</t>
   </si>
   <si>
@@ -474,9 +472,6 @@
     <t>Pack</t>
   </si>
   <si>
-    <t>0.9</t>
-  </si>
-  <si>
     <t>0.10</t>
   </si>
   <si>
@@ -523,6 +518,42 @@
   </si>
   <si>
     <t>init_cap</t>
+  </si>
+  <si>
+    <t>solarPV_Ingot</t>
+  </si>
+  <si>
+    <t>solarPV_Wafer</t>
+  </si>
+  <si>
+    <t>solarPV_Cell</t>
+  </si>
+  <si>
+    <t>windon_Blade</t>
+  </si>
+  <si>
+    <t>windon_Tower</t>
+  </si>
+  <si>
+    <t>windon_Nacelle</t>
+  </si>
+  <si>
+    <t>windon_Assembly</t>
+  </si>
+  <si>
+    <t>windoff_Foundation</t>
+  </si>
+  <si>
+    <t>windoff_Assembly</t>
+  </si>
+  <si>
+    <t>bateries_Cell</t>
+  </si>
+  <si>
+    <t>batteries_Pack</t>
+  </si>
+  <si>
+    <t>solarPV_Module</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1152,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B1" t="s">
         <v>82</v>
@@ -1136,7 +1167,7 @@
         <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G1" t="s">
         <v>74</v>
@@ -1176,7 +1207,7 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1326,7 +1357,7 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1352,7 +1383,7 @@
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1378,7 +1409,7 @@
         <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1427,7 +1458,7 @@
         <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1464,13 +1495,13 @@
         <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1615,7 +1646,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
         <v>108</v>
@@ -1686,19 +1717,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
         <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1883,19 +1914,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
         <v>142</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>143</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>144</v>
-      </c>
-      <c r="D1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1903,7 +1934,7 @@
         <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
@@ -1912,7 +1943,7 @@
         <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1926,10 +1957,10 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1946,7 +1977,7 @@
         <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1954,7 +1985,7 @@
         <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
         <v>114</v>
@@ -1963,7 +1994,7 @@
         <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1971,7 +2002,7 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
         <v>76</v>
@@ -1980,7 +2011,7 @@
         <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1988,7 +2019,7 @@
         <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
         <v>76</v>
@@ -1997,7 +2028,7 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2005,7 +2036,7 @@
         <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
         <v>76</v>
@@ -2014,7 +2045,7 @@
         <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2022,7 +2053,7 @@
         <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
         <v>76</v>
@@ -2031,7 +2062,7 @@
         <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2039,7 +2070,7 @@
         <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
         <v>76</v>
@@ -2048,7 +2079,7 @@
         <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2056,7 +2087,7 @@
         <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
         <v>76</v>
@@ -2065,7 +2096,7 @@
         <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2073,16 +2104,16 @@
         <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
         <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2097,10 +2128,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" t="s">
         <v>120</v>
-      </c>
-      <c r="B1" t="s">
-        <v>121</v>
       </c>
       <c r="C1" t="s">
         <v>82</v>
@@ -2109,13 +2140,13 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" t="s">
         <v>153</v>
-      </c>
-      <c r="F1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -2132,10 +2163,10 @@
         <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" t="s">
         <v>125</v>
+      </c>
+      <c r="F2">
+        <v>1000000</v>
       </c>
       <c r="G2" t="s">
         <v>99</v>
@@ -2152,16 +2183,16 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F3" t="s">
-        <v>141</v>
+        <v>126</v>
+      </c>
+      <c r="F3">
+        <v>1000000</v>
       </c>
       <c r="G3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2178,13 +2209,13 @@
         <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" t="s">
-        <v>110</v>
+        <v>127</v>
+      </c>
+      <c r="F4">
+        <v>1000000</v>
       </c>
       <c r="G4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2201,13 +2232,13 @@
         <v>93</v>
       </c>
       <c r="E5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5">
+        <v>1000000</v>
+      </c>
+      <c r="G5" t="s">
         <v>129</v>
-      </c>
-      <c r="F5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2224,10 +2255,10 @@
         <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
-      </c>
-      <c r="F6" t="s">
-        <v>140</v>
+        <v>130</v>
+      </c>
+      <c r="F6">
+        <v>1000000</v>
       </c>
       <c r="G6" t="s">
         <v>87</v>
@@ -2247,10 +2278,10 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" t="s">
-        <v>141</v>
+        <v>122</v>
+      </c>
+      <c r="F7">
+        <v>1000000</v>
       </c>
       <c r="G7" t="s">
         <v>110</v>
@@ -2272,8 +2303,8 @@
       <c r="E8" t="s">
         <v>107</v>
       </c>
-      <c r="F8" t="s">
-        <v>125</v>
+      <c r="F8">
+        <v>1000000</v>
       </c>
       <c r="G8" t="s">
         <v>99</v>
@@ -2290,16 +2321,16 @@
         <v>76</v>
       </c>
       <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
         <v>132</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9">
+        <v>1000000</v>
+      </c>
+      <c r="G9" t="s">
         <v>133</v>
-      </c>
-      <c r="F9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2313,16 +2344,16 @@
         <v>77</v>
       </c>
       <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" t="s">
         <v>135</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10">
+        <v>1000000</v>
+      </c>
+      <c r="G10" t="s">
         <v>136</v>
-      </c>
-      <c r="F10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2336,16 +2367,16 @@
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F11" t="s">
-        <v>110</v>
+        <v>123</v>
+      </c>
+      <c r="F11">
+        <v>1000000</v>
       </c>
       <c r="G11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2362,13 +2393,13 @@
         <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" t="s">
-        <v>87</v>
+        <v>122</v>
+      </c>
+      <c r="F12">
+        <v>1000000</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2382,21 +2413,1180 @@
         <v>114</v>
       </c>
       <c r="D13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13">
+        <v>1000000</v>
+      </c>
+      <c r="G13" t="s">
         <v>139</v>
-      </c>
-      <c r="E13" t="s">
-        <v>138</v>
-      </c>
-      <c r="F13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G13" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B74DFEF-01D9-4B2D-A936-BF616F091054}">
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L1" t="s">
+        <v>164</v>
+      </c>
+      <c r="M1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2">
+        <v>9999999</v>
+      </c>
+      <c r="C2">
+        <v>9999999</v>
+      </c>
+      <c r="D2">
+        <v>9999999</v>
+      </c>
+      <c r="E2">
+        <v>250240</v>
+      </c>
+      <c r="F2">
+        <v>9999999</v>
+      </c>
+      <c r="G2">
+        <v>9999999</v>
+      </c>
+      <c r="H2">
+        <v>9999999</v>
+      </c>
+      <c r="I2" s="8">
+        <v>1052044.8400000001</v>
+      </c>
+      <c r="J2">
+        <v>9999999</v>
+      </c>
+      <c r="K2" s="8">
+        <v>1775265.6417320003</v>
+      </c>
+      <c r="L2">
+        <v>9999999</v>
+      </c>
+      <c r="M2">
+        <v>280439.83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>9999999</v>
+      </c>
+      <c r="C3">
+        <v>9999999</v>
+      </c>
+      <c r="D3">
+        <v>9999999</v>
+      </c>
+      <c r="E3">
+        <v>246486.39999999999</v>
+      </c>
+      <c r="F3">
+        <v>9999999</v>
+      </c>
+      <c r="G3">
+        <v>9999999</v>
+      </c>
+      <c r="H3">
+        <v>9999999</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1042480.7960000001</v>
+      </c>
+      <c r="J3">
+        <v>9999999</v>
+      </c>
+      <c r="K3" s="8">
+        <v>1722922.372057667</v>
+      </c>
+      <c r="L3">
+        <v>9999999</v>
+      </c>
+      <c r="M3">
+        <v>274754.90999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>9999999</v>
+      </c>
+      <c r="C4">
+        <v>9999999</v>
+      </c>
+      <c r="D4">
+        <v>9999999</v>
+      </c>
+      <c r="E4">
+        <v>242789.10399999999</v>
+      </c>
+      <c r="F4">
+        <v>9999999</v>
+      </c>
+      <c r="G4">
+        <v>9999999</v>
+      </c>
+      <c r="H4">
+        <v>9999999</v>
+      </c>
+      <c r="I4" s="8">
+        <v>1032916.7520000001</v>
+      </c>
+      <c r="J4">
+        <v>9999999</v>
+      </c>
+      <c r="K4" s="8">
+        <v>1670579.1023833335</v>
+      </c>
+      <c r="L4">
+        <v>9999999</v>
+      </c>
+      <c r="M4">
+        <v>269179.44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2027</v>
+      </c>
+      <c r="B5">
+        <v>9999999</v>
+      </c>
+      <c r="C5">
+        <v>9999999</v>
+      </c>
+      <c r="D5">
+        <v>9999999</v>
+      </c>
+      <c r="E5">
+        <v>239147.26740000001</v>
+      </c>
+      <c r="F5">
+        <v>9999999</v>
+      </c>
+      <c r="G5">
+        <v>9999999</v>
+      </c>
+      <c r="H5">
+        <v>9999999</v>
+      </c>
+      <c r="I5" s="8">
+        <v>1023352.708</v>
+      </c>
+      <c r="J5">
+        <v>9999999</v>
+      </c>
+      <c r="K5" s="8">
+        <v>1618235.832709</v>
+      </c>
+      <c r="L5">
+        <v>9999999</v>
+      </c>
+      <c r="M5">
+        <v>263711.78000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2028</v>
+      </c>
+      <c r="B6">
+        <v>9999999</v>
+      </c>
+      <c r="C6">
+        <v>9999999</v>
+      </c>
+      <c r="D6">
+        <v>9999999</v>
+      </c>
+      <c r="E6">
+        <v>235560.05840000001</v>
+      </c>
+      <c r="F6">
+        <v>9999999</v>
+      </c>
+      <c r="G6">
+        <v>9999999</v>
+      </c>
+      <c r="H6">
+        <v>9999999</v>
+      </c>
+      <c r="I6" s="8">
+        <v>1013788.6639999999</v>
+      </c>
+      <c r="J6">
+        <v>9999999</v>
+      </c>
+      <c r="K6" s="8">
+        <v>1565892.5630346665</v>
+      </c>
+      <c r="L6">
+        <v>9999999</v>
+      </c>
+      <c r="M6">
+        <v>258350.32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2029</v>
+      </c>
+      <c r="B7">
+        <v>9999999</v>
+      </c>
+      <c r="C7">
+        <v>9999999</v>
+      </c>
+      <c r="D7">
+        <v>9999999</v>
+      </c>
+      <c r="E7">
+        <v>232026.65760000001</v>
+      </c>
+      <c r="F7">
+        <v>9999999</v>
+      </c>
+      <c r="G7">
+        <v>9999999</v>
+      </c>
+      <c r="H7">
+        <v>9999999</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1004224.62</v>
+      </c>
+      <c r="J7">
+        <v>9999999</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1513549.293360333</v>
+      </c>
+      <c r="L7">
+        <v>9999999</v>
+      </c>
+      <c r="M7">
+        <v>253093.46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2030</v>
+      </c>
+      <c r="B8">
+        <v>9999999</v>
+      </c>
+      <c r="C8">
+        <v>9999999</v>
+      </c>
+      <c r="D8">
+        <v>9999999</v>
+      </c>
+      <c r="E8">
+        <v>228546.25769999999</v>
+      </c>
+      <c r="F8">
+        <v>9999999</v>
+      </c>
+      <c r="G8">
+        <v>9999999</v>
+      </c>
+      <c r="H8">
+        <v>9999999</v>
+      </c>
+      <c r="I8" s="8">
+        <v>994660.57600000012</v>
+      </c>
+      <c r="J8">
+        <v>9999999</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1461206.0236859999</v>
+      </c>
+      <c r="L8">
+        <v>9999999</v>
+      </c>
+      <c r="M8">
+        <v>247939.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2031</v>
+      </c>
+      <c r="B9">
+        <v>9999999</v>
+      </c>
+      <c r="C9">
+        <v>9999999</v>
+      </c>
+      <c r="D9">
+        <v>9999999</v>
+      </c>
+      <c r="E9">
+        <v>225118.0638</v>
+      </c>
+      <c r="F9">
+        <v>9999999</v>
+      </c>
+      <c r="G9">
+        <v>9999999</v>
+      </c>
+      <c r="H9">
+        <v>9999999</v>
+      </c>
+      <c r="I9" s="8">
+        <v>992747.76720000012</v>
+      </c>
+      <c r="J9">
+        <v>9999999</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1444015.15599508</v>
+      </c>
+      <c r="L9">
+        <v>9999999</v>
+      </c>
+      <c r="M9">
+        <v>242887.37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2032</v>
+      </c>
+      <c r="B10">
+        <v>9999999</v>
+      </c>
+      <c r="C10">
+        <v>9999999</v>
+      </c>
+      <c r="D10">
+        <v>9999999</v>
+      </c>
+      <c r="E10">
+        <v>221741.2929</v>
+      </c>
+      <c r="F10">
+        <v>9999999</v>
+      </c>
+      <c r="G10">
+        <v>9999999</v>
+      </c>
+      <c r="H10">
+        <v>9999999</v>
+      </c>
+      <c r="I10" s="8">
+        <v>990834.9584</v>
+      </c>
+      <c r="J10">
+        <v>9999999</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1426824.2883041599</v>
+      </c>
+      <c r="L10">
+        <v>9999999</v>
+      </c>
+      <c r="M10">
+        <v>237935.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2033</v>
+      </c>
+      <c r="B11">
+        <v>9999999</v>
+      </c>
+      <c r="C11">
+        <v>9999999</v>
+      </c>
+      <c r="D11">
+        <v>9999999</v>
+      </c>
+      <c r="E11">
+        <v>218415.1735</v>
+      </c>
+      <c r="F11">
+        <v>9999999</v>
+      </c>
+      <c r="G11">
+        <v>9999999</v>
+      </c>
+      <c r="H11">
+        <v>9999999</v>
+      </c>
+      <c r="I11" s="8">
+        <v>988922.1496</v>
+      </c>
+      <c r="J11">
+        <v>9999999</v>
+      </c>
+      <c r="K11" s="8">
+        <v>1409633.42061324</v>
+      </c>
+      <c r="L11">
+        <v>9999999</v>
+      </c>
+      <c r="M11">
+        <v>233081.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2034</v>
+      </c>
+      <c r="B12">
+        <v>9999999</v>
+      </c>
+      <c r="C12">
+        <v>9999999</v>
+      </c>
+      <c r="D12">
+        <v>9999999</v>
+      </c>
+      <c r="E12">
+        <v>215138.94589999999</v>
+      </c>
+      <c r="F12">
+        <v>9999999</v>
+      </c>
+      <c r="G12">
+        <v>9999999</v>
+      </c>
+      <c r="H12">
+        <v>9999999</v>
+      </c>
+      <c r="I12" s="8">
+        <v>987009.34079999989</v>
+      </c>
+      <c r="J12">
+        <v>9999999</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1392442.5529223196</v>
+      </c>
+      <c r="L12">
+        <v>9999999</v>
+      </c>
+      <c r="M12">
+        <v>228324.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2035</v>
+      </c>
+      <c r="B13">
+        <v>9999999</v>
+      </c>
+      <c r="C13">
+        <v>9999999</v>
+      </c>
+      <c r="D13">
+        <v>9999999</v>
+      </c>
+      <c r="E13">
+        <v>211911.86170000001</v>
+      </c>
+      <c r="F13">
+        <v>9999999</v>
+      </c>
+      <c r="G13">
+        <v>9999999</v>
+      </c>
+      <c r="H13">
+        <v>9999999</v>
+      </c>
+      <c r="I13" s="8">
+        <v>985096.53199999989</v>
+      </c>
+      <c r="J13">
+        <v>9999999</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1375251.6852313997</v>
+      </c>
+      <c r="L13">
+        <v>9999999</v>
+      </c>
+      <c r="M13">
+        <v>223663.91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2036</v>
+      </c>
+      <c r="B14">
+        <v>9999999</v>
+      </c>
+      <c r="C14">
+        <v>9999999</v>
+      </c>
+      <c r="D14">
+        <v>9999999</v>
+      </c>
+      <c r="E14">
+        <v>208733.1838</v>
+      </c>
+      <c r="F14">
+        <v>9999999</v>
+      </c>
+      <c r="G14">
+        <v>9999999</v>
+      </c>
+      <c r="H14">
+        <v>9999999</v>
+      </c>
+      <c r="I14" s="8">
+        <v>983183.72319999977</v>
+      </c>
+      <c r="J14">
+        <v>9999999</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1358060.8175404796</v>
+      </c>
+      <c r="L14">
+        <v>9999999</v>
+      </c>
+      <c r="M14">
+        <v>219097.32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2037</v>
+      </c>
+      <c r="B15">
+        <v>9999999</v>
+      </c>
+      <c r="C15">
+        <v>9999999</v>
+      </c>
+      <c r="D15">
+        <v>9999999</v>
+      </c>
+      <c r="E15">
+        <v>205602.18599999999</v>
+      </c>
+      <c r="F15">
+        <v>9999999</v>
+      </c>
+      <c r="G15">
+        <v>9999999</v>
+      </c>
+      <c r="H15">
+        <v>9999999</v>
+      </c>
+      <c r="I15" s="8">
+        <v>981270.91439999978</v>
+      </c>
+      <c r="J15">
+        <v>9999999</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1340869.9498495597</v>
+      </c>
+      <c r="L15">
+        <v>9999999</v>
+      </c>
+      <c r="M15">
+        <v>214623.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2038</v>
+      </c>
+      <c r="B16">
+        <v>9999999</v>
+      </c>
+      <c r="C16">
+        <v>9999999</v>
+      </c>
+      <c r="D16">
+        <v>9999999</v>
+      </c>
+      <c r="E16">
+        <v>202518.1532</v>
+      </c>
+      <c r="F16">
+        <v>9999999</v>
+      </c>
+      <c r="G16">
+        <v>9999999</v>
+      </c>
+      <c r="H16">
+        <v>9999999</v>
+      </c>
+      <c r="I16" s="8">
+        <v>979358.10559999966</v>
+      </c>
+      <c r="J16">
+        <v>9999999</v>
+      </c>
+      <c r="K16" s="8">
+        <v>1323679.0821586396</v>
+      </c>
+      <c r="L16">
+        <v>9999999</v>
+      </c>
+      <c r="M16">
+        <v>210241.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2039</v>
+      </c>
+      <c r="B17">
+        <v>9999999</v>
+      </c>
+      <c r="C17">
+        <v>9999999</v>
+      </c>
+      <c r="D17">
+        <v>9999999</v>
+      </c>
+      <c r="E17">
+        <v>199480.38089999999</v>
+      </c>
+      <c r="F17">
+        <v>9999999</v>
+      </c>
+      <c r="G17">
+        <v>9999999</v>
+      </c>
+      <c r="H17">
+        <v>9999999</v>
+      </c>
+      <c r="I17" s="8">
+        <v>977445.29679999966</v>
+      </c>
+      <c r="J17">
+        <v>9999999</v>
+      </c>
+      <c r="K17" s="8">
+        <v>1306488.2144677194</v>
+      </c>
+      <c r="L17">
+        <v>9999999</v>
+      </c>
+      <c r="M17">
+        <v>205949.84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2040</v>
+      </c>
+      <c r="B18">
+        <v>9999999</v>
+      </c>
+      <c r="C18">
+        <v>9999999</v>
+      </c>
+      <c r="D18">
+        <v>9999999</v>
+      </c>
+      <c r="E18">
+        <v>196488.1752</v>
+      </c>
+      <c r="F18">
+        <v>9999999</v>
+      </c>
+      <c r="G18">
+        <v>9999999</v>
+      </c>
+      <c r="H18">
+        <v>9999999</v>
+      </c>
+      <c r="I18" s="8">
+        <v>975532.48799999955</v>
+      </c>
+      <c r="J18">
+        <v>9999999</v>
+      </c>
+      <c r="K18" s="8">
+        <v>1288027.7959324</v>
+      </c>
+      <c r="L18">
+        <v>9999999</v>
+      </c>
+      <c r="M18">
+        <v>201747.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2041</v>
+      </c>
+      <c r="B19">
+        <v>9999999</v>
+      </c>
+      <c r="C19">
+        <v>9999999</v>
+      </c>
+      <c r="D19">
+        <v>9999999</v>
+      </c>
+      <c r="E19">
+        <v>193540.85260000001</v>
+      </c>
+      <c r="F19">
+        <v>9999999</v>
+      </c>
+      <c r="G19">
+        <v>9999999</v>
+      </c>
+      <c r="H19">
+        <v>9999999</v>
+      </c>
+      <c r="I19" s="8">
+        <v>973619.67919999966</v>
+      </c>
+      <c r="J19">
+        <v>9999999</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1288154.7510168403</v>
+      </c>
+      <c r="L19">
+        <v>9999999</v>
+      </c>
+      <c r="M19">
+        <v>197632.19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2042</v>
+      </c>
+      <c r="B20">
+        <v>9999999</v>
+      </c>
+      <c r="C20">
+        <v>9999999</v>
+      </c>
+      <c r="D20">
+        <v>9999999</v>
+      </c>
+      <c r="E20">
+        <v>190637.73980000001</v>
+      </c>
+      <c r="F20">
+        <v>9999999</v>
+      </c>
+      <c r="G20">
+        <v>9999999</v>
+      </c>
+      <c r="H20">
+        <v>9999999</v>
+      </c>
+      <c r="I20" s="8">
+        <v>971706.87039999955</v>
+      </c>
+      <c r="J20">
+        <v>9999999</v>
+      </c>
+      <c r="K20" s="8">
+        <v>1288281.7061012802</v>
+      </c>
+      <c r="L20">
+        <v>9999999</v>
+      </c>
+      <c r="M20">
+        <v>193603.83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2043</v>
+      </c>
+      <c r="B21">
+        <v>9999999</v>
+      </c>
+      <c r="C21">
+        <v>9999999</v>
+      </c>
+      <c r="D21">
+        <v>9999999</v>
+      </c>
+      <c r="E21">
+        <v>187778.17370000001</v>
+      </c>
+      <c r="F21">
+        <v>9999999</v>
+      </c>
+      <c r="G21">
+        <v>9999999</v>
+      </c>
+      <c r="H21">
+        <v>9999999</v>
+      </c>
+      <c r="I21" s="8">
+        <v>969794.06159999955</v>
+      </c>
+      <c r="J21">
+        <v>9999999</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1288408.6611857202</v>
+      </c>
+      <c r="L21">
+        <v>9999999</v>
+      </c>
+      <c r="M21">
+        <v>189660.87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2044</v>
+      </c>
+      <c r="B22">
+        <v>9999999</v>
+      </c>
+      <c r="C22">
+        <v>9999999</v>
+      </c>
+      <c r="D22">
+        <v>9999999</v>
+      </c>
+      <c r="E22">
+        <v>184961.50109999999</v>
+      </c>
+      <c r="F22">
+        <v>9999999</v>
+      </c>
+      <c r="G22">
+        <v>9999999</v>
+      </c>
+      <c r="H22">
+        <v>9999999</v>
+      </c>
+      <c r="I22" s="8">
+        <v>967881.25279999943</v>
+      </c>
+      <c r="J22">
+        <v>9999999</v>
+      </c>
+      <c r="K22" s="8">
+        <v>1288535.6162701603</v>
+      </c>
+      <c r="L22">
+        <v>9999999</v>
+      </c>
+      <c r="M22">
+        <v>185802.14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2045</v>
+      </c>
+      <c r="B23">
+        <v>9999999</v>
+      </c>
+      <c r="C23">
+        <v>9999999</v>
+      </c>
+      <c r="D23">
+        <v>9999999</v>
+      </c>
+      <c r="E23">
+        <v>182187.07860000001</v>
+      </c>
+      <c r="F23">
+        <v>9999999</v>
+      </c>
+      <c r="G23">
+        <v>9999999</v>
+      </c>
+      <c r="H23">
+        <v>9999999</v>
+      </c>
+      <c r="I23" s="8">
+        <v>965968.44399999944</v>
+      </c>
+      <c r="J23">
+        <v>9999999</v>
+      </c>
+      <c r="K23" s="8">
+        <v>1288662.5713546001</v>
+      </c>
+      <c r="L23">
+        <v>9999999</v>
+      </c>
+      <c r="M23">
+        <v>182026.51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2046</v>
+      </c>
+      <c r="B24">
+        <v>9999999</v>
+      </c>
+      <c r="C24">
+        <v>9999999</v>
+      </c>
+      <c r="D24">
+        <v>9999999</v>
+      </c>
+      <c r="E24">
+        <v>179454.27239999999</v>
+      </c>
+      <c r="F24">
+        <v>9999999</v>
+      </c>
+      <c r="G24">
+        <v>9999999</v>
+      </c>
+      <c r="H24">
+        <v>9999999</v>
+      </c>
+      <c r="I24" s="8">
+        <v>964055.63519999932</v>
+      </c>
+      <c r="J24">
+        <v>9999999</v>
+      </c>
+      <c r="K24" s="8">
+        <v>1288789.5264390404</v>
+      </c>
+      <c r="L24">
+        <v>9999999</v>
+      </c>
+      <c r="M24">
+        <v>178332.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2047</v>
+      </c>
+      <c r="B25">
+        <v>9999999</v>
+      </c>
+      <c r="C25">
+        <v>9999999</v>
+      </c>
+      <c r="D25">
+        <v>9999999</v>
+      </c>
+      <c r="E25">
+        <v>176762.4583</v>
+      </c>
+      <c r="F25">
+        <v>9999999</v>
+      </c>
+      <c r="G25">
+        <v>9999999</v>
+      </c>
+      <c r="H25">
+        <v>9999999</v>
+      </c>
+      <c r="I25" s="8">
+        <v>962142.82639999932</v>
+      </c>
+      <c r="J25">
+        <v>9999999</v>
+      </c>
+      <c r="K25" s="8">
+        <v>1288916.4815234803</v>
+      </c>
+      <c r="L25">
+        <v>9999999</v>
+      </c>
+      <c r="M25">
+        <v>174720.11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2048</v>
+      </c>
+      <c r="B26">
+        <v>9999999</v>
+      </c>
+      <c r="C26">
+        <v>9999999</v>
+      </c>
+      <c r="D26">
+        <v>9999999</v>
+      </c>
+      <c r="E26">
+        <v>174111.0214</v>
+      </c>
+      <c r="F26">
+        <v>9999999</v>
+      </c>
+      <c r="G26">
+        <v>9999999</v>
+      </c>
+      <c r="H26">
+        <v>9999999</v>
+      </c>
+      <c r="I26" s="8">
+        <v>960230.01759999921</v>
+      </c>
+      <c r="J26">
+        <v>9999999</v>
+      </c>
+      <c r="K26" s="8">
+        <v>1289043.4366079206</v>
+      </c>
+      <c r="L26">
+        <v>9999999</v>
+      </c>
+      <c r="M26">
+        <v>171187.17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2049</v>
+      </c>
+      <c r="B27">
+        <v>9999999</v>
+      </c>
+      <c r="C27">
+        <v>9999999</v>
+      </c>
+      <c r="D27">
+        <v>9999999</v>
+      </c>
+      <c r="E27">
+        <v>171499.3561</v>
+      </c>
+      <c r="F27">
+        <v>9999999</v>
+      </c>
+      <c r="G27">
+        <v>9999999</v>
+      </c>
+      <c r="H27">
+        <v>9999999</v>
+      </c>
+      <c r="I27" s="8">
+        <v>958317.20879999921</v>
+      </c>
+      <c r="J27">
+        <v>9999999</v>
+      </c>
+      <c r="K27" s="8">
+        <v>1289170.3916923604</v>
+      </c>
+      <c r="L27">
+        <v>9999999</v>
+      </c>
+      <c r="M27">
+        <v>167732.98000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2050</v>
+      </c>
+      <c r="B28">
+        <v>9999999</v>
+      </c>
+      <c r="C28">
+        <v>9999999</v>
+      </c>
+      <c r="D28">
+        <v>9999999</v>
+      </c>
+      <c r="E28">
+        <v>168926.8658</v>
+      </c>
+      <c r="F28">
+        <v>9999999</v>
+      </c>
+      <c r="G28">
+        <v>9999999</v>
+      </c>
+      <c r="H28">
+        <v>9999999</v>
+      </c>
+      <c r="I28" s="8">
+        <v>956404.40000000026</v>
+      </c>
+      <c r="J28">
+        <v>9999999</v>
+      </c>
+      <c r="K28" s="8">
+        <v>1289297.3467768</v>
+      </c>
+      <c r="L28">
+        <v>9999999</v>
+      </c>
+      <c r="M28">
+        <v>164356.51999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A20A2E7-1617-4C82-9341-AEA66E3C0C5A}"/>
+  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11A5AAD5-D1C8-4FB3-A394-84735324E4CB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="14" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="8" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="152">
   <si>
     <t>Value</t>
   </si>
@@ -310,9 +310,6 @@
     <t>Material</t>
   </si>
   <si>
-    <t>Ingot</t>
-  </si>
-  <si>
     <t>Silicon</t>
   </si>
   <si>
@@ -421,58 +418,16 @@
     <t>Wafer</t>
   </si>
   <si>
-    <t>80.0</t>
-  </si>
-  <si>
-    <t>20.0</t>
-  </si>
-  <si>
-    <t>4.0</t>
-  </si>
-  <si>
-    <t>120.0</t>
-  </si>
-  <si>
-    <t>70.0</t>
-  </si>
-  <si>
-    <t>60.0</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
     <t>1.0</t>
-  </si>
-  <si>
-    <t>90.0</t>
   </si>
   <si>
     <t>Assembly</t>
   </si>
   <si>
-    <t>10.0</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>200.0</t>
-  </si>
-  <si>
-    <t>250.0</t>
-  </si>
-  <si>
-    <t>30.0</t>
-  </si>
-  <si>
     <t>Pack</t>
-  </si>
-  <si>
-    <t>0.10</t>
   </si>
   <si>
     <t>Cons_Tech</t>
@@ -514,13 +469,7 @@
     <t>opex_var_base</t>
   </si>
   <si>
-    <t>import_cost_part</t>
-  </si>
-  <si>
     <t>init_cap</t>
-  </si>
-  <si>
-    <t>solarPV_Ingot</t>
   </si>
   <si>
     <t>solarPV_Wafer</t>
@@ -554,6 +503,12 @@
   </si>
   <si>
     <t>solarPV_Module</t>
+  </si>
+  <si>
+    <t>Polysilicon</t>
+  </si>
+  <si>
+    <t>solarPV_Polysilicon</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1107,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
         <v>82</v>
@@ -1167,7 +1122,7 @@
         <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="G1" t="s">
         <v>74</v>
@@ -1184,7 +1139,7 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1193,7 +1148,7 @@
         <v>150</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>24000</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1207,7 +1162,7 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1216,7 +1171,7 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1230,7 +1185,7 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1239,7 +1194,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>7000</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1253,7 +1208,7 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1262,7 +1217,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>22000</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1279,7 +1234,7 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1305,7 +1260,7 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1331,7 +1286,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1357,7 +1312,7 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1383,7 +1338,7 @@
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1409,7 +1364,7 @@
         <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1432,10 +1387,10 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1455,10 +1410,10 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1495,13 +1450,13 @@
         <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="F1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1509,19 +1464,19 @@
         <v>75</v>
       </c>
       <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
         <v>86</v>
       </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>87</v>
-      </c>
-      <c r="F2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1529,19 +1484,19 @@
         <v>75</v>
       </c>
       <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
         <v>89</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>90</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" t="s">
         <v>91</v>
-      </c>
-      <c r="E3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1549,19 +1504,19 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
         <v>93</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>94</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>95</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>96</v>
-      </c>
-      <c r="F4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1569,19 +1524,19 @@
         <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" t="s">
         <v>98</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" t="s">
         <v>99</v>
-      </c>
-      <c r="E5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1589,19 +1544,19 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
         <v>101</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>102</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" t="s">
         <v>103</v>
-      </c>
-      <c r="E6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1609,19 +1564,19 @@
         <v>76</v>
       </c>
       <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
         <v>105</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>106</v>
       </c>
-      <c r="D7" t="s">
-        <v>107</v>
-      </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1629,19 +1584,19 @@
         <v>76</v>
       </c>
       <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" t="s">
         <v>108</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>109</v>
       </c>
-      <c r="D8" t="s">
-        <v>110</v>
-      </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1649,59 +1604,59 @@
         <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
         <v>111</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" t="s">
         <v>112</v>
-      </c>
-      <c r="E9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
         <v>114</v>
       </c>
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>115</v>
       </c>
-      <c r="D10" t="s">
-        <v>116</v>
-      </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" t="s">
         <v>117</v>
       </c>
-      <c r="D11" t="s">
-        <v>118</v>
-      </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1717,19 +1672,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B1" t="s">
         <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="E1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1737,7 +1692,7 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -1754,7 +1709,7 @@
         <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3">
         <v>5000</v>
@@ -1771,7 +1726,7 @@
         <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4">
         <v>5000000</v>
@@ -1788,7 +1743,7 @@
         <v>2024</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5">
         <v>2000000</v>
@@ -1805,7 +1760,7 @@
         <v>2024</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6">
         <v>500000</v>
@@ -1822,7 +1777,7 @@
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7">
         <v>10000000</v>
@@ -1839,7 +1794,7 @@
         <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8">
         <v>800000</v>
@@ -1856,7 +1811,7 @@
         <v>2024</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <v>20000</v>
@@ -1873,7 +1828,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10">
         <v>150000</v>
@@ -1890,7 +1845,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11">
         <v>50000</v>
@@ -1914,19 +1869,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D1" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1934,16 +1889,16 @@
         <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1951,16 +1906,16 @@
         <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
         <v>75</v>
       </c>
       <c r="D3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
         <v>121</v>
-      </c>
-      <c r="E3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1968,33 +1923,33 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
         <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2002,16 +1957,16 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
         <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2019,16 +1974,16 @@
         <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
         <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2036,16 +1991,16 @@
         <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2053,16 +2008,16 @@
         <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
         <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2070,16 +2025,16 @@
         <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2087,16 +2042,16 @@
         <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
         <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2104,16 +2059,16 @@
         <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
         <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2123,15 +2078,15 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE844EE-882F-4833-8B87-00A8BB665263}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" t="s">
         <v>119</v>
-      </c>
-      <c r="B1" t="s">
-        <v>120</v>
       </c>
       <c r="C1" t="s">
         <v>82</v>
@@ -2140,16 +2095,13 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -2160,19 +2112,16 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" t="s">
-        <v>125</v>
+        <v>150</v>
+      </c>
+      <c r="E2">
+        <v>1000</v>
       </c>
       <c r="F2">
         <v>1000000</v>
       </c>
-      <c r="G2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -2183,19 +2132,16 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" t="s">
-        <v>126</v>
+        <v>120</v>
+      </c>
+      <c r="E3">
+        <v>1000</v>
       </c>
       <c r="F3">
         <v>1000000</v>
       </c>
-      <c r="G3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -2206,19 +2152,16 @@
         <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
       </c>
       <c r="F4">
         <v>1000000</v>
       </c>
-      <c r="G4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -2229,19 +2172,16 @@
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" t="s">
-        <v>128</v>
+        <v>92</v>
+      </c>
+      <c r="E5">
+        <v>1000</v>
       </c>
       <c r="F5">
         <v>1000000</v>
       </c>
-      <c r="G5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2024</v>
       </c>
@@ -2252,19 +2192,16 @@
         <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" t="s">
-        <v>130</v>
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>1000</v>
       </c>
       <c r="F6">
         <v>1000000</v>
       </c>
-      <c r="G6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2024</v>
       </c>
@@ -2275,19 +2212,16 @@
         <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" t="s">
-        <v>122</v>
+        <v>104</v>
+      </c>
+      <c r="E7">
+        <v>1000</v>
       </c>
       <c r="F7">
         <v>1000000</v>
       </c>
-      <c r="G7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -2298,19 +2232,16 @@
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" t="s">
         <v>107</v>
+      </c>
+      <c r="E8">
+        <v>1000</v>
       </c>
       <c r="F8">
         <v>1000000</v>
       </c>
-      <c r="G8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2024</v>
       </c>
@@ -2321,19 +2252,16 @@
         <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" t="s">
-        <v>132</v>
+        <v>122</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
       </c>
       <c r="F9">
         <v>1000000</v>
       </c>
-      <c r="G9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -2344,19 +2272,16 @@
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" t="s">
-        <v>135</v>
+        <v>123</v>
+      </c>
+      <c r="E10">
+        <v>1000</v>
       </c>
       <c r="F10">
         <v>1000000</v>
       </c>
-      <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -2367,19 +2292,16 @@
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" t="s">
-        <v>123</v>
+        <v>122</v>
+      </c>
+      <c r="E11">
+        <v>1000</v>
       </c>
       <c r="F11">
         <v>1000000</v>
       </c>
-      <c r="G11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -2387,22 +2309,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>122</v>
+        <v>88</v>
+      </c>
+      <c r="E12">
+        <v>1000</v>
       </c>
       <c r="F12">
         <v>1000000</v>
       </c>
-      <c r="G12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2024</v>
       </c>
@@ -2410,19 +2329,16 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" t="s">
-        <v>137</v>
+        <v>124</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
       </c>
       <c r="F13">
         <v>1000000</v>
-      </c>
-      <c r="G13" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2441,40 +2357,40 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C1" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D1" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="F1" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="G1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="H1" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="I1" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="J1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="K1" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="L1" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="M1" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -2482,7 +2398,7 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C2">
         <v>9999999</v>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11A5AAD5-D1C8-4FB3-A394-84735324E4CB}"/>
+  <xr:revisionPtr revIDLastSave="313" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{109EDEA0-1EB9-4F59-9537-2F6A9E6EB3A3}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="8" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="14" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="151">
   <si>
     <t>Value</t>
   </si>
@@ -427,9 +427,6 @@
     <t>Foundation</t>
   </si>
   <si>
-    <t>Pack</t>
-  </si>
-  <si>
     <t>Cons_Tech</t>
   </si>
   <si>
@@ -496,12 +493,6 @@
     <t>windoff_Assembly</t>
   </si>
   <si>
-    <t>bateries_Cell</t>
-  </si>
-  <si>
-    <t>batteries_Pack</t>
-  </si>
-  <si>
     <t>solarPV_Module</t>
   </si>
   <si>
@@ -509,6 +500,12 @@
   </si>
   <si>
     <t>solarPV_Polysilicon</t>
+  </si>
+  <si>
+    <t>Batteries_Assembly</t>
+  </si>
+  <si>
+    <t>Batteries_Cell</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1119,7 @@
         <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G1" t="s">
         <v>74</v>
@@ -1139,7 +1136,7 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1413,7 +1410,7 @@
         <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1450,13 +1447,13 @@
         <v>84</v>
       </c>
       <c r="D1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" t="s">
         <v>131</v>
       </c>
-      <c r="E1" t="s">
-        <v>132</v>
-      </c>
       <c r="F1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1464,7 +1461,7 @@
         <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
         <v>85</v>
@@ -1678,13 +1675,13 @@
         <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" t="s">
         <v>133</v>
-      </c>
-      <c r="E1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1869,19 +1866,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
         <v>125</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>126</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>127</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>128</v>
-      </c>
-      <c r="E1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1895,7 +1892,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
         <v>121</v>
@@ -1940,7 +1937,7 @@
         <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
         <v>113</v>
@@ -2095,10 +2092,10 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" t="s">
         <v>136</v>
-      </c>
-      <c r="F1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2112,7 +2109,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E2">
         <v>1000</v>
@@ -2332,7 +2329,7 @@
         <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E13">
         <v>1000</v>
@@ -2357,40 +2354,40 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
         <v>139</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" t="s">
         <v>140</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M1" t="s">
         <v>149</v>
-      </c>
-      <c r="F1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K1" t="s">
-        <v>146</v>
-      </c>
-      <c r="L1" t="s">
-        <v>147</v>
-      </c>
-      <c r="M1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -2425,7 +2422,7 @@
         <v>9999999</v>
       </c>
       <c r="K2" s="8">
-        <v>1775265.6417320003</v>
+        <v>1775265.64</v>
       </c>
       <c r="L2">
         <v>9999999</v>
@@ -2460,13 +2457,13 @@
         <v>9999999</v>
       </c>
       <c r="I3" s="8">
-        <v>1042480.7960000001</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J3">
         <v>9999999</v>
       </c>
       <c r="K3" s="8">
-        <v>1722922.372057667</v>
+        <v>1775265.64</v>
       </c>
       <c r="L3">
         <v>9999999</v>
@@ -2501,13 +2498,13 @@
         <v>9999999</v>
       </c>
       <c r="I4" s="8">
-        <v>1032916.7520000001</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J4">
         <v>9999999</v>
       </c>
       <c r="K4" s="8">
-        <v>1670579.1023833335</v>
+        <v>1775265.64</v>
       </c>
       <c r="L4">
         <v>9999999</v>
@@ -2542,13 +2539,13 @@
         <v>9999999</v>
       </c>
       <c r="I5" s="8">
-        <v>1023352.708</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J5">
         <v>9999999</v>
       </c>
       <c r="K5" s="8">
-        <v>1618235.832709</v>
+        <v>1775265.64</v>
       </c>
       <c r="L5">
         <v>9999999</v>
@@ -2583,13 +2580,13 @@
         <v>9999999</v>
       </c>
       <c r="I6" s="8">
-        <v>1013788.6639999999</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J6">
         <v>9999999</v>
       </c>
       <c r="K6" s="8">
-        <v>1565892.5630346665</v>
+        <v>1775265.64</v>
       </c>
       <c r="L6">
         <v>9999999</v>
@@ -2624,13 +2621,13 @@
         <v>9999999</v>
       </c>
       <c r="I7" s="8">
-        <v>1004224.62</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J7">
         <v>9999999</v>
       </c>
       <c r="K7" s="8">
-        <v>1513549.293360333</v>
+        <v>1775265.64</v>
       </c>
       <c r="L7">
         <v>9999999</v>
@@ -2665,13 +2662,13 @@
         <v>9999999</v>
       </c>
       <c r="I8" s="8">
-        <v>994660.57600000012</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J8">
         <v>9999999</v>
       </c>
       <c r="K8" s="8">
-        <v>1461206.0236859999</v>
+        <v>1775265.64</v>
       </c>
       <c r="L8">
         <v>9999999</v>
@@ -2706,13 +2703,13 @@
         <v>9999999</v>
       </c>
       <c r="I9" s="8">
-        <v>992747.76720000012</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J9">
         <v>9999999</v>
       </c>
       <c r="K9" s="8">
-        <v>1444015.15599508</v>
+        <v>1775265.64</v>
       </c>
       <c r="L9">
         <v>9999999</v>
@@ -2747,13 +2744,13 @@
         <v>9999999</v>
       </c>
       <c r="I10" s="8">
-        <v>990834.9584</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J10">
         <v>9999999</v>
       </c>
       <c r="K10" s="8">
-        <v>1426824.2883041599</v>
+        <v>1775265.64</v>
       </c>
       <c r="L10">
         <v>9999999</v>
@@ -2788,13 +2785,13 @@
         <v>9999999</v>
       </c>
       <c r="I11" s="8">
-        <v>988922.1496</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J11">
         <v>9999999</v>
       </c>
       <c r="K11" s="8">
-        <v>1409633.42061324</v>
+        <v>1775265.64</v>
       </c>
       <c r="L11">
         <v>9999999</v>
@@ -2829,13 +2826,13 @@
         <v>9999999</v>
       </c>
       <c r="I12" s="8">
-        <v>987009.34079999989</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J12">
         <v>9999999</v>
       </c>
       <c r="K12" s="8">
-        <v>1392442.5529223196</v>
+        <v>1775265.64</v>
       </c>
       <c r="L12">
         <v>9999999</v>
@@ -2870,13 +2867,13 @@
         <v>9999999</v>
       </c>
       <c r="I13" s="8">
-        <v>985096.53199999989</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J13">
         <v>9999999</v>
       </c>
       <c r="K13" s="8">
-        <v>1375251.6852313997</v>
+        <v>1775265.64</v>
       </c>
       <c r="L13">
         <v>9999999</v>
@@ -2911,13 +2908,13 @@
         <v>9999999</v>
       </c>
       <c r="I14" s="8">
-        <v>983183.72319999977</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J14">
         <v>9999999</v>
       </c>
       <c r="K14" s="8">
-        <v>1358060.8175404796</v>
+        <v>1775265.64</v>
       </c>
       <c r="L14">
         <v>9999999</v>
@@ -2952,13 +2949,13 @@
         <v>9999999</v>
       </c>
       <c r="I15" s="8">
-        <v>981270.91439999978</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J15">
         <v>9999999</v>
       </c>
       <c r="K15" s="8">
-        <v>1340869.9498495597</v>
+        <v>1775265.64</v>
       </c>
       <c r="L15">
         <v>9999999</v>
@@ -2993,13 +2990,13 @@
         <v>9999999</v>
       </c>
       <c r="I16" s="8">
-        <v>979358.10559999966</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J16">
         <v>9999999</v>
       </c>
       <c r="K16" s="8">
-        <v>1323679.0821586396</v>
+        <v>1775265.64</v>
       </c>
       <c r="L16">
         <v>9999999</v>
@@ -3034,13 +3031,13 @@
         <v>9999999</v>
       </c>
       <c r="I17" s="8">
-        <v>977445.29679999966</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J17">
         <v>9999999</v>
       </c>
       <c r="K17" s="8">
-        <v>1306488.2144677194</v>
+        <v>1775265.64</v>
       </c>
       <c r="L17">
         <v>9999999</v>
@@ -3075,13 +3072,13 @@
         <v>9999999</v>
       </c>
       <c r="I18" s="8">
-        <v>975532.48799999955</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J18">
         <v>9999999</v>
       </c>
       <c r="K18" s="8">
-        <v>1288027.7959324</v>
+        <v>1775265.64</v>
       </c>
       <c r="L18">
         <v>9999999</v>
@@ -3116,13 +3113,13 @@
         <v>9999999</v>
       </c>
       <c r="I19" s="8">
-        <v>973619.67919999966</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J19">
         <v>9999999</v>
       </c>
       <c r="K19" s="8">
-        <v>1288154.7510168403</v>
+        <v>1775265.64</v>
       </c>
       <c r="L19">
         <v>9999999</v>
@@ -3157,13 +3154,13 @@
         <v>9999999</v>
       </c>
       <c r="I20" s="8">
-        <v>971706.87039999955</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J20">
         <v>9999999</v>
       </c>
       <c r="K20" s="8">
-        <v>1288281.7061012802</v>
+        <v>1775265.64</v>
       </c>
       <c r="L20">
         <v>9999999</v>
@@ -3198,13 +3195,13 @@
         <v>9999999</v>
       </c>
       <c r="I21" s="8">
-        <v>969794.06159999955</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J21">
         <v>9999999</v>
       </c>
       <c r="K21" s="8">
-        <v>1288408.6611857202</v>
+        <v>1775265.64</v>
       </c>
       <c r="L21">
         <v>9999999</v>
@@ -3239,13 +3236,13 @@
         <v>9999999</v>
       </c>
       <c r="I22" s="8">
-        <v>967881.25279999943</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J22">
         <v>9999999</v>
       </c>
       <c r="K22" s="8">
-        <v>1288535.6162701603</v>
+        <v>1775265.64</v>
       </c>
       <c r="L22">
         <v>9999999</v>
@@ -3280,13 +3277,13 @@
         <v>9999999</v>
       </c>
       <c r="I23" s="8">
-        <v>965968.44399999944</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J23">
         <v>9999999</v>
       </c>
       <c r="K23" s="8">
-        <v>1288662.5713546001</v>
+        <v>1775265.64</v>
       </c>
       <c r="L23">
         <v>9999999</v>
@@ -3321,13 +3318,13 @@
         <v>9999999</v>
       </c>
       <c r="I24" s="8">
-        <v>964055.63519999932</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J24">
         <v>9999999</v>
       </c>
       <c r="K24" s="8">
-        <v>1288789.5264390404</v>
+        <v>1775265.64</v>
       </c>
       <c r="L24">
         <v>9999999</v>
@@ -3362,13 +3359,13 @@
         <v>9999999</v>
       </c>
       <c r="I25" s="8">
-        <v>962142.82639999932</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J25">
         <v>9999999</v>
       </c>
       <c r="K25" s="8">
-        <v>1288916.4815234803</v>
+        <v>1775265.64</v>
       </c>
       <c r="L25">
         <v>9999999</v>
@@ -3403,13 +3400,13 @@
         <v>9999999</v>
       </c>
       <c r="I26" s="8">
-        <v>960230.01759999921</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J26">
         <v>9999999</v>
       </c>
       <c r="K26" s="8">
-        <v>1289043.4366079206</v>
+        <v>1775265.64</v>
       </c>
       <c r="L26">
         <v>9999999</v>
@@ -3444,13 +3441,13 @@
         <v>9999999</v>
       </c>
       <c r="I27" s="8">
-        <v>958317.20879999921</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J27">
         <v>9999999</v>
       </c>
       <c r="K27" s="8">
-        <v>1289170.3916923604</v>
+        <v>1775265.64</v>
       </c>
       <c r="L27">
         <v>9999999</v>
@@ -3485,13 +3482,13 @@
         <v>9999999</v>
       </c>
       <c r="I28" s="8">
-        <v>956404.40000000026</v>
+        <v>1052044.8400000001</v>
       </c>
       <c r="J28">
         <v>9999999</v>
       </c>
       <c r="K28" s="8">
-        <v>1289297.3467768</v>
+        <v>1775265.64</v>
       </c>
       <c r="L28">
         <v>9999999</v>
@@ -15272,26 +15269,6 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -15299,6 +15276,26 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{109EDEA0-1EB9-4F59-9537-2F6A9E6EB3A3}"/>
+  <xr:revisionPtr revIDLastSave="314" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48D5A401-35C7-4493-814E-E5354DD6F0B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="14" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
@@ -2457,13 +2457,13 @@
         <v>9999999</v>
       </c>
       <c r="I3" s="8">
-        <v>1052044.8400000001</v>
+        <v>1042480.8</v>
       </c>
       <c r="J3">
         <v>9999999</v>
       </c>
       <c r="K3" s="8">
-        <v>1775265.64</v>
+        <v>1722922.37</v>
       </c>
       <c r="L3">
         <v>9999999</v>
@@ -2498,13 +2498,13 @@
         <v>9999999</v>
       </c>
       <c r="I4" s="8">
-        <v>1052044.8400000001</v>
+        <v>1032916.75</v>
       </c>
       <c r="J4">
         <v>9999999</v>
       </c>
       <c r="K4" s="8">
-        <v>1775265.64</v>
+        <v>1670579.1</v>
       </c>
       <c r="L4">
         <v>9999999</v>
@@ -2539,13 +2539,13 @@
         <v>9999999</v>
       </c>
       <c r="I5" s="8">
-        <v>1052044.8400000001</v>
+        <v>1023352.71</v>
       </c>
       <c r="J5">
         <v>9999999</v>
       </c>
       <c r="K5" s="8">
-        <v>1775265.64</v>
+        <v>1618235.83</v>
       </c>
       <c r="L5">
         <v>9999999</v>
@@ -2580,13 +2580,13 @@
         <v>9999999</v>
       </c>
       <c r="I6" s="8">
-        <v>1052044.8400000001</v>
+        <v>1013788.66</v>
       </c>
       <c r="J6">
         <v>9999999</v>
       </c>
       <c r="K6" s="8">
-        <v>1775265.64</v>
+        <v>1565892.56</v>
       </c>
       <c r="L6">
         <v>9999999</v>
@@ -2621,13 +2621,13 @@
         <v>9999999</v>
       </c>
       <c r="I7" s="8">
-        <v>1052044.8400000001</v>
+        <v>1004224.62</v>
       </c>
       <c r="J7">
         <v>9999999</v>
       </c>
       <c r="K7" s="8">
-        <v>1775265.64</v>
+        <v>1513549.29</v>
       </c>
       <c r="L7">
         <v>9999999</v>
@@ -2662,13 +2662,13 @@
         <v>9999999</v>
       </c>
       <c r="I8" s="8">
-        <v>1052044.8400000001</v>
+        <v>994660.58</v>
       </c>
       <c r="J8">
         <v>9999999</v>
       </c>
       <c r="K8" s="8">
-        <v>1775265.64</v>
+        <v>1461206.02</v>
       </c>
       <c r="L8">
         <v>9999999</v>
@@ -2703,13 +2703,13 @@
         <v>9999999</v>
       </c>
       <c r="I9" s="8">
-        <v>1052044.8400000001</v>
+        <v>992747.77</v>
       </c>
       <c r="J9">
         <v>9999999</v>
       </c>
       <c r="K9" s="8">
-        <v>1775265.64</v>
+        <v>1444015.16</v>
       </c>
       <c r="L9">
         <v>9999999</v>
@@ -2744,13 +2744,13 @@
         <v>9999999</v>
       </c>
       <c r="I10" s="8">
-        <v>1052044.8400000001</v>
+        <v>990834.96</v>
       </c>
       <c r="J10">
         <v>9999999</v>
       </c>
       <c r="K10" s="8">
-        <v>1775265.64</v>
+        <v>1426824.29</v>
       </c>
       <c r="L10">
         <v>9999999</v>
@@ -2785,13 +2785,13 @@
         <v>9999999</v>
       </c>
       <c r="I11" s="8">
-        <v>1052044.8400000001</v>
+        <v>988922.15</v>
       </c>
       <c r="J11">
         <v>9999999</v>
       </c>
       <c r="K11" s="8">
-        <v>1775265.64</v>
+        <v>1409633.42</v>
       </c>
       <c r="L11">
         <v>9999999</v>
@@ -2826,13 +2826,13 @@
         <v>9999999</v>
       </c>
       <c r="I12" s="8">
-        <v>1052044.8400000001</v>
+        <v>987009.34</v>
       </c>
       <c r="J12">
         <v>9999999</v>
       </c>
       <c r="K12" s="8">
-        <v>1775265.64</v>
+        <v>1392442.55</v>
       </c>
       <c r="L12">
         <v>9999999</v>
@@ -2867,13 +2867,13 @@
         <v>9999999</v>
       </c>
       <c r="I13" s="8">
-        <v>1052044.8400000001</v>
+        <v>985096.53</v>
       </c>
       <c r="J13">
         <v>9999999</v>
       </c>
       <c r="K13" s="8">
-        <v>1775265.64</v>
+        <v>1375251.69</v>
       </c>
       <c r="L13">
         <v>9999999</v>
@@ -2908,13 +2908,13 @@
         <v>9999999</v>
       </c>
       <c r="I14" s="8">
-        <v>1052044.8400000001</v>
+        <v>983183.72</v>
       </c>
       <c r="J14">
         <v>9999999</v>
       </c>
       <c r="K14" s="8">
-        <v>1775265.64</v>
+        <v>1358060.82</v>
       </c>
       <c r="L14">
         <v>9999999</v>
@@ -2949,13 +2949,13 @@
         <v>9999999</v>
       </c>
       <c r="I15" s="8">
-        <v>1052044.8400000001</v>
+        <v>981270.91</v>
       </c>
       <c r="J15">
         <v>9999999</v>
       </c>
       <c r="K15" s="8">
-        <v>1775265.64</v>
+        <v>1340869.95</v>
       </c>
       <c r="L15">
         <v>9999999</v>
@@ -2990,13 +2990,13 @@
         <v>9999999</v>
       </c>
       <c r="I16" s="8">
-        <v>1052044.8400000001</v>
+        <v>979358.11</v>
       </c>
       <c r="J16">
         <v>9999999</v>
       </c>
       <c r="K16" s="8">
-        <v>1775265.64</v>
+        <v>1323679.08</v>
       </c>
       <c r="L16">
         <v>9999999</v>
@@ -3031,13 +3031,13 @@
         <v>9999999</v>
       </c>
       <c r="I17" s="8">
-        <v>1052044.8400000001</v>
+        <v>977445.3</v>
       </c>
       <c r="J17">
         <v>9999999</v>
       </c>
       <c r="K17" s="8">
-        <v>1775265.64</v>
+        <v>1306488.21</v>
       </c>
       <c r="L17">
         <v>9999999</v>
@@ -3072,13 +3072,13 @@
         <v>9999999</v>
       </c>
       <c r="I18" s="8">
-        <v>1052044.8400000001</v>
+        <v>975532.49</v>
       </c>
       <c r="J18">
         <v>9999999</v>
       </c>
       <c r="K18" s="8">
-        <v>1775265.64</v>
+        <v>1288027.8</v>
       </c>
       <c r="L18">
         <v>9999999</v>
@@ -3113,13 +3113,13 @@
         <v>9999999</v>
       </c>
       <c r="I19" s="8">
-        <v>1052044.8400000001</v>
+        <v>973619.68</v>
       </c>
       <c r="J19">
         <v>9999999</v>
       </c>
       <c r="K19" s="8">
-        <v>1775265.64</v>
+        <v>1288154.75</v>
       </c>
       <c r="L19">
         <v>9999999</v>
@@ -3154,13 +3154,13 @@
         <v>9999999</v>
       </c>
       <c r="I20" s="8">
-        <v>1052044.8400000001</v>
+        <v>971706.87</v>
       </c>
       <c r="J20">
         <v>9999999</v>
       </c>
       <c r="K20" s="8">
-        <v>1775265.64</v>
+        <v>1288281.71</v>
       </c>
       <c r="L20">
         <v>9999999</v>
@@ -3195,13 +3195,13 @@
         <v>9999999</v>
       </c>
       <c r="I21" s="8">
-        <v>1052044.8400000001</v>
+        <v>969794.06</v>
       </c>
       <c r="J21">
         <v>9999999</v>
       </c>
       <c r="K21" s="8">
-        <v>1775265.64</v>
+        <v>1288408.6599999999</v>
       </c>
       <c r="L21">
         <v>9999999</v>
@@ -3236,13 +3236,13 @@
         <v>9999999</v>
       </c>
       <c r="I22" s="8">
-        <v>1052044.8400000001</v>
+        <v>967881.25</v>
       </c>
       <c r="J22">
         <v>9999999</v>
       </c>
       <c r="K22" s="8">
-        <v>1775265.64</v>
+        <v>1288535.6200000001</v>
       </c>
       <c r="L22">
         <v>9999999</v>
@@ -3277,13 +3277,13 @@
         <v>9999999</v>
       </c>
       <c r="I23" s="8">
-        <v>1052044.8400000001</v>
+        <v>965968.44</v>
       </c>
       <c r="J23">
         <v>9999999</v>
       </c>
       <c r="K23" s="8">
-        <v>1775265.64</v>
+        <v>1288662.57</v>
       </c>
       <c r="L23">
         <v>9999999</v>
@@ -3318,13 +3318,13 @@
         <v>9999999</v>
       </c>
       <c r="I24" s="8">
-        <v>1052044.8400000001</v>
+        <v>964055.64</v>
       </c>
       <c r="J24">
         <v>9999999</v>
       </c>
       <c r="K24" s="8">
-        <v>1775265.64</v>
+        <v>1288789.53</v>
       </c>
       <c r="L24">
         <v>9999999</v>
@@ -3359,13 +3359,13 @@
         <v>9999999</v>
       </c>
       <c r="I25" s="8">
-        <v>1052044.8400000001</v>
+        <v>962142.83</v>
       </c>
       <c r="J25">
         <v>9999999</v>
       </c>
       <c r="K25" s="8">
-        <v>1775265.64</v>
+        <v>1288916.48</v>
       </c>
       <c r="L25">
         <v>9999999</v>
@@ -3400,13 +3400,13 @@
         <v>9999999</v>
       </c>
       <c r="I26" s="8">
-        <v>1052044.8400000001</v>
+        <v>960230.02</v>
       </c>
       <c r="J26">
         <v>9999999</v>
       </c>
       <c r="K26" s="8">
-        <v>1775265.64</v>
+        <v>1289043.44</v>
       </c>
       <c r="L26">
         <v>9999999</v>
@@ -3441,13 +3441,13 @@
         <v>9999999</v>
       </c>
       <c r="I27" s="8">
-        <v>1052044.8400000001</v>
+        <v>958317.21</v>
       </c>
       <c r="J27">
         <v>9999999</v>
       </c>
       <c r="K27" s="8">
-        <v>1775265.64</v>
+        <v>1289170.3899999999</v>
       </c>
       <c r="L27">
         <v>9999999</v>
@@ -3482,13 +3482,13 @@
         <v>9999999</v>
       </c>
       <c r="I28" s="8">
-        <v>1052044.8400000001</v>
+        <v>956404.4</v>
       </c>
       <c r="J28">
         <v>9999999</v>
       </c>
       <c r="K28" s="8">
-        <v>1775265.64</v>
+        <v>1289297.3500000001</v>
       </c>
       <c r="L28">
         <v>9999999</v>
@@ -15269,6 +15269,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -15276,26 +15296,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="314" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48D5A401-35C7-4493-814E-E5354DD6F0B1}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C07CE4-8C5D-4311-B8B6-913E977DEB40}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="14" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="151">
   <si>
     <t>Value</t>
   </si>
@@ -424,9 +424,6 @@
     <t>Assembly</t>
   </si>
   <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>Cons_Tech</t>
   </si>
   <si>
@@ -507,6 +504,9 @@
   <si>
     <t>Batteries_Cell</t>
   </si>
+  <si>
+    <t>finished, happens on-site so no limitation, will be limited by installable capacity</t>
+  </si>
 </sst>
 </file>
 
@@ -570,7 +570,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -604,6 +604,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -680,7 +686,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -710,6 +716,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -1099,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C0D52F-0ADA-4AC5-8A50-4699398C8904}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1119,7 +1126,7 @@
         <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G1" t="s">
         <v>74</v>
@@ -1136,7 +1143,7 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1144,7 +1151,7 @@
       <c r="E2">
         <v>150</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>24000</v>
       </c>
       <c r="G2">
@@ -1167,7 +1174,7 @@
       <c r="E3">
         <v>100</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7">
         <v>2000</v>
       </c>
       <c r="G3">
@@ -1190,7 +1197,7 @@
       <c r="E4">
         <v>100</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>7000</v>
       </c>
       <c r="G4">
@@ -1213,7 +1220,7 @@
       <c r="E5">
         <v>100</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>22000</v>
       </c>
       <c r="G5">
@@ -1239,8 +1246,8 @@
       <c r="E6">
         <v>100</v>
       </c>
-      <c r="F6">
-        <v>100</v>
+      <c r="F6" s="7">
+        <v>27000</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1265,8 +1272,8 @@
       <c r="E7">
         <v>100</v>
       </c>
-      <c r="F7">
-        <v>100</v>
+      <c r="F7" s="7">
+        <v>27000</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1291,8 +1298,8 @@
       <c r="E8">
         <v>100</v>
       </c>
-      <c r="F8">
-        <v>100</v>
+      <c r="F8" s="7">
+        <v>27000</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1317,14 +1324,14 @@
       <c r="E9">
         <v>100</v>
       </c>
-      <c r="F9">
-        <v>100</v>
+      <c r="F9" s="7">
+        <v>999999</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1335,7 +1342,7 @@
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1361,22 +1368,19 @@
         <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="F11" s="7">
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1384,19 +1388,16 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12">
+        <v>107</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="E12">
-        <v>80</v>
-      </c>
-      <c r="F12">
-        <v>100</v>
+      <c r="F12" s="7">
+        <v>1</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1407,7 +1408,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
         <v>122</v>
@@ -1416,13 +1417,62 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>20</v>
-      </c>
-      <c r="F13">
         <v>100</v>
+      </c>
+      <c r="F13" s="7">
+        <v>999999</v>
       </c>
       <c r="G13">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>80</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1433,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA1A697-84AA-4F97-BE70-81695B57512E}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1447,13 +1497,13 @@
         <v>84</v>
       </c>
       <c r="D1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" t="s">
         <v>130</v>
       </c>
-      <c r="E1" t="s">
-        <v>131</v>
-      </c>
       <c r="F1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1461,7 +1511,7 @@
         <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
         <v>85</v>
@@ -1618,41 +1668,121 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>113</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" t="s">
         <v>88</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
         <v>116</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D15" t="s">
         <v>117</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E15" t="s">
         <v>117</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F15" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1675,13 +1805,13 @@
         <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" t="s">
         <v>132</v>
-      </c>
-      <c r="E1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1861,24 +1991,24 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{996B2112-D2EE-4E9F-B294-4222E881A3C9}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
         <v>124</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>125</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>126</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>127</v>
-      </c>
-      <c r="E1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1892,7 +2022,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
         <v>121</v>
@@ -2008,7 +2138,7 @@
         <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>100</v>
@@ -2025,7 +2155,7 @@
         <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>104</v>
@@ -2042,29 +2172,12 @@
         <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
         <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2075,7 +2188,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE844EE-882F-4833-8B87-00A8BB665263}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2092,10 +2205,10 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" t="s">
         <v>135</v>
-      </c>
-      <c r="F1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2109,13 +2222,13 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2">
-        <v>1000000</v>
+        <v>146</v>
+      </c>
+      <c r="E2" s="13">
+        <v>55200</v>
+      </c>
+      <c r="F2" s="13">
+        <v>3220.0000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2131,11 +2244,11 @@
       <c r="D3" t="s">
         <v>120</v>
       </c>
-      <c r="E3">
-        <v>1000</v>
-      </c>
-      <c r="F3">
-        <v>1000000</v>
+      <c r="E3" s="13">
+        <v>92000</v>
+      </c>
+      <c r="F3" s="13">
+        <v>4600</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2151,11 +2264,11 @@
       <c r="D4" t="s">
         <v>88</v>
       </c>
-      <c r="E4">
-        <v>1000</v>
-      </c>
-      <c r="F4">
-        <v>1000000</v>
+      <c r="E4" s="13">
+        <v>165600</v>
+      </c>
+      <c r="F4" s="13">
+        <v>8280</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2171,11 +2284,11 @@
       <c r="D5" t="s">
         <v>92</v>
       </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
-      <c r="F5">
-        <v>1000000</v>
+      <c r="E5" s="13">
+        <v>46000</v>
+      </c>
+      <c r="F5" s="13">
+        <v>2300</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2191,11 +2304,11 @@
       <c r="D6" t="s">
         <v>100</v>
       </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
-      <c r="F6">
-        <v>1000000</v>
+      <c r="E6" s="13">
+        <v>73600</v>
+      </c>
+      <c r="F6" s="13">
+        <v>3680.0000000000009</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2211,11 +2324,11 @@
       <c r="D7" t="s">
         <v>104</v>
       </c>
-      <c r="E7">
-        <v>1000</v>
-      </c>
-      <c r="F7">
-        <v>1000000</v>
+      <c r="E7" s="13">
+        <v>82800</v>
+      </c>
+      <c r="F7" s="13">
+        <v>4140</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2231,11 +2344,11 @@
       <c r="D8" t="s">
         <v>107</v>
       </c>
-      <c r="E8">
-        <v>1000</v>
-      </c>
-      <c r="F8">
-        <v>1000000</v>
+      <c r="E8" s="13">
+        <v>276000</v>
+      </c>
+      <c r="F8" s="13">
+        <v>13800</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2251,11 +2364,11 @@
       <c r="D9" t="s">
         <v>122</v>
       </c>
-      <c r="E9">
-        <v>1000</v>
-      </c>
-      <c r="F9">
-        <v>1000000</v>
+      <c r="E9" s="13">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2269,13 +2382,13 @@
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10">
-        <v>1000</v>
-      </c>
-      <c r="F10">
-        <v>1000000</v>
+        <v>100</v>
+      </c>
+      <c r="E10" s="13">
+        <v>165600</v>
+      </c>
+      <c r="F10" s="13">
+        <v>8280</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2289,13 +2402,13 @@
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11">
-        <v>1000</v>
-      </c>
-      <c r="F11">
-        <v>1000000</v>
+        <v>104</v>
+      </c>
+      <c r="E11" s="13">
+        <v>202400</v>
+      </c>
+      <c r="F11" s="13">
+        <v>10120</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2306,16 +2419,16 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12">
-        <v>1000</v>
-      </c>
-      <c r="F12">
-        <v>1000000</v>
+        <v>107</v>
+      </c>
+      <c r="E12" s="13">
+        <v>202400</v>
+      </c>
+      <c r="F12" s="13">
+        <v>10120</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2326,16 +2439,56 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
         <v>122</v>
       </c>
-      <c r="E13">
-        <v>1000</v>
-      </c>
-      <c r="F13">
-        <v>1000000</v>
+      <c r="E13" s="13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2024</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="13">
+        <v>92000</v>
+      </c>
+      <c r="F14" s="13">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2024</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="13">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2354,40 +2507,40 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K1" t="s">
+        <v>144</v>
+      </c>
+      <c r="L1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" t="s">
         <v>148</v>
-      </c>
-      <c r="C1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J1" t="s">
-        <v>144</v>
-      </c>
-      <c r="K1" t="s">
-        <v>145</v>
-      </c>
-      <c r="L1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -15269,26 +15422,6 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -15296,6 +15429,26 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C07CE4-8C5D-4311-B8B6-913E977DEB40}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF8DBB7-6D38-454A-A4D6-ADC9D831B385}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="6" activeTab="13" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="154">
   <si>
     <t>Value</t>
   </si>
@@ -484,9 +484,6 @@
     <t>windon_Assembly</t>
   </si>
   <si>
-    <t>windoff_Foundation</t>
-  </si>
-  <si>
     <t>windoff_Assembly</t>
   </si>
   <si>
@@ -506,6 +503,18 @@
   </si>
   <si>
     <t>finished, happens on-site so no limitation, will be limited by installable capacity</t>
+  </si>
+  <si>
+    <t>windoff_Blade</t>
+  </si>
+  <si>
+    <t>windoff_Tower</t>
+  </si>
+  <si>
+    <t>windoff_Nacelle</t>
+  </si>
+  <si>
+    <t>opex_fixed</t>
   </si>
 </sst>
 </file>
@@ -713,10 +722,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -1143,7 +1152,7 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1331,7 +1340,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1472,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1511,7 +1520,7 @@
         <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
         <v>85</v>
@@ -2022,7 +2031,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
         <v>121</v>
@@ -2188,10 +2197,10 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE844EE-882F-4833-8B87-00A8BB665263}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>118</v>
       </c>
@@ -2210,8 +2219,11 @@
       <c r="F1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -2222,16 +2234,19 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" s="13">
+        <v>145</v>
+      </c>
+      <c r="E2" s="12">
         <v>55200</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
+        <v>1449.0000000000002</v>
+      </c>
+      <c r="G2" s="12">
         <v>3220.0000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -2244,14 +2259,17 @@
       <c r="D3" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>92000</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
+        <v>3312</v>
+      </c>
+      <c r="G3" s="12">
         <v>4600</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -2264,14 +2282,17 @@
       <c r="D4" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>165600</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
+        <v>14904</v>
+      </c>
+      <c r="G4" s="12">
         <v>8280</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -2284,14 +2305,17 @@
       <c r="D5" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>46000</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
+        <v>12420</v>
+      </c>
+      <c r="G5" s="12">
         <v>2300</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2024</v>
       </c>
@@ -2304,14 +2328,17 @@
       <c r="D6" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <v>73600</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
+        <v>20976.000000000007</v>
+      </c>
+      <c r="G6" s="12">
         <v>3680.0000000000009</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2024</v>
       </c>
@@ -2324,14 +2351,17 @@
       <c r="D7" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>82800</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
+        <v>7866</v>
+      </c>
+      <c r="G7" s="12">
         <v>4140</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -2344,14 +2374,17 @@
       <c r="D8" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>276000</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
+        <v>26220</v>
+      </c>
+      <c r="G8" s="12">
         <v>13800</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2024</v>
       </c>
@@ -2364,14 +2397,17 @@
       <c r="D9" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>1</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -2384,14 +2420,17 @@
       <c r="D10" t="s">
         <v>100</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>165600</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
+        <v>47196</v>
+      </c>
+      <c r="G10" s="12">
         <v>8280</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -2404,14 +2443,17 @@
       <c r="D11" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>202400</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
+        <v>19228</v>
+      </c>
+      <c r="G11" s="12">
         <v>10120</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -2424,14 +2466,17 @@
       <c r="D12" t="s">
         <v>107</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>202400</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
+        <v>19228</v>
+      </c>
+      <c r="G12" s="12">
         <v>10120</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2024</v>
       </c>
@@ -2444,14 +2489,17 @@
       <c r="D13" t="s">
         <v>122</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>1</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2024</v>
       </c>
@@ -2464,14 +2512,17 @@
       <c r="D14" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <v>92000</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
+        <v>13524</v>
+      </c>
+      <c r="G14" s="12">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2024</v>
       </c>
@@ -2484,10 +2535,13 @@
       <c r="D15" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>1</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
+        <v>1</v>
+      </c>
+      <c r="G15" s="12">
         <v>1</v>
       </c>
     </row>
@@ -2499,15 +2553,15 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B74DFEF-01D9-4B2D-A936-BF616F091054}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C1" t="s">
         <v>137</v>
@@ -2516,7 +2570,7 @@
         <v>138</v>
       </c>
       <c r="E1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F1" t="s">
         <v>139</v>
@@ -2531,19 +2585,25 @@
         <v>142</v>
       </c>
       <c r="J1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" t="s">
         <v>143</v>
       </c>
-      <c r="K1" t="s">
-        <v>144</v>
-      </c>
-      <c r="L1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -2574,17 +2634,23 @@
       <c r="J2">
         <v>9999999</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2">
+        <v>9999999</v>
+      </c>
+      <c r="L2">
+        <v>9999999</v>
+      </c>
+      <c r="M2" s="8">
         <v>1775265.64</v>
       </c>
-      <c r="L2">
-        <v>9999999</v>
-      </c>
-      <c r="M2">
+      <c r="N2">
+        <v>9999999</v>
+      </c>
+      <c r="O2">
         <v>280439.83</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -2615,17 +2681,23 @@
       <c r="J3">
         <v>9999999</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3">
+        <v>9999999</v>
+      </c>
+      <c r="L3">
+        <v>9999999</v>
+      </c>
+      <c r="M3" s="8">
         <v>1722922.37</v>
       </c>
-      <c r="L3">
-        <v>9999999</v>
-      </c>
-      <c r="M3">
+      <c r="N3">
+        <v>9999999</v>
+      </c>
+      <c r="O3">
         <v>274754.90999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -2656,17 +2728,23 @@
       <c r="J4">
         <v>9999999</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4">
+        <v>9999999</v>
+      </c>
+      <c r="L4">
+        <v>9999999</v>
+      </c>
+      <c r="M4" s="8">
         <v>1670579.1</v>
       </c>
-      <c r="L4">
-        <v>9999999</v>
-      </c>
-      <c r="M4">
+      <c r="N4">
+        <v>9999999</v>
+      </c>
+      <c r="O4">
         <v>269179.44</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2027</v>
       </c>
@@ -2697,17 +2775,23 @@
       <c r="J5">
         <v>9999999</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5">
+        <v>9999999</v>
+      </c>
+      <c r="L5">
+        <v>9999999</v>
+      </c>
+      <c r="M5" s="8">
         <v>1618235.83</v>
       </c>
-      <c r="L5">
-        <v>9999999</v>
-      </c>
-      <c r="M5">
+      <c r="N5">
+        <v>9999999</v>
+      </c>
+      <c r="O5">
         <v>263711.78000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2028</v>
       </c>
@@ -2738,17 +2822,23 @@
       <c r="J6">
         <v>9999999</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6">
+        <v>9999999</v>
+      </c>
+      <c r="L6">
+        <v>9999999</v>
+      </c>
+      <c r="M6" s="8">
         <v>1565892.56</v>
       </c>
-      <c r="L6">
-        <v>9999999</v>
-      </c>
-      <c r="M6">
+      <c r="N6">
+        <v>9999999</v>
+      </c>
+      <c r="O6">
         <v>258350.32</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2029</v>
       </c>
@@ -2779,17 +2869,23 @@
       <c r="J7">
         <v>9999999</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7">
+        <v>9999999</v>
+      </c>
+      <c r="L7">
+        <v>9999999</v>
+      </c>
+      <c r="M7" s="8">
         <v>1513549.29</v>
       </c>
-      <c r="L7">
-        <v>9999999</v>
-      </c>
-      <c r="M7">
+      <c r="N7">
+        <v>9999999</v>
+      </c>
+      <c r="O7">
         <v>253093.46</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2030</v>
       </c>
@@ -2820,17 +2916,23 @@
       <c r="J8">
         <v>9999999</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8">
+        <v>9999999</v>
+      </c>
+      <c r="L8">
+        <v>9999999</v>
+      </c>
+      <c r="M8" s="8">
         <v>1461206.02</v>
       </c>
-      <c r="L8">
-        <v>9999999</v>
-      </c>
-      <c r="M8">
+      <c r="N8">
+        <v>9999999</v>
+      </c>
+      <c r="O8">
         <v>247939.65</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2031</v>
       </c>
@@ -2861,17 +2963,23 @@
       <c r="J9">
         <v>9999999</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9">
+        <v>9999999</v>
+      </c>
+      <c r="L9">
+        <v>9999999</v>
+      </c>
+      <c r="M9" s="8">
         <v>1444015.16</v>
       </c>
-      <c r="L9">
-        <v>9999999</v>
-      </c>
-      <c r="M9">
+      <c r="N9">
+        <v>9999999</v>
+      </c>
+      <c r="O9">
         <v>242887.37</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2032</v>
       </c>
@@ -2902,17 +3010,23 @@
       <c r="J10">
         <v>9999999</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10">
+        <v>9999999</v>
+      </c>
+      <c r="L10">
+        <v>9999999</v>
+      </c>
+      <c r="M10" s="8">
         <v>1426824.29</v>
       </c>
-      <c r="L10">
-        <v>9999999</v>
-      </c>
-      <c r="M10">
+      <c r="N10">
+        <v>9999999</v>
+      </c>
+      <c r="O10">
         <v>237935.1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2033</v>
       </c>
@@ -2943,17 +3057,23 @@
       <c r="J11">
         <v>9999999</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11">
+        <v>9999999</v>
+      </c>
+      <c r="L11">
+        <v>9999999</v>
+      </c>
+      <c r="M11" s="8">
         <v>1409633.42</v>
       </c>
-      <c r="L11">
-        <v>9999999</v>
-      </c>
-      <c r="M11">
+      <c r="N11">
+        <v>9999999</v>
+      </c>
+      <c r="O11">
         <v>233081.4</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2034</v>
       </c>
@@ -2984,17 +3104,23 @@
       <c r="J12">
         <v>9999999</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12">
+        <v>9999999</v>
+      </c>
+      <c r="L12">
+        <v>9999999</v>
+      </c>
+      <c r="M12" s="8">
         <v>1392442.55</v>
       </c>
-      <c r="L12">
-        <v>9999999</v>
-      </c>
-      <c r="M12">
+      <c r="N12">
+        <v>9999999</v>
+      </c>
+      <c r="O12">
         <v>228324.82</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2035</v>
       </c>
@@ -3025,17 +3151,23 @@
       <c r="J13">
         <v>9999999</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13">
+        <v>9999999</v>
+      </c>
+      <c r="L13">
+        <v>9999999</v>
+      </c>
+      <c r="M13" s="8">
         <v>1375251.69</v>
       </c>
-      <c r="L13">
-        <v>9999999</v>
-      </c>
-      <c r="M13">
+      <c r="N13">
+        <v>9999999</v>
+      </c>
+      <c r="O13">
         <v>223663.91</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2036</v>
       </c>
@@ -3066,17 +3198,23 @@
       <c r="J14">
         <v>9999999</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14">
+        <v>9999999</v>
+      </c>
+      <c r="L14">
+        <v>9999999</v>
+      </c>
+      <c r="M14" s="8">
         <v>1358060.82</v>
       </c>
-      <c r="L14">
-        <v>9999999</v>
-      </c>
-      <c r="M14">
+      <c r="N14">
+        <v>9999999</v>
+      </c>
+      <c r="O14">
         <v>219097.32</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2037</v>
       </c>
@@ -3107,17 +3245,23 @@
       <c r="J15">
         <v>9999999</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15">
+        <v>9999999</v>
+      </c>
+      <c r="L15">
+        <v>9999999</v>
+      </c>
+      <c r="M15" s="8">
         <v>1340869.95</v>
       </c>
-      <c r="L15">
-        <v>9999999</v>
-      </c>
-      <c r="M15">
+      <c r="N15">
+        <v>9999999</v>
+      </c>
+      <c r="O15">
         <v>214623.65</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2038</v>
       </c>
@@ -3148,17 +3292,23 @@
       <c r="J16">
         <v>9999999</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16">
+        <v>9999999</v>
+      </c>
+      <c r="L16">
+        <v>9999999</v>
+      </c>
+      <c r="M16" s="8">
         <v>1323679.08</v>
       </c>
-      <c r="L16">
-        <v>9999999</v>
-      </c>
-      <c r="M16">
+      <c r="N16">
+        <v>9999999</v>
+      </c>
+      <c r="O16">
         <v>210241.6</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -3189,17 +3339,23 @@
       <c r="J17">
         <v>9999999</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17">
+        <v>9999999</v>
+      </c>
+      <c r="L17">
+        <v>9999999</v>
+      </c>
+      <c r="M17" s="8">
         <v>1306488.21</v>
       </c>
-      <c r="L17">
-        <v>9999999</v>
-      </c>
-      <c r="M17">
+      <c r="N17">
+        <v>9999999</v>
+      </c>
+      <c r="O17">
         <v>205949.84</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2040</v>
       </c>
@@ -3230,17 +3386,23 @@
       <c r="J18">
         <v>9999999</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18">
+        <v>9999999</v>
+      </c>
+      <c r="L18">
+        <v>9999999</v>
+      </c>
+      <c r="M18" s="8">
         <v>1288027.8</v>
       </c>
-      <c r="L18">
-        <v>9999999</v>
-      </c>
-      <c r="M18">
+      <c r="N18">
+        <v>9999999</v>
+      </c>
+      <c r="O18">
         <v>201747.12</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -3271,17 +3433,23 @@
       <c r="J19">
         <v>9999999</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19">
+        <v>9999999</v>
+      </c>
+      <c r="L19">
+        <v>9999999</v>
+      </c>
+      <c r="M19" s="8">
         <v>1288154.75</v>
       </c>
-      <c r="L19">
-        <v>9999999</v>
-      </c>
-      <c r="M19">
+      <c r="N19">
+        <v>9999999</v>
+      </c>
+      <c r="O19">
         <v>197632.19</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2042</v>
       </c>
@@ -3312,17 +3480,23 @@
       <c r="J20">
         <v>9999999</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20">
+        <v>9999999</v>
+      </c>
+      <c r="L20">
+        <v>9999999</v>
+      </c>
+      <c r="M20" s="8">
         <v>1288281.71</v>
       </c>
-      <c r="L20">
-        <v>9999999</v>
-      </c>
-      <c r="M20">
+      <c r="N20">
+        <v>9999999</v>
+      </c>
+      <c r="O20">
         <v>193603.83</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2043</v>
       </c>
@@ -3353,17 +3527,23 @@
       <c r="J21">
         <v>9999999</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21">
+        <v>9999999</v>
+      </c>
+      <c r="L21">
+        <v>9999999</v>
+      </c>
+      <c r="M21" s="8">
         <v>1288408.6599999999</v>
       </c>
-      <c r="L21">
-        <v>9999999</v>
-      </c>
-      <c r="M21">
+      <c r="N21">
+        <v>9999999</v>
+      </c>
+      <c r="O21">
         <v>189660.87</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2044</v>
       </c>
@@ -3394,17 +3574,23 @@
       <c r="J22">
         <v>9999999</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22">
+        <v>9999999</v>
+      </c>
+      <c r="L22">
+        <v>9999999</v>
+      </c>
+      <c r="M22" s="8">
         <v>1288535.6200000001</v>
       </c>
-      <c r="L22">
-        <v>9999999</v>
-      </c>
-      <c r="M22">
+      <c r="N22">
+        <v>9999999</v>
+      </c>
+      <c r="O22">
         <v>185802.14</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2045</v>
       </c>
@@ -3435,17 +3621,23 @@
       <c r="J23">
         <v>9999999</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23">
+        <v>9999999</v>
+      </c>
+      <c r="L23">
+        <v>9999999</v>
+      </c>
+      <c r="M23" s="8">
         <v>1288662.57</v>
       </c>
-      <c r="L23">
-        <v>9999999</v>
-      </c>
-      <c r="M23">
+      <c r="N23">
+        <v>9999999</v>
+      </c>
+      <c r="O23">
         <v>182026.51</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2046</v>
       </c>
@@ -3476,17 +3668,23 @@
       <c r="J24">
         <v>9999999</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24">
+        <v>9999999</v>
+      </c>
+      <c r="L24">
+        <v>9999999</v>
+      </c>
+      <c r="M24" s="8">
         <v>1288789.53</v>
       </c>
-      <c r="L24">
-        <v>9999999</v>
-      </c>
-      <c r="M24">
+      <c r="N24">
+        <v>9999999</v>
+      </c>
+      <c r="O24">
         <v>178332.87</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2047</v>
       </c>
@@ -3517,17 +3715,23 @@
       <c r="J25">
         <v>9999999</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25">
+        <v>9999999</v>
+      </c>
+      <c r="L25">
+        <v>9999999</v>
+      </c>
+      <c r="M25" s="8">
         <v>1288916.48</v>
       </c>
-      <c r="L25">
-        <v>9999999</v>
-      </c>
-      <c r="M25">
+      <c r="N25">
+        <v>9999999</v>
+      </c>
+      <c r="O25">
         <v>174720.11</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2048</v>
       </c>
@@ -3558,17 +3762,23 @@
       <c r="J26">
         <v>9999999</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26">
+        <v>9999999</v>
+      </c>
+      <c r="L26">
+        <v>9999999</v>
+      </c>
+      <c r="M26" s="8">
         <v>1289043.44</v>
       </c>
-      <c r="L26">
-        <v>9999999</v>
-      </c>
-      <c r="M26">
+      <c r="N26">
+        <v>9999999</v>
+      </c>
+      <c r="O26">
         <v>171187.17</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2049</v>
       </c>
@@ -3599,17 +3809,23 @@
       <c r="J27">
         <v>9999999</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27">
+        <v>9999999</v>
+      </c>
+      <c r="L27">
+        <v>9999999</v>
+      </c>
+      <c r="M27" s="8">
         <v>1289170.3899999999</v>
       </c>
-      <c r="L27">
-        <v>9999999</v>
-      </c>
-      <c r="M27">
+      <c r="N27">
+        <v>9999999</v>
+      </c>
+      <c r="O27">
         <v>167732.98000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2050</v>
       </c>
@@ -3640,13 +3856,19 @@
       <c r="J28">
         <v>9999999</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28">
+        <v>9999999</v>
+      </c>
+      <c r="L28">
+        <v>9999999</v>
+      </c>
+      <c r="M28" s="8">
         <v>1289297.3500000001</v>
       </c>
-      <c r="L28">
-        <v>9999999</v>
-      </c>
-      <c r="M28">
+      <c r="N28">
+        <v>9999999</v>
+      </c>
+      <c r="O28">
         <v>164356.51999999999</v>
       </c>
     </row>
@@ -14043,7 +14265,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="A2" s="13">
         <v>2024</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -14057,7 +14279,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
+      <c r="A3" s="13"/>
       <c r="B3" s="11" t="s">
         <v>70</v>
       </c>
@@ -14070,7 +14292,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -14082,7 +14304,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
@@ -14094,7 +14316,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>2025</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -14108,7 +14330,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
@@ -14120,7 +14342,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
@@ -14132,7 +14354,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="11" t="s">
         <v>68</v>
       </c>
@@ -14145,7 +14367,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -14159,7 +14381,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
@@ -14171,7 +14393,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -14183,7 +14405,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -14196,7 +14418,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>2027</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -14210,7 +14432,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
+      <c r="A15" s="13"/>
       <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
@@ -14222,7 +14444,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
@@ -14234,7 +14456,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
+      <c r="A17" s="13"/>
       <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
@@ -14247,7 +14469,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>2028</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -14261,7 +14483,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
@@ -14273,7 +14495,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
@@ -14285,7 +14507,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
+      <c r="A21" s="13"/>
       <c r="B21" s="11" t="s">
         <v>68</v>
       </c>
@@ -14298,7 +14520,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+      <c r="A22" s="13">
         <v>2029</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -14312,7 +14534,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
+      <c r="A23" s="13"/>
       <c r="B23" s="11" t="s">
         <v>70</v>
       </c>
@@ -14324,7 +14546,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
+      <c r="A24" s="13"/>
       <c r="B24" s="11" t="s">
         <v>71</v>
       </c>
@@ -14336,7 +14558,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
+      <c r="A25" s="13"/>
       <c r="B25" s="11" t="s">
         <v>68</v>
       </c>
@@ -14349,7 +14571,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>2030</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -14363,7 +14585,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
+      <c r="A27" s="13"/>
       <c r="B27" s="11" t="s">
         <v>70</v>
       </c>
@@ -14375,7 +14597,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
+      <c r="A28" s="13"/>
       <c r="B28" s="11" t="s">
         <v>71</v>
       </c>
@@ -14387,7 +14609,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
+      <c r="A29" s="13"/>
       <c r="B29" s="11" t="s">
         <v>68</v>
       </c>
@@ -14400,7 +14622,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
+      <c r="A30" s="13">
         <v>2031</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -14414,7 +14636,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
+      <c r="A31" s="13"/>
       <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
@@ -14426,7 +14648,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="11" t="s">
         <v>71</v>
       </c>
@@ -14438,7 +14660,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
+      <c r="A33" s="13"/>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
@@ -14451,7 +14673,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
+      <c r="A34" s="13">
         <v>2032</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -14465,7 +14687,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
       <c r="B35" s="11" t="s">
         <v>70</v>
       </c>
@@ -14477,7 +14699,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
+      <c r="A36" s="13"/>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
@@ -14489,7 +14711,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
+      <c r="A37" s="13"/>
       <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
@@ -14502,7 +14724,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
+      <c r="A38" s="13">
         <v>2033</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -14516,7 +14738,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
+      <c r="A39" s="13"/>
       <c r="B39" s="11" t="s">
         <v>70</v>
       </c>
@@ -14528,7 +14750,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
+      <c r="A40" s="13"/>
       <c r="B40" s="11" t="s">
         <v>71</v>
       </c>
@@ -14540,7 +14762,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
+      <c r="A41" s="13"/>
       <c r="B41" s="11" t="s">
         <v>68</v>
       </c>
@@ -14553,7 +14775,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="12">
+      <c r="A42" s="13">
         <v>2034</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -14567,7 +14789,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
+      <c r="A43" s="13"/>
       <c r="B43" s="11" t="s">
         <v>70</v>
       </c>
@@ -14579,7 +14801,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
+      <c r="A44" s="13"/>
       <c r="B44" s="11" t="s">
         <v>71</v>
       </c>
@@ -14591,7 +14813,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
+      <c r="A45" s="13"/>
       <c r="B45" s="11" t="s">
         <v>68</v>
       </c>
@@ -14604,7 +14826,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
+      <c r="A46" s="13">
         <v>2035</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -14618,7 +14840,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+      <c r="A47" s="13"/>
       <c r="B47" s="11" t="s">
         <v>70</v>
       </c>
@@ -14630,7 +14852,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+      <c r="A48" s="13"/>
       <c r="B48" s="11" t="s">
         <v>71</v>
       </c>
@@ -14642,7 +14864,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+      <c r="A49" s="13"/>
       <c r="B49" s="11" t="s">
         <v>68</v>
       </c>
@@ -14655,7 +14877,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="12">
+      <c r="A50" s="13">
         <v>2036</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -14669,7 +14891,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+      <c r="A51" s="13"/>
       <c r="B51" s="11" t="s">
         <v>70</v>
       </c>
@@ -14681,7 +14903,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+      <c r="A52" s="13"/>
       <c r="B52" s="11" t="s">
         <v>71</v>
       </c>
@@ -14693,7 +14915,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="13"/>
       <c r="B53" s="11" t="s">
         <v>68</v>
       </c>
@@ -14706,7 +14928,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="12">
+      <c r="A54" s="13">
         <v>2037</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -14720,7 +14942,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+      <c r="A55" s="13"/>
       <c r="B55" s="11" t="s">
         <v>70</v>
       </c>
@@ -14732,7 +14954,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+      <c r="A56" s="13"/>
       <c r="B56" s="11" t="s">
         <v>71</v>
       </c>
@@ -14744,7 +14966,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+      <c r="A57" s="13"/>
       <c r="B57" s="11" t="s">
         <v>68</v>
       </c>
@@ -14757,7 +14979,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="12">
+      <c r="A58" s="13">
         <v>2038</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -14771,7 +14993,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+      <c r="A59" s="13"/>
       <c r="B59" s="11" t="s">
         <v>70</v>
       </c>
@@ -14783,7 +15005,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
+      <c r="A60" s="13"/>
       <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
@@ -14795,7 +15017,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+      <c r="A61" s="13"/>
       <c r="B61" s="11" t="s">
         <v>68</v>
       </c>
@@ -14808,7 +15030,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="12">
+      <c r="A62" s="13">
         <v>2039</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -14822,7 +15044,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
+      <c r="A63" s="13"/>
       <c r="B63" s="11" t="s">
         <v>70</v>
       </c>
@@ -14834,7 +15056,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
+      <c r="A64" s="13"/>
       <c r="B64" s="11" t="s">
         <v>71</v>
       </c>
@@ -14846,7 +15068,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
+      <c r="A65" s="13"/>
       <c r="B65" s="11" t="s">
         <v>68</v>
       </c>
@@ -14859,7 +15081,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="12">
+      <c r="A66" s="13">
         <v>2040</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -14873,7 +15095,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="12"/>
+      <c r="A67" s="13"/>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
@@ -14885,7 +15107,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="12"/>
+      <c r="A68" s="13"/>
       <c r="B68" s="11" t="s">
         <v>71</v>
       </c>
@@ -14897,7 +15119,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="12"/>
+      <c r="A69" s="13"/>
       <c r="B69" s="11" t="s">
         <v>68</v>
       </c>
@@ -14910,7 +15132,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="12">
+      <c r="A70" s="13">
         <v>2041</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -14924,7 +15146,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="12"/>
+      <c r="A71" s="13"/>
       <c r="B71" s="11" t="s">
         <v>70</v>
       </c>
@@ -14936,7 +15158,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="12"/>
+      <c r="A72" s="13"/>
       <c r="B72" s="11" t="s">
         <v>71</v>
       </c>
@@ -14948,7 +15170,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="12"/>
+      <c r="A73" s="13"/>
       <c r="B73" s="11" t="s">
         <v>68</v>
       </c>
@@ -14961,7 +15183,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="12">
+      <c r="A74" s="13">
         <v>2042</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -14975,7 +15197,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="12"/>
+      <c r="A75" s="13"/>
       <c r="B75" s="11" t="s">
         <v>70</v>
       </c>
@@ -14987,7 +15209,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="12"/>
+      <c r="A76" s="13"/>
       <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
@@ -14999,7 +15221,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="12"/>
+      <c r="A77" s="13"/>
       <c r="B77" s="11" t="s">
         <v>68</v>
       </c>
@@ -15012,7 +15234,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="12">
+      <c r="A78" s="13">
         <v>2043</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -15026,7 +15248,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="12"/>
+      <c r="A79" s="13"/>
       <c r="B79" s="11" t="s">
         <v>70</v>
       </c>
@@ -15038,7 +15260,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="12"/>
+      <c r="A80" s="13"/>
       <c r="B80" s="11" t="s">
         <v>71</v>
       </c>
@@ -15050,7 +15272,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="12"/>
+      <c r="A81" s="13"/>
       <c r="B81" s="11" t="s">
         <v>68</v>
       </c>
@@ -15063,7 +15285,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="12">
+      <c r="A82" s="13">
         <v>2044</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -15077,7 +15299,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="12"/>
+      <c r="A83" s="13"/>
       <c r="B83" s="11" t="s">
         <v>70</v>
       </c>
@@ -15089,7 +15311,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="12"/>
+      <c r="A84" s="13"/>
       <c r="B84" s="11" t="s">
         <v>71</v>
       </c>
@@ -15101,7 +15323,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="12"/>
+      <c r="A85" s="13"/>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
@@ -15114,7 +15336,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="12">
+      <c r="A86" s="13">
         <v>2045</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -15128,7 +15350,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="12"/>
+      <c r="A87" s="13"/>
       <c r="B87" s="11" t="s">
         <v>70</v>
       </c>
@@ -15140,7 +15362,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="12"/>
+      <c r="A88" s="13"/>
       <c r="B88" s="11" t="s">
         <v>71</v>
       </c>
@@ -15152,7 +15374,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="12"/>
+      <c r="A89" s="13"/>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
@@ -15165,7 +15387,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="12">
+      <c r="A90" s="13">
         <v>2046</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -15179,7 +15401,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="12"/>
+      <c r="A91" s="13"/>
       <c r="B91" s="11" t="s">
         <v>70</v>
       </c>
@@ -15191,7 +15413,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="12"/>
+      <c r="A92" s="13"/>
       <c r="B92" s="11" t="s">
         <v>71</v>
       </c>
@@ -15203,7 +15425,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="12"/>
+      <c r="A93" s="13"/>
       <c r="B93" s="11" t="s">
         <v>68</v>
       </c>
@@ -15216,7 +15438,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="12">
+      <c r="A94" s="13">
         <v>2047</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -15230,7 +15452,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="12"/>
+      <c r="A95" s="13"/>
       <c r="B95" s="11" t="s">
         <v>70</v>
       </c>
@@ -15242,7 +15464,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="12"/>
+      <c r="A96" s="13"/>
       <c r="B96" s="11" t="s">
         <v>71</v>
       </c>
@@ -15254,7 +15476,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="12"/>
+      <c r="A97" s="13"/>
       <c r="B97" s="11" t="s">
         <v>68</v>
       </c>
@@ -15267,7 +15489,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="12">
+      <c r="A98" s="13">
         <v>2048</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -15281,7 +15503,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="12"/>
+      <c r="A99" s="13"/>
       <c r="B99" s="11" t="s">
         <v>70</v>
       </c>
@@ -15293,7 +15515,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
+      <c r="A100" s="13"/>
       <c r="B100" s="11" t="s">
         <v>71</v>
       </c>
@@ -15305,7 +15527,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="12"/>
+      <c r="A101" s="13"/>
       <c r="B101" s="11" t="s">
         <v>68</v>
       </c>
@@ -15318,7 +15540,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="12">
+      <c r="A102" s="13">
         <v>2049</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -15332,7 +15554,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="12"/>
+      <c r="A103" s="13"/>
       <c r="B103" s="11" t="s">
         <v>70</v>
       </c>
@@ -15344,7 +15566,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="12"/>
+      <c r="A104" s="13"/>
       <c r="B104" s="11" t="s">
         <v>71</v>
       </c>
@@ -15356,7 +15578,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="12"/>
+      <c r="A105" s="13"/>
       <c r="B105" s="11" t="s">
         <v>68</v>
       </c>
@@ -15369,7 +15591,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="12">
+      <c r="A106" s="13">
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -15383,7 +15605,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="12"/>
+      <c r="A107" s="13"/>
       <c r="B107" s="11" t="s">
         <v>70</v>
       </c>
@@ -15395,7 +15617,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="12"/>
+      <c r="A108" s="13"/>
       <c r="B108" s="11" t="s">
         <v>71</v>
       </c>
@@ -15407,7 +15629,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="12"/>
+      <c r="A109" s="13"/>
       <c r="B109" s="11" t="s">
         <v>68</v>
       </c>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="403" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF8DBB7-6D38-454A-A4D6-ADC9D831B385}"/>
+  <xr:revisionPtr revIDLastSave="483" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A619CE2A-1920-42BB-88FA-2AAB6AD008B4}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="6" activeTab="13" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="7" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="153">
   <si>
     <t>Value</t>
   </si>
@@ -310,25 +310,10 @@
     <t>Material</t>
   </si>
   <si>
-    <t>Silicon</t>
-  </si>
-  <si>
-    <t>3.0</t>
-  </si>
-  <si>
     <t>0.95</t>
   </si>
   <si>
     <t>Cell</t>
-  </si>
-  <si>
-    <t>Silver</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>0.98</t>
   </si>
   <si>
     <t>Module</t>
@@ -337,34 +322,7 @@
     <t>Glass</t>
   </si>
   <si>
-    <t>40.0</t>
-  </si>
-  <si>
-    <t>38.0</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Aluminum</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
     <t>Blade</t>
-  </si>
-  <si>
-    <t>Composite</t>
-  </si>
-  <si>
-    <t>12.0</t>
-  </si>
-  <si>
-    <t>0.50</t>
   </si>
   <si>
     <t>Tower</t>
@@ -373,25 +331,7 @@
     <t>Steel</t>
   </si>
   <si>
-    <t>150.0</t>
-  </si>
-  <si>
     <t>Nacelle</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>RareEarth</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>0.80</t>
   </si>
   <si>
     <t>Batteries</t>
@@ -515,6 +455,63 @@
   </si>
   <si>
     <t>opex_fixed</t>
+  </si>
+  <si>
+    <t>Al</t>
+  </si>
+  <si>
+    <t>Polymers</t>
+  </si>
+  <si>
+    <t>Cu</t>
+  </si>
+  <si>
+    <t>Ag</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>CFRP</t>
+  </si>
+  <si>
+    <t>GFRP</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Zn</t>
+  </si>
+  <si>
+    <t>Dy</t>
+  </si>
+  <si>
+    <t>Nd</t>
+  </si>
+  <si>
+    <t>Pr</t>
+  </si>
+  <si>
+    <t>Cast iron</t>
+  </si>
+  <si>
+    <t>Mn</t>
+  </si>
+  <si>
+    <t>Mo</t>
+  </si>
+  <si>
+    <t>Ni</t>
+  </si>
+  <si>
+    <t>Cr</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>0.98</t>
   </si>
 </sst>
 </file>
@@ -695,7 +692,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -723,6 +720,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1120,7 +1120,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
         <v>82</v>
@@ -1135,7 +1135,7 @@
         <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="G1" t="s">
         <v>74</v>
@@ -1152,12 +1152,12 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="12">
         <v>150</v>
       </c>
       <c r="F2" s="7">
@@ -1175,13 +1175,13 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>100</v>
+      <c r="E3" s="12">
+        <v>125</v>
       </c>
       <c r="F3" s="7">
         <v>2000</v>
@@ -1198,13 +1198,13 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>100</v>
+      <c r="E4" s="12">
+        <v>76</v>
       </c>
       <c r="F4" s="7">
         <v>7000</v>
@@ -1221,13 +1221,13 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>100</v>
+      <c r="E5" s="12">
+        <v>75</v>
       </c>
       <c r="F5" s="7">
         <v>22000</v>
@@ -1247,15 +1247,15 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="12">
+        <v>60</v>
+      </c>
+      <c r="F6">
         <v>27000</v>
       </c>
       <c r="G6">
@@ -1273,15 +1273,15 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="12">
+        <v>55</v>
+      </c>
+      <c r="F7">
         <v>27000</v>
       </c>
       <c r="G7">
@@ -1299,15 +1299,15 @@
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="12">
+        <v>35</v>
+      </c>
+      <c r="F8">
         <v>27000</v>
       </c>
       <c r="G8">
@@ -1325,22 +1325,22 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
         <v>999999</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1351,13 +1351,13 @@
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10">
-        <v>100</v>
+      <c r="E10" s="12">
+        <v>60</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -1377,15 +1377,15 @@
         <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="12">
+        <v>55</v>
+      </c>
+      <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
@@ -1400,12 +1400,12 @@
         <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7">
+        <v>92</v>
+      </c>
+      <c r="E12" s="12">
+        <v>35</v>
+      </c>
+      <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
@@ -1420,15 +1420,15 @@
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13">
-        <v>100</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
         <v>999999</v>
       </c>
       <c r="G13">
@@ -1440,16 +1440,16 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14">
-        <v>80</v>
+      <c r="E14" s="12">
+        <v>40</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -1463,25 +1463,25 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="E15">
-        <v>20</v>
-      </c>
-      <c r="F15">
-        <v>100</v>
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <v>999999</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1492,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA1A697-84AA-4F97-BE70-81695B57512E}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1506,296 +1506,817 @@
         <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="F1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="E2" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="12">
+        <v>46.4</v>
+      </c>
+      <c r="E3" s="12">
+        <v>46.4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="12">
+        <v>8.6000000000000014</v>
+      </c>
+      <c r="E4" s="12">
+        <v>8.6000000000000014</v>
+      </c>
+      <c r="F4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E5" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1.9012500000000002E-2</v>
+      </c>
+      <c r="E6" s="12">
+        <v>1.9012500000000002E-2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="12">
+        <v>3.803015625</v>
+      </c>
+      <c r="E7" s="12">
+        <v>3.803015625</v>
+      </c>
+      <c r="F7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0.94859999999999989</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0.94859999999999989</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="12">
+        <v>6.9563999999999995</v>
+      </c>
+      <c r="E9" s="12">
+        <v>6.9563999999999995</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1.17E-3</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1.17E-3</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="12">
+        <v>8.1</v>
+      </c>
+      <c r="E11" s="12">
+        <v>8.1</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="12">
+        <v>114.72499999999999</v>
+      </c>
+      <c r="E12" s="12">
+        <v>114.72499999999999</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="E13" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="12">
+        <v>5.47E-3</v>
+      </c>
+      <c r="E14" s="12">
+        <v>5.47E-3</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="12">
+        <v>4.7689999999999996E-2</v>
+      </c>
+      <c r="E15" s="12">
+        <v>4.7689999999999996E-2</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D16" s="12">
+        <v>7.2699999999999996E-3</v>
+      </c>
+      <c r="E16" s="12">
+        <v>7.2699999999999996E-3</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="12">
+        <v>2.7909999999999999</v>
+      </c>
+      <c r="E17" s="12">
+        <v>2.7909999999999999</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="12">
+        <v>2.2925</v>
+      </c>
+      <c r="E18" s="12">
+        <v>2.2925</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="12">
+        <v>18.945</v>
+      </c>
+      <c r="E19" s="12">
+        <v>18.945</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="12">
+        <v>0.78549999999999998</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0.78549999999999998</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.1045</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0.1045</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="12">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="12">
+        <v>0.50024999999999997</v>
+      </c>
+      <c r="E23" s="12">
+        <v>0.50024999999999997</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="12">
+        <v>0.97139999999999993</v>
+      </c>
+      <c r="E24" s="12">
+        <v>0.97139999999999993</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="12">
+        <v>7.1236000000000006</v>
+      </c>
+      <c r="E25" s="12">
+        <v>7.1236000000000006</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="12">
+        <v>3.4500000000000004E-3</v>
+      </c>
+      <c r="E26" s="12">
+        <v>3.4500000000000004E-3</v>
+      </c>
+      <c r="F26" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="E27" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="F27" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C28" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="12">
+        <v>116.77</v>
+      </c>
+      <c r="E28" s="12">
+        <v>116.77</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="E29" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="12">
+        <v>1.1259999999999999E-2</v>
+      </c>
+      <c r="E30" s="12">
+        <v>1.1259999999999999E-2</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="12">
+        <v>0.11219</v>
+      </c>
+      <c r="E31" s="12">
+        <v>0.11219</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="12">
+        <v>2.0460000000000002E-2</v>
+      </c>
+      <c r="E32" s="12">
+        <v>2.0460000000000002E-2</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="12">
+        <v>4.04</v>
+      </c>
+      <c r="E33" s="12">
+        <v>4.04</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="12">
+        <v>3.2574999999999998</v>
+      </c>
+      <c r="E34" s="12">
+        <v>3.2574999999999998</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" s="12">
+        <v>19.89</v>
+      </c>
+      <c r="E35" s="12">
+        <v>19.89</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" s="12">
+        <v>0.79039999999999999</v>
+      </c>
+      <c r="E36" s="12">
+        <v>0.79039999999999999</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="12">
+        <v>0.10940000000000001</v>
+      </c>
+      <c r="E37" s="12">
+        <v>0.10940000000000001</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="12">
+        <v>0.32230000000000003</v>
+      </c>
+      <c r="E38" s="12">
+        <v>0.32230000000000003</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="12">
+        <v>0.5272</v>
+      </c>
+      <c r="E39" s="12">
+        <v>0.5272</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" t="s">
         <v>86</v>
       </c>
-      <c r="F2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" t="s">
+        <v>95</v>
+      </c>
+      <c r="F40" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>93</v>
       </c>
-      <c r="D4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="B41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D41" t="s">
         <v>97</v>
       </c>
-      <c r="D5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" t="s">
-        <v>96</v>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1803,24 +2324,24 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BB5A9E-0DE2-4C9D-A6F4-EBF765E41A9E}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
         <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1828,7 +2349,7 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -1845,7 +2366,7 @@
         <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3">
         <v>5000</v>
@@ -1862,7 +2383,7 @@
         <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="C4">
         <v>5000000</v>
@@ -1879,7 +2400,7 @@
         <v>2024</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="C5">
         <v>2000000</v>
@@ -1896,7 +2417,7 @@
         <v>2024</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>500000</v>
@@ -1913,7 +2434,7 @@
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>10000000</v>
@@ -1930,7 +2451,7 @@
         <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="C8">
         <v>800000</v>
@@ -1947,7 +2468,7 @@
         <v>2024</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C9">
         <v>20000</v>
@@ -1964,7 +2485,7 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C10">
         <v>150000</v>
@@ -1981,15 +2502,253 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C11">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="D11">
         <v>30000</v>
       </c>
       <c r="E11">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12">
+        <v>150000</v>
+      </c>
+      <c r="D12">
+        <v>30000</v>
+      </c>
+      <c r="E12">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2024</v>
+      </c>
+      <c r="B13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13">
+        <v>150000</v>
+      </c>
+      <c r="D13">
+        <v>30000</v>
+      </c>
+      <c r="E13">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2024</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14">
+        <v>150000</v>
+      </c>
+      <c r="D14">
+        <v>30000</v>
+      </c>
+      <c r="E14">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2024</v>
+      </c>
+      <c r="B15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15">
+        <v>150000</v>
+      </c>
+      <c r="D15">
+        <v>30000</v>
+      </c>
+      <c r="E15">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16">
+        <v>150000</v>
+      </c>
+      <c r="D16">
+        <v>30000</v>
+      </c>
+      <c r="E16">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2024</v>
+      </c>
+      <c r="B17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17">
+        <v>150000</v>
+      </c>
+      <c r="D17">
+        <v>30000</v>
+      </c>
+      <c r="E17">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2024</v>
+      </c>
+      <c r="B18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18">
+        <v>150000</v>
+      </c>
+      <c r="D18">
+        <v>30000</v>
+      </c>
+      <c r="E18">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2024</v>
+      </c>
+      <c r="B19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19">
+        <v>150000</v>
+      </c>
+      <c r="D19">
+        <v>30000</v>
+      </c>
+      <c r="E19">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2024</v>
+      </c>
+      <c r="B20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20">
+        <v>150000</v>
+      </c>
+      <c r="D20">
+        <v>30000</v>
+      </c>
+      <c r="E20">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2024</v>
+      </c>
+      <c r="B21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21">
+        <v>150000</v>
+      </c>
+      <c r="D21">
+        <v>30000</v>
+      </c>
+      <c r="E21">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2024</v>
+      </c>
+      <c r="B22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22">
+        <v>150000</v>
+      </c>
+      <c r="D22">
+        <v>30000</v>
+      </c>
+      <c r="E22">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2024</v>
+      </c>
+      <c r="B23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23">
+        <v>150000</v>
+      </c>
+      <c r="D23">
+        <v>30000</v>
+      </c>
+      <c r="E23">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2024</v>
+      </c>
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24">
+        <v>150000</v>
+      </c>
+      <c r="D24">
+        <v>30000</v>
+      </c>
+      <c r="E24">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25">
+        <v>150000</v>
+      </c>
+      <c r="D25">
+        <v>30000</v>
+      </c>
+      <c r="E25">
         <v>35000</v>
       </c>
     </row>
@@ -2005,19 +2764,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E1" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2025,16 +2784,16 @@
         <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2042,16 +2801,16 @@
         <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2059,33 +2818,33 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
         <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2093,16 +2852,16 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
         <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2110,16 +2869,16 @@
         <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2127,16 +2886,16 @@
         <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2144,16 +2903,16 @@
         <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
         <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2161,16 +2920,16 @@
         <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2178,16 +2937,16 @@
         <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2202,10 +2961,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
         <v>82</v>
@@ -2214,13 +2973,13 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="G1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -2234,7 +2993,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="E2" s="12">
         <v>55200</v>
@@ -2257,7 +3016,7 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E3" s="12">
         <v>92000</v>
@@ -2280,7 +3039,7 @@
         <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" s="12">
         <v>165600</v>
@@ -2303,7 +3062,7 @@
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E5" s="12">
         <v>46000</v>
@@ -2326,7 +3085,7 @@
         <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E6" s="12">
         <v>73600</v>
@@ -2349,7 +3108,7 @@
         <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E7" s="12">
         <v>82800</v>
@@ -2372,7 +3131,7 @@
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E8" s="12">
         <v>276000</v>
@@ -2395,7 +3154,7 @@
         <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
@@ -2418,7 +3177,7 @@
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E10" s="12">
         <v>165600</v>
@@ -2441,7 +3200,7 @@
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E11" s="12">
         <v>202400</v>
@@ -2464,7 +3223,7 @@
         <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E12" s="12">
         <v>202400</v>
@@ -2487,7 +3246,7 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E13" s="12">
         <v>1</v>
@@ -2507,10 +3266,10 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E14" s="12">
         <v>92000</v>
@@ -2530,10 +3289,10 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E15" s="12">
         <v>1</v>
@@ -2561,46 +3320,46 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="D1" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="F1" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="G1" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H1" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I1" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="J1" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="K1" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="L1" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="M1" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="N1" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="O1" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -14265,7 +15024,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>2024</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -14279,7 +15038,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
+      <c r="A3" s="14"/>
       <c r="B3" s="11" t="s">
         <v>70</v>
       </c>
@@ -14292,7 +15051,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
+      <c r="A4" s="14"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -14304,7 +15063,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
+      <c r="A5" s="14"/>
       <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
@@ -14316,7 +15075,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>2025</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -14330,7 +15089,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
+      <c r="A7" s="14"/>
       <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
@@ -14342,7 +15101,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
@@ -14354,7 +15113,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="11" t="s">
         <v>68</v>
       </c>
@@ -14367,7 +15126,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -14381,7 +15140,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
@@ -14393,7 +15152,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -14405,7 +15164,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -14418,7 +15177,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>2027</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -14432,7 +15191,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
@@ -14444,7 +15203,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
@@ -14456,7 +15215,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="14"/>
       <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
@@ -14469,7 +15228,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>2028</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -14483,7 +15242,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
@@ -14495,7 +15254,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="14"/>
       <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
@@ -14507,7 +15266,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="14"/>
       <c r="B21" s="11" t="s">
         <v>68</v>
       </c>
@@ -14520,7 +15279,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>2029</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -14534,7 +15293,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
+      <c r="A23" s="14"/>
       <c r="B23" s="11" t="s">
         <v>70</v>
       </c>
@@ -14546,7 +15305,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
+      <c r="A24" s="14"/>
       <c r="B24" s="11" t="s">
         <v>71</v>
       </c>
@@ -14558,7 +15317,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="11" t="s">
         <v>68</v>
       </c>
@@ -14571,7 +15330,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>2030</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -14585,7 +15344,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
+      <c r="A27" s="14"/>
       <c r="B27" s="11" t="s">
         <v>70</v>
       </c>
@@ -14597,7 +15356,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+      <c r="A28" s="14"/>
       <c r="B28" s="11" t="s">
         <v>71</v>
       </c>
@@ -14609,7 +15368,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
+      <c r="A29" s="14"/>
       <c r="B29" s="11" t="s">
         <v>68</v>
       </c>
@@ -14622,7 +15381,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="13">
+      <c r="A30" s="14">
         <v>2031</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -14636,7 +15395,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="A31" s="14"/>
       <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
@@ -14648,7 +15407,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
+      <c r="A32" s="14"/>
       <c r="B32" s="11" t="s">
         <v>71</v>
       </c>
@@ -14660,7 +15419,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
+      <c r="A33" s="14"/>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
@@ -14673,7 +15432,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="13">
+      <c r="A34" s="14">
         <v>2032</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -14687,7 +15446,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
+      <c r="A35" s="14"/>
       <c r="B35" s="11" t="s">
         <v>70</v>
       </c>
@@ -14699,7 +15458,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="13"/>
+      <c r="A36" s="14"/>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
@@ -14711,7 +15470,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="13"/>
+      <c r="A37" s="14"/>
       <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
@@ -14724,7 +15483,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="13">
+      <c r="A38" s="14">
         <v>2033</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -14738,7 +15497,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="13"/>
+      <c r="A39" s="14"/>
       <c r="B39" s="11" t="s">
         <v>70</v>
       </c>
@@ -14750,7 +15509,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="13"/>
+      <c r="A40" s="14"/>
       <c r="B40" s="11" t="s">
         <v>71</v>
       </c>
@@ -14762,7 +15521,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
+      <c r="A41" s="14"/>
       <c r="B41" s="11" t="s">
         <v>68</v>
       </c>
@@ -14775,7 +15534,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="13">
+      <c r="A42" s="14">
         <v>2034</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -14789,7 +15548,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
+      <c r="A43" s="14"/>
       <c r="B43" s="11" t="s">
         <v>70</v>
       </c>
@@ -14801,7 +15560,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
+      <c r="A44" s="14"/>
       <c r="B44" s="11" t="s">
         <v>71</v>
       </c>
@@ -14813,7 +15572,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="13"/>
+      <c r="A45" s="14"/>
       <c r="B45" s="11" t="s">
         <v>68</v>
       </c>
@@ -14826,7 +15585,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="13">
+      <c r="A46" s="14">
         <v>2035</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -14840,7 +15599,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="13"/>
+      <c r="A47" s="14"/>
       <c r="B47" s="11" t="s">
         <v>70</v>
       </c>
@@ -14852,7 +15611,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="13"/>
+      <c r="A48" s="14"/>
       <c r="B48" s="11" t="s">
         <v>71</v>
       </c>
@@ -14864,7 +15623,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="13"/>
+      <c r="A49" s="14"/>
       <c r="B49" s="11" t="s">
         <v>68</v>
       </c>
@@ -14877,7 +15636,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
+      <c r="A50" s="14">
         <v>2036</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -14891,7 +15650,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
+      <c r="A51" s="14"/>
       <c r="B51" s="11" t="s">
         <v>70</v>
       </c>
@@ -14903,7 +15662,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
+      <c r="A52" s="14"/>
       <c r="B52" s="11" t="s">
         <v>71</v>
       </c>
@@ -14915,7 +15674,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
+      <c r="A53" s="14"/>
       <c r="B53" s="11" t="s">
         <v>68</v>
       </c>
@@ -14928,7 +15687,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="13">
+      <c r="A54" s="14">
         <v>2037</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -14942,7 +15701,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
+      <c r="A55" s="14"/>
       <c r="B55" s="11" t="s">
         <v>70</v>
       </c>
@@ -14954,7 +15713,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
+      <c r="A56" s="14"/>
       <c r="B56" s="11" t="s">
         <v>71</v>
       </c>
@@ -14966,7 +15725,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
+      <c r="A57" s="14"/>
       <c r="B57" s="11" t="s">
         <v>68</v>
       </c>
@@ -14979,7 +15738,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="13">
+      <c r="A58" s="14">
         <v>2038</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -14993,7 +15752,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
+      <c r="A59" s="14"/>
       <c r="B59" s="11" t="s">
         <v>70</v>
       </c>
@@ -15005,7 +15764,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="13"/>
+      <c r="A60" s="14"/>
       <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
@@ -15017,7 +15776,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
+      <c r="A61" s="14"/>
       <c r="B61" s="11" t="s">
         <v>68</v>
       </c>
@@ -15030,7 +15789,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="13">
+      <c r="A62" s="14">
         <v>2039</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -15044,7 +15803,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
+      <c r="A63" s="14"/>
       <c r="B63" s="11" t="s">
         <v>70</v>
       </c>
@@ -15056,7 +15815,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="13"/>
+      <c r="A64" s="14"/>
       <c r="B64" s="11" t="s">
         <v>71</v>
       </c>
@@ -15068,7 +15827,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
+      <c r="A65" s="14"/>
       <c r="B65" s="11" t="s">
         <v>68</v>
       </c>
@@ -15081,7 +15840,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="13">
+      <c r="A66" s="14">
         <v>2040</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -15095,7 +15854,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
+      <c r="A67" s="14"/>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
@@ -15107,7 +15866,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="13"/>
+      <c r="A68" s="14"/>
       <c r="B68" s="11" t="s">
         <v>71</v>
       </c>
@@ -15119,7 +15878,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
+      <c r="A69" s="14"/>
       <c r="B69" s="11" t="s">
         <v>68</v>
       </c>
@@ -15132,7 +15891,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="13">
+      <c r="A70" s="14">
         <v>2041</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -15146,7 +15905,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
+      <c r="A71" s="14"/>
       <c r="B71" s="11" t="s">
         <v>70</v>
       </c>
@@ -15158,7 +15917,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
+      <c r="A72" s="14"/>
       <c r="B72" s="11" t="s">
         <v>71</v>
       </c>
@@ -15170,7 +15929,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
+      <c r="A73" s="14"/>
       <c r="B73" s="11" t="s">
         <v>68</v>
       </c>
@@ -15183,7 +15942,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="13">
+      <c r="A74" s="14">
         <v>2042</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -15197,7 +15956,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
+      <c r="A75" s="14"/>
       <c r="B75" s="11" t="s">
         <v>70</v>
       </c>
@@ -15209,7 +15968,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
+      <c r="A76" s="14"/>
       <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
@@ -15221,7 +15980,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
+      <c r="A77" s="14"/>
       <c r="B77" s="11" t="s">
         <v>68</v>
       </c>
@@ -15234,7 +15993,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="13">
+      <c r="A78" s="14">
         <v>2043</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -15248,7 +16007,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
+      <c r="A79" s="14"/>
       <c r="B79" s="11" t="s">
         <v>70</v>
       </c>
@@ -15260,7 +16019,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
+      <c r="A80" s="14"/>
       <c r="B80" s="11" t="s">
         <v>71</v>
       </c>
@@ -15272,7 +16031,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
+      <c r="A81" s="14"/>
       <c r="B81" s="11" t="s">
         <v>68</v>
       </c>
@@ -15285,7 +16044,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="13">
+      <c r="A82" s="14">
         <v>2044</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -15299,7 +16058,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
+      <c r="A83" s="14"/>
       <c r="B83" s="11" t="s">
         <v>70</v>
       </c>
@@ -15311,7 +16070,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
+      <c r="A84" s="14"/>
       <c r="B84" s="11" t="s">
         <v>71</v>
       </c>
@@ -15323,7 +16082,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
+      <c r="A85" s="14"/>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
@@ -15336,7 +16095,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="13">
+      <c r="A86" s="14">
         <v>2045</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -15350,7 +16109,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
+      <c r="A87" s="14"/>
       <c r="B87" s="11" t="s">
         <v>70</v>
       </c>
@@ -15362,7 +16121,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
+      <c r="A88" s="14"/>
       <c r="B88" s="11" t="s">
         <v>71</v>
       </c>
@@ -15374,7 +16133,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="13"/>
+      <c r="A89" s="14"/>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
@@ -15387,7 +16146,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="13">
+      <c r="A90" s="14">
         <v>2046</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -15401,7 +16160,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="13"/>
+      <c r="A91" s="14"/>
       <c r="B91" s="11" t="s">
         <v>70</v>
       </c>
@@ -15413,7 +16172,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="13"/>
+      <c r="A92" s="14"/>
       <c r="B92" s="11" t="s">
         <v>71</v>
       </c>
@@ -15425,7 +16184,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="13"/>
+      <c r="A93" s="14"/>
       <c r="B93" s="11" t="s">
         <v>68</v>
       </c>
@@ -15438,7 +16197,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="13">
+      <c r="A94" s="14">
         <v>2047</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -15452,7 +16211,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="13"/>
+      <c r="A95" s="14"/>
       <c r="B95" s="11" t="s">
         <v>70</v>
       </c>
@@ -15464,7 +16223,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="13"/>
+      <c r="A96" s="14"/>
       <c r="B96" s="11" t="s">
         <v>71</v>
       </c>
@@ -15476,7 +16235,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="13"/>
+      <c r="A97" s="14"/>
       <c r="B97" s="11" t="s">
         <v>68</v>
       </c>
@@ -15489,7 +16248,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="13">
+      <c r="A98" s="14">
         <v>2048</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -15503,7 +16262,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="13"/>
+      <c r="A99" s="14"/>
       <c r="B99" s="11" t="s">
         <v>70</v>
       </c>
@@ -15515,7 +16274,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="13"/>
+      <c r="A100" s="14"/>
       <c r="B100" s="11" t="s">
         <v>71</v>
       </c>
@@ -15527,7 +16286,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="13"/>
+      <c r="A101" s="14"/>
       <c r="B101" s="11" t="s">
         <v>68</v>
       </c>
@@ -15540,7 +16299,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="13">
+      <c r="A102" s="14">
         <v>2049</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -15554,7 +16313,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="13"/>
+      <c r="A103" s="14"/>
       <c r="B103" s="11" t="s">
         <v>70</v>
       </c>
@@ -15566,7 +16325,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="13"/>
+      <c r="A104" s="14"/>
       <c r="B104" s="11" t="s">
         <v>71</v>
       </c>
@@ -15578,7 +16337,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="13"/>
+      <c r="A105" s="14"/>
       <c r="B105" s="11" t="s">
         <v>68</v>
       </c>
@@ -15591,7 +16350,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="13">
+      <c r="A106" s="14">
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -15605,7 +16364,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="13"/>
+      <c r="A107" s="14"/>
       <c r="B107" s="11" t="s">
         <v>70</v>
       </c>
@@ -15617,7 +16376,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="13"/>
+      <c r="A108" s="14"/>
       <c r="B108" s="11" t="s">
         <v>71</v>
       </c>
@@ -15629,7 +16388,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="13"/>
+      <c r="A109" s="14"/>
       <c r="B109" s="11" t="s">
         <v>68</v>
       </c>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="483" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A619CE2A-1920-42BB-88FA-2AAB6AD008B4}"/>
+  <xr:revisionPtr revIDLastSave="527" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53855C72-BC49-44AD-93CD-BB20AB1B0FC3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="7" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="8" activeTab="12" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -25,9 +25,12 @@
     <sheet name="Tech_Stage_Specs" sheetId="14" r:id="rId10"/>
     <sheet name="Material_Intensity" sheetId="15" r:id="rId11"/>
     <sheet name="Material_Market" sheetId="17" r:id="rId12"/>
-    <sheet name="Component_Map" sheetId="18" r:id="rId13"/>
-    <sheet name="Cost_Data" sheetId="16" r:id="rId14"/>
-    <sheet name="Import_Cost_Stage" sheetId="19" r:id="rId15"/>
+    <sheet name="mining_limit" sheetId="20" r:id="rId13"/>
+    <sheet name="mining_cost" sheetId="21" r:id="rId14"/>
+    <sheet name="import_cost_mining" sheetId="22" r:id="rId15"/>
+    <sheet name="Component_Map" sheetId="18" r:id="rId16"/>
+    <sheet name="Cost_Data" sheetId="16" r:id="rId17"/>
+    <sheet name="Import_Cost_Stage" sheetId="19" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
@@ -53,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="153">
   <si>
     <t>Value</t>
   </si>
@@ -522,7 +525,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,8 +578,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -616,6 +624,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,7 +706,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -723,7 +737,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -750,10 +770,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2324,7 +2340,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BB5A9E-0DE2-4C9D-A6F4-EBF765E41A9E}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2349,16 +2365,16 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="C2">
-        <v>1000000</v>
+        <v>5000</v>
       </c>
       <c r="D2">
-        <v>1800</v>
+        <v>650000</v>
       </c>
       <c r="E2">
-        <v>2200</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2366,16 +2382,16 @@
         <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="C3">
-        <v>5000</v>
+        <v>5000000</v>
       </c>
       <c r="D3">
-        <v>650000</v>
+        <v>100</v>
       </c>
       <c r="E3">
-        <v>700000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2383,16 +2399,16 @@
         <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C4">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="E4">
-        <v>150</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2400,16 +2416,16 @@
         <v>2024</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C5">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
       <c r="D5">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="E5">
-        <v>2500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2417,16 +2433,16 @@
         <v>2024</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C6">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="D6">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="E6">
-        <v>3500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2434,16 +2450,16 @@
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C7">
-        <v>10000000</v>
+        <v>20000</v>
       </c>
       <c r="D7">
-        <v>600</v>
+        <v>40000</v>
       </c>
       <c r="E7">
-        <v>800</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2451,16 +2467,16 @@
         <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C8">
-        <v>800000</v>
+        <v>150000</v>
       </c>
       <c r="D8">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="E8">
-        <v>9500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2468,16 +2484,16 @@
         <v>2024</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="C9">
-        <v>20000</v>
+        <v>150000</v>
       </c>
       <c r="D9">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="E9">
-        <v>50000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2485,16 +2501,16 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C10">
         <v>150000</v>
       </c>
       <c r="D10">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="E10">
-        <v>18000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2502,7 +2518,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C11">
         <v>150000</v>
@@ -2519,7 +2535,7 @@
         <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="C12">
         <v>150000</v>
@@ -2536,7 +2552,7 @@
         <v>2024</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C13">
         <v>150000</v>
@@ -2553,7 +2569,7 @@
         <v>2024</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C14">
         <v>150000</v>
@@ -2570,7 +2586,7 @@
         <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C15">
         <v>150000</v>
@@ -2587,7 +2603,7 @@
         <v>2024</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C16">
         <v>150000</v>
@@ -2604,7 +2620,7 @@
         <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C17">
         <v>150000</v>
@@ -2621,7 +2637,7 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C18">
         <v>150000</v>
@@ -2638,7 +2654,7 @@
         <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C19">
         <v>150000</v>
@@ -2655,7 +2671,7 @@
         <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C20">
         <v>150000</v>
@@ -2672,7 +2688,7 @@
         <v>2024</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="C21">
         <v>150000</v>
@@ -2689,7 +2705,7 @@
         <v>2024</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="C22">
         <v>150000</v>
@@ -2698,57 +2714,6 @@
         <v>30000</v>
       </c>
       <c r="E22">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2024</v>
-      </c>
-      <c r="B23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23">
-        <v>150000</v>
-      </c>
-      <c r="D23">
-        <v>30000</v>
-      </c>
-      <c r="E23">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2024</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24">
-        <v>150000</v>
-      </c>
-      <c r="D24">
-        <v>30000</v>
-      </c>
-      <c r="E24">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2024</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25">
-        <v>150000</v>
-      </c>
-      <c r="D25">
-        <v>30000</v>
-      </c>
-      <c r="E25">
         <v>35000</v>
       </c>
     </row>
@@ -2758,6 +2723,5748 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA468E9E-004D-4F86-817A-29F43A769A51}">
+  <dimension ref="A1:V28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="16">
+        <v>2024</v>
+      </c>
+      <c r="B2">
+        <v>5000</v>
+      </c>
+      <c r="C2">
+        <v>5000000</v>
+      </c>
+      <c r="D2">
+        <v>500000</v>
+      </c>
+      <c r="E2">
+        <v>10000000</v>
+      </c>
+      <c r="F2">
+        <v>800000</v>
+      </c>
+      <c r="G2">
+        <v>20000</v>
+      </c>
+      <c r="H2">
+        <v>150000</v>
+      </c>
+      <c r="I2">
+        <v>150000</v>
+      </c>
+      <c r="J2">
+        <v>150000</v>
+      </c>
+      <c r="K2">
+        <v>150000</v>
+      </c>
+      <c r="L2">
+        <v>150000</v>
+      </c>
+      <c r="M2">
+        <v>150000</v>
+      </c>
+      <c r="N2">
+        <v>150000</v>
+      </c>
+      <c r="O2">
+        <v>150000</v>
+      </c>
+      <c r="P2">
+        <v>150000</v>
+      </c>
+      <c r="Q2">
+        <v>150000</v>
+      </c>
+      <c r="R2">
+        <v>150000</v>
+      </c>
+      <c r="S2">
+        <v>150000</v>
+      </c>
+      <c r="T2">
+        <v>150000</v>
+      </c>
+      <c r="U2">
+        <v>150000</v>
+      </c>
+      <c r="V2">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>5000</v>
+      </c>
+      <c r="C3">
+        <v>5000000</v>
+      </c>
+      <c r="D3">
+        <v>500000</v>
+      </c>
+      <c r="E3">
+        <v>10000000</v>
+      </c>
+      <c r="F3">
+        <v>800000</v>
+      </c>
+      <c r="G3">
+        <v>20000</v>
+      </c>
+      <c r="H3">
+        <v>150000</v>
+      </c>
+      <c r="I3">
+        <v>150000</v>
+      </c>
+      <c r="J3">
+        <v>150000</v>
+      </c>
+      <c r="K3">
+        <v>150000</v>
+      </c>
+      <c r="L3">
+        <v>150000</v>
+      </c>
+      <c r="M3">
+        <v>150000</v>
+      </c>
+      <c r="N3">
+        <v>150000</v>
+      </c>
+      <c r="O3">
+        <v>150000</v>
+      </c>
+      <c r="P3">
+        <v>150000</v>
+      </c>
+      <c r="Q3">
+        <v>150000</v>
+      </c>
+      <c r="R3">
+        <v>150000</v>
+      </c>
+      <c r="S3">
+        <v>150000</v>
+      </c>
+      <c r="T3">
+        <v>150000</v>
+      </c>
+      <c r="U3">
+        <v>150000</v>
+      </c>
+      <c r="V3">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>5000</v>
+      </c>
+      <c r="C4">
+        <v>5000000</v>
+      </c>
+      <c r="D4">
+        <v>500000</v>
+      </c>
+      <c r="E4">
+        <v>10000000</v>
+      </c>
+      <c r="F4">
+        <v>800000</v>
+      </c>
+      <c r="G4">
+        <v>20000</v>
+      </c>
+      <c r="H4">
+        <v>150000</v>
+      </c>
+      <c r="I4">
+        <v>150000</v>
+      </c>
+      <c r="J4">
+        <v>150000</v>
+      </c>
+      <c r="K4">
+        <v>150000</v>
+      </c>
+      <c r="L4">
+        <v>150000</v>
+      </c>
+      <c r="M4">
+        <v>150000</v>
+      </c>
+      <c r="N4">
+        <v>150000</v>
+      </c>
+      <c r="O4">
+        <v>150000</v>
+      </c>
+      <c r="P4">
+        <v>150000</v>
+      </c>
+      <c r="Q4">
+        <v>150000</v>
+      </c>
+      <c r="R4">
+        <v>150000</v>
+      </c>
+      <c r="S4">
+        <v>150000</v>
+      </c>
+      <c r="T4">
+        <v>150000</v>
+      </c>
+      <c r="U4">
+        <v>150000</v>
+      </c>
+      <c r="V4">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B5">
+        <v>5000</v>
+      </c>
+      <c r="C5">
+        <v>5000000</v>
+      </c>
+      <c r="D5">
+        <v>500000</v>
+      </c>
+      <c r="E5">
+        <v>10000000</v>
+      </c>
+      <c r="F5">
+        <v>800000</v>
+      </c>
+      <c r="G5">
+        <v>20000</v>
+      </c>
+      <c r="H5">
+        <v>150000</v>
+      </c>
+      <c r="I5">
+        <v>150000</v>
+      </c>
+      <c r="J5">
+        <v>150000</v>
+      </c>
+      <c r="K5">
+        <v>150000</v>
+      </c>
+      <c r="L5">
+        <v>150000</v>
+      </c>
+      <c r="M5">
+        <v>150000</v>
+      </c>
+      <c r="N5">
+        <v>150000</v>
+      </c>
+      <c r="O5">
+        <v>150000</v>
+      </c>
+      <c r="P5">
+        <v>150000</v>
+      </c>
+      <c r="Q5">
+        <v>150000</v>
+      </c>
+      <c r="R5">
+        <v>150000</v>
+      </c>
+      <c r="S5">
+        <v>150000</v>
+      </c>
+      <c r="T5">
+        <v>150000</v>
+      </c>
+      <c r="U5">
+        <v>150000</v>
+      </c>
+      <c r="V5">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>2028</v>
+      </c>
+      <c r="B6">
+        <v>5000</v>
+      </c>
+      <c r="C6">
+        <v>5000000</v>
+      </c>
+      <c r="D6">
+        <v>500000</v>
+      </c>
+      <c r="E6">
+        <v>10000000</v>
+      </c>
+      <c r="F6">
+        <v>800000</v>
+      </c>
+      <c r="G6">
+        <v>20000</v>
+      </c>
+      <c r="H6">
+        <v>150000</v>
+      </c>
+      <c r="I6">
+        <v>150000</v>
+      </c>
+      <c r="J6">
+        <v>150000</v>
+      </c>
+      <c r="K6">
+        <v>150000</v>
+      </c>
+      <c r="L6">
+        <v>150000</v>
+      </c>
+      <c r="M6">
+        <v>150000</v>
+      </c>
+      <c r="N6">
+        <v>150000</v>
+      </c>
+      <c r="O6">
+        <v>150000</v>
+      </c>
+      <c r="P6">
+        <v>150000</v>
+      </c>
+      <c r="Q6">
+        <v>150000</v>
+      </c>
+      <c r="R6">
+        <v>150000</v>
+      </c>
+      <c r="S6">
+        <v>150000</v>
+      </c>
+      <c r="T6">
+        <v>150000</v>
+      </c>
+      <c r="U6">
+        <v>150000</v>
+      </c>
+      <c r="V6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>2029</v>
+      </c>
+      <c r="B7">
+        <v>5000</v>
+      </c>
+      <c r="C7">
+        <v>5000000</v>
+      </c>
+      <c r="D7">
+        <v>500000</v>
+      </c>
+      <c r="E7">
+        <v>10000000</v>
+      </c>
+      <c r="F7">
+        <v>800000</v>
+      </c>
+      <c r="G7">
+        <v>20000</v>
+      </c>
+      <c r="H7">
+        <v>150000</v>
+      </c>
+      <c r="I7">
+        <v>150000</v>
+      </c>
+      <c r="J7">
+        <v>150000</v>
+      </c>
+      <c r="K7">
+        <v>150000</v>
+      </c>
+      <c r="L7">
+        <v>150000</v>
+      </c>
+      <c r="M7">
+        <v>150000</v>
+      </c>
+      <c r="N7">
+        <v>150000</v>
+      </c>
+      <c r="O7">
+        <v>150000</v>
+      </c>
+      <c r="P7">
+        <v>150000</v>
+      </c>
+      <c r="Q7">
+        <v>150000</v>
+      </c>
+      <c r="R7">
+        <v>150000</v>
+      </c>
+      <c r="S7">
+        <v>150000</v>
+      </c>
+      <c r="T7">
+        <v>150000</v>
+      </c>
+      <c r="U7">
+        <v>150000</v>
+      </c>
+      <c r="V7">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>2030</v>
+      </c>
+      <c r="B8">
+        <v>5000</v>
+      </c>
+      <c r="C8">
+        <v>5000000</v>
+      </c>
+      <c r="D8">
+        <v>500000</v>
+      </c>
+      <c r="E8">
+        <v>10000000</v>
+      </c>
+      <c r="F8">
+        <v>800000</v>
+      </c>
+      <c r="G8">
+        <v>20000</v>
+      </c>
+      <c r="H8">
+        <v>150000</v>
+      </c>
+      <c r="I8">
+        <v>150000</v>
+      </c>
+      <c r="J8">
+        <v>150000</v>
+      </c>
+      <c r="K8">
+        <v>150000</v>
+      </c>
+      <c r="L8">
+        <v>150000</v>
+      </c>
+      <c r="M8">
+        <v>150000</v>
+      </c>
+      <c r="N8">
+        <v>150000</v>
+      </c>
+      <c r="O8">
+        <v>150000</v>
+      </c>
+      <c r="P8">
+        <v>150000</v>
+      </c>
+      <c r="Q8">
+        <v>150000</v>
+      </c>
+      <c r="R8">
+        <v>150000</v>
+      </c>
+      <c r="S8">
+        <v>150000</v>
+      </c>
+      <c r="T8">
+        <v>150000</v>
+      </c>
+      <c r="U8">
+        <v>150000</v>
+      </c>
+      <c r="V8">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>2031</v>
+      </c>
+      <c r="B9">
+        <v>5000</v>
+      </c>
+      <c r="C9">
+        <v>5000000</v>
+      </c>
+      <c r="D9">
+        <v>500000</v>
+      </c>
+      <c r="E9">
+        <v>10000000</v>
+      </c>
+      <c r="F9">
+        <v>800000</v>
+      </c>
+      <c r="G9">
+        <v>20000</v>
+      </c>
+      <c r="H9">
+        <v>150000</v>
+      </c>
+      <c r="I9">
+        <v>150000</v>
+      </c>
+      <c r="J9">
+        <v>150000</v>
+      </c>
+      <c r="K9">
+        <v>150000</v>
+      </c>
+      <c r="L9">
+        <v>150000</v>
+      </c>
+      <c r="M9">
+        <v>150000</v>
+      </c>
+      <c r="N9">
+        <v>150000</v>
+      </c>
+      <c r="O9">
+        <v>150000</v>
+      </c>
+      <c r="P9">
+        <v>150000</v>
+      </c>
+      <c r="Q9">
+        <v>150000</v>
+      </c>
+      <c r="R9">
+        <v>150000</v>
+      </c>
+      <c r="S9">
+        <v>150000</v>
+      </c>
+      <c r="T9">
+        <v>150000</v>
+      </c>
+      <c r="U9">
+        <v>150000</v>
+      </c>
+      <c r="V9">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>2032</v>
+      </c>
+      <c r="B10">
+        <v>5000</v>
+      </c>
+      <c r="C10">
+        <v>5000000</v>
+      </c>
+      <c r="D10">
+        <v>500000</v>
+      </c>
+      <c r="E10">
+        <v>10000000</v>
+      </c>
+      <c r="F10">
+        <v>800000</v>
+      </c>
+      <c r="G10">
+        <v>20000</v>
+      </c>
+      <c r="H10">
+        <v>150000</v>
+      </c>
+      <c r="I10">
+        <v>150000</v>
+      </c>
+      <c r="J10">
+        <v>150000</v>
+      </c>
+      <c r="K10">
+        <v>150000</v>
+      </c>
+      <c r="L10">
+        <v>150000</v>
+      </c>
+      <c r="M10">
+        <v>150000</v>
+      </c>
+      <c r="N10">
+        <v>150000</v>
+      </c>
+      <c r="O10">
+        <v>150000</v>
+      </c>
+      <c r="P10">
+        <v>150000</v>
+      </c>
+      <c r="Q10">
+        <v>150000</v>
+      </c>
+      <c r="R10">
+        <v>150000</v>
+      </c>
+      <c r="S10">
+        <v>150000</v>
+      </c>
+      <c r="T10">
+        <v>150000</v>
+      </c>
+      <c r="U10">
+        <v>150000</v>
+      </c>
+      <c r="V10">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>2033</v>
+      </c>
+      <c r="B11">
+        <v>5000</v>
+      </c>
+      <c r="C11">
+        <v>5000000</v>
+      </c>
+      <c r="D11">
+        <v>500000</v>
+      </c>
+      <c r="E11">
+        <v>10000000</v>
+      </c>
+      <c r="F11">
+        <v>800000</v>
+      </c>
+      <c r="G11">
+        <v>20000</v>
+      </c>
+      <c r="H11">
+        <v>150000</v>
+      </c>
+      <c r="I11">
+        <v>150000</v>
+      </c>
+      <c r="J11">
+        <v>150000</v>
+      </c>
+      <c r="K11">
+        <v>150000</v>
+      </c>
+      <c r="L11">
+        <v>150000</v>
+      </c>
+      <c r="M11">
+        <v>150000</v>
+      </c>
+      <c r="N11">
+        <v>150000</v>
+      </c>
+      <c r="O11">
+        <v>150000</v>
+      </c>
+      <c r="P11">
+        <v>150000</v>
+      </c>
+      <c r="Q11">
+        <v>150000</v>
+      </c>
+      <c r="R11">
+        <v>150000</v>
+      </c>
+      <c r="S11">
+        <v>150000</v>
+      </c>
+      <c r="T11">
+        <v>150000</v>
+      </c>
+      <c r="U11">
+        <v>150000</v>
+      </c>
+      <c r="V11">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>2034</v>
+      </c>
+      <c r="B12">
+        <v>5000</v>
+      </c>
+      <c r="C12">
+        <v>5000000</v>
+      </c>
+      <c r="D12">
+        <v>500000</v>
+      </c>
+      <c r="E12">
+        <v>10000000</v>
+      </c>
+      <c r="F12">
+        <v>800000</v>
+      </c>
+      <c r="G12">
+        <v>20000</v>
+      </c>
+      <c r="H12">
+        <v>150000</v>
+      </c>
+      <c r="I12">
+        <v>150000</v>
+      </c>
+      <c r="J12">
+        <v>150000</v>
+      </c>
+      <c r="K12">
+        <v>150000</v>
+      </c>
+      <c r="L12">
+        <v>150000</v>
+      </c>
+      <c r="M12">
+        <v>150000</v>
+      </c>
+      <c r="N12">
+        <v>150000</v>
+      </c>
+      <c r="O12">
+        <v>150000</v>
+      </c>
+      <c r="P12">
+        <v>150000</v>
+      </c>
+      <c r="Q12">
+        <v>150000</v>
+      </c>
+      <c r="R12">
+        <v>150000</v>
+      </c>
+      <c r="S12">
+        <v>150000</v>
+      </c>
+      <c r="T12">
+        <v>150000</v>
+      </c>
+      <c r="U12">
+        <v>150000</v>
+      </c>
+      <c r="V12">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>2035</v>
+      </c>
+      <c r="B13">
+        <v>5000</v>
+      </c>
+      <c r="C13">
+        <v>5000000</v>
+      </c>
+      <c r="D13">
+        <v>500000</v>
+      </c>
+      <c r="E13">
+        <v>10000000</v>
+      </c>
+      <c r="F13">
+        <v>800000</v>
+      </c>
+      <c r="G13">
+        <v>20000</v>
+      </c>
+      <c r="H13">
+        <v>150000</v>
+      </c>
+      <c r="I13">
+        <v>150000</v>
+      </c>
+      <c r="J13">
+        <v>150000</v>
+      </c>
+      <c r="K13">
+        <v>150000</v>
+      </c>
+      <c r="L13">
+        <v>150000</v>
+      </c>
+      <c r="M13">
+        <v>150000</v>
+      </c>
+      <c r="N13">
+        <v>150000</v>
+      </c>
+      <c r="O13">
+        <v>150000</v>
+      </c>
+      <c r="P13">
+        <v>150000</v>
+      </c>
+      <c r="Q13">
+        <v>150000</v>
+      </c>
+      <c r="R13">
+        <v>150000</v>
+      </c>
+      <c r="S13">
+        <v>150000</v>
+      </c>
+      <c r="T13">
+        <v>150000</v>
+      </c>
+      <c r="U13">
+        <v>150000</v>
+      </c>
+      <c r="V13">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>2036</v>
+      </c>
+      <c r="B14">
+        <v>5000</v>
+      </c>
+      <c r="C14">
+        <v>5000000</v>
+      </c>
+      <c r="D14">
+        <v>500000</v>
+      </c>
+      <c r="E14">
+        <v>10000000</v>
+      </c>
+      <c r="F14">
+        <v>800000</v>
+      </c>
+      <c r="G14">
+        <v>20000</v>
+      </c>
+      <c r="H14">
+        <v>150000</v>
+      </c>
+      <c r="I14">
+        <v>150000</v>
+      </c>
+      <c r="J14">
+        <v>150000</v>
+      </c>
+      <c r="K14">
+        <v>150000</v>
+      </c>
+      <c r="L14">
+        <v>150000</v>
+      </c>
+      <c r="M14">
+        <v>150000</v>
+      </c>
+      <c r="N14">
+        <v>150000</v>
+      </c>
+      <c r="O14">
+        <v>150000</v>
+      </c>
+      <c r="P14">
+        <v>150000</v>
+      </c>
+      <c r="Q14">
+        <v>150000</v>
+      </c>
+      <c r="R14">
+        <v>150000</v>
+      </c>
+      <c r="S14">
+        <v>150000</v>
+      </c>
+      <c r="T14">
+        <v>150000</v>
+      </c>
+      <c r="U14">
+        <v>150000</v>
+      </c>
+      <c r="V14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>2037</v>
+      </c>
+      <c r="B15">
+        <v>5000</v>
+      </c>
+      <c r="C15">
+        <v>5000000</v>
+      </c>
+      <c r="D15">
+        <v>500000</v>
+      </c>
+      <c r="E15">
+        <v>10000000</v>
+      </c>
+      <c r="F15">
+        <v>800000</v>
+      </c>
+      <c r="G15">
+        <v>20000</v>
+      </c>
+      <c r="H15">
+        <v>150000</v>
+      </c>
+      <c r="I15">
+        <v>150000</v>
+      </c>
+      <c r="J15">
+        <v>150000</v>
+      </c>
+      <c r="K15">
+        <v>150000</v>
+      </c>
+      <c r="L15">
+        <v>150000</v>
+      </c>
+      <c r="M15">
+        <v>150000</v>
+      </c>
+      <c r="N15">
+        <v>150000</v>
+      </c>
+      <c r="O15">
+        <v>150000</v>
+      </c>
+      <c r="P15">
+        <v>150000</v>
+      </c>
+      <c r="Q15">
+        <v>150000</v>
+      </c>
+      <c r="R15">
+        <v>150000</v>
+      </c>
+      <c r="S15">
+        <v>150000</v>
+      </c>
+      <c r="T15">
+        <v>150000</v>
+      </c>
+      <c r="U15">
+        <v>150000</v>
+      </c>
+      <c r="V15">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>2038</v>
+      </c>
+      <c r="B16">
+        <v>5000</v>
+      </c>
+      <c r="C16">
+        <v>5000000</v>
+      </c>
+      <c r="D16">
+        <v>500000</v>
+      </c>
+      <c r="E16">
+        <v>10000000</v>
+      </c>
+      <c r="F16">
+        <v>800000</v>
+      </c>
+      <c r="G16">
+        <v>20000</v>
+      </c>
+      <c r="H16">
+        <v>150000</v>
+      </c>
+      <c r="I16">
+        <v>150000</v>
+      </c>
+      <c r="J16">
+        <v>150000</v>
+      </c>
+      <c r="K16">
+        <v>150000</v>
+      </c>
+      <c r="L16">
+        <v>150000</v>
+      </c>
+      <c r="M16">
+        <v>150000</v>
+      </c>
+      <c r="N16">
+        <v>150000</v>
+      </c>
+      <c r="O16">
+        <v>150000</v>
+      </c>
+      <c r="P16">
+        <v>150000</v>
+      </c>
+      <c r="Q16">
+        <v>150000</v>
+      </c>
+      <c r="R16">
+        <v>150000</v>
+      </c>
+      <c r="S16">
+        <v>150000</v>
+      </c>
+      <c r="T16">
+        <v>150000</v>
+      </c>
+      <c r="U16">
+        <v>150000</v>
+      </c>
+      <c r="V16">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>2039</v>
+      </c>
+      <c r="B17">
+        <v>5000</v>
+      </c>
+      <c r="C17">
+        <v>5000000</v>
+      </c>
+      <c r="D17">
+        <v>500000</v>
+      </c>
+      <c r="E17">
+        <v>10000000</v>
+      </c>
+      <c r="F17">
+        <v>800000</v>
+      </c>
+      <c r="G17">
+        <v>20000</v>
+      </c>
+      <c r="H17">
+        <v>150000</v>
+      </c>
+      <c r="I17">
+        <v>150000</v>
+      </c>
+      <c r="J17">
+        <v>150000</v>
+      </c>
+      <c r="K17">
+        <v>150000</v>
+      </c>
+      <c r="L17">
+        <v>150000</v>
+      </c>
+      <c r="M17">
+        <v>150000</v>
+      </c>
+      <c r="N17">
+        <v>150000</v>
+      </c>
+      <c r="O17">
+        <v>150000</v>
+      </c>
+      <c r="P17">
+        <v>150000</v>
+      </c>
+      <c r="Q17">
+        <v>150000</v>
+      </c>
+      <c r="R17">
+        <v>150000</v>
+      </c>
+      <c r="S17">
+        <v>150000</v>
+      </c>
+      <c r="T17">
+        <v>150000</v>
+      </c>
+      <c r="U17">
+        <v>150000</v>
+      </c>
+      <c r="V17">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>2040</v>
+      </c>
+      <c r="B18">
+        <v>5000</v>
+      </c>
+      <c r="C18">
+        <v>5000000</v>
+      </c>
+      <c r="D18">
+        <v>500000</v>
+      </c>
+      <c r="E18">
+        <v>10000000</v>
+      </c>
+      <c r="F18">
+        <v>800000</v>
+      </c>
+      <c r="G18">
+        <v>20000</v>
+      </c>
+      <c r="H18">
+        <v>150000</v>
+      </c>
+      <c r="I18">
+        <v>150000</v>
+      </c>
+      <c r="J18">
+        <v>150000</v>
+      </c>
+      <c r="K18">
+        <v>150000</v>
+      </c>
+      <c r="L18">
+        <v>150000</v>
+      </c>
+      <c r="M18">
+        <v>150000</v>
+      </c>
+      <c r="N18">
+        <v>150000</v>
+      </c>
+      <c r="O18">
+        <v>150000</v>
+      </c>
+      <c r="P18">
+        <v>150000</v>
+      </c>
+      <c r="Q18">
+        <v>150000</v>
+      </c>
+      <c r="R18">
+        <v>150000</v>
+      </c>
+      <c r="S18">
+        <v>150000</v>
+      </c>
+      <c r="T18">
+        <v>150000</v>
+      </c>
+      <c r="U18">
+        <v>150000</v>
+      </c>
+      <c r="V18">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>2041</v>
+      </c>
+      <c r="B19">
+        <v>5000</v>
+      </c>
+      <c r="C19">
+        <v>5000000</v>
+      </c>
+      <c r="D19">
+        <v>500000</v>
+      </c>
+      <c r="E19">
+        <v>10000000</v>
+      </c>
+      <c r="F19">
+        <v>800000</v>
+      </c>
+      <c r="G19">
+        <v>20000</v>
+      </c>
+      <c r="H19">
+        <v>150000</v>
+      </c>
+      <c r="I19">
+        <v>150000</v>
+      </c>
+      <c r="J19">
+        <v>150000</v>
+      </c>
+      <c r="K19">
+        <v>150000</v>
+      </c>
+      <c r="L19">
+        <v>150000</v>
+      </c>
+      <c r="M19">
+        <v>150000</v>
+      </c>
+      <c r="N19">
+        <v>150000</v>
+      </c>
+      <c r="O19">
+        <v>150000</v>
+      </c>
+      <c r="P19">
+        <v>150000</v>
+      </c>
+      <c r="Q19">
+        <v>150000</v>
+      </c>
+      <c r="R19">
+        <v>150000</v>
+      </c>
+      <c r="S19">
+        <v>150000</v>
+      </c>
+      <c r="T19">
+        <v>150000</v>
+      </c>
+      <c r="U19">
+        <v>150000</v>
+      </c>
+      <c r="V19">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>2042</v>
+      </c>
+      <c r="B20">
+        <v>5000</v>
+      </c>
+      <c r="C20">
+        <v>5000000</v>
+      </c>
+      <c r="D20">
+        <v>500000</v>
+      </c>
+      <c r="E20">
+        <v>10000000</v>
+      </c>
+      <c r="F20">
+        <v>800000</v>
+      </c>
+      <c r="G20">
+        <v>20000</v>
+      </c>
+      <c r="H20">
+        <v>150000</v>
+      </c>
+      <c r="I20">
+        <v>150000</v>
+      </c>
+      <c r="J20">
+        <v>150000</v>
+      </c>
+      <c r="K20">
+        <v>150000</v>
+      </c>
+      <c r="L20">
+        <v>150000</v>
+      </c>
+      <c r="M20">
+        <v>150000</v>
+      </c>
+      <c r="N20">
+        <v>150000</v>
+      </c>
+      <c r="O20">
+        <v>150000</v>
+      </c>
+      <c r="P20">
+        <v>150000</v>
+      </c>
+      <c r="Q20">
+        <v>150000</v>
+      </c>
+      <c r="R20">
+        <v>150000</v>
+      </c>
+      <c r="S20">
+        <v>150000</v>
+      </c>
+      <c r="T20">
+        <v>150000</v>
+      </c>
+      <c r="U20">
+        <v>150000</v>
+      </c>
+      <c r="V20">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="16">
+        <v>2043</v>
+      </c>
+      <c r="B21">
+        <v>5000</v>
+      </c>
+      <c r="C21">
+        <v>5000000</v>
+      </c>
+      <c r="D21">
+        <v>500000</v>
+      </c>
+      <c r="E21">
+        <v>10000000</v>
+      </c>
+      <c r="F21">
+        <v>800000</v>
+      </c>
+      <c r="G21">
+        <v>20000</v>
+      </c>
+      <c r="H21">
+        <v>150000</v>
+      </c>
+      <c r="I21">
+        <v>150000</v>
+      </c>
+      <c r="J21">
+        <v>150000</v>
+      </c>
+      <c r="K21">
+        <v>150000</v>
+      </c>
+      <c r="L21">
+        <v>150000</v>
+      </c>
+      <c r="M21">
+        <v>150000</v>
+      </c>
+      <c r="N21">
+        <v>150000</v>
+      </c>
+      <c r="O21">
+        <v>150000</v>
+      </c>
+      <c r="P21">
+        <v>150000</v>
+      </c>
+      <c r="Q21">
+        <v>150000</v>
+      </c>
+      <c r="R21">
+        <v>150000</v>
+      </c>
+      <c r="S21">
+        <v>150000</v>
+      </c>
+      <c r="T21">
+        <v>150000</v>
+      </c>
+      <c r="U21">
+        <v>150000</v>
+      </c>
+      <c r="V21">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>2044</v>
+      </c>
+      <c r="B22">
+        <v>5000</v>
+      </c>
+      <c r="C22">
+        <v>5000000</v>
+      </c>
+      <c r="D22">
+        <v>500000</v>
+      </c>
+      <c r="E22">
+        <v>10000000</v>
+      </c>
+      <c r="F22">
+        <v>800000</v>
+      </c>
+      <c r="G22">
+        <v>20000</v>
+      </c>
+      <c r="H22">
+        <v>150000</v>
+      </c>
+      <c r="I22">
+        <v>150000</v>
+      </c>
+      <c r="J22">
+        <v>150000</v>
+      </c>
+      <c r="K22">
+        <v>150000</v>
+      </c>
+      <c r="L22">
+        <v>150000</v>
+      </c>
+      <c r="M22">
+        <v>150000</v>
+      </c>
+      <c r="N22">
+        <v>150000</v>
+      </c>
+      <c r="O22">
+        <v>150000</v>
+      </c>
+      <c r="P22">
+        <v>150000</v>
+      </c>
+      <c r="Q22">
+        <v>150000</v>
+      </c>
+      <c r="R22">
+        <v>150000</v>
+      </c>
+      <c r="S22">
+        <v>150000</v>
+      </c>
+      <c r="T22">
+        <v>150000</v>
+      </c>
+      <c r="U22">
+        <v>150000</v>
+      </c>
+      <c r="V22">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>2045</v>
+      </c>
+      <c r="B23">
+        <v>5000</v>
+      </c>
+      <c r="C23">
+        <v>5000000</v>
+      </c>
+      <c r="D23">
+        <v>500000</v>
+      </c>
+      <c r="E23">
+        <v>10000000</v>
+      </c>
+      <c r="F23">
+        <v>800000</v>
+      </c>
+      <c r="G23">
+        <v>20000</v>
+      </c>
+      <c r="H23">
+        <v>150000</v>
+      </c>
+      <c r="I23">
+        <v>150000</v>
+      </c>
+      <c r="J23">
+        <v>150000</v>
+      </c>
+      <c r="K23">
+        <v>150000</v>
+      </c>
+      <c r="L23">
+        <v>150000</v>
+      </c>
+      <c r="M23">
+        <v>150000</v>
+      </c>
+      <c r="N23">
+        <v>150000</v>
+      </c>
+      <c r="O23">
+        <v>150000</v>
+      </c>
+      <c r="P23">
+        <v>150000</v>
+      </c>
+      <c r="Q23">
+        <v>150000</v>
+      </c>
+      <c r="R23">
+        <v>150000</v>
+      </c>
+      <c r="S23">
+        <v>150000</v>
+      </c>
+      <c r="T23">
+        <v>150000</v>
+      </c>
+      <c r="U23">
+        <v>150000</v>
+      </c>
+      <c r="V23">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>2046</v>
+      </c>
+      <c r="B24">
+        <v>5000</v>
+      </c>
+      <c r="C24">
+        <v>5000000</v>
+      </c>
+      <c r="D24">
+        <v>500000</v>
+      </c>
+      <c r="E24">
+        <v>10000000</v>
+      </c>
+      <c r="F24">
+        <v>800000</v>
+      </c>
+      <c r="G24">
+        <v>20000</v>
+      </c>
+      <c r="H24">
+        <v>150000</v>
+      </c>
+      <c r="I24">
+        <v>150000</v>
+      </c>
+      <c r="J24">
+        <v>150000</v>
+      </c>
+      <c r="K24">
+        <v>150000</v>
+      </c>
+      <c r="L24">
+        <v>150000</v>
+      </c>
+      <c r="M24">
+        <v>150000</v>
+      </c>
+      <c r="N24">
+        <v>150000</v>
+      </c>
+      <c r="O24">
+        <v>150000</v>
+      </c>
+      <c r="P24">
+        <v>150000</v>
+      </c>
+      <c r="Q24">
+        <v>150000</v>
+      </c>
+      <c r="R24">
+        <v>150000</v>
+      </c>
+      <c r="S24">
+        <v>150000</v>
+      </c>
+      <c r="T24">
+        <v>150000</v>
+      </c>
+      <c r="U24">
+        <v>150000</v>
+      </c>
+      <c r="V24">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <v>2047</v>
+      </c>
+      <c r="B25">
+        <v>5000</v>
+      </c>
+      <c r="C25">
+        <v>5000000</v>
+      </c>
+      <c r="D25">
+        <v>500000</v>
+      </c>
+      <c r="E25">
+        <v>10000000</v>
+      </c>
+      <c r="F25">
+        <v>800000</v>
+      </c>
+      <c r="G25">
+        <v>20000</v>
+      </c>
+      <c r="H25">
+        <v>150000</v>
+      </c>
+      <c r="I25">
+        <v>150000</v>
+      </c>
+      <c r="J25">
+        <v>150000</v>
+      </c>
+      <c r="K25">
+        <v>150000</v>
+      </c>
+      <c r="L25">
+        <v>150000</v>
+      </c>
+      <c r="M25">
+        <v>150000</v>
+      </c>
+      <c r="N25">
+        <v>150000</v>
+      </c>
+      <c r="O25">
+        <v>150000</v>
+      </c>
+      <c r="P25">
+        <v>150000</v>
+      </c>
+      <c r="Q25">
+        <v>150000</v>
+      </c>
+      <c r="R25">
+        <v>150000</v>
+      </c>
+      <c r="S25">
+        <v>150000</v>
+      </c>
+      <c r="T25">
+        <v>150000</v>
+      </c>
+      <c r="U25">
+        <v>150000</v>
+      </c>
+      <c r="V25">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
+        <v>2048</v>
+      </c>
+      <c r="B26">
+        <v>5000</v>
+      </c>
+      <c r="C26">
+        <v>5000000</v>
+      </c>
+      <c r="D26">
+        <v>500000</v>
+      </c>
+      <c r="E26">
+        <v>10000000</v>
+      </c>
+      <c r="F26">
+        <v>800000</v>
+      </c>
+      <c r="G26">
+        <v>20000</v>
+      </c>
+      <c r="H26">
+        <v>150000</v>
+      </c>
+      <c r="I26">
+        <v>150000</v>
+      </c>
+      <c r="J26">
+        <v>150000</v>
+      </c>
+      <c r="K26">
+        <v>150000</v>
+      </c>
+      <c r="L26">
+        <v>150000</v>
+      </c>
+      <c r="M26">
+        <v>150000</v>
+      </c>
+      <c r="N26">
+        <v>150000</v>
+      </c>
+      <c r="O26">
+        <v>150000</v>
+      </c>
+      <c r="P26">
+        <v>150000</v>
+      </c>
+      <c r="Q26">
+        <v>150000</v>
+      </c>
+      <c r="R26">
+        <v>150000</v>
+      </c>
+      <c r="S26">
+        <v>150000</v>
+      </c>
+      <c r="T26">
+        <v>150000</v>
+      </c>
+      <c r="U26">
+        <v>150000</v>
+      </c>
+      <c r="V26">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>2049</v>
+      </c>
+      <c r="B27">
+        <v>5000</v>
+      </c>
+      <c r="C27">
+        <v>5000000</v>
+      </c>
+      <c r="D27">
+        <v>500000</v>
+      </c>
+      <c r="E27">
+        <v>10000000</v>
+      </c>
+      <c r="F27">
+        <v>800000</v>
+      </c>
+      <c r="G27">
+        <v>20000</v>
+      </c>
+      <c r="H27">
+        <v>150000</v>
+      </c>
+      <c r="I27">
+        <v>150000</v>
+      </c>
+      <c r="J27">
+        <v>150000</v>
+      </c>
+      <c r="K27">
+        <v>150000</v>
+      </c>
+      <c r="L27">
+        <v>150000</v>
+      </c>
+      <c r="M27">
+        <v>150000</v>
+      </c>
+      <c r="N27">
+        <v>150000</v>
+      </c>
+      <c r="O27">
+        <v>150000</v>
+      </c>
+      <c r="P27">
+        <v>150000</v>
+      </c>
+      <c r="Q27">
+        <v>150000</v>
+      </c>
+      <c r="R27">
+        <v>150000</v>
+      </c>
+      <c r="S27">
+        <v>150000</v>
+      </c>
+      <c r="T27">
+        <v>150000</v>
+      </c>
+      <c r="U27">
+        <v>150000</v>
+      </c>
+      <c r="V27">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>2050</v>
+      </c>
+      <c r="B28">
+        <v>5000</v>
+      </c>
+      <c r="C28">
+        <v>5000000</v>
+      </c>
+      <c r="D28">
+        <v>500000</v>
+      </c>
+      <c r="E28">
+        <v>10000000</v>
+      </c>
+      <c r="F28">
+        <v>800000</v>
+      </c>
+      <c r="G28">
+        <v>20000</v>
+      </c>
+      <c r="H28">
+        <v>150000</v>
+      </c>
+      <c r="I28">
+        <v>150000</v>
+      </c>
+      <c r="J28">
+        <v>150000</v>
+      </c>
+      <c r="K28">
+        <v>150000</v>
+      </c>
+      <c r="L28">
+        <v>150000</v>
+      </c>
+      <c r="M28">
+        <v>150000</v>
+      </c>
+      <c r="N28">
+        <v>150000</v>
+      </c>
+      <c r="O28">
+        <v>150000</v>
+      </c>
+      <c r="P28">
+        <v>150000</v>
+      </c>
+      <c r="Q28">
+        <v>150000</v>
+      </c>
+      <c r="R28">
+        <v>150000</v>
+      </c>
+      <c r="S28">
+        <v>150000</v>
+      </c>
+      <c r="T28">
+        <v>150000</v>
+      </c>
+      <c r="U28">
+        <v>150000</v>
+      </c>
+      <c r="V28">
+        <v>150000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3497A18D-E10F-4371-B6A4-3051915122F0}">
+  <dimension ref="A1:V28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="16">
+        <v>2024</v>
+      </c>
+      <c r="B2">
+        <v>650000</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>3000</v>
+      </c>
+      <c r="E2">
+        <v>600</v>
+      </c>
+      <c r="F2">
+        <v>8000</v>
+      </c>
+      <c r="G2">
+        <v>40000</v>
+      </c>
+      <c r="H2">
+        <v>15000</v>
+      </c>
+      <c r="I2">
+        <v>30000</v>
+      </c>
+      <c r="J2">
+        <v>30000</v>
+      </c>
+      <c r="K2">
+        <v>30000</v>
+      </c>
+      <c r="L2">
+        <v>30000</v>
+      </c>
+      <c r="M2">
+        <v>30000</v>
+      </c>
+      <c r="N2">
+        <v>30000</v>
+      </c>
+      <c r="O2">
+        <v>30000</v>
+      </c>
+      <c r="P2">
+        <v>30000</v>
+      </c>
+      <c r="Q2">
+        <v>30000</v>
+      </c>
+      <c r="R2">
+        <v>30000</v>
+      </c>
+      <c r="S2">
+        <v>30000</v>
+      </c>
+      <c r="T2">
+        <v>30000</v>
+      </c>
+      <c r="U2">
+        <v>30000</v>
+      </c>
+      <c r="V2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>650000</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>3000</v>
+      </c>
+      <c r="E3">
+        <v>600</v>
+      </c>
+      <c r="F3">
+        <v>8000</v>
+      </c>
+      <c r="G3">
+        <v>40000</v>
+      </c>
+      <c r="H3">
+        <v>15000</v>
+      </c>
+      <c r="I3">
+        <v>30000</v>
+      </c>
+      <c r="J3">
+        <v>30000</v>
+      </c>
+      <c r="K3">
+        <v>30000</v>
+      </c>
+      <c r="L3">
+        <v>30000</v>
+      </c>
+      <c r="M3">
+        <v>30000</v>
+      </c>
+      <c r="N3">
+        <v>30000</v>
+      </c>
+      <c r="O3">
+        <v>30000</v>
+      </c>
+      <c r="P3">
+        <v>30000</v>
+      </c>
+      <c r="Q3">
+        <v>30000</v>
+      </c>
+      <c r="R3">
+        <v>30000</v>
+      </c>
+      <c r="S3">
+        <v>30000</v>
+      </c>
+      <c r="T3">
+        <v>30000</v>
+      </c>
+      <c r="U3">
+        <v>30000</v>
+      </c>
+      <c r="V3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>650000</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>3000</v>
+      </c>
+      <c r="E4">
+        <v>600</v>
+      </c>
+      <c r="F4">
+        <v>8000</v>
+      </c>
+      <c r="G4">
+        <v>40000</v>
+      </c>
+      <c r="H4">
+        <v>15000</v>
+      </c>
+      <c r="I4">
+        <v>30000</v>
+      </c>
+      <c r="J4">
+        <v>30000</v>
+      </c>
+      <c r="K4">
+        <v>30000</v>
+      </c>
+      <c r="L4">
+        <v>30000</v>
+      </c>
+      <c r="M4">
+        <v>30000</v>
+      </c>
+      <c r="N4">
+        <v>30000</v>
+      </c>
+      <c r="O4">
+        <v>30000</v>
+      </c>
+      <c r="P4">
+        <v>30000</v>
+      </c>
+      <c r="Q4">
+        <v>30000</v>
+      </c>
+      <c r="R4">
+        <v>30000</v>
+      </c>
+      <c r="S4">
+        <v>30000</v>
+      </c>
+      <c r="T4">
+        <v>30000</v>
+      </c>
+      <c r="U4">
+        <v>30000</v>
+      </c>
+      <c r="V4">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B5">
+        <v>650000</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>3000</v>
+      </c>
+      <c r="E5">
+        <v>600</v>
+      </c>
+      <c r="F5">
+        <v>8000</v>
+      </c>
+      <c r="G5">
+        <v>40000</v>
+      </c>
+      <c r="H5">
+        <v>15000</v>
+      </c>
+      <c r="I5">
+        <v>30000</v>
+      </c>
+      <c r="J5">
+        <v>30000</v>
+      </c>
+      <c r="K5">
+        <v>30000</v>
+      </c>
+      <c r="L5">
+        <v>30000</v>
+      </c>
+      <c r="M5">
+        <v>30000</v>
+      </c>
+      <c r="N5">
+        <v>30000</v>
+      </c>
+      <c r="O5">
+        <v>30000</v>
+      </c>
+      <c r="P5">
+        <v>30000</v>
+      </c>
+      <c r="Q5">
+        <v>30000</v>
+      </c>
+      <c r="R5">
+        <v>30000</v>
+      </c>
+      <c r="S5">
+        <v>30000</v>
+      </c>
+      <c r="T5">
+        <v>30000</v>
+      </c>
+      <c r="U5">
+        <v>30000</v>
+      </c>
+      <c r="V5">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>2028</v>
+      </c>
+      <c r="B6">
+        <v>650000</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>3000</v>
+      </c>
+      <c r="E6">
+        <v>600</v>
+      </c>
+      <c r="F6">
+        <v>8000</v>
+      </c>
+      <c r="G6">
+        <v>40000</v>
+      </c>
+      <c r="H6">
+        <v>15000</v>
+      </c>
+      <c r="I6">
+        <v>30000</v>
+      </c>
+      <c r="J6">
+        <v>30000</v>
+      </c>
+      <c r="K6">
+        <v>30000</v>
+      </c>
+      <c r="L6">
+        <v>30000</v>
+      </c>
+      <c r="M6">
+        <v>30000</v>
+      </c>
+      <c r="N6">
+        <v>30000</v>
+      </c>
+      <c r="O6">
+        <v>30000</v>
+      </c>
+      <c r="P6">
+        <v>30000</v>
+      </c>
+      <c r="Q6">
+        <v>30000</v>
+      </c>
+      <c r="R6">
+        <v>30000</v>
+      </c>
+      <c r="S6">
+        <v>30000</v>
+      </c>
+      <c r="T6">
+        <v>30000</v>
+      </c>
+      <c r="U6">
+        <v>30000</v>
+      </c>
+      <c r="V6">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>2029</v>
+      </c>
+      <c r="B7">
+        <v>650000</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>3000</v>
+      </c>
+      <c r="E7">
+        <v>600</v>
+      </c>
+      <c r="F7">
+        <v>8000</v>
+      </c>
+      <c r="G7">
+        <v>40000</v>
+      </c>
+      <c r="H7">
+        <v>15000</v>
+      </c>
+      <c r="I7">
+        <v>30000</v>
+      </c>
+      <c r="J7">
+        <v>30000</v>
+      </c>
+      <c r="K7">
+        <v>30000</v>
+      </c>
+      <c r="L7">
+        <v>30000</v>
+      </c>
+      <c r="M7">
+        <v>30000</v>
+      </c>
+      <c r="N7">
+        <v>30000</v>
+      </c>
+      <c r="O7">
+        <v>30000</v>
+      </c>
+      <c r="P7">
+        <v>30000</v>
+      </c>
+      <c r="Q7">
+        <v>30000</v>
+      </c>
+      <c r="R7">
+        <v>30000</v>
+      </c>
+      <c r="S7">
+        <v>30000</v>
+      </c>
+      <c r="T7">
+        <v>30000</v>
+      </c>
+      <c r="U7">
+        <v>30000</v>
+      </c>
+      <c r="V7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>2030</v>
+      </c>
+      <c r="B8">
+        <v>650000</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>3000</v>
+      </c>
+      <c r="E8">
+        <v>600</v>
+      </c>
+      <c r="F8">
+        <v>8000</v>
+      </c>
+      <c r="G8">
+        <v>40000</v>
+      </c>
+      <c r="H8">
+        <v>15000</v>
+      </c>
+      <c r="I8">
+        <v>30000</v>
+      </c>
+      <c r="J8">
+        <v>30000</v>
+      </c>
+      <c r="K8">
+        <v>30000</v>
+      </c>
+      <c r="L8">
+        <v>30000</v>
+      </c>
+      <c r="M8">
+        <v>30000</v>
+      </c>
+      <c r="N8">
+        <v>30000</v>
+      </c>
+      <c r="O8">
+        <v>30000</v>
+      </c>
+      <c r="P8">
+        <v>30000</v>
+      </c>
+      <c r="Q8">
+        <v>30000</v>
+      </c>
+      <c r="R8">
+        <v>30000</v>
+      </c>
+      <c r="S8">
+        <v>30000</v>
+      </c>
+      <c r="T8">
+        <v>30000</v>
+      </c>
+      <c r="U8">
+        <v>30000</v>
+      </c>
+      <c r="V8">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>2031</v>
+      </c>
+      <c r="B9">
+        <v>650000</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>3000</v>
+      </c>
+      <c r="E9">
+        <v>600</v>
+      </c>
+      <c r="F9">
+        <v>8000</v>
+      </c>
+      <c r="G9">
+        <v>40000</v>
+      </c>
+      <c r="H9">
+        <v>15000</v>
+      </c>
+      <c r="I9">
+        <v>30000</v>
+      </c>
+      <c r="J9">
+        <v>30000</v>
+      </c>
+      <c r="K9">
+        <v>30000</v>
+      </c>
+      <c r="L9">
+        <v>30000</v>
+      </c>
+      <c r="M9">
+        <v>30000</v>
+      </c>
+      <c r="N9">
+        <v>30000</v>
+      </c>
+      <c r="O9">
+        <v>30000</v>
+      </c>
+      <c r="P9">
+        <v>30000</v>
+      </c>
+      <c r="Q9">
+        <v>30000</v>
+      </c>
+      <c r="R9">
+        <v>30000</v>
+      </c>
+      <c r="S9">
+        <v>30000</v>
+      </c>
+      <c r="T9">
+        <v>30000</v>
+      </c>
+      <c r="U9">
+        <v>30000</v>
+      </c>
+      <c r="V9">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>2032</v>
+      </c>
+      <c r="B10">
+        <v>650000</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>3000</v>
+      </c>
+      <c r="E10">
+        <v>600</v>
+      </c>
+      <c r="F10">
+        <v>8000</v>
+      </c>
+      <c r="G10">
+        <v>40000</v>
+      </c>
+      <c r="H10">
+        <v>15000</v>
+      </c>
+      <c r="I10">
+        <v>30000</v>
+      </c>
+      <c r="J10">
+        <v>30000</v>
+      </c>
+      <c r="K10">
+        <v>30000</v>
+      </c>
+      <c r="L10">
+        <v>30000</v>
+      </c>
+      <c r="M10">
+        <v>30000</v>
+      </c>
+      <c r="N10">
+        <v>30000</v>
+      </c>
+      <c r="O10">
+        <v>30000</v>
+      </c>
+      <c r="P10">
+        <v>30000</v>
+      </c>
+      <c r="Q10">
+        <v>30000</v>
+      </c>
+      <c r="R10">
+        <v>30000</v>
+      </c>
+      <c r="S10">
+        <v>30000</v>
+      </c>
+      <c r="T10">
+        <v>30000</v>
+      </c>
+      <c r="U10">
+        <v>30000</v>
+      </c>
+      <c r="V10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>2033</v>
+      </c>
+      <c r="B11">
+        <v>650000</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>3000</v>
+      </c>
+      <c r="E11">
+        <v>600</v>
+      </c>
+      <c r="F11">
+        <v>8000</v>
+      </c>
+      <c r="G11">
+        <v>40000</v>
+      </c>
+      <c r="H11">
+        <v>15000</v>
+      </c>
+      <c r="I11">
+        <v>30000</v>
+      </c>
+      <c r="J11">
+        <v>30000</v>
+      </c>
+      <c r="K11">
+        <v>30000</v>
+      </c>
+      <c r="L11">
+        <v>30000</v>
+      </c>
+      <c r="M11">
+        <v>30000</v>
+      </c>
+      <c r="N11">
+        <v>30000</v>
+      </c>
+      <c r="O11">
+        <v>30000</v>
+      </c>
+      <c r="P11">
+        <v>30000</v>
+      </c>
+      <c r="Q11">
+        <v>30000</v>
+      </c>
+      <c r="R11">
+        <v>30000</v>
+      </c>
+      <c r="S11">
+        <v>30000</v>
+      </c>
+      <c r="T11">
+        <v>30000</v>
+      </c>
+      <c r="U11">
+        <v>30000</v>
+      </c>
+      <c r="V11">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>2034</v>
+      </c>
+      <c r="B12">
+        <v>650000</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>3000</v>
+      </c>
+      <c r="E12">
+        <v>600</v>
+      </c>
+      <c r="F12">
+        <v>8000</v>
+      </c>
+      <c r="G12">
+        <v>40000</v>
+      </c>
+      <c r="H12">
+        <v>15000</v>
+      </c>
+      <c r="I12">
+        <v>30000</v>
+      </c>
+      <c r="J12">
+        <v>30000</v>
+      </c>
+      <c r="K12">
+        <v>30000</v>
+      </c>
+      <c r="L12">
+        <v>30000</v>
+      </c>
+      <c r="M12">
+        <v>30000</v>
+      </c>
+      <c r="N12">
+        <v>30000</v>
+      </c>
+      <c r="O12">
+        <v>30000</v>
+      </c>
+      <c r="P12">
+        <v>30000</v>
+      </c>
+      <c r="Q12">
+        <v>30000</v>
+      </c>
+      <c r="R12">
+        <v>30000</v>
+      </c>
+      <c r="S12">
+        <v>30000</v>
+      </c>
+      <c r="T12">
+        <v>30000</v>
+      </c>
+      <c r="U12">
+        <v>30000</v>
+      </c>
+      <c r="V12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>2035</v>
+      </c>
+      <c r="B13">
+        <v>650000</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>3000</v>
+      </c>
+      <c r="E13">
+        <v>600</v>
+      </c>
+      <c r="F13">
+        <v>8000</v>
+      </c>
+      <c r="G13">
+        <v>40000</v>
+      </c>
+      <c r="H13">
+        <v>15000</v>
+      </c>
+      <c r="I13">
+        <v>30000</v>
+      </c>
+      <c r="J13">
+        <v>30000</v>
+      </c>
+      <c r="K13">
+        <v>30000</v>
+      </c>
+      <c r="L13">
+        <v>30000</v>
+      </c>
+      <c r="M13">
+        <v>30000</v>
+      </c>
+      <c r="N13">
+        <v>30000</v>
+      </c>
+      <c r="O13">
+        <v>30000</v>
+      </c>
+      <c r="P13">
+        <v>30000</v>
+      </c>
+      <c r="Q13">
+        <v>30000</v>
+      </c>
+      <c r="R13">
+        <v>30000</v>
+      </c>
+      <c r="S13">
+        <v>30000</v>
+      </c>
+      <c r="T13">
+        <v>30000</v>
+      </c>
+      <c r="U13">
+        <v>30000</v>
+      </c>
+      <c r="V13">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>2036</v>
+      </c>
+      <c r="B14">
+        <v>650000</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>3000</v>
+      </c>
+      <c r="E14">
+        <v>600</v>
+      </c>
+      <c r="F14">
+        <v>8000</v>
+      </c>
+      <c r="G14">
+        <v>40000</v>
+      </c>
+      <c r="H14">
+        <v>15000</v>
+      </c>
+      <c r="I14">
+        <v>30000</v>
+      </c>
+      <c r="J14">
+        <v>30000</v>
+      </c>
+      <c r="K14">
+        <v>30000</v>
+      </c>
+      <c r="L14">
+        <v>30000</v>
+      </c>
+      <c r="M14">
+        <v>30000</v>
+      </c>
+      <c r="N14">
+        <v>30000</v>
+      </c>
+      <c r="O14">
+        <v>30000</v>
+      </c>
+      <c r="P14">
+        <v>30000</v>
+      </c>
+      <c r="Q14">
+        <v>30000</v>
+      </c>
+      <c r="R14">
+        <v>30000</v>
+      </c>
+      <c r="S14">
+        <v>30000</v>
+      </c>
+      <c r="T14">
+        <v>30000</v>
+      </c>
+      <c r="U14">
+        <v>30000</v>
+      </c>
+      <c r="V14">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>2037</v>
+      </c>
+      <c r="B15">
+        <v>650000</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>3000</v>
+      </c>
+      <c r="E15">
+        <v>600</v>
+      </c>
+      <c r="F15">
+        <v>8000</v>
+      </c>
+      <c r="G15">
+        <v>40000</v>
+      </c>
+      <c r="H15">
+        <v>15000</v>
+      </c>
+      <c r="I15">
+        <v>30000</v>
+      </c>
+      <c r="J15">
+        <v>30000</v>
+      </c>
+      <c r="K15">
+        <v>30000</v>
+      </c>
+      <c r="L15">
+        <v>30000</v>
+      </c>
+      <c r="M15">
+        <v>30000</v>
+      </c>
+      <c r="N15">
+        <v>30000</v>
+      </c>
+      <c r="O15">
+        <v>30000</v>
+      </c>
+      <c r="P15">
+        <v>30000</v>
+      </c>
+      <c r="Q15">
+        <v>30000</v>
+      </c>
+      <c r="R15">
+        <v>30000</v>
+      </c>
+      <c r="S15">
+        <v>30000</v>
+      </c>
+      <c r="T15">
+        <v>30000</v>
+      </c>
+      <c r="U15">
+        <v>30000</v>
+      </c>
+      <c r="V15">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>2038</v>
+      </c>
+      <c r="B16">
+        <v>650000</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>3000</v>
+      </c>
+      <c r="E16">
+        <v>600</v>
+      </c>
+      <c r="F16">
+        <v>8000</v>
+      </c>
+      <c r="G16">
+        <v>40000</v>
+      </c>
+      <c r="H16">
+        <v>15000</v>
+      </c>
+      <c r="I16">
+        <v>30000</v>
+      </c>
+      <c r="J16">
+        <v>30000</v>
+      </c>
+      <c r="K16">
+        <v>30000</v>
+      </c>
+      <c r="L16">
+        <v>30000</v>
+      </c>
+      <c r="M16">
+        <v>30000</v>
+      </c>
+      <c r="N16">
+        <v>30000</v>
+      </c>
+      <c r="O16">
+        <v>30000</v>
+      </c>
+      <c r="P16">
+        <v>30000</v>
+      </c>
+      <c r="Q16">
+        <v>30000</v>
+      </c>
+      <c r="R16">
+        <v>30000</v>
+      </c>
+      <c r="S16">
+        <v>30000</v>
+      </c>
+      <c r="T16">
+        <v>30000</v>
+      </c>
+      <c r="U16">
+        <v>30000</v>
+      </c>
+      <c r="V16">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>2039</v>
+      </c>
+      <c r="B17">
+        <v>650000</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>3000</v>
+      </c>
+      <c r="E17">
+        <v>600</v>
+      </c>
+      <c r="F17">
+        <v>8000</v>
+      </c>
+      <c r="G17">
+        <v>40000</v>
+      </c>
+      <c r="H17">
+        <v>15000</v>
+      </c>
+      <c r="I17">
+        <v>30000</v>
+      </c>
+      <c r="J17">
+        <v>30000</v>
+      </c>
+      <c r="K17">
+        <v>30000</v>
+      </c>
+      <c r="L17">
+        <v>30000</v>
+      </c>
+      <c r="M17">
+        <v>30000</v>
+      </c>
+      <c r="N17">
+        <v>30000</v>
+      </c>
+      <c r="O17">
+        <v>30000</v>
+      </c>
+      <c r="P17">
+        <v>30000</v>
+      </c>
+      <c r="Q17">
+        <v>30000</v>
+      </c>
+      <c r="R17">
+        <v>30000</v>
+      </c>
+      <c r="S17">
+        <v>30000</v>
+      </c>
+      <c r="T17">
+        <v>30000</v>
+      </c>
+      <c r="U17">
+        <v>30000</v>
+      </c>
+      <c r="V17">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>2040</v>
+      </c>
+      <c r="B18">
+        <v>650000</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18">
+        <v>3000</v>
+      </c>
+      <c r="E18">
+        <v>600</v>
+      </c>
+      <c r="F18">
+        <v>8000</v>
+      </c>
+      <c r="G18">
+        <v>40000</v>
+      </c>
+      <c r="H18">
+        <v>15000</v>
+      </c>
+      <c r="I18">
+        <v>30000</v>
+      </c>
+      <c r="J18">
+        <v>30000</v>
+      </c>
+      <c r="K18">
+        <v>30000</v>
+      </c>
+      <c r="L18">
+        <v>30000</v>
+      </c>
+      <c r="M18">
+        <v>30000</v>
+      </c>
+      <c r="N18">
+        <v>30000</v>
+      </c>
+      <c r="O18">
+        <v>30000</v>
+      </c>
+      <c r="P18">
+        <v>30000</v>
+      </c>
+      <c r="Q18">
+        <v>30000</v>
+      </c>
+      <c r="R18">
+        <v>30000</v>
+      </c>
+      <c r="S18">
+        <v>30000</v>
+      </c>
+      <c r="T18">
+        <v>30000</v>
+      </c>
+      <c r="U18">
+        <v>30000</v>
+      </c>
+      <c r="V18">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>2041</v>
+      </c>
+      <c r="B19">
+        <v>650000</v>
+      </c>
+      <c r="C19">
+        <v>100</v>
+      </c>
+      <c r="D19">
+        <v>3000</v>
+      </c>
+      <c r="E19">
+        <v>600</v>
+      </c>
+      <c r="F19">
+        <v>8000</v>
+      </c>
+      <c r="G19">
+        <v>40000</v>
+      </c>
+      <c r="H19">
+        <v>15000</v>
+      </c>
+      <c r="I19">
+        <v>30000</v>
+      </c>
+      <c r="J19">
+        <v>30000</v>
+      </c>
+      <c r="K19">
+        <v>30000</v>
+      </c>
+      <c r="L19">
+        <v>30000</v>
+      </c>
+      <c r="M19">
+        <v>30000</v>
+      </c>
+      <c r="N19">
+        <v>30000</v>
+      </c>
+      <c r="O19">
+        <v>30000</v>
+      </c>
+      <c r="P19">
+        <v>30000</v>
+      </c>
+      <c r="Q19">
+        <v>30000</v>
+      </c>
+      <c r="R19">
+        <v>30000</v>
+      </c>
+      <c r="S19">
+        <v>30000</v>
+      </c>
+      <c r="T19">
+        <v>30000</v>
+      </c>
+      <c r="U19">
+        <v>30000</v>
+      </c>
+      <c r="V19">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>2042</v>
+      </c>
+      <c r="B20">
+        <v>650000</v>
+      </c>
+      <c r="C20">
+        <v>100</v>
+      </c>
+      <c r="D20">
+        <v>3000</v>
+      </c>
+      <c r="E20">
+        <v>600</v>
+      </c>
+      <c r="F20">
+        <v>8000</v>
+      </c>
+      <c r="G20">
+        <v>40000</v>
+      </c>
+      <c r="H20">
+        <v>15000</v>
+      </c>
+      <c r="I20">
+        <v>30000</v>
+      </c>
+      <c r="J20">
+        <v>30000</v>
+      </c>
+      <c r="K20">
+        <v>30000</v>
+      </c>
+      <c r="L20">
+        <v>30000</v>
+      </c>
+      <c r="M20">
+        <v>30000</v>
+      </c>
+      <c r="N20">
+        <v>30000</v>
+      </c>
+      <c r="O20">
+        <v>30000</v>
+      </c>
+      <c r="P20">
+        <v>30000</v>
+      </c>
+      <c r="Q20">
+        <v>30000</v>
+      </c>
+      <c r="R20">
+        <v>30000</v>
+      </c>
+      <c r="S20">
+        <v>30000</v>
+      </c>
+      <c r="T20">
+        <v>30000</v>
+      </c>
+      <c r="U20">
+        <v>30000</v>
+      </c>
+      <c r="V20">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="16">
+        <v>2043</v>
+      </c>
+      <c r="B21">
+        <v>650000</v>
+      </c>
+      <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>3000</v>
+      </c>
+      <c r="E21">
+        <v>600</v>
+      </c>
+      <c r="F21">
+        <v>8000</v>
+      </c>
+      <c r="G21">
+        <v>40000</v>
+      </c>
+      <c r="H21">
+        <v>15000</v>
+      </c>
+      <c r="I21">
+        <v>30000</v>
+      </c>
+      <c r="J21">
+        <v>30000</v>
+      </c>
+      <c r="K21">
+        <v>30000</v>
+      </c>
+      <c r="L21">
+        <v>30000</v>
+      </c>
+      <c r="M21">
+        <v>30000</v>
+      </c>
+      <c r="N21">
+        <v>30000</v>
+      </c>
+      <c r="O21">
+        <v>30000</v>
+      </c>
+      <c r="P21">
+        <v>30000</v>
+      </c>
+      <c r="Q21">
+        <v>30000</v>
+      </c>
+      <c r="R21">
+        <v>30000</v>
+      </c>
+      <c r="S21">
+        <v>30000</v>
+      </c>
+      <c r="T21">
+        <v>30000</v>
+      </c>
+      <c r="U21">
+        <v>30000</v>
+      </c>
+      <c r="V21">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>2044</v>
+      </c>
+      <c r="B22">
+        <v>650000</v>
+      </c>
+      <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22">
+        <v>3000</v>
+      </c>
+      <c r="E22">
+        <v>600</v>
+      </c>
+      <c r="F22">
+        <v>8000</v>
+      </c>
+      <c r="G22">
+        <v>40000</v>
+      </c>
+      <c r="H22">
+        <v>15000</v>
+      </c>
+      <c r="I22">
+        <v>30000</v>
+      </c>
+      <c r="J22">
+        <v>30000</v>
+      </c>
+      <c r="K22">
+        <v>30000</v>
+      </c>
+      <c r="L22">
+        <v>30000</v>
+      </c>
+      <c r="M22">
+        <v>30000</v>
+      </c>
+      <c r="N22">
+        <v>30000</v>
+      </c>
+      <c r="O22">
+        <v>30000</v>
+      </c>
+      <c r="P22">
+        <v>30000</v>
+      </c>
+      <c r="Q22">
+        <v>30000</v>
+      </c>
+      <c r="R22">
+        <v>30000</v>
+      </c>
+      <c r="S22">
+        <v>30000</v>
+      </c>
+      <c r="T22">
+        <v>30000</v>
+      </c>
+      <c r="U22">
+        <v>30000</v>
+      </c>
+      <c r="V22">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>2045</v>
+      </c>
+      <c r="B23">
+        <v>650000</v>
+      </c>
+      <c r="C23">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>3000</v>
+      </c>
+      <c r="E23">
+        <v>600</v>
+      </c>
+      <c r="F23">
+        <v>8000</v>
+      </c>
+      <c r="G23">
+        <v>40000</v>
+      </c>
+      <c r="H23">
+        <v>15000</v>
+      </c>
+      <c r="I23">
+        <v>30000</v>
+      </c>
+      <c r="J23">
+        <v>30000</v>
+      </c>
+      <c r="K23">
+        <v>30000</v>
+      </c>
+      <c r="L23">
+        <v>30000</v>
+      </c>
+      <c r="M23">
+        <v>30000</v>
+      </c>
+      <c r="N23">
+        <v>30000</v>
+      </c>
+      <c r="O23">
+        <v>30000</v>
+      </c>
+      <c r="P23">
+        <v>30000</v>
+      </c>
+      <c r="Q23">
+        <v>30000</v>
+      </c>
+      <c r="R23">
+        <v>30000</v>
+      </c>
+      <c r="S23">
+        <v>30000</v>
+      </c>
+      <c r="T23">
+        <v>30000</v>
+      </c>
+      <c r="U23">
+        <v>30000</v>
+      </c>
+      <c r="V23">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>2046</v>
+      </c>
+      <c r="B24">
+        <v>650000</v>
+      </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>3000</v>
+      </c>
+      <c r="E24">
+        <v>600</v>
+      </c>
+      <c r="F24">
+        <v>8000</v>
+      </c>
+      <c r="G24">
+        <v>40000</v>
+      </c>
+      <c r="H24">
+        <v>15000</v>
+      </c>
+      <c r="I24">
+        <v>30000</v>
+      </c>
+      <c r="J24">
+        <v>30000</v>
+      </c>
+      <c r="K24">
+        <v>30000</v>
+      </c>
+      <c r="L24">
+        <v>30000</v>
+      </c>
+      <c r="M24">
+        <v>30000</v>
+      </c>
+      <c r="N24">
+        <v>30000</v>
+      </c>
+      <c r="O24">
+        <v>30000</v>
+      </c>
+      <c r="P24">
+        <v>30000</v>
+      </c>
+      <c r="Q24">
+        <v>30000</v>
+      </c>
+      <c r="R24">
+        <v>30000</v>
+      </c>
+      <c r="S24">
+        <v>30000</v>
+      </c>
+      <c r="T24">
+        <v>30000</v>
+      </c>
+      <c r="U24">
+        <v>30000</v>
+      </c>
+      <c r="V24">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <v>2047</v>
+      </c>
+      <c r="B25">
+        <v>650000</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>3000</v>
+      </c>
+      <c r="E25">
+        <v>600</v>
+      </c>
+      <c r="F25">
+        <v>8000</v>
+      </c>
+      <c r="G25">
+        <v>40000</v>
+      </c>
+      <c r="H25">
+        <v>15000</v>
+      </c>
+      <c r="I25">
+        <v>30000</v>
+      </c>
+      <c r="J25">
+        <v>30000</v>
+      </c>
+      <c r="K25">
+        <v>30000</v>
+      </c>
+      <c r="L25">
+        <v>30000</v>
+      </c>
+      <c r="M25">
+        <v>30000</v>
+      </c>
+      <c r="N25">
+        <v>30000</v>
+      </c>
+      <c r="O25">
+        <v>30000</v>
+      </c>
+      <c r="P25">
+        <v>30000</v>
+      </c>
+      <c r="Q25">
+        <v>30000</v>
+      </c>
+      <c r="R25">
+        <v>30000</v>
+      </c>
+      <c r="S25">
+        <v>30000</v>
+      </c>
+      <c r="T25">
+        <v>30000</v>
+      </c>
+      <c r="U25">
+        <v>30000</v>
+      </c>
+      <c r="V25">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
+        <v>2048</v>
+      </c>
+      <c r="B26">
+        <v>650000</v>
+      </c>
+      <c r="C26">
+        <v>100</v>
+      </c>
+      <c r="D26">
+        <v>3000</v>
+      </c>
+      <c r="E26">
+        <v>600</v>
+      </c>
+      <c r="F26">
+        <v>8000</v>
+      </c>
+      <c r="G26">
+        <v>40000</v>
+      </c>
+      <c r="H26">
+        <v>15000</v>
+      </c>
+      <c r="I26">
+        <v>30000</v>
+      </c>
+      <c r="J26">
+        <v>30000</v>
+      </c>
+      <c r="K26">
+        <v>30000</v>
+      </c>
+      <c r="L26">
+        <v>30000</v>
+      </c>
+      <c r="M26">
+        <v>30000</v>
+      </c>
+      <c r="N26">
+        <v>30000</v>
+      </c>
+      <c r="O26">
+        <v>30000</v>
+      </c>
+      <c r="P26">
+        <v>30000</v>
+      </c>
+      <c r="Q26">
+        <v>30000</v>
+      </c>
+      <c r="R26">
+        <v>30000</v>
+      </c>
+      <c r="S26">
+        <v>30000</v>
+      </c>
+      <c r="T26">
+        <v>30000</v>
+      </c>
+      <c r="U26">
+        <v>30000</v>
+      </c>
+      <c r="V26">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>2049</v>
+      </c>
+      <c r="B27">
+        <v>650000</v>
+      </c>
+      <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27">
+        <v>3000</v>
+      </c>
+      <c r="E27">
+        <v>600</v>
+      </c>
+      <c r="F27">
+        <v>8000</v>
+      </c>
+      <c r="G27">
+        <v>40000</v>
+      </c>
+      <c r="H27">
+        <v>15000</v>
+      </c>
+      <c r="I27">
+        <v>30000</v>
+      </c>
+      <c r="J27">
+        <v>30000</v>
+      </c>
+      <c r="K27">
+        <v>30000</v>
+      </c>
+      <c r="L27">
+        <v>30000</v>
+      </c>
+      <c r="M27">
+        <v>30000</v>
+      </c>
+      <c r="N27">
+        <v>30000</v>
+      </c>
+      <c r="O27">
+        <v>30000</v>
+      </c>
+      <c r="P27">
+        <v>30000</v>
+      </c>
+      <c r="Q27">
+        <v>30000</v>
+      </c>
+      <c r="R27">
+        <v>30000</v>
+      </c>
+      <c r="S27">
+        <v>30000</v>
+      </c>
+      <c r="T27">
+        <v>30000</v>
+      </c>
+      <c r="U27">
+        <v>30000</v>
+      </c>
+      <c r="V27">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>2050</v>
+      </c>
+      <c r="B28">
+        <v>650000</v>
+      </c>
+      <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28">
+        <v>3000</v>
+      </c>
+      <c r="E28">
+        <v>600</v>
+      </c>
+      <c r="F28">
+        <v>8000</v>
+      </c>
+      <c r="G28">
+        <v>40000</v>
+      </c>
+      <c r="H28">
+        <v>15000</v>
+      </c>
+      <c r="I28">
+        <v>30000</v>
+      </c>
+      <c r="J28">
+        <v>30000</v>
+      </c>
+      <c r="K28">
+        <v>30000</v>
+      </c>
+      <c r="L28">
+        <v>30000</v>
+      </c>
+      <c r="M28">
+        <v>30000</v>
+      </c>
+      <c r="N28">
+        <v>30000</v>
+      </c>
+      <c r="O28">
+        <v>30000</v>
+      </c>
+      <c r="P28">
+        <v>30000</v>
+      </c>
+      <c r="Q28">
+        <v>30000</v>
+      </c>
+      <c r="R28">
+        <v>30000</v>
+      </c>
+      <c r="S28">
+        <v>30000</v>
+      </c>
+      <c r="T28">
+        <v>30000</v>
+      </c>
+      <c r="U28">
+        <v>30000</v>
+      </c>
+      <c r="V28">
+        <v>30000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0643026C-02E1-4FD1-A973-B34B54E790E8}">
+  <dimension ref="A1:V28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="16">
+        <v>2024</v>
+      </c>
+      <c r="B2">
+        <v>700000</v>
+      </c>
+      <c r="C2">
+        <v>150</v>
+      </c>
+      <c r="D2">
+        <v>3500</v>
+      </c>
+      <c r="E2">
+        <v>800</v>
+      </c>
+      <c r="F2">
+        <v>9500</v>
+      </c>
+      <c r="G2">
+        <v>50000</v>
+      </c>
+      <c r="H2">
+        <v>18000</v>
+      </c>
+      <c r="I2">
+        <v>35000</v>
+      </c>
+      <c r="J2">
+        <v>35000</v>
+      </c>
+      <c r="K2">
+        <v>35000</v>
+      </c>
+      <c r="L2">
+        <v>35000</v>
+      </c>
+      <c r="M2">
+        <v>35000</v>
+      </c>
+      <c r="N2">
+        <v>35000</v>
+      </c>
+      <c r="O2">
+        <v>35000</v>
+      </c>
+      <c r="P2">
+        <v>35000</v>
+      </c>
+      <c r="Q2">
+        <v>35000</v>
+      </c>
+      <c r="R2">
+        <v>35000</v>
+      </c>
+      <c r="S2">
+        <v>35000</v>
+      </c>
+      <c r="T2">
+        <v>35000</v>
+      </c>
+      <c r="U2">
+        <v>35000</v>
+      </c>
+      <c r="V2">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>700000</v>
+      </c>
+      <c r="C3">
+        <v>150</v>
+      </c>
+      <c r="D3">
+        <v>3500</v>
+      </c>
+      <c r="E3">
+        <v>800</v>
+      </c>
+      <c r="F3">
+        <v>9500</v>
+      </c>
+      <c r="G3">
+        <v>50000</v>
+      </c>
+      <c r="H3">
+        <v>18000</v>
+      </c>
+      <c r="I3">
+        <v>35000</v>
+      </c>
+      <c r="J3">
+        <v>35000</v>
+      </c>
+      <c r="K3">
+        <v>35000</v>
+      </c>
+      <c r="L3">
+        <v>35000</v>
+      </c>
+      <c r="M3">
+        <v>35000</v>
+      </c>
+      <c r="N3">
+        <v>35000</v>
+      </c>
+      <c r="O3">
+        <v>35000</v>
+      </c>
+      <c r="P3">
+        <v>35000</v>
+      </c>
+      <c r="Q3">
+        <v>35000</v>
+      </c>
+      <c r="R3">
+        <v>35000</v>
+      </c>
+      <c r="S3">
+        <v>35000</v>
+      </c>
+      <c r="T3">
+        <v>35000</v>
+      </c>
+      <c r="U3">
+        <v>35000</v>
+      </c>
+      <c r="V3">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>700000</v>
+      </c>
+      <c r="C4">
+        <v>150</v>
+      </c>
+      <c r="D4">
+        <v>3500</v>
+      </c>
+      <c r="E4">
+        <v>800</v>
+      </c>
+      <c r="F4">
+        <v>9500</v>
+      </c>
+      <c r="G4">
+        <v>50000</v>
+      </c>
+      <c r="H4">
+        <v>18000</v>
+      </c>
+      <c r="I4">
+        <v>35000</v>
+      </c>
+      <c r="J4">
+        <v>35000</v>
+      </c>
+      <c r="K4">
+        <v>35000</v>
+      </c>
+      <c r="L4">
+        <v>35000</v>
+      </c>
+      <c r="M4">
+        <v>35000</v>
+      </c>
+      <c r="N4">
+        <v>35000</v>
+      </c>
+      <c r="O4">
+        <v>35000</v>
+      </c>
+      <c r="P4">
+        <v>35000</v>
+      </c>
+      <c r="Q4">
+        <v>35000</v>
+      </c>
+      <c r="R4">
+        <v>35000</v>
+      </c>
+      <c r="S4">
+        <v>35000</v>
+      </c>
+      <c r="T4">
+        <v>35000</v>
+      </c>
+      <c r="U4">
+        <v>35000</v>
+      </c>
+      <c r="V4">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B5">
+        <v>700000</v>
+      </c>
+      <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5">
+        <v>3500</v>
+      </c>
+      <c r="E5">
+        <v>800</v>
+      </c>
+      <c r="F5">
+        <v>9500</v>
+      </c>
+      <c r="G5">
+        <v>50000</v>
+      </c>
+      <c r="H5">
+        <v>18000</v>
+      </c>
+      <c r="I5">
+        <v>35000</v>
+      </c>
+      <c r="J5">
+        <v>35000</v>
+      </c>
+      <c r="K5">
+        <v>35000</v>
+      </c>
+      <c r="L5">
+        <v>35000</v>
+      </c>
+      <c r="M5">
+        <v>35000</v>
+      </c>
+      <c r="N5">
+        <v>35000</v>
+      </c>
+      <c r="O5">
+        <v>35000</v>
+      </c>
+      <c r="P5">
+        <v>35000</v>
+      </c>
+      <c r="Q5">
+        <v>35000</v>
+      </c>
+      <c r="R5">
+        <v>35000</v>
+      </c>
+      <c r="S5">
+        <v>35000</v>
+      </c>
+      <c r="T5">
+        <v>35000</v>
+      </c>
+      <c r="U5">
+        <v>35000</v>
+      </c>
+      <c r="V5">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>2028</v>
+      </c>
+      <c r="B6">
+        <v>700000</v>
+      </c>
+      <c r="C6">
+        <v>150</v>
+      </c>
+      <c r="D6">
+        <v>3500</v>
+      </c>
+      <c r="E6">
+        <v>800</v>
+      </c>
+      <c r="F6">
+        <v>9500</v>
+      </c>
+      <c r="G6">
+        <v>50000</v>
+      </c>
+      <c r="H6">
+        <v>18000</v>
+      </c>
+      <c r="I6">
+        <v>35000</v>
+      </c>
+      <c r="J6">
+        <v>35000</v>
+      </c>
+      <c r="K6">
+        <v>35000</v>
+      </c>
+      <c r="L6">
+        <v>35000</v>
+      </c>
+      <c r="M6">
+        <v>35000</v>
+      </c>
+      <c r="N6">
+        <v>35000</v>
+      </c>
+      <c r="O6">
+        <v>35000</v>
+      </c>
+      <c r="P6">
+        <v>35000</v>
+      </c>
+      <c r="Q6">
+        <v>35000</v>
+      </c>
+      <c r="R6">
+        <v>35000</v>
+      </c>
+      <c r="S6">
+        <v>35000</v>
+      </c>
+      <c r="T6">
+        <v>35000</v>
+      </c>
+      <c r="U6">
+        <v>35000</v>
+      </c>
+      <c r="V6">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>2029</v>
+      </c>
+      <c r="B7">
+        <v>700000</v>
+      </c>
+      <c r="C7">
+        <v>150</v>
+      </c>
+      <c r="D7">
+        <v>3500</v>
+      </c>
+      <c r="E7">
+        <v>800</v>
+      </c>
+      <c r="F7">
+        <v>9500</v>
+      </c>
+      <c r="G7">
+        <v>50000</v>
+      </c>
+      <c r="H7">
+        <v>18000</v>
+      </c>
+      <c r="I7">
+        <v>35000</v>
+      </c>
+      <c r="J7">
+        <v>35000</v>
+      </c>
+      <c r="K7">
+        <v>35000</v>
+      </c>
+      <c r="L7">
+        <v>35000</v>
+      </c>
+      <c r="M7">
+        <v>35000</v>
+      </c>
+      <c r="N7">
+        <v>35000</v>
+      </c>
+      <c r="O7">
+        <v>35000</v>
+      </c>
+      <c r="P7">
+        <v>35000</v>
+      </c>
+      <c r="Q7">
+        <v>35000</v>
+      </c>
+      <c r="R7">
+        <v>35000</v>
+      </c>
+      <c r="S7">
+        <v>35000</v>
+      </c>
+      <c r="T7">
+        <v>35000</v>
+      </c>
+      <c r="U7">
+        <v>35000</v>
+      </c>
+      <c r="V7">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>2030</v>
+      </c>
+      <c r="B8">
+        <v>700000</v>
+      </c>
+      <c r="C8">
+        <v>150</v>
+      </c>
+      <c r="D8">
+        <v>3500</v>
+      </c>
+      <c r="E8">
+        <v>800</v>
+      </c>
+      <c r="F8">
+        <v>9500</v>
+      </c>
+      <c r="G8">
+        <v>50000</v>
+      </c>
+      <c r="H8">
+        <v>18000</v>
+      </c>
+      <c r="I8">
+        <v>35000</v>
+      </c>
+      <c r="J8">
+        <v>35000</v>
+      </c>
+      <c r="K8">
+        <v>35000</v>
+      </c>
+      <c r="L8">
+        <v>35000</v>
+      </c>
+      <c r="M8">
+        <v>35000</v>
+      </c>
+      <c r="N8">
+        <v>35000</v>
+      </c>
+      <c r="O8">
+        <v>35000</v>
+      </c>
+      <c r="P8">
+        <v>35000</v>
+      </c>
+      <c r="Q8">
+        <v>35000</v>
+      </c>
+      <c r="R8">
+        <v>35000</v>
+      </c>
+      <c r="S8">
+        <v>35000</v>
+      </c>
+      <c r="T8">
+        <v>35000</v>
+      </c>
+      <c r="U8">
+        <v>35000</v>
+      </c>
+      <c r="V8">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>2031</v>
+      </c>
+      <c r="B9">
+        <v>700000</v>
+      </c>
+      <c r="C9">
+        <v>150</v>
+      </c>
+      <c r="D9">
+        <v>3500</v>
+      </c>
+      <c r="E9">
+        <v>800</v>
+      </c>
+      <c r="F9">
+        <v>9500</v>
+      </c>
+      <c r="G9">
+        <v>50000</v>
+      </c>
+      <c r="H9">
+        <v>18000</v>
+      </c>
+      <c r="I9">
+        <v>35000</v>
+      </c>
+      <c r="J9">
+        <v>35000</v>
+      </c>
+      <c r="K9">
+        <v>35000</v>
+      </c>
+      <c r="L9">
+        <v>35000</v>
+      </c>
+      <c r="M9">
+        <v>35000</v>
+      </c>
+      <c r="N9">
+        <v>35000</v>
+      </c>
+      <c r="O9">
+        <v>35000</v>
+      </c>
+      <c r="P9">
+        <v>35000</v>
+      </c>
+      <c r="Q9">
+        <v>35000</v>
+      </c>
+      <c r="R9">
+        <v>35000</v>
+      </c>
+      <c r="S9">
+        <v>35000</v>
+      </c>
+      <c r="T9">
+        <v>35000</v>
+      </c>
+      <c r="U9">
+        <v>35000</v>
+      </c>
+      <c r="V9">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>2032</v>
+      </c>
+      <c r="B10">
+        <v>700000</v>
+      </c>
+      <c r="C10">
+        <v>150</v>
+      </c>
+      <c r="D10">
+        <v>3500</v>
+      </c>
+      <c r="E10">
+        <v>800</v>
+      </c>
+      <c r="F10">
+        <v>9500</v>
+      </c>
+      <c r="G10">
+        <v>50000</v>
+      </c>
+      <c r="H10">
+        <v>18000</v>
+      </c>
+      <c r="I10">
+        <v>35000</v>
+      </c>
+      <c r="J10">
+        <v>35000</v>
+      </c>
+      <c r="K10">
+        <v>35000</v>
+      </c>
+      <c r="L10">
+        <v>35000</v>
+      </c>
+      <c r="M10">
+        <v>35000</v>
+      </c>
+      <c r="N10">
+        <v>35000</v>
+      </c>
+      <c r="O10">
+        <v>35000</v>
+      </c>
+      <c r="P10">
+        <v>35000</v>
+      </c>
+      <c r="Q10">
+        <v>35000</v>
+      </c>
+      <c r="R10">
+        <v>35000</v>
+      </c>
+      <c r="S10">
+        <v>35000</v>
+      </c>
+      <c r="T10">
+        <v>35000</v>
+      </c>
+      <c r="U10">
+        <v>35000</v>
+      </c>
+      <c r="V10">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>2033</v>
+      </c>
+      <c r="B11">
+        <v>700000</v>
+      </c>
+      <c r="C11">
+        <v>150</v>
+      </c>
+      <c r="D11">
+        <v>3500</v>
+      </c>
+      <c r="E11">
+        <v>800</v>
+      </c>
+      <c r="F11">
+        <v>9500</v>
+      </c>
+      <c r="G11">
+        <v>50000</v>
+      </c>
+      <c r="H11">
+        <v>18000</v>
+      </c>
+      <c r="I11">
+        <v>35000</v>
+      </c>
+      <c r="J11">
+        <v>35000</v>
+      </c>
+      <c r="K11">
+        <v>35000</v>
+      </c>
+      <c r="L11">
+        <v>35000</v>
+      </c>
+      <c r="M11">
+        <v>35000</v>
+      </c>
+      <c r="N11">
+        <v>35000</v>
+      </c>
+      <c r="O11">
+        <v>35000</v>
+      </c>
+      <c r="P11">
+        <v>35000</v>
+      </c>
+      <c r="Q11">
+        <v>35000</v>
+      </c>
+      <c r="R11">
+        <v>35000</v>
+      </c>
+      <c r="S11">
+        <v>35000</v>
+      </c>
+      <c r="T11">
+        <v>35000</v>
+      </c>
+      <c r="U11">
+        <v>35000</v>
+      </c>
+      <c r="V11">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>2034</v>
+      </c>
+      <c r="B12">
+        <v>700000</v>
+      </c>
+      <c r="C12">
+        <v>150</v>
+      </c>
+      <c r="D12">
+        <v>3500</v>
+      </c>
+      <c r="E12">
+        <v>800</v>
+      </c>
+      <c r="F12">
+        <v>9500</v>
+      </c>
+      <c r="G12">
+        <v>50000</v>
+      </c>
+      <c r="H12">
+        <v>18000</v>
+      </c>
+      <c r="I12">
+        <v>35000</v>
+      </c>
+      <c r="J12">
+        <v>35000</v>
+      </c>
+      <c r="K12">
+        <v>35000</v>
+      </c>
+      <c r="L12">
+        <v>35000</v>
+      </c>
+      <c r="M12">
+        <v>35000</v>
+      </c>
+      <c r="N12">
+        <v>35000</v>
+      </c>
+      <c r="O12">
+        <v>35000</v>
+      </c>
+      <c r="P12">
+        <v>35000</v>
+      </c>
+      <c r="Q12">
+        <v>35000</v>
+      </c>
+      <c r="R12">
+        <v>35000</v>
+      </c>
+      <c r="S12">
+        <v>35000</v>
+      </c>
+      <c r="T12">
+        <v>35000</v>
+      </c>
+      <c r="U12">
+        <v>35000</v>
+      </c>
+      <c r="V12">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>2035</v>
+      </c>
+      <c r="B13">
+        <v>700000</v>
+      </c>
+      <c r="C13">
+        <v>150</v>
+      </c>
+      <c r="D13">
+        <v>3500</v>
+      </c>
+      <c r="E13">
+        <v>800</v>
+      </c>
+      <c r="F13">
+        <v>9500</v>
+      </c>
+      <c r="G13">
+        <v>50000</v>
+      </c>
+      <c r="H13">
+        <v>18000</v>
+      </c>
+      <c r="I13">
+        <v>35000</v>
+      </c>
+      <c r="J13">
+        <v>35000</v>
+      </c>
+      <c r="K13">
+        <v>35000</v>
+      </c>
+      <c r="L13">
+        <v>35000</v>
+      </c>
+      <c r="M13">
+        <v>35000</v>
+      </c>
+      <c r="N13">
+        <v>35000</v>
+      </c>
+      <c r="O13">
+        <v>35000</v>
+      </c>
+      <c r="P13">
+        <v>35000</v>
+      </c>
+      <c r="Q13">
+        <v>35000</v>
+      </c>
+      <c r="R13">
+        <v>35000</v>
+      </c>
+      <c r="S13">
+        <v>35000</v>
+      </c>
+      <c r="T13">
+        <v>35000</v>
+      </c>
+      <c r="U13">
+        <v>35000</v>
+      </c>
+      <c r="V13">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>2036</v>
+      </c>
+      <c r="B14">
+        <v>700000</v>
+      </c>
+      <c r="C14">
+        <v>150</v>
+      </c>
+      <c r="D14">
+        <v>3500</v>
+      </c>
+      <c r="E14">
+        <v>800</v>
+      </c>
+      <c r="F14">
+        <v>9500</v>
+      </c>
+      <c r="G14">
+        <v>50000</v>
+      </c>
+      <c r="H14">
+        <v>18000</v>
+      </c>
+      <c r="I14">
+        <v>35000</v>
+      </c>
+      <c r="J14">
+        <v>35000</v>
+      </c>
+      <c r="K14">
+        <v>35000</v>
+      </c>
+      <c r="L14">
+        <v>35000</v>
+      </c>
+      <c r="M14">
+        <v>35000</v>
+      </c>
+      <c r="N14">
+        <v>35000</v>
+      </c>
+      <c r="O14">
+        <v>35000</v>
+      </c>
+      <c r="P14">
+        <v>35000</v>
+      </c>
+      <c r="Q14">
+        <v>35000</v>
+      </c>
+      <c r="R14">
+        <v>35000</v>
+      </c>
+      <c r="S14">
+        <v>35000</v>
+      </c>
+      <c r="T14">
+        <v>35000</v>
+      </c>
+      <c r="U14">
+        <v>35000</v>
+      </c>
+      <c r="V14">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>2037</v>
+      </c>
+      <c r="B15">
+        <v>700000</v>
+      </c>
+      <c r="C15">
+        <v>150</v>
+      </c>
+      <c r="D15">
+        <v>3500</v>
+      </c>
+      <c r="E15">
+        <v>800</v>
+      </c>
+      <c r="F15">
+        <v>9500</v>
+      </c>
+      <c r="G15">
+        <v>50000</v>
+      </c>
+      <c r="H15">
+        <v>18000</v>
+      </c>
+      <c r="I15">
+        <v>35000</v>
+      </c>
+      <c r="J15">
+        <v>35000</v>
+      </c>
+      <c r="K15">
+        <v>35000</v>
+      </c>
+      <c r="L15">
+        <v>35000</v>
+      </c>
+      <c r="M15">
+        <v>35000</v>
+      </c>
+      <c r="N15">
+        <v>35000</v>
+      </c>
+      <c r="O15">
+        <v>35000</v>
+      </c>
+      <c r="P15">
+        <v>35000</v>
+      </c>
+      <c r="Q15">
+        <v>35000</v>
+      </c>
+      <c r="R15">
+        <v>35000</v>
+      </c>
+      <c r="S15">
+        <v>35000</v>
+      </c>
+      <c r="T15">
+        <v>35000</v>
+      </c>
+      <c r="U15">
+        <v>35000</v>
+      </c>
+      <c r="V15">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>2038</v>
+      </c>
+      <c r="B16">
+        <v>700000</v>
+      </c>
+      <c r="C16">
+        <v>150</v>
+      </c>
+      <c r="D16">
+        <v>3500</v>
+      </c>
+      <c r="E16">
+        <v>800</v>
+      </c>
+      <c r="F16">
+        <v>9500</v>
+      </c>
+      <c r="G16">
+        <v>50000</v>
+      </c>
+      <c r="H16">
+        <v>18000</v>
+      </c>
+      <c r="I16">
+        <v>35000</v>
+      </c>
+      <c r="J16">
+        <v>35000</v>
+      </c>
+      <c r="K16">
+        <v>35000</v>
+      </c>
+      <c r="L16">
+        <v>35000</v>
+      </c>
+      <c r="M16">
+        <v>35000</v>
+      </c>
+      <c r="N16">
+        <v>35000</v>
+      </c>
+      <c r="O16">
+        <v>35000</v>
+      </c>
+      <c r="P16">
+        <v>35000</v>
+      </c>
+      <c r="Q16">
+        <v>35000</v>
+      </c>
+      <c r="R16">
+        <v>35000</v>
+      </c>
+      <c r="S16">
+        <v>35000</v>
+      </c>
+      <c r="T16">
+        <v>35000</v>
+      </c>
+      <c r="U16">
+        <v>35000</v>
+      </c>
+      <c r="V16">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>2039</v>
+      </c>
+      <c r="B17">
+        <v>700000</v>
+      </c>
+      <c r="C17">
+        <v>150</v>
+      </c>
+      <c r="D17">
+        <v>3500</v>
+      </c>
+      <c r="E17">
+        <v>800</v>
+      </c>
+      <c r="F17">
+        <v>9500</v>
+      </c>
+      <c r="G17">
+        <v>50000</v>
+      </c>
+      <c r="H17">
+        <v>18000</v>
+      </c>
+      <c r="I17">
+        <v>35000</v>
+      </c>
+      <c r="J17">
+        <v>35000</v>
+      </c>
+      <c r="K17">
+        <v>35000</v>
+      </c>
+      <c r="L17">
+        <v>35000</v>
+      </c>
+      <c r="M17">
+        <v>35000</v>
+      </c>
+      <c r="N17">
+        <v>35000</v>
+      </c>
+      <c r="O17">
+        <v>35000</v>
+      </c>
+      <c r="P17">
+        <v>35000</v>
+      </c>
+      <c r="Q17">
+        <v>35000</v>
+      </c>
+      <c r="R17">
+        <v>35000</v>
+      </c>
+      <c r="S17">
+        <v>35000</v>
+      </c>
+      <c r="T17">
+        <v>35000</v>
+      </c>
+      <c r="U17">
+        <v>35000</v>
+      </c>
+      <c r="V17">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>2040</v>
+      </c>
+      <c r="B18">
+        <v>700000</v>
+      </c>
+      <c r="C18">
+        <v>150</v>
+      </c>
+      <c r="D18">
+        <v>3500</v>
+      </c>
+      <c r="E18">
+        <v>800</v>
+      </c>
+      <c r="F18">
+        <v>9500</v>
+      </c>
+      <c r="G18">
+        <v>50000</v>
+      </c>
+      <c r="H18">
+        <v>18000</v>
+      </c>
+      <c r="I18">
+        <v>35000</v>
+      </c>
+      <c r="J18">
+        <v>35000</v>
+      </c>
+      <c r="K18">
+        <v>35000</v>
+      </c>
+      <c r="L18">
+        <v>35000</v>
+      </c>
+      <c r="M18">
+        <v>35000</v>
+      </c>
+      <c r="N18">
+        <v>35000</v>
+      </c>
+      <c r="O18">
+        <v>35000</v>
+      </c>
+      <c r="P18">
+        <v>35000</v>
+      </c>
+      <c r="Q18">
+        <v>35000</v>
+      </c>
+      <c r="R18">
+        <v>35000</v>
+      </c>
+      <c r="S18">
+        <v>35000</v>
+      </c>
+      <c r="T18">
+        <v>35000</v>
+      </c>
+      <c r="U18">
+        <v>35000</v>
+      </c>
+      <c r="V18">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>2041</v>
+      </c>
+      <c r="B19">
+        <v>700000</v>
+      </c>
+      <c r="C19">
+        <v>150</v>
+      </c>
+      <c r="D19">
+        <v>3500</v>
+      </c>
+      <c r="E19">
+        <v>800</v>
+      </c>
+      <c r="F19">
+        <v>9500</v>
+      </c>
+      <c r="G19">
+        <v>50000</v>
+      </c>
+      <c r="H19">
+        <v>18000</v>
+      </c>
+      <c r="I19">
+        <v>35000</v>
+      </c>
+      <c r="J19">
+        <v>35000</v>
+      </c>
+      <c r="K19">
+        <v>35000</v>
+      </c>
+      <c r="L19">
+        <v>35000</v>
+      </c>
+      <c r="M19">
+        <v>35000</v>
+      </c>
+      <c r="N19">
+        <v>35000</v>
+      </c>
+      <c r="O19">
+        <v>35000</v>
+      </c>
+      <c r="P19">
+        <v>35000</v>
+      </c>
+      <c r="Q19">
+        <v>35000</v>
+      </c>
+      <c r="R19">
+        <v>35000</v>
+      </c>
+      <c r="S19">
+        <v>35000</v>
+      </c>
+      <c r="T19">
+        <v>35000</v>
+      </c>
+      <c r="U19">
+        <v>35000</v>
+      </c>
+      <c r="V19">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>2042</v>
+      </c>
+      <c r="B20">
+        <v>700000</v>
+      </c>
+      <c r="C20">
+        <v>150</v>
+      </c>
+      <c r="D20">
+        <v>3500</v>
+      </c>
+      <c r="E20">
+        <v>800</v>
+      </c>
+      <c r="F20">
+        <v>9500</v>
+      </c>
+      <c r="G20">
+        <v>50000</v>
+      </c>
+      <c r="H20">
+        <v>18000</v>
+      </c>
+      <c r="I20">
+        <v>35000</v>
+      </c>
+      <c r="J20">
+        <v>35000</v>
+      </c>
+      <c r="K20">
+        <v>35000</v>
+      </c>
+      <c r="L20">
+        <v>35000</v>
+      </c>
+      <c r="M20">
+        <v>35000</v>
+      </c>
+      <c r="N20">
+        <v>35000</v>
+      </c>
+      <c r="O20">
+        <v>35000</v>
+      </c>
+      <c r="P20">
+        <v>35000</v>
+      </c>
+      <c r="Q20">
+        <v>35000</v>
+      </c>
+      <c r="R20">
+        <v>35000</v>
+      </c>
+      <c r="S20">
+        <v>35000</v>
+      </c>
+      <c r="T20">
+        <v>35000</v>
+      </c>
+      <c r="U20">
+        <v>35000</v>
+      </c>
+      <c r="V20">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="16">
+        <v>2043</v>
+      </c>
+      <c r="B21">
+        <v>700000</v>
+      </c>
+      <c r="C21">
+        <v>150</v>
+      </c>
+      <c r="D21">
+        <v>3500</v>
+      </c>
+      <c r="E21">
+        <v>800</v>
+      </c>
+      <c r="F21">
+        <v>9500</v>
+      </c>
+      <c r="G21">
+        <v>50000</v>
+      </c>
+      <c r="H21">
+        <v>18000</v>
+      </c>
+      <c r="I21">
+        <v>35000</v>
+      </c>
+      <c r="J21">
+        <v>35000</v>
+      </c>
+      <c r="K21">
+        <v>35000</v>
+      </c>
+      <c r="L21">
+        <v>35000</v>
+      </c>
+      <c r="M21">
+        <v>35000</v>
+      </c>
+      <c r="N21">
+        <v>35000</v>
+      </c>
+      <c r="O21">
+        <v>35000</v>
+      </c>
+      <c r="P21">
+        <v>35000</v>
+      </c>
+      <c r="Q21">
+        <v>35000</v>
+      </c>
+      <c r="R21">
+        <v>35000</v>
+      </c>
+      <c r="S21">
+        <v>35000</v>
+      </c>
+      <c r="T21">
+        <v>35000</v>
+      </c>
+      <c r="U21">
+        <v>35000</v>
+      </c>
+      <c r="V21">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>2044</v>
+      </c>
+      <c r="B22">
+        <v>700000</v>
+      </c>
+      <c r="C22">
+        <v>150</v>
+      </c>
+      <c r="D22">
+        <v>3500</v>
+      </c>
+      <c r="E22">
+        <v>800</v>
+      </c>
+      <c r="F22">
+        <v>9500</v>
+      </c>
+      <c r="G22">
+        <v>50000</v>
+      </c>
+      <c r="H22">
+        <v>18000</v>
+      </c>
+      <c r="I22">
+        <v>35000</v>
+      </c>
+      <c r="J22">
+        <v>35000</v>
+      </c>
+      <c r="K22">
+        <v>35000</v>
+      </c>
+      <c r="L22">
+        <v>35000</v>
+      </c>
+      <c r="M22">
+        <v>35000</v>
+      </c>
+      <c r="N22">
+        <v>35000</v>
+      </c>
+      <c r="O22">
+        <v>35000</v>
+      </c>
+      <c r="P22">
+        <v>35000</v>
+      </c>
+      <c r="Q22">
+        <v>35000</v>
+      </c>
+      <c r="R22">
+        <v>35000</v>
+      </c>
+      <c r="S22">
+        <v>35000</v>
+      </c>
+      <c r="T22">
+        <v>35000</v>
+      </c>
+      <c r="U22">
+        <v>35000</v>
+      </c>
+      <c r="V22">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>2045</v>
+      </c>
+      <c r="B23">
+        <v>700000</v>
+      </c>
+      <c r="C23">
+        <v>150</v>
+      </c>
+      <c r="D23">
+        <v>3500</v>
+      </c>
+      <c r="E23">
+        <v>800</v>
+      </c>
+      <c r="F23">
+        <v>9500</v>
+      </c>
+      <c r="G23">
+        <v>50000</v>
+      </c>
+      <c r="H23">
+        <v>18000</v>
+      </c>
+      <c r="I23">
+        <v>35000</v>
+      </c>
+      <c r="J23">
+        <v>35000</v>
+      </c>
+      <c r="K23">
+        <v>35000</v>
+      </c>
+      <c r="L23">
+        <v>35000</v>
+      </c>
+      <c r="M23">
+        <v>35000</v>
+      </c>
+      <c r="N23">
+        <v>35000</v>
+      </c>
+      <c r="O23">
+        <v>35000</v>
+      </c>
+      <c r="P23">
+        <v>35000</v>
+      </c>
+      <c r="Q23">
+        <v>35000</v>
+      </c>
+      <c r="R23">
+        <v>35000</v>
+      </c>
+      <c r="S23">
+        <v>35000</v>
+      </c>
+      <c r="T23">
+        <v>35000</v>
+      </c>
+      <c r="U23">
+        <v>35000</v>
+      </c>
+      <c r="V23">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>2046</v>
+      </c>
+      <c r="B24">
+        <v>700000</v>
+      </c>
+      <c r="C24">
+        <v>150</v>
+      </c>
+      <c r="D24">
+        <v>3500</v>
+      </c>
+      <c r="E24">
+        <v>800</v>
+      </c>
+      <c r="F24">
+        <v>9500</v>
+      </c>
+      <c r="G24">
+        <v>50000</v>
+      </c>
+      <c r="H24">
+        <v>18000</v>
+      </c>
+      <c r="I24">
+        <v>35000</v>
+      </c>
+      <c r="J24">
+        <v>35000</v>
+      </c>
+      <c r="K24">
+        <v>35000</v>
+      </c>
+      <c r="L24">
+        <v>35000</v>
+      </c>
+      <c r="M24">
+        <v>35000</v>
+      </c>
+      <c r="N24">
+        <v>35000</v>
+      </c>
+      <c r="O24">
+        <v>35000</v>
+      </c>
+      <c r="P24">
+        <v>35000</v>
+      </c>
+      <c r="Q24">
+        <v>35000</v>
+      </c>
+      <c r="R24">
+        <v>35000</v>
+      </c>
+      <c r="S24">
+        <v>35000</v>
+      </c>
+      <c r="T24">
+        <v>35000</v>
+      </c>
+      <c r="U24">
+        <v>35000</v>
+      </c>
+      <c r="V24">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <v>2047</v>
+      </c>
+      <c r="B25">
+        <v>700000</v>
+      </c>
+      <c r="C25">
+        <v>150</v>
+      </c>
+      <c r="D25">
+        <v>3500</v>
+      </c>
+      <c r="E25">
+        <v>800</v>
+      </c>
+      <c r="F25">
+        <v>9500</v>
+      </c>
+      <c r="G25">
+        <v>50000</v>
+      </c>
+      <c r="H25">
+        <v>18000</v>
+      </c>
+      <c r="I25">
+        <v>35000</v>
+      </c>
+      <c r="J25">
+        <v>35000</v>
+      </c>
+      <c r="K25">
+        <v>35000</v>
+      </c>
+      <c r="L25">
+        <v>35000</v>
+      </c>
+      <c r="M25">
+        <v>35000</v>
+      </c>
+      <c r="N25">
+        <v>35000</v>
+      </c>
+      <c r="O25">
+        <v>35000</v>
+      </c>
+      <c r="P25">
+        <v>35000</v>
+      </c>
+      <c r="Q25">
+        <v>35000</v>
+      </c>
+      <c r="R25">
+        <v>35000</v>
+      </c>
+      <c r="S25">
+        <v>35000</v>
+      </c>
+      <c r="T25">
+        <v>35000</v>
+      </c>
+      <c r="U25">
+        <v>35000</v>
+      </c>
+      <c r="V25">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
+        <v>2048</v>
+      </c>
+      <c r="B26">
+        <v>700000</v>
+      </c>
+      <c r="C26">
+        <v>150</v>
+      </c>
+      <c r="D26">
+        <v>3500</v>
+      </c>
+      <c r="E26">
+        <v>800</v>
+      </c>
+      <c r="F26">
+        <v>9500</v>
+      </c>
+      <c r="G26">
+        <v>50000</v>
+      </c>
+      <c r="H26">
+        <v>18000</v>
+      </c>
+      <c r="I26">
+        <v>35000</v>
+      </c>
+      <c r="J26">
+        <v>35000</v>
+      </c>
+      <c r="K26">
+        <v>35000</v>
+      </c>
+      <c r="L26">
+        <v>35000</v>
+      </c>
+      <c r="M26">
+        <v>35000</v>
+      </c>
+      <c r="N26">
+        <v>35000</v>
+      </c>
+      <c r="O26">
+        <v>35000</v>
+      </c>
+      <c r="P26">
+        <v>35000</v>
+      </c>
+      <c r="Q26">
+        <v>35000</v>
+      </c>
+      <c r="R26">
+        <v>35000</v>
+      </c>
+      <c r="S26">
+        <v>35000</v>
+      </c>
+      <c r="T26">
+        <v>35000</v>
+      </c>
+      <c r="U26">
+        <v>35000</v>
+      </c>
+      <c r="V26">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>2049</v>
+      </c>
+      <c r="B27">
+        <v>700000</v>
+      </c>
+      <c r="C27">
+        <v>150</v>
+      </c>
+      <c r="D27">
+        <v>3500</v>
+      </c>
+      <c r="E27">
+        <v>800</v>
+      </c>
+      <c r="F27">
+        <v>9500</v>
+      </c>
+      <c r="G27">
+        <v>50000</v>
+      </c>
+      <c r="H27">
+        <v>18000</v>
+      </c>
+      <c r="I27">
+        <v>35000</v>
+      </c>
+      <c r="J27">
+        <v>35000</v>
+      </c>
+      <c r="K27">
+        <v>35000</v>
+      </c>
+      <c r="L27">
+        <v>35000</v>
+      </c>
+      <c r="M27">
+        <v>35000</v>
+      </c>
+      <c r="N27">
+        <v>35000</v>
+      </c>
+      <c r="O27">
+        <v>35000</v>
+      </c>
+      <c r="P27">
+        <v>35000</v>
+      </c>
+      <c r="Q27">
+        <v>35000</v>
+      </c>
+      <c r="R27">
+        <v>35000</v>
+      </c>
+      <c r="S27">
+        <v>35000</v>
+      </c>
+      <c r="T27">
+        <v>35000</v>
+      </c>
+      <c r="U27">
+        <v>35000</v>
+      </c>
+      <c r="V27">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>2050</v>
+      </c>
+      <c r="B28">
+        <v>700000</v>
+      </c>
+      <c r="C28">
+        <v>150</v>
+      </c>
+      <c r="D28">
+        <v>3500</v>
+      </c>
+      <c r="E28">
+        <v>800</v>
+      </c>
+      <c r="F28">
+        <v>9500</v>
+      </c>
+      <c r="G28">
+        <v>50000</v>
+      </c>
+      <c r="H28">
+        <v>18000</v>
+      </c>
+      <c r="I28">
+        <v>35000</v>
+      </c>
+      <c r="J28">
+        <v>35000</v>
+      </c>
+      <c r="K28">
+        <v>35000</v>
+      </c>
+      <c r="L28">
+        <v>35000</v>
+      </c>
+      <c r="M28">
+        <v>35000</v>
+      </c>
+      <c r="N28">
+        <v>35000</v>
+      </c>
+      <c r="O28">
+        <v>35000</v>
+      </c>
+      <c r="P28">
+        <v>35000</v>
+      </c>
+      <c r="Q28">
+        <v>35000</v>
+      </c>
+      <c r="R28">
+        <v>35000</v>
+      </c>
+      <c r="S28">
+        <v>35000</v>
+      </c>
+      <c r="T28">
+        <v>35000</v>
+      </c>
+      <c r="U28">
+        <v>35000</v>
+      </c>
+      <c r="V28">
+        <v>35000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{996B2112-D2EE-4E9F-B294-4222E881A3C9}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2954,7 +8661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE844EE-882F-4833-8B87-00A8BB665263}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3310,7 +9017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B74DFEF-01D9-4B2D-A936-BF616F091054}">
   <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13211,12 +18918,12 @@
         <v>5</v>
       </c>
       <c r="P2" s="6">
-        <v>76.923000000000002</v>
+        <v>70.922028124999997</v>
       </c>
       <c r="Q2" s="6">
-        <v>76.923000000000002</v>
-      </c>
-      <c r="R2" s="6">
+        <v>70.922028124999997</v>
+      </c>
+      <c r="R2" s="14">
         <v>0.85</v>
       </c>
       <c r="S2" s="6">
@@ -13294,12 +19001,12 @@
         <v>5</v>
       </c>
       <c r="P3" s="6">
-        <v>118</v>
+        <v>171.04915999999997</v>
       </c>
       <c r="Q3" s="6">
-        <v>118</v>
-      </c>
-      <c r="R3" s="6">
+        <v>171.04915999999997</v>
+      </c>
+      <c r="R3" s="14">
         <v>0.95</v>
       </c>
       <c r="S3" s="6">
@@ -13377,12 +19084,12 @@
         <v>5</v>
       </c>
       <c r="P4" s="6">
-        <v>118</v>
+        <v>162.10234999999997</v>
       </c>
       <c r="Q4" s="6">
-        <v>118</v>
-      </c>
-      <c r="R4" s="6">
+        <v>162.10234999999997</v>
+      </c>
+      <c r="R4" s="14">
         <v>0.95</v>
       </c>
       <c r="S4" s="6">
@@ -13465,7 +19172,7 @@
       <c r="Q5" s="6">
         <v>20</v>
       </c>
-      <c r="R5" s="6">
+      <c r="R5" s="14">
         <v>0.7</v>
       </c>
       <c r="S5" s="6">
@@ -15024,7 +20731,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
+      <c r="A2" s="15">
         <v>2024</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -15038,7 +20745,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
+      <c r="A3" s="15"/>
       <c r="B3" s="11" t="s">
         <v>70</v>
       </c>
@@ -15051,7 +20758,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -15063,7 +20770,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
+      <c r="A5" s="15"/>
       <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
@@ -15075,7 +20782,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <v>2025</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -15089,7 +20796,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
@@ -15101,7 +20808,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
@@ -15113,7 +20820,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="11" t="s">
         <v>68</v>
       </c>
@@ -15126,7 +20833,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -15140,7 +20847,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
@@ -15152,7 +20859,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -15164,7 +20871,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -15177,7 +20884,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
+      <c r="A14" s="15">
         <v>2027</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -15191,7 +20898,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
@@ -15203,7 +20910,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
@@ -15215,7 +20922,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
@@ -15228,7 +20935,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+      <c r="A18" s="15">
         <v>2028</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -15242,7 +20949,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
@@ -15254,7 +20961,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
@@ -15266,7 +20973,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="11" t="s">
         <v>68</v>
       </c>
@@ -15279,7 +20986,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <v>2029</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -15293,7 +21000,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="11" t="s">
         <v>70</v>
       </c>
@@ -15305,7 +21012,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="11" t="s">
         <v>71</v>
       </c>
@@ -15317,7 +21024,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="11" t="s">
         <v>68</v>
       </c>
@@ -15330,7 +21037,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <v>2030</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -15344,7 +21051,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="14"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="11" t="s">
         <v>70</v>
       </c>
@@ -15356,7 +21063,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="11" t="s">
         <v>71</v>
       </c>
@@ -15368,7 +21075,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="11" t="s">
         <v>68</v>
       </c>
@@ -15381,7 +21088,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="14">
+      <c r="A30" s="15">
         <v>2031</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -15395,7 +21102,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="14"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
@@ -15407,7 +21114,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="11" t="s">
         <v>71</v>
       </c>
@@ -15419,7 +21126,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
@@ -15432,7 +21139,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="14">
+      <c r="A34" s="15">
         <v>2032</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -15446,7 +21153,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="14"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="11" t="s">
         <v>70</v>
       </c>
@@ -15458,7 +21165,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="14"/>
+      <c r="A36" s="15"/>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
@@ -15470,7 +21177,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="14"/>
+      <c r="A37" s="15"/>
       <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
@@ -15483,7 +21190,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
+      <c r="A38" s="15">
         <v>2033</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -15497,7 +21204,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="14"/>
+      <c r="A39" s="15"/>
       <c r="B39" s="11" t="s">
         <v>70</v>
       </c>
@@ -15509,7 +21216,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="14"/>
+      <c r="A40" s="15"/>
       <c r="B40" s="11" t="s">
         <v>71</v>
       </c>
@@ -15521,7 +21228,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="14"/>
+      <c r="A41" s="15"/>
       <c r="B41" s="11" t="s">
         <v>68</v>
       </c>
@@ -15534,7 +21241,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="14">
+      <c r="A42" s="15">
         <v>2034</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -15548,7 +21255,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="14"/>
+      <c r="A43" s="15"/>
       <c r="B43" s="11" t="s">
         <v>70</v>
       </c>
@@ -15560,7 +21267,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="14"/>
+      <c r="A44" s="15"/>
       <c r="B44" s="11" t="s">
         <v>71</v>
       </c>
@@ -15572,7 +21279,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="14"/>
+      <c r="A45" s="15"/>
       <c r="B45" s="11" t="s">
         <v>68</v>
       </c>
@@ -15585,7 +21292,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="14">
+      <c r="A46" s="15">
         <v>2035</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -15599,7 +21306,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="14"/>
+      <c r="A47" s="15"/>
       <c r="B47" s="11" t="s">
         <v>70</v>
       </c>
@@ -15611,7 +21318,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="14"/>
+      <c r="A48" s="15"/>
       <c r="B48" s="11" t="s">
         <v>71</v>
       </c>
@@ -15623,7 +21330,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="14"/>
+      <c r="A49" s="15"/>
       <c r="B49" s="11" t="s">
         <v>68</v>
       </c>
@@ -15636,7 +21343,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="14">
+      <c r="A50" s="15">
         <v>2036</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -15650,7 +21357,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="14"/>
+      <c r="A51" s="15"/>
       <c r="B51" s="11" t="s">
         <v>70</v>
       </c>
@@ -15662,7 +21369,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="14"/>
+      <c r="A52" s="15"/>
       <c r="B52" s="11" t="s">
         <v>71</v>
       </c>
@@ -15674,7 +21381,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="14"/>
+      <c r="A53" s="15"/>
       <c r="B53" s="11" t="s">
         <v>68</v>
       </c>
@@ -15687,7 +21394,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="14">
+      <c r="A54" s="15">
         <v>2037</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -15701,7 +21408,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="14"/>
+      <c r="A55" s="15"/>
       <c r="B55" s="11" t="s">
         <v>70</v>
       </c>
@@ -15713,7 +21420,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="14"/>
+      <c r="A56" s="15"/>
       <c r="B56" s="11" t="s">
         <v>71</v>
       </c>
@@ -15725,7 +21432,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="14"/>
+      <c r="A57" s="15"/>
       <c r="B57" s="11" t="s">
         <v>68</v>
       </c>
@@ -15738,7 +21445,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="14">
+      <c r="A58" s="15">
         <v>2038</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -15752,7 +21459,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="14"/>
+      <c r="A59" s="15"/>
       <c r="B59" s="11" t="s">
         <v>70</v>
       </c>
@@ -15764,7 +21471,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="14"/>
+      <c r="A60" s="15"/>
       <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
@@ -15776,7 +21483,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="14"/>
+      <c r="A61" s="15"/>
       <c r="B61" s="11" t="s">
         <v>68</v>
       </c>
@@ -15789,7 +21496,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="14">
+      <c r="A62" s="15">
         <v>2039</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -15803,7 +21510,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="14"/>
+      <c r="A63" s="15"/>
       <c r="B63" s="11" t="s">
         <v>70</v>
       </c>
@@ -15815,7 +21522,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="14"/>
+      <c r="A64" s="15"/>
       <c r="B64" s="11" t="s">
         <v>71</v>
       </c>
@@ -15827,7 +21534,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="14"/>
+      <c r="A65" s="15"/>
       <c r="B65" s="11" t="s">
         <v>68</v>
       </c>
@@ -15840,7 +21547,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="14">
+      <c r="A66" s="15">
         <v>2040</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -15854,7 +21561,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="14"/>
+      <c r="A67" s="15"/>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
@@ -15866,7 +21573,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="14"/>
+      <c r="A68" s="15"/>
       <c r="B68" s="11" t="s">
         <v>71</v>
       </c>
@@ -15878,7 +21585,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="14"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="11" t="s">
         <v>68</v>
       </c>
@@ -15891,7 +21598,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="14">
+      <c r="A70" s="15">
         <v>2041</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -15905,7 +21612,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="14"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="11" t="s">
         <v>70</v>
       </c>
@@ -15917,7 +21624,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="11" t="s">
         <v>71</v>
       </c>
@@ -15929,7 +21636,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="14"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="11" t="s">
         <v>68</v>
       </c>
@@ -15942,7 +21649,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="14">
+      <c r="A74" s="15">
         <v>2042</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -15956,7 +21663,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="14"/>
+      <c r="A75" s="15"/>
       <c r="B75" s="11" t="s">
         <v>70</v>
       </c>
@@ -15968,7 +21675,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="14"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
@@ -15980,7 +21687,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="14"/>
+      <c r="A77" s="15"/>
       <c r="B77" s="11" t="s">
         <v>68</v>
       </c>
@@ -15993,7 +21700,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="14">
+      <c r="A78" s="15">
         <v>2043</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -16007,7 +21714,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="14"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="11" t="s">
         <v>70</v>
       </c>
@@ -16019,7 +21726,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="14"/>
+      <c r="A80" s="15"/>
       <c r="B80" s="11" t="s">
         <v>71</v>
       </c>
@@ -16031,7 +21738,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="14"/>
+      <c r="A81" s="15"/>
       <c r="B81" s="11" t="s">
         <v>68</v>
       </c>
@@ -16044,7 +21751,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="14">
+      <c r="A82" s="15">
         <v>2044</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -16058,7 +21765,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="14"/>
+      <c r="A83" s="15"/>
       <c r="B83" s="11" t="s">
         <v>70</v>
       </c>
@@ -16070,7 +21777,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="14"/>
+      <c r="A84" s="15"/>
       <c r="B84" s="11" t="s">
         <v>71</v>
       </c>
@@ -16082,7 +21789,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="14"/>
+      <c r="A85" s="15"/>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
@@ -16095,7 +21802,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="14">
+      <c r="A86" s="15">
         <v>2045</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -16109,7 +21816,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="14"/>
+      <c r="A87" s="15"/>
       <c r="B87" s="11" t="s">
         <v>70</v>
       </c>
@@ -16121,7 +21828,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="14"/>
+      <c r="A88" s="15"/>
       <c r="B88" s="11" t="s">
         <v>71</v>
       </c>
@@ -16133,7 +21840,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="14"/>
+      <c r="A89" s="15"/>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
@@ -16146,7 +21853,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="14">
+      <c r="A90" s="15">
         <v>2046</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -16160,7 +21867,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="14"/>
+      <c r="A91" s="15"/>
       <c r="B91" s="11" t="s">
         <v>70</v>
       </c>
@@ -16172,7 +21879,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="14"/>
+      <c r="A92" s="15"/>
       <c r="B92" s="11" t="s">
         <v>71</v>
       </c>
@@ -16184,7 +21891,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="14"/>
+      <c r="A93" s="15"/>
       <c r="B93" s="11" t="s">
         <v>68</v>
       </c>
@@ -16197,7 +21904,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="14">
+      <c r="A94" s="15">
         <v>2047</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -16211,7 +21918,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="14"/>
+      <c r="A95" s="15"/>
       <c r="B95" s="11" t="s">
         <v>70</v>
       </c>
@@ -16223,7 +21930,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="14"/>
+      <c r="A96" s="15"/>
       <c r="B96" s="11" t="s">
         <v>71</v>
       </c>
@@ -16235,7 +21942,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="14"/>
+      <c r="A97" s="15"/>
       <c r="B97" s="11" t="s">
         <v>68</v>
       </c>
@@ -16248,7 +21955,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="14">
+      <c r="A98" s="15">
         <v>2048</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -16262,7 +21969,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="14"/>
+      <c r="A99" s="15"/>
       <c r="B99" s="11" t="s">
         <v>70</v>
       </c>
@@ -16274,7 +21981,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="14"/>
+      <c r="A100" s="15"/>
       <c r="B100" s="11" t="s">
         <v>71</v>
       </c>
@@ -16286,7 +21993,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="14"/>
+      <c r="A101" s="15"/>
       <c r="B101" s="11" t="s">
         <v>68</v>
       </c>
@@ -16299,7 +22006,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="14">
+      <c r="A102" s="15">
         <v>2049</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -16313,7 +22020,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="14"/>
+      <c r="A103" s="15"/>
       <c r="B103" s="11" t="s">
         <v>70</v>
       </c>
@@ -16325,7 +22032,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="14"/>
+      <c r="A104" s="15"/>
       <c r="B104" s="11" t="s">
         <v>71</v>
       </c>
@@ -16337,7 +22044,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="14"/>
+      <c r="A105" s="15"/>
       <c r="B105" s="11" t="s">
         <v>68</v>
       </c>
@@ -16350,7 +22057,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="14">
+      <c r="A106" s="15">
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -16364,7 +22071,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="14"/>
+      <c r="A107" s="15"/>
       <c r="B107" s="11" t="s">
         <v>70</v>
       </c>
@@ -16376,7 +22083,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="14"/>
+      <c r="A108" s="15"/>
       <c r="B108" s="11" t="s">
         <v>71</v>
       </c>
@@ -16388,7 +22095,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="14"/>
+      <c r="A109" s="15"/>
       <c r="B109" s="11" t="s">
         <v>68</v>
       </c>
@@ -16403,6 +22110,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -16410,26 +22137,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="527" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53855C72-BC49-44AD-93CD-BB20AB1B0FC3}"/>
+  <xr:revisionPtr revIDLastSave="605" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60C394FD-8E8C-4C4C-A2B5-938D74E72AFF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="8" activeTab="12" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="12" activeTab="14" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -24,13 +24,14 @@
     <sheet name="gas_block" sheetId="13" r:id="rId9"/>
     <sheet name="Tech_Stage_Specs" sheetId="14" r:id="rId10"/>
     <sheet name="Material_Intensity" sheetId="15" r:id="rId11"/>
-    <sheet name="Material_Market" sheetId="17" r:id="rId12"/>
-    <sheet name="mining_limit" sheetId="20" r:id="rId13"/>
-    <sheet name="mining_cost" sheetId="21" r:id="rId14"/>
-    <sheet name="import_cost_mining" sheetId="22" r:id="rId15"/>
-    <sheet name="Component_Map" sheetId="18" r:id="rId16"/>
-    <sheet name="Cost_Data" sheetId="16" r:id="rId17"/>
-    <sheet name="Import_Cost_Stage" sheetId="19" r:id="rId18"/>
+    <sheet name="mining_limit" sheetId="20" r:id="rId12"/>
+    <sheet name="mining_cost" sheetId="21" r:id="rId13"/>
+    <sheet name="import_cost_mining" sheetId="22" r:id="rId14"/>
+    <sheet name="energy_transition_factor" sheetId="23" r:id="rId15"/>
+    <sheet name="ore_metal_factor" sheetId="24" r:id="rId16"/>
+    <sheet name="Component_Map" sheetId="18" r:id="rId17"/>
+    <sheet name="Cost_Data" sheetId="16" r:id="rId18"/>
+    <sheet name="Import_Cost_Stage" sheetId="19" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="150">
   <si>
     <t>Value</t>
   </si>
@@ -389,15 +390,6 @@
   </si>
   <si>
     <t>scrap_content</t>
-  </si>
-  <si>
-    <t>mining_cost</t>
-  </si>
-  <si>
-    <t>import_cost</t>
-  </si>
-  <si>
-    <t>mining_limit</t>
   </si>
   <si>
     <t>capex_base</t>
@@ -740,10 +732,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -770,6 +762,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1151,7 +1147,7 @@
         <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G1" t="s">
         <v>74</v>
@@ -1168,7 +1164,7 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1356,7 +1352,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1539,7 +1535,7 @@
         <v>87</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12">
         <v>7.5</v>
@@ -1579,7 +1575,7 @@
         <v>87</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D4" s="12">
         <v>8.6000000000000014</v>
@@ -1599,7 +1595,7 @@
         <v>87</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D5" s="12">
         <v>4.5999999999999996</v>
@@ -1619,7 +1615,7 @@
         <v>86</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D6" s="12">
         <v>1.9012500000000002E-2</v>
@@ -1636,10 +1632,10 @@
         <v>75</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D7" s="12">
         <v>3.803015625</v>
@@ -1659,7 +1655,7 @@
         <v>89</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D8" s="12">
         <v>0.94859999999999989</v>
@@ -1679,7 +1675,7 @@
         <v>89</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D9" s="12">
         <v>6.9563999999999995</v>
@@ -1699,7 +1695,7 @@
         <v>89</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D10" s="12">
         <v>1.17E-3</v>
@@ -1719,7 +1715,7 @@
         <v>89</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D11" s="12">
         <v>8.1</v>
@@ -1748,7 +1744,7 @@
         <v>114.72499999999999</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1759,7 +1755,7 @@
         <v>90</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D13" s="12">
         <v>5.5</v>
@@ -1768,7 +1764,7 @@
         <v>5.5</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1779,7 +1775,7 @@
         <v>92</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D14" s="12">
         <v>5.47E-3</v>
@@ -1799,7 +1795,7 @@
         <v>92</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D15" s="12">
         <v>4.7689999999999996E-2</v>
@@ -1819,7 +1815,7 @@
         <v>92</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D16" s="12">
         <v>7.2699999999999996E-3</v>
@@ -1839,7 +1835,7 @@
         <v>92</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D17" s="12">
         <v>2.7909999999999999</v>
@@ -1848,7 +1844,7 @@
         <v>2.7909999999999999</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1859,7 +1855,7 @@
         <v>92</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D18" s="12">
         <v>2.2925</v>
@@ -1868,7 +1864,7 @@
         <v>2.2925</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1879,7 +1875,7 @@
         <v>92</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D19" s="12">
         <v>18.945</v>
@@ -1899,7 +1895,7 @@
         <v>92</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D20" s="12">
         <v>0.78549999999999998</v>
@@ -1919,7 +1915,7 @@
         <v>92</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D21" s="12">
         <v>0.1045</v>
@@ -1939,7 +1935,7 @@
         <v>92</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D22" s="12">
         <v>0.39200000000000002</v>
@@ -1959,7 +1955,7 @@
         <v>92</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D23" s="12">
         <v>0.50024999999999997</v>
@@ -1979,7 +1975,7 @@
         <v>89</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D24" s="12">
         <v>0.97139999999999993</v>
@@ -1999,7 +1995,7 @@
         <v>89</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D25" s="12">
         <v>7.1236000000000006</v>
@@ -2019,7 +2015,7 @@
         <v>89</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D26" s="12">
         <v>3.4500000000000004E-3</v>
@@ -2039,7 +2035,7 @@
         <v>89</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D27" s="12">
         <v>11.6</v>
@@ -2068,7 +2064,7 @@
         <v>116.77</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2079,7 +2075,7 @@
         <v>90</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D29" s="12">
         <v>5.5</v>
@@ -2088,7 +2084,7 @@
         <v>5.5</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2099,7 +2095,7 @@
         <v>92</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D30" s="12">
         <v>1.1259999999999999E-2</v>
@@ -2119,7 +2115,7 @@
         <v>92</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D31" s="12">
         <v>0.11219</v>
@@ -2139,7 +2135,7 @@
         <v>92</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D32" s="12">
         <v>2.0460000000000002E-2</v>
@@ -2159,7 +2155,7 @@
         <v>92</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D33" s="12">
         <v>4.04</v>
@@ -2168,7 +2164,7 @@
         <v>4.04</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2179,7 +2175,7 @@
         <v>92</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D34" s="12">
         <v>3.2574999999999998</v>
@@ -2188,7 +2184,7 @@
         <v>3.2574999999999998</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2199,7 +2195,7 @@
         <v>92</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D35" s="12">
         <v>19.89</v>
@@ -2219,7 +2215,7 @@
         <v>92</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D36" s="12">
         <v>0.79039999999999999</v>
@@ -2239,7 +2235,7 @@
         <v>92</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D37" s="12">
         <v>0.10940000000000001</v>
@@ -2259,7 +2255,7 @@
         <v>92</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D38" s="12">
         <v>0.32230000000000003</v>
@@ -2279,7 +2275,7 @@
         <v>92</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D39" s="12">
         <v>0.5272</v>
@@ -2339,390 +2335,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BB5A9E-0DE2-4C9D-A6F4-EBF765E41A9E}">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2024</v>
-      </c>
-      <c r="B2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2">
-        <v>5000</v>
-      </c>
-      <c r="D2">
-        <v>650000</v>
-      </c>
-      <c r="E2">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2024</v>
-      </c>
-      <c r="B3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3">
-        <v>5000000</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2024</v>
-      </c>
-      <c r="B4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4">
-        <v>500000</v>
-      </c>
-      <c r="D4">
-        <v>3000</v>
-      </c>
-      <c r="E4">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2024</v>
-      </c>
-      <c r="B5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5">
-        <v>10000000</v>
-      </c>
-      <c r="D5">
-        <v>600</v>
-      </c>
-      <c r="E5">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2024</v>
-      </c>
-      <c r="B6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6">
-        <v>800000</v>
-      </c>
-      <c r="D6">
-        <v>8000</v>
-      </c>
-      <c r="E6">
-        <v>9500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2024</v>
-      </c>
-      <c r="B7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7">
-        <v>20000</v>
-      </c>
-      <c r="D7">
-        <v>40000</v>
-      </c>
-      <c r="E7">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2024</v>
-      </c>
-      <c r="B8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8">
-        <v>150000</v>
-      </c>
-      <c r="D8">
-        <v>15000</v>
-      </c>
-      <c r="E8">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2024</v>
-      </c>
-      <c r="B9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9">
-        <v>150000</v>
-      </c>
-      <c r="D9">
-        <v>30000</v>
-      </c>
-      <c r="E9">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2024</v>
-      </c>
-      <c r="B10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10">
-        <v>150000</v>
-      </c>
-      <c r="D10">
-        <v>30000</v>
-      </c>
-      <c r="E10">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2024</v>
-      </c>
-      <c r="B11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11">
-        <v>150000</v>
-      </c>
-      <c r="D11">
-        <v>30000</v>
-      </c>
-      <c r="E11">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2024</v>
-      </c>
-      <c r="B12" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12">
-        <v>150000</v>
-      </c>
-      <c r="D12">
-        <v>30000</v>
-      </c>
-      <c r="E12">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2024</v>
-      </c>
-      <c r="B13" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13">
-        <v>150000</v>
-      </c>
-      <c r="D13">
-        <v>30000</v>
-      </c>
-      <c r="E13">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2024</v>
-      </c>
-      <c r="B14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14">
-        <v>150000</v>
-      </c>
-      <c r="D14">
-        <v>30000</v>
-      </c>
-      <c r="E14">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2024</v>
-      </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15">
-        <v>150000</v>
-      </c>
-      <c r="D15">
-        <v>30000</v>
-      </c>
-      <c r="E15">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C16">
-        <v>150000</v>
-      </c>
-      <c r="D16">
-        <v>30000</v>
-      </c>
-      <c r="E16">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2024</v>
-      </c>
-      <c r="B17" t="s">
-        <v>147</v>
-      </c>
-      <c r="C17">
-        <v>150000</v>
-      </c>
-      <c r="D17">
-        <v>30000</v>
-      </c>
-      <c r="E17">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2024</v>
-      </c>
-      <c r="B18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18">
-        <v>150000</v>
-      </c>
-      <c r="D18">
-        <v>30000</v>
-      </c>
-      <c r="E18">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2024</v>
-      </c>
-      <c r="B19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19">
-        <v>150000</v>
-      </c>
-      <c r="D19">
-        <v>30000</v>
-      </c>
-      <c r="E19">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2024</v>
-      </c>
-      <c r="B20" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20">
-        <v>150000</v>
-      </c>
-      <c r="D20">
-        <v>30000</v>
-      </c>
-      <c r="E20">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2024</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21">
-        <v>150000</v>
-      </c>
-      <c r="D21">
-        <v>30000</v>
-      </c>
-      <c r="E21">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2024</v>
-      </c>
-      <c r="B22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22">
-        <v>150000</v>
-      </c>
-      <c r="D22">
-        <v>30000</v>
-      </c>
-      <c r="E22">
-        <v>35000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA468E9E-004D-4F86-817A-29F43A769A51}">
   <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2731,85 +2343,85 @@
       <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="F1" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="I1" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="N1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="Q1" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="R1" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="P1" s="16" t="s">
+      <c r="S1" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="T1" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="U1" s="16" t="s">
+      <c r="U1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="V1" s="15" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="15">
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C2">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D2">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E2">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F2">
         <v>800000</v>
@@ -2836,10 +2448,10 @@
         <v>150000</v>
       </c>
       <c r="N2">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O2">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P2">
         <v>150000</v>
@@ -2864,20 +2476,20 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C3">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D3">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E3">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F3">
         <v>800000</v>
@@ -2904,10 +2516,10 @@
         <v>150000</v>
       </c>
       <c r="N3">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O3">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P3">
         <v>150000</v>
@@ -2932,20 +2544,20 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C4">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D4">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E4">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F4">
         <v>800000</v>
@@ -2972,10 +2584,10 @@
         <v>150000</v>
       </c>
       <c r="N4">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O4">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P4">
         <v>150000</v>
@@ -3000,20 +2612,20 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C5">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D5">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E5">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F5">
         <v>800000</v>
@@ -3040,10 +2652,10 @@
         <v>150000</v>
       </c>
       <c r="N5">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O5">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P5">
         <v>150000</v>
@@ -3068,20 +2680,20 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="15">
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C6">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D6">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E6">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F6">
         <v>800000</v>
@@ -3108,10 +2720,10 @@
         <v>150000</v>
       </c>
       <c r="N6">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O6">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P6">
         <v>150000</v>
@@ -3136,20 +2748,20 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
+      <c r="A7" s="15">
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C7">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D7">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E7">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F7">
         <v>800000</v>
@@ -3176,10 +2788,10 @@
         <v>150000</v>
       </c>
       <c r="N7">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O7">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P7">
         <v>150000</v>
@@ -3204,20 +2816,20 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="16">
+      <c r="A8" s="15">
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C8">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D8">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E8">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F8">
         <v>800000</v>
@@ -3244,10 +2856,10 @@
         <v>150000</v>
       </c>
       <c r="N8">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O8">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P8">
         <v>150000</v>
@@ -3272,20 +2884,20 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
+      <c r="A9" s="15">
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C9">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D9">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E9">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F9">
         <v>800000</v>
@@ -3312,10 +2924,10 @@
         <v>150000</v>
       </c>
       <c r="N9">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O9">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P9">
         <v>150000</v>
@@ -3340,20 +2952,20 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+      <c r="A10" s="15">
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C10">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D10">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E10">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F10">
         <v>800000</v>
@@ -3380,10 +2992,10 @@
         <v>150000</v>
       </c>
       <c r="N10">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O10">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P10">
         <v>150000</v>
@@ -3408,20 +3020,20 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
+      <c r="A11" s="15">
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C11">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D11">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E11">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F11">
         <v>800000</v>
@@ -3448,10 +3060,10 @@
         <v>150000</v>
       </c>
       <c r="N11">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O11">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P11">
         <v>150000</v>
@@ -3476,20 +3088,20 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+      <c r="A12" s="15">
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C12">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D12">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E12">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F12">
         <v>800000</v>
@@ -3516,10 +3128,10 @@
         <v>150000</v>
       </c>
       <c r="N12">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O12">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P12">
         <v>150000</v>
@@ -3544,20 +3156,20 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
+      <c r="A13" s="15">
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C13">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D13">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E13">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F13">
         <v>800000</v>
@@ -3584,10 +3196,10 @@
         <v>150000</v>
       </c>
       <c r="N13">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O13">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P13">
         <v>150000</v>
@@ -3612,20 +3224,20 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
+      <c r="A14" s="15">
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C14">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D14">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E14">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F14">
         <v>800000</v>
@@ -3652,10 +3264,10 @@
         <v>150000</v>
       </c>
       <c r="N14">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O14">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P14">
         <v>150000</v>
@@ -3680,20 +3292,20 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
+      <c r="A15" s="15">
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C15">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D15">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E15">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F15">
         <v>800000</v>
@@ -3720,10 +3332,10 @@
         <v>150000</v>
       </c>
       <c r="N15">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O15">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P15">
         <v>150000</v>
@@ -3748,20 +3360,20 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
+      <c r="A16" s="15">
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C16">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D16">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E16">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F16">
         <v>800000</v>
@@ -3788,10 +3400,10 @@
         <v>150000</v>
       </c>
       <c r="N16">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O16">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P16">
         <v>150000</v>
@@ -3816,20 +3428,20 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+      <c r="A17" s="15">
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C17">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D17">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E17">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F17">
         <v>800000</v>
@@ -3856,10 +3468,10 @@
         <v>150000</v>
       </c>
       <c r="N17">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O17">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P17">
         <v>150000</v>
@@ -3884,20 +3496,20 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="A18" s="15">
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C18">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D18">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E18">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F18">
         <v>800000</v>
@@ -3924,10 +3536,10 @@
         <v>150000</v>
       </c>
       <c r="N18">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O18">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P18">
         <v>150000</v>
@@ -3952,20 +3564,20 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
+      <c r="A19" s="15">
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C19">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D19">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E19">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F19">
         <v>800000</v>
@@ -3992,10 +3604,10 @@
         <v>150000</v>
       </c>
       <c r="N19">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O19">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P19">
         <v>150000</v>
@@ -4020,20 +3632,20 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
+      <c r="A20" s="15">
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C20">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D20">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E20">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F20">
         <v>800000</v>
@@ -4060,10 +3672,10 @@
         <v>150000</v>
       </c>
       <c r="N20">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O20">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P20">
         <v>150000</v>
@@ -4088,20 +3700,20 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
+      <c r="A21" s="15">
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C21">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D21">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E21">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F21">
         <v>800000</v>
@@ -4128,10 +3740,10 @@
         <v>150000</v>
       </c>
       <c r="N21">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O21">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P21">
         <v>150000</v>
@@ -4156,20 +3768,20 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="A22" s="15">
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C22">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D22">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E22">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F22">
         <v>800000</v>
@@ -4196,10 +3808,10 @@
         <v>150000</v>
       </c>
       <c r="N22">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O22">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P22">
         <v>150000</v>
@@ -4224,20 +3836,20 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
+      <c r="A23" s="15">
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C23">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D23">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E23">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F23">
         <v>800000</v>
@@ -4264,10 +3876,10 @@
         <v>150000</v>
       </c>
       <c r="N23">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O23">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P23">
         <v>150000</v>
@@ -4292,20 +3904,20 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
+      <c r="A24" s="15">
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C24">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D24">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E24">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F24">
         <v>800000</v>
@@ -4332,10 +3944,10 @@
         <v>150000</v>
       </c>
       <c r="N24">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O24">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P24">
         <v>150000</v>
@@ -4360,20 +3972,20 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
+      <c r="A25" s="15">
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C25">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D25">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E25">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F25">
         <v>800000</v>
@@ -4400,10 +4012,10 @@
         <v>150000</v>
       </c>
       <c r="N25">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O25">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P25">
         <v>150000</v>
@@ -4428,20 +4040,20 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
+      <c r="A26" s="15">
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C26">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D26">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E26">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F26">
         <v>800000</v>
@@ -4468,10 +4080,10 @@
         <v>150000</v>
       </c>
       <c r="N26">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O26">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P26">
         <v>150000</v>
@@ -4496,20 +4108,20 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
+      <c r="A27" s="15">
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C27">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D27">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E27">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F27">
         <v>800000</v>
@@ -4536,10 +4148,10 @@
         <v>150000</v>
       </c>
       <c r="N27">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O27">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P27">
         <v>150000</v>
@@ -4564,20 +4176,20 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
+      <c r="A28" s="15">
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>5000</v>
+        <v>57100000</v>
       </c>
       <c r="C28">
-        <v>5000000</v>
+        <v>58100000</v>
       </c>
       <c r="D28">
-        <v>500000</v>
+        <v>1961</v>
       </c>
       <c r="E28">
-        <v>10000000</v>
+        <v>167000</v>
       </c>
       <c r="F28">
         <v>800000</v>
@@ -4604,10 +4216,10 @@
         <v>150000</v>
       </c>
       <c r="N28">
-        <v>150000</v>
+        <v>1760000</v>
       </c>
       <c r="O28">
-        <v>150000</v>
+        <v>960000</v>
       </c>
       <c r="P28">
         <v>150000</v>
@@ -4636,7 +4248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3497A18D-E10F-4371-B6A4-3051915122F0}">
   <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4645,72 +4257,72 @@
       <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="F1" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="I1" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="N1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="Q1" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="R1" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="P1" s="16" t="s">
+      <c r="S1" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="T1" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="U1" s="16" t="s">
+      <c r="U1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="V1" s="15" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="15">
         <v>2024</v>
       </c>
       <c r="B2">
@@ -4778,7 +4390,7 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <v>2025</v>
       </c>
       <c r="B3">
@@ -4846,7 +4458,7 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <v>2026</v>
       </c>
       <c r="B4">
@@ -4914,7 +4526,7 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>2027</v>
       </c>
       <c r="B5">
@@ -4982,7 +4594,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="15">
         <v>2028</v>
       </c>
       <c r="B6">
@@ -5050,7 +4662,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
+      <c r="A7" s="15">
         <v>2029</v>
       </c>
       <c r="B7">
@@ -5118,7 +4730,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="16">
+      <c r="A8" s="15">
         <v>2030</v>
       </c>
       <c r="B8">
@@ -5186,7 +4798,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
+      <c r="A9" s="15">
         <v>2031</v>
       </c>
       <c r="B9">
@@ -5254,7 +4866,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+      <c r="A10" s="15">
         <v>2032</v>
       </c>
       <c r="B10">
@@ -5322,7 +4934,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
+      <c r="A11" s="15">
         <v>2033</v>
       </c>
       <c r="B11">
@@ -5390,7 +5002,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+      <c r="A12" s="15">
         <v>2034</v>
       </c>
       <c r="B12">
@@ -5458,7 +5070,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
+      <c r="A13" s="15">
         <v>2035</v>
       </c>
       <c r="B13">
@@ -5526,7 +5138,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
+      <c r="A14" s="15">
         <v>2036</v>
       </c>
       <c r="B14">
@@ -5594,7 +5206,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
+      <c r="A15" s="15">
         <v>2037</v>
       </c>
       <c r="B15">
@@ -5662,7 +5274,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
+      <c r="A16" s="15">
         <v>2038</v>
       </c>
       <c r="B16">
@@ -5730,7 +5342,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+      <c r="A17" s="15">
         <v>2039</v>
       </c>
       <c r="B17">
@@ -5798,7 +5410,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="A18" s="15">
         <v>2040</v>
       </c>
       <c r="B18">
@@ -5866,7 +5478,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
+      <c r="A19" s="15">
         <v>2041</v>
       </c>
       <c r="B19">
@@ -5934,7 +5546,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
+      <c r="A20" s="15">
         <v>2042</v>
       </c>
       <c r="B20">
@@ -6002,7 +5614,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
+      <c r="A21" s="15">
         <v>2043</v>
       </c>
       <c r="B21">
@@ -6070,7 +5682,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="A22" s="15">
         <v>2044</v>
       </c>
       <c r="B22">
@@ -6138,7 +5750,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
+      <c r="A23" s="15">
         <v>2045</v>
       </c>
       <c r="B23">
@@ -6206,7 +5818,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
+      <c r="A24" s="15">
         <v>2046</v>
       </c>
       <c r="B24">
@@ -6274,7 +5886,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
+      <c r="A25" s="15">
         <v>2047</v>
       </c>
       <c r="B25">
@@ -6342,7 +5954,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
+      <c r="A26" s="15">
         <v>2048</v>
       </c>
       <c r="B26">
@@ -6410,7 +6022,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
+      <c r="A27" s="15">
         <v>2049</v>
       </c>
       <c r="B27">
@@ -6478,7 +6090,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
+      <c r="A28" s="15">
         <v>2050</v>
       </c>
       <c r="B28">
@@ -6550,7 +6162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0643026C-02E1-4FD1-A973-B34B54E790E8}">
   <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6559,72 +6171,72 @@
       <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="F1" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="I1" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="N1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="Q1" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="R1" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="P1" s="16" t="s">
+      <c r="S1" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="T1" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="U1" s="16" t="s">
+      <c r="U1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="V1" s="15" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="15">
         <v>2024</v>
       </c>
       <c r="B2">
@@ -6692,7 +6304,7 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <v>2025</v>
       </c>
       <c r="B3">
@@ -6760,7 +6372,7 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <v>2026</v>
       </c>
       <c r="B4">
@@ -6828,7 +6440,7 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>2027</v>
       </c>
       <c r="B5">
@@ -6896,7 +6508,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="15">
         <v>2028</v>
       </c>
       <c r="B6">
@@ -6964,7 +6576,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
+      <c r="A7" s="15">
         <v>2029</v>
       </c>
       <c r="B7">
@@ -7032,7 +6644,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="16">
+      <c r="A8" s="15">
         <v>2030</v>
       </c>
       <c r="B8">
@@ -7100,7 +6712,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
+      <c r="A9" s="15">
         <v>2031</v>
       </c>
       <c r="B9">
@@ -7168,7 +6780,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+      <c r="A10" s="15">
         <v>2032</v>
       </c>
       <c r="B10">
@@ -7236,7 +6848,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
+      <c r="A11" s="15">
         <v>2033</v>
       </c>
       <c r="B11">
@@ -7304,7 +6916,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+      <c r="A12" s="15">
         <v>2034</v>
       </c>
       <c r="B12">
@@ -7372,7 +6984,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
+      <c r="A13" s="15">
         <v>2035</v>
       </c>
       <c r="B13">
@@ -7440,7 +7052,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
+      <c r="A14" s="15">
         <v>2036</v>
       </c>
       <c r="B14">
@@ -7508,7 +7120,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
+      <c r="A15" s="15">
         <v>2037</v>
       </c>
       <c r="B15">
@@ -7576,7 +7188,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
+      <c r="A16" s="15">
         <v>2038</v>
       </c>
       <c r="B16">
@@ -7644,7 +7256,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+      <c r="A17" s="15">
         <v>2039</v>
       </c>
       <c r="B17">
@@ -7712,7 +7324,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="A18" s="15">
         <v>2040</v>
       </c>
       <c r="B18">
@@ -7780,7 +7392,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
+      <c r="A19" s="15">
         <v>2041</v>
       </c>
       <c r="B19">
@@ -7848,7 +7460,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
+      <c r="A20" s="15">
         <v>2042</v>
       </c>
       <c r="B20">
@@ -7916,7 +7528,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
+      <c r="A21" s="15">
         <v>2043</v>
       </c>
       <c r="B21">
@@ -7984,7 +7596,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="A22" s="15">
         <v>2044</v>
       </c>
       <c r="B22">
@@ -8052,7 +7664,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
+      <c r="A23" s="15">
         <v>2045</v>
       </c>
       <c r="B23">
@@ -8120,7 +7732,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
+      <c r="A24" s="15">
         <v>2046</v>
       </c>
       <c r="B24">
@@ -8188,7 +7800,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
+      <c r="A25" s="15">
         <v>2047</v>
       </c>
       <c r="B25">
@@ -8256,7 +7868,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
+      <c r="A26" s="15">
         <v>2048</v>
       </c>
       <c r="B26">
@@ -8324,7 +7936,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
+      <c r="A27" s="15">
         <v>2049</v>
       </c>
       <c r="B27">
@@ -8392,7 +8004,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
+      <c r="A28" s="15">
         <v>2050</v>
       </c>
       <c r="B28">
@@ -8457,6 +8069,1920 @@
       </c>
       <c r="V28">
         <v>35000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28476978-BEE9-428F-A843-1F40BF462E1E}">
+  <dimension ref="A1:V28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>2024</v>
+      </c>
+      <c r="B2">
+        <v>0.02</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0.25</v>
+      </c>
+      <c r="E2">
+        <v>0.06</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>0.25</v>
+      </c>
+      <c r="O2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>0.02</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.25</v>
+      </c>
+      <c r="E3">
+        <v>0.06</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0.25</v>
+      </c>
+      <c r="O3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>0.02</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0.25</v>
+      </c>
+      <c r="E4">
+        <v>0.06</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0.25</v>
+      </c>
+      <c r="O4">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B5">
+        <v>0.02</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0.25</v>
+      </c>
+      <c r="E5">
+        <v>0.06</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.25</v>
+      </c>
+      <c r="O5">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>2028</v>
+      </c>
+      <c r="B6">
+        <v>0.02</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0.25</v>
+      </c>
+      <c r="E6">
+        <v>0.06</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0.25</v>
+      </c>
+      <c r="O6">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>2029</v>
+      </c>
+      <c r="B7">
+        <v>0.02</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0.25</v>
+      </c>
+      <c r="E7">
+        <v>0.06</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0.25</v>
+      </c>
+      <c r="O7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>2030</v>
+      </c>
+      <c r="B8">
+        <v>0.02</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0.25</v>
+      </c>
+      <c r="E8">
+        <v>0.06</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>0.25</v>
+      </c>
+      <c r="O8">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>2031</v>
+      </c>
+      <c r="B9">
+        <v>0.02</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0.25</v>
+      </c>
+      <c r="E9">
+        <v>0.06</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>0.25</v>
+      </c>
+      <c r="O9">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>2032</v>
+      </c>
+      <c r="B10">
+        <v>0.02</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0.25</v>
+      </c>
+      <c r="E10">
+        <v>0.06</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>0.25</v>
+      </c>
+      <c r="O10">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>2033</v>
+      </c>
+      <c r="B11">
+        <v>0.02</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0.25</v>
+      </c>
+      <c r="E11">
+        <v>0.06</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>0.25</v>
+      </c>
+      <c r="O11">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>2034</v>
+      </c>
+      <c r="B12">
+        <v>0.02</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0.25</v>
+      </c>
+      <c r="E12">
+        <v>0.06</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>0.25</v>
+      </c>
+      <c r="O12">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>2035</v>
+      </c>
+      <c r="B13">
+        <v>0.02</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0.25</v>
+      </c>
+      <c r="E13">
+        <v>0.06</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>0.25</v>
+      </c>
+      <c r="O13">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
+        <v>2036</v>
+      </c>
+      <c r="B14">
+        <v>0.02</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0.25</v>
+      </c>
+      <c r="E14">
+        <v>0.06</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>0.25</v>
+      </c>
+      <c r="O14">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
+        <v>2037</v>
+      </c>
+      <c r="B15">
+        <v>0.02</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0.25</v>
+      </c>
+      <c r="E15">
+        <v>0.06</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>0.25</v>
+      </c>
+      <c r="O15">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>2038</v>
+      </c>
+      <c r="B16">
+        <v>0.02</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0.25</v>
+      </c>
+      <c r="E16">
+        <v>0.06</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>0.25</v>
+      </c>
+      <c r="O16">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>2039</v>
+      </c>
+      <c r="B17">
+        <v>0.02</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0.25</v>
+      </c>
+      <c r="E17">
+        <v>0.06</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>0.25</v>
+      </c>
+      <c r="O17">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
+        <v>2040</v>
+      </c>
+      <c r="B18">
+        <v>0.02</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0.25</v>
+      </c>
+      <c r="E18">
+        <v>0.06</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>0.25</v>
+      </c>
+      <c r="O18">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>2041</v>
+      </c>
+      <c r="B19">
+        <v>0.02</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0.25</v>
+      </c>
+      <c r="E19">
+        <v>0.06</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>0.25</v>
+      </c>
+      <c r="O19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
+        <v>2042</v>
+      </c>
+      <c r="B20">
+        <v>0.02</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0.25</v>
+      </c>
+      <c r="E20">
+        <v>0.06</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>0.25</v>
+      </c>
+      <c r="O20">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>2043</v>
+      </c>
+      <c r="B21">
+        <v>0.02</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0.25</v>
+      </c>
+      <c r="E21">
+        <v>0.06</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0.25</v>
+      </c>
+      <c r="O21">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
+        <v>2044</v>
+      </c>
+      <c r="B22">
+        <v>0.02</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0.25</v>
+      </c>
+      <c r="E22">
+        <v>0.06</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>0.25</v>
+      </c>
+      <c r="O22">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="15">
+        <v>2045</v>
+      </c>
+      <c r="B23">
+        <v>0.02</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0.25</v>
+      </c>
+      <c r="E23">
+        <v>0.06</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>0.25</v>
+      </c>
+      <c r="O23">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="15">
+        <v>2046</v>
+      </c>
+      <c r="B24">
+        <v>0.02</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0.25</v>
+      </c>
+      <c r="E24">
+        <v>0.06</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>0.25</v>
+      </c>
+      <c r="O24">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
+        <v>2047</v>
+      </c>
+      <c r="B25">
+        <v>0.02</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0.25</v>
+      </c>
+      <c r="E25">
+        <v>0.06</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>0.25</v>
+      </c>
+      <c r="O25">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="15">
+        <v>2048</v>
+      </c>
+      <c r="B26">
+        <v>0.02</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0.25</v>
+      </c>
+      <c r="E26">
+        <v>0.06</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>0.25</v>
+      </c>
+      <c r="O26">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="15">
+        <v>2049</v>
+      </c>
+      <c r="B27">
+        <v>0.02</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0.25</v>
+      </c>
+      <c r="E27">
+        <v>0.06</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>0.25</v>
+      </c>
+      <c r="O27">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
+        <v>2050</v>
+      </c>
+      <c r="B28">
+        <v>0.02</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0.25</v>
+      </c>
+      <c r="E28">
+        <v>0.06</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>0.25</v>
+      </c>
+      <c r="O28">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <v>1</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8465,6 +9991,1920 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C3AB9FD-44ED-4E59-8956-C20ADB98B718}">
+  <dimension ref="A1:V28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>2024</v>
+      </c>
+      <c r="B2">
+        <v>0.75</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>5.25</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>0.75</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>5.25</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>0.75</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>5.25</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B5">
+        <v>0.75</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>5.25</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>2028</v>
+      </c>
+      <c r="B6">
+        <v>0.75</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>5.25</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>2029</v>
+      </c>
+      <c r="B7">
+        <v>0.75</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>5.25</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>2030</v>
+      </c>
+      <c r="B8">
+        <v>0.75</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>5.25</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>2031</v>
+      </c>
+      <c r="B9">
+        <v>0.75</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>5.25</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>2032</v>
+      </c>
+      <c r="B10">
+        <v>0.75</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>5.25</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>2033</v>
+      </c>
+      <c r="B11">
+        <v>0.75</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>5.25</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>2034</v>
+      </c>
+      <c r="B12">
+        <v>0.75</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>5.25</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>2035</v>
+      </c>
+      <c r="B13">
+        <v>0.75</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>5.25</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
+        <v>2036</v>
+      </c>
+      <c r="B14">
+        <v>0.75</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>5.25</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
+        <v>2037</v>
+      </c>
+      <c r="B15">
+        <v>0.75</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>5.25</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>2038</v>
+      </c>
+      <c r="B16">
+        <v>0.75</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>5.25</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>2039</v>
+      </c>
+      <c r="B17">
+        <v>0.75</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>5.25</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
+        <v>2040</v>
+      </c>
+      <c r="B18">
+        <v>0.75</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>5.25</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>2041</v>
+      </c>
+      <c r="B19">
+        <v>0.75</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>5.25</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
+        <v>2042</v>
+      </c>
+      <c r="B20">
+        <v>0.75</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>5.25</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>2043</v>
+      </c>
+      <c r="B21">
+        <v>0.75</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>5.25</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
+        <v>2044</v>
+      </c>
+      <c r="B22">
+        <v>0.75</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>5.25</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="15">
+        <v>2045</v>
+      </c>
+      <c r="B23">
+        <v>0.75</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>5.25</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="15">
+        <v>2046</v>
+      </c>
+      <c r="B24">
+        <v>0.75</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>5.25</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
+        <v>2047</v>
+      </c>
+      <c r="B25">
+        <v>0.75</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>5.25</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="15">
+        <v>2048</v>
+      </c>
+      <c r="B26">
+        <v>0.75</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>5.25</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="15">
+        <v>2049</v>
+      </c>
+      <c r="B27">
+        <v>0.75</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>5.25</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
+        <v>2050</v>
+      </c>
+      <c r="B28">
+        <v>0.75</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>5.25</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <v>1</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{996B2112-D2EE-4E9F-B294-4222E881A3C9}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8497,7 +11937,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
         <v>101</v>
@@ -8661,7 +12101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE844EE-882F-4833-8B87-00A8BB665263}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8680,13 +12120,13 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -8700,7 +12140,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E2" s="12">
         <v>55200</v>
@@ -9017,7 +12457,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B74DFEF-01D9-4B2D-A936-BF616F091054}">
   <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9027,46 +12467,46 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" t="s">
         <v>117</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>118</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O1" t="s">
         <v>124</v>
-      </c>
-      <c r="F1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L1" t="s">
-        <v>132</v>
-      </c>
-      <c r="M1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -20731,7 +24171,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="16">
         <v>2024</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -20745,7 +24185,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="11" t="s">
         <v>70</v>
       </c>
@@ -20758,7 +24198,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -20770,7 +24210,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
@@ -20782,7 +24222,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <v>2025</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -20796,7 +24236,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
@@ -20808,7 +24248,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
@@ -20820,7 +24260,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="11" t="s">
         <v>68</v>
       </c>
@@ -20833,7 +24273,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="16">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -20847,7 +24287,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
@@ -20859,7 +24299,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -20871,7 +24311,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -20884,7 +24324,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="16">
         <v>2027</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -20898,7 +24338,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
@@ -20910,7 +24350,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
@@ -20922,7 +24362,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="16"/>
       <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
@@ -20935,7 +24375,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="16">
         <v>2028</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -20949,7 +24389,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
@@ -20961,7 +24401,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="15"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
@@ -20973,7 +24413,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="11" t="s">
         <v>68</v>
       </c>
@@ -20986,7 +24426,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="16">
         <v>2029</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -21000,7 +24440,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="11" t="s">
         <v>70</v>
       </c>
@@ -21012,7 +24452,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="11" t="s">
         <v>71</v>
       </c>
@@ -21024,7 +24464,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="16"/>
       <c r="B25" s="11" t="s">
         <v>68</v>
       </c>
@@ -21037,7 +24477,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="16">
         <v>2030</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -21051,7 +24491,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="16"/>
       <c r="B27" s="11" t="s">
         <v>70</v>
       </c>
@@ -21063,7 +24503,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="11" t="s">
         <v>71</v>
       </c>
@@ -21075,7 +24515,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="11" t="s">
         <v>68</v>
       </c>
@@ -21088,7 +24528,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="15">
+      <c r="A30" s="16">
         <v>2031</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -21102,7 +24542,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
@@ -21114,7 +24554,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
+      <c r="A32" s="16"/>
       <c r="B32" s="11" t="s">
         <v>71</v>
       </c>
@@ -21126,7 +24566,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="16"/>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
@@ -21139,7 +24579,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="15">
+      <c r="A34" s="16">
         <v>2032</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -21153,7 +24593,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="16"/>
       <c r="B35" s="11" t="s">
         <v>70</v>
       </c>
@@ -21165,7 +24605,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
+      <c r="A36" s="16"/>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
@@ -21177,7 +24617,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="16"/>
       <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
@@ -21190,7 +24630,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="15">
+      <c r="A38" s="16">
         <v>2033</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -21204,7 +24644,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="16"/>
       <c r="B39" s="11" t="s">
         <v>70</v>
       </c>
@@ -21216,7 +24656,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
+      <c r="A40" s="16"/>
       <c r="B40" s="11" t="s">
         <v>71</v>
       </c>
@@ -21228,7 +24668,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
+      <c r="A41" s="16"/>
       <c r="B41" s="11" t="s">
         <v>68</v>
       </c>
@@ -21241,7 +24681,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
+      <c r="A42" s="16">
         <v>2034</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -21255,7 +24695,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
+      <c r="A43" s="16"/>
       <c r="B43" s="11" t="s">
         <v>70</v>
       </c>
@@ -21267,7 +24707,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
+      <c r="A44" s="16"/>
       <c r="B44" s="11" t="s">
         <v>71</v>
       </c>
@@ -21279,7 +24719,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="16"/>
       <c r="B45" s="11" t="s">
         <v>68</v>
       </c>
@@ -21292,7 +24732,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="15">
+      <c r="A46" s="16">
         <v>2035</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -21306,7 +24746,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="16"/>
       <c r="B47" s="11" t="s">
         <v>70</v>
       </c>
@@ -21318,7 +24758,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
+      <c r="A48" s="16"/>
       <c r="B48" s="11" t="s">
         <v>71</v>
       </c>
@@ -21330,7 +24770,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="16"/>
       <c r="B49" s="11" t="s">
         <v>68</v>
       </c>
@@ -21343,7 +24783,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
+      <c r="A50" s="16">
         <v>2036</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -21357,7 +24797,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="16"/>
       <c r="B51" s="11" t="s">
         <v>70</v>
       </c>
@@ -21369,7 +24809,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="15"/>
+      <c r="A52" s="16"/>
       <c r="B52" s="11" t="s">
         <v>71</v>
       </c>
@@ -21381,7 +24821,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="16"/>
       <c r="B53" s="11" t="s">
         <v>68</v>
       </c>
@@ -21394,7 +24834,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="15">
+      <c r="A54" s="16">
         <v>2037</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -21408,7 +24848,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="11" t="s">
         <v>70</v>
       </c>
@@ -21420,7 +24860,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="11" t="s">
         <v>71</v>
       </c>
@@ -21432,7 +24872,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="11" t="s">
         <v>68</v>
       </c>
@@ -21445,7 +24885,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="15">
+      <c r="A58" s="16">
         <v>2038</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -21459,7 +24899,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="11" t="s">
         <v>70</v>
       </c>
@@ -21471,7 +24911,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="15"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
@@ -21483,7 +24923,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="11" t="s">
         <v>68</v>
       </c>
@@ -21496,7 +24936,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="15">
+      <c r="A62" s="16">
         <v>2039</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -21510,7 +24950,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="11" t="s">
         <v>70</v>
       </c>
@@ -21522,7 +24962,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="15"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="11" t="s">
         <v>71</v>
       </c>
@@ -21534,7 +24974,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="11" t="s">
         <v>68</v>
       </c>
@@ -21547,7 +24987,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="15">
+      <c r="A66" s="16">
         <v>2040</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -21561,7 +25001,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
@@ -21573,7 +25013,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="15"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="11" t="s">
         <v>71</v>
       </c>
@@ -21585,7 +25025,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="11" t="s">
         <v>68</v>
       </c>
@@ -21598,7 +25038,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="15">
+      <c r="A70" s="16">
         <v>2041</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -21612,7 +25052,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="11" t="s">
         <v>70</v>
       </c>
@@ -21624,7 +25064,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="15"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="11" t="s">
         <v>71</v>
       </c>
@@ -21636,7 +25076,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="11" t="s">
         <v>68</v>
       </c>
@@ -21649,7 +25089,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="15">
+      <c r="A74" s="16">
         <v>2042</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -21663,7 +25103,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="11" t="s">
         <v>70</v>
       </c>
@@ -21675,7 +25115,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="15"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
@@ -21687,7 +25127,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="11" t="s">
         <v>68</v>
       </c>
@@ -21700,7 +25140,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="15">
+      <c r="A78" s="16">
         <v>2043</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -21714,7 +25154,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="11" t="s">
         <v>70</v>
       </c>
@@ -21726,7 +25166,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="15"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="11" t="s">
         <v>71</v>
       </c>
@@ -21738,7 +25178,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="16"/>
       <c r="B81" s="11" t="s">
         <v>68</v>
       </c>
@@ -21751,7 +25191,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="15">
+      <c r="A82" s="16">
         <v>2044</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -21765,7 +25205,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="16"/>
       <c r="B83" s="11" t="s">
         <v>70</v>
       </c>
@@ -21777,7 +25217,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="15"/>
+      <c r="A84" s="16"/>
       <c r="B84" s="11" t="s">
         <v>71</v>
       </c>
@@ -21789,7 +25229,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="16"/>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
@@ -21802,7 +25242,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="15">
+      <c r="A86" s="16">
         <v>2045</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -21816,7 +25256,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="16"/>
       <c r="B87" s="11" t="s">
         <v>70</v>
       </c>
@@ -21828,7 +25268,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="15"/>
+      <c r="A88" s="16"/>
       <c r="B88" s="11" t="s">
         <v>71</v>
       </c>
@@ -21840,7 +25280,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="16"/>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
@@ -21853,7 +25293,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="15">
+      <c r="A90" s="16">
         <v>2046</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -21867,7 +25307,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="16"/>
       <c r="B91" s="11" t="s">
         <v>70</v>
       </c>
@@ -21879,7 +25319,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
+      <c r="A92" s="16"/>
       <c r="B92" s="11" t="s">
         <v>71</v>
       </c>
@@ -21891,7 +25331,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="16"/>
       <c r="B93" s="11" t="s">
         <v>68</v>
       </c>
@@ -21904,7 +25344,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="15">
+      <c r="A94" s="16">
         <v>2047</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -21918,7 +25358,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="16"/>
       <c r="B95" s="11" t="s">
         <v>70</v>
       </c>
@@ -21930,7 +25370,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="15"/>
+      <c r="A96" s="16"/>
       <c r="B96" s="11" t="s">
         <v>71</v>
       </c>
@@ -21942,7 +25382,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="16"/>
       <c r="B97" s="11" t="s">
         <v>68</v>
       </c>
@@ -21955,7 +25395,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="15">
+      <c r="A98" s="16">
         <v>2048</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -21969,7 +25409,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="16"/>
       <c r="B99" s="11" t="s">
         <v>70</v>
       </c>
@@ -21981,7 +25421,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="15"/>
+      <c r="A100" s="16"/>
       <c r="B100" s="11" t="s">
         <v>71</v>
       </c>
@@ -21993,7 +25433,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="16"/>
       <c r="B101" s="11" t="s">
         <v>68</v>
       </c>
@@ -22006,7 +25446,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="15">
+      <c r="A102" s="16">
         <v>2049</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -22020,7 +25460,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
+      <c r="A103" s="16"/>
       <c r="B103" s="11" t="s">
         <v>70</v>
       </c>
@@ -22032,7 +25472,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="15"/>
+      <c r="A104" s="16"/>
       <c r="B104" s="11" t="s">
         <v>71</v>
       </c>
@@ -22044,7 +25484,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
+      <c r="A105" s="16"/>
       <c r="B105" s="11" t="s">
         <v>68</v>
       </c>
@@ -22057,7 +25497,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="15">
+      <c r="A106" s="16">
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -22071,7 +25511,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="16"/>
       <c r="B107" s="11" t="s">
         <v>70</v>
       </c>
@@ -22083,7 +25523,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="15"/>
+      <c r="A108" s="16"/>
       <c r="B108" s="11" t="s">
         <v>71</v>
       </c>
@@ -22095,7 +25535,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="16"/>
       <c r="B109" s="11" t="s">
         <v>68</v>
       </c>
@@ -22110,26 +25550,6 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -22137,6 +25557,26 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="605" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60C394FD-8E8C-4C4C-A2B5-938D74E72AFF}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77662A64-A8E0-4D4A-B470-EAA904996A10}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="12" activeTab="14" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="18" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -1506,6 +1506,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA1A697-84AA-4F97-BE70-81695B57512E}">
   <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -12517,13 +12520,13 @@
         <v>38640</v>
       </c>
       <c r="C2">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D2">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E2">
-        <v>250240</v>
+        <v>165600</v>
       </c>
       <c r="F2">
         <v>9999999</v>
@@ -12561,16 +12564,16 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C3">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D3">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E3">
-        <v>246486.39999999999</v>
+        <v>165600</v>
       </c>
       <c r="F3">
         <v>9999999</v>
@@ -12608,16 +12611,16 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C4">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D4">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E4">
-        <v>242789.10399999999</v>
+        <v>165600</v>
       </c>
       <c r="F4">
         <v>9999999</v>
@@ -12655,16 +12658,16 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C5">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D5">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E5">
-        <v>239147.26740000001</v>
+        <v>165600</v>
       </c>
       <c r="F5">
         <v>9999999</v>
@@ -12702,16 +12705,16 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C6">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D6">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E6">
-        <v>235560.05840000001</v>
+        <v>165600</v>
       </c>
       <c r="F6">
         <v>9999999</v>
@@ -12749,16 +12752,16 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C7">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D7">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E7">
-        <v>232026.65760000001</v>
+        <v>165600</v>
       </c>
       <c r="F7">
         <v>9999999</v>
@@ -12796,16 +12799,16 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C8">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D8">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E8">
-        <v>228546.25769999999</v>
+        <v>165600</v>
       </c>
       <c r="F8">
         <v>9999999</v>
@@ -12843,16 +12846,16 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C9">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D9">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E9">
-        <v>225118.0638</v>
+        <v>165600</v>
       </c>
       <c r="F9">
         <v>9999999</v>
@@ -12890,16 +12893,16 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C10">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D10">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E10">
-        <v>221741.2929</v>
+        <v>165600</v>
       </c>
       <c r="F10">
         <v>9999999</v>
@@ -12937,16 +12940,16 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C11">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D11">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E11">
-        <v>218415.1735</v>
+        <v>165600</v>
       </c>
       <c r="F11">
         <v>9999999</v>
@@ -12984,16 +12987,16 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C12">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D12">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E12">
-        <v>215138.94589999999</v>
+        <v>165600</v>
       </c>
       <c r="F12">
         <v>9999999</v>
@@ -13031,16 +13034,16 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C13">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D13">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E13">
-        <v>211911.86170000001</v>
+        <v>165600</v>
       </c>
       <c r="F13">
         <v>9999999</v>
@@ -13078,16 +13081,16 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C14">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D14">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E14">
-        <v>208733.1838</v>
+        <v>165600</v>
       </c>
       <c r="F14">
         <v>9999999</v>
@@ -13125,16 +13128,16 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C15">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D15">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E15">
-        <v>205602.18599999999</v>
+        <v>165600</v>
       </c>
       <c r="F15">
         <v>9999999</v>
@@ -13172,16 +13175,16 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C16">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D16">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E16">
-        <v>202518.1532</v>
+        <v>165600</v>
       </c>
       <c r="F16">
         <v>9999999</v>
@@ -13219,16 +13222,16 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C17">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D17">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E17">
-        <v>199480.38089999999</v>
+        <v>165600</v>
       </c>
       <c r="F17">
         <v>9999999</v>
@@ -13266,16 +13269,16 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C18">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D18">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E18">
-        <v>196488.1752</v>
+        <v>165600</v>
       </c>
       <c r="F18">
         <v>9999999</v>
@@ -13313,16 +13316,16 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C19">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D19">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E19">
-        <v>193540.85260000001</v>
+        <v>165600</v>
       </c>
       <c r="F19">
         <v>9999999</v>
@@ -13360,16 +13363,16 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C20">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D20">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E20">
-        <v>190637.73980000001</v>
+        <v>165600</v>
       </c>
       <c r="F20">
         <v>9999999</v>
@@ -13407,16 +13410,16 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C21">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D21">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E21">
-        <v>187778.17370000001</v>
+        <v>165600</v>
       </c>
       <c r="F21">
         <v>9999999</v>
@@ -13454,16 +13457,16 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C22">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D22">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E22">
-        <v>184961.50109999999</v>
+        <v>165600</v>
       </c>
       <c r="F22">
         <v>9999999</v>
@@ -13501,16 +13504,16 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C23">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D23">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E23">
-        <v>182187.07860000001</v>
+        <v>165600</v>
       </c>
       <c r="F23">
         <v>9999999</v>
@@ -13548,16 +13551,16 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C24">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D24">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E24">
-        <v>179454.27239999999</v>
+        <v>165600</v>
       </c>
       <c r="F24">
         <v>9999999</v>
@@ -13595,16 +13598,16 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C25">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D25">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E25">
-        <v>176762.4583</v>
+        <v>165600</v>
       </c>
       <c r="F25">
         <v>9999999</v>
@@ -13642,16 +13645,16 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C26">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D26">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E26">
-        <v>174111.0214</v>
+        <v>165600</v>
       </c>
       <c r="F26">
         <v>9999999</v>
@@ -13689,16 +13692,16 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C27">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D27">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E27">
-        <v>171499.3561</v>
+        <v>165600</v>
       </c>
       <c r="F27">
         <v>9999999</v>
@@ -13736,16 +13739,16 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>9999999</v>
+        <v>38640</v>
       </c>
       <c r="C28">
-        <v>9999999</v>
+        <v>55200</v>
       </c>
       <c r="D28">
-        <v>9999999</v>
+        <v>82800</v>
       </c>
       <c r="E28">
-        <v>168926.8658</v>
+        <v>165600</v>
       </c>
       <c r="F28">
         <v>9999999</v>
@@ -25550,6 +25553,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -25557,26 +25580,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77662A64-A8E0-4D4A-B470-EAA904996A10}"/>
+  <xr:revisionPtr revIDLastSave="627" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CCA5427-6049-44BF-9AE3-CCDE81E7DAB2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="18" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="38280" yWindow="-1710" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="13" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -4329,67 +4329,67 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D2">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F2">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O2">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -4397,67 +4397,67 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D3">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E3">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F3">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O3">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -4465,67 +4465,67 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D4">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E4">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F4">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O4">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -4533,67 +4533,67 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D5">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E5">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F5">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O5">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -4601,67 +4601,67 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D6">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E6">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F6">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O6">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -4669,67 +4669,67 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D7">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E7">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F7">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O7">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V7">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -4737,67 +4737,67 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D8">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E8">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F8">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O8">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V8">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -4805,67 +4805,67 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D9">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E9">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F9">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O9">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U9">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V9">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -4873,67 +4873,67 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D10">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E10">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F10">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O10">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -4941,67 +4941,67 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D11">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E11">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F11">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O11">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -5009,67 +5009,67 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D12">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E12">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F12">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O12">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -5077,67 +5077,67 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D13">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E13">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F13">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O13">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -5145,67 +5145,67 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D14">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E14">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F14">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N14">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O14">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V14">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -5213,67 +5213,67 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D15">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E15">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F15">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O15">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V15">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -5281,67 +5281,67 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D16">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E16">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F16">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O16">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V16">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -5349,67 +5349,67 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D17">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E17">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F17">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N17">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O17">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U17">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -5417,67 +5417,67 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D18">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E18">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F18">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O18">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V18">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -5485,67 +5485,67 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D19">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E19">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F19">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O19">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -5553,67 +5553,67 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C20">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D20">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E20">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F20">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N20">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O20">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -5621,67 +5621,67 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D21">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E21">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F21">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O21">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
@@ -5689,67 +5689,67 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D22">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E22">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F22">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O22">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V22">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -5757,67 +5757,67 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D23">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E23">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F23">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O23">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V23">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -5825,67 +5825,67 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D24">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E24">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F24">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O24">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -5893,67 +5893,67 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C25">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D25">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E25">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F25">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O25">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
@@ -5961,67 +5961,67 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C26">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D26">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E26">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F26">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N26">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O26">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U26">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V26">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
@@ -6029,67 +6029,67 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D27">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E27">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F27">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O27">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U27">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V27">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
@@ -6097,67 +6097,67 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>650000</v>
+        <v>83.72</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D28">
-        <v>3000</v>
+        <v>2540000</v>
       </c>
       <c r="E28">
-        <v>600</v>
+        <v>2484</v>
       </c>
       <c r="F28">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>40000</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="N28">
-        <v>30000</v>
+        <v>1800</v>
       </c>
       <c r="O28">
-        <v>30000</v>
+        <v>6800</v>
       </c>
       <c r="P28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="Q28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="R28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="S28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="T28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="U28">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="V28">
-        <v>30000</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6243,67 +6243,67 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C2">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D2">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E2">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F2">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O2">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -6311,67 +6311,67 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C3">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D3">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E3">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F3">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O3">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -6379,67 +6379,67 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C4">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D4">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E4">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F4">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O4">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -6447,67 +6447,67 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D5">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E5">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F5">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O5">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -6515,67 +6515,67 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C6">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D6">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E6">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F6">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O6">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -6583,67 +6583,67 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C7">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D7">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E7">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F7">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O7">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V7">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -6651,67 +6651,67 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C8">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D8">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E8">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F8">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O8">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V8">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -6719,67 +6719,67 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C9">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D9">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E9">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F9">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O9">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U9">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V9">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -6787,67 +6787,67 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C10">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D10">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E10">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F10">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O10">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -6855,67 +6855,67 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C11">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D11">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E11">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F11">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O11">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -6923,67 +6923,67 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C12">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D12">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E12">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F12">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O12">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -6991,67 +6991,67 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C13">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D13">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E13">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F13">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O13">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -7059,67 +7059,67 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C14">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D14">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E14">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F14">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N14">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O14">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V14">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -7127,67 +7127,67 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C15">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D15">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E15">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F15">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O15">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V15">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -7195,67 +7195,67 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C16">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D16">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E16">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F16">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O16">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V16">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -7263,67 +7263,67 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C17">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D17">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E17">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F17">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N17">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O17">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U17">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -7331,67 +7331,67 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C18">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D18">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E18">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F18">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O18">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V18">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -7399,67 +7399,67 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C19">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D19">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E19">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F19">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O19">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -7467,67 +7467,67 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C20">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D20">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E20">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F20">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N20">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O20">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -7535,67 +7535,67 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D21">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E21">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F21">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O21">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
@@ -7603,67 +7603,67 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C22">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D22">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E22">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F22">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O22">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V22">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -7671,67 +7671,67 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C23">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D23">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E23">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F23">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O23">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V23">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -7739,67 +7739,67 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C24">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D24">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E24">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F24">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O24">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -7807,67 +7807,67 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C25">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D25">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E25">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F25">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O25">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
@@ -7875,67 +7875,67 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C26">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D26">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E26">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F26">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N26">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O26">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U26">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V26">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
@@ -7943,67 +7943,67 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C27">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D27">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E27">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F27">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O27">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U27">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V27">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
@@ -8011,67 +8011,67 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>700000</v>
+        <v>83.72</v>
       </c>
       <c r="C28">
-        <v>150</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D28">
-        <v>3500</v>
+        <v>2540000</v>
       </c>
       <c r="E28">
-        <v>800</v>
+        <v>2484</v>
       </c>
       <c r="F28">
-        <v>9500</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>18000</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="N28">
-        <v>35000</v>
+        <v>1800</v>
       </c>
       <c r="O28">
-        <v>35000</v>
+        <v>6800</v>
       </c>
       <c r="P28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="Q28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="R28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="S28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="T28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="U28">
-        <v>35000</v>
+        <v>1</v>
       </c>
       <c r="V28">
-        <v>35000</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="627" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CCA5427-6049-44BF-9AE3-CCDE81E7DAB2}"/>
+  <xr:revisionPtr revIDLastSave="688" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF99B2D8-6013-44D2-BC0C-7C6E7DC34F3E}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-1710" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="13" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="7" activeTab="13" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="153">
   <si>
     <t>Value</t>
   </si>
@@ -508,6 +508,15 @@
   <si>
     <t>0.98</t>
   </si>
+  <si>
+    <t>0.994</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
 </sst>
 </file>
 
@@ -698,7 +707,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -726,9 +735,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -737,6 +743,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -1504,7 +1514,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA1A697-84AA-4F97-BE70-81695B57512E}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -1541,13 +1551,13 @@
         <v>131</v>
       </c>
       <c r="D2" s="12">
-        <v>7.5</v>
+        <v>11.080597014925374</v>
       </c>
       <c r="E2" s="12">
-        <v>7.5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>85</v>
+        <v>11.080597014925374</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1566,8 +1576,8 @@
       <c r="E3" s="12">
         <v>46.4</v>
       </c>
-      <c r="F3" t="s">
-        <v>85</v>
+      <c r="F3" s="12" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1581,12 +1591,12 @@
         <v>132</v>
       </c>
       <c r="D4" s="12">
-        <v>8.6000000000000014</v>
+        <v>7.6179104477611936</v>
       </c>
       <c r="E4" s="12">
-        <v>8.6000000000000014</v>
-      </c>
-      <c r="F4" t="s">
+        <v>7.6179104477611936</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1601,13 +1611,13 @@
         <v>133</v>
       </c>
       <c r="D5" s="12">
-        <v>4.5999999999999996</v>
+        <v>0.62328358208955215</v>
       </c>
       <c r="E5" s="12">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F5" t="s">
-        <v>85</v>
+        <v>0.62328358208955215</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1621,13 +1631,13 @@
         <v>134</v>
       </c>
       <c r="D6" s="12">
-        <v>1.9012500000000002E-2</v>
+        <v>2.0776119402985072E-2</v>
       </c>
       <c r="E6" s="12">
-        <v>1.9012500000000002E-2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>85</v>
+        <v>2.0776119402985072E-2</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1641,33 +1651,33 @@
         <v>135</v>
       </c>
       <c r="D7" s="12">
-        <v>3.803015625</v>
+        <v>3.047164179104477</v>
       </c>
       <c r="E7" s="12">
-        <v>3.803015625</v>
-      </c>
-      <c r="F7" t="s">
-        <v>85</v>
+        <v>3.047164179104477</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D8" s="12">
-        <v>0.94859999999999989</v>
+        <v>0.20776119402985074</v>
       </c>
       <c r="E8" s="12">
-        <v>0.94859999999999989</v>
-      </c>
-      <c r="F8" s="13">
-        <v>0</v>
+        <v>0.20776119402985074</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1678,15 +1688,15 @@
         <v>89</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="12">
-        <v>6.9563999999999995</v>
-      </c>
-      <c r="E9" s="12">
-        <v>6.9563999999999995</v>
-      </c>
-      <c r="F9" s="13">
+        <v>136</v>
+      </c>
+      <c r="D9" s="16">
+        <v>0.94859999999999989</v>
+      </c>
+      <c r="E9" s="16">
+        <v>0.94859999999999989</v>
+      </c>
+      <c r="F9" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1698,15 +1708,15 @@
         <v>89</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" s="12">
-        <v>1.17E-3</v>
-      </c>
-      <c r="E10" s="12">
-        <v>1.17E-3</v>
-      </c>
-      <c r="F10" s="13">
+        <v>137</v>
+      </c>
+      <c r="D10" s="16">
+        <v>6.9563999999999995</v>
+      </c>
+      <c r="E10" s="16">
+        <v>6.9563999999999995</v>
+      </c>
+      <c r="F10" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1718,15 +1728,15 @@
         <v>89</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="12">
-        <v>8.1</v>
-      </c>
-      <c r="E11" s="12">
-        <v>8.1</v>
-      </c>
-      <c r="F11" s="13">
+        <v>138</v>
+      </c>
+      <c r="D11" s="16">
+        <v>1.17E-3</v>
+      </c>
+      <c r="E11" s="16">
+        <v>1.17E-3</v>
+      </c>
+      <c r="F11" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1735,19 +1745,19 @@
         <v>76</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="12">
-        <v>114.72499999999999</v>
-      </c>
-      <c r="E12" s="12">
-        <v>114.72499999999999</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>148</v>
+        <v>132</v>
+      </c>
+      <c r="D12" s="16">
+        <v>8.1</v>
+      </c>
+      <c r="E12" s="16">
+        <v>8.1</v>
+      </c>
+      <c r="F12" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1758,16 +1768,16 @@
         <v>90</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="12">
-        <v>5.5</v>
-      </c>
-      <c r="E13" s="12">
-        <v>5.5</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>149</v>
+        <v>91</v>
+      </c>
+      <c r="D13" s="16">
+        <v>114.72499999999999</v>
+      </c>
+      <c r="E13" s="16">
+        <v>114.72499999999999</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1775,19 +1785,19 @@
         <v>76</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="12">
-        <v>5.47E-3</v>
-      </c>
-      <c r="E14" s="12">
-        <v>5.47E-3</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>85</v>
+        <v>139</v>
+      </c>
+      <c r="D14" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="E14" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1798,15 +1808,15 @@
         <v>92</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" s="12">
-        <v>4.7689999999999996E-2</v>
-      </c>
-      <c r="E15" s="12">
-        <v>4.7689999999999996E-2</v>
-      </c>
-      <c r="F15" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="16">
+        <v>5.47E-3</v>
+      </c>
+      <c r="E15" s="16">
+        <v>5.47E-3</v>
+      </c>
+      <c r="F15" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1818,15 +1828,15 @@
         <v>92</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="12">
-        <v>7.2699999999999996E-3</v>
-      </c>
-      <c r="E16" s="12">
-        <v>7.2699999999999996E-3</v>
-      </c>
-      <c r="F16" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="16">
+        <v>4.7689999999999996E-2</v>
+      </c>
+      <c r="E16" s="16">
+        <v>4.7689999999999996E-2</v>
+      </c>
+      <c r="F16" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1838,16 +1848,16 @@
         <v>92</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D17" s="12">
-        <v>2.7909999999999999</v>
-      </c>
-      <c r="E17" s="12">
-        <v>2.7909999999999999</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+      <c r="D17" s="16">
+        <v>7.2699999999999996E-3</v>
+      </c>
+      <c r="E17" s="16">
+        <v>7.2699999999999996E-3</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1858,15 +1868,15 @@
         <v>92</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" s="12">
-        <v>2.2925</v>
-      </c>
-      <c r="E18" s="12">
-        <v>2.2925</v>
-      </c>
-      <c r="F18" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="16">
+        <v>2.7909999999999999</v>
+      </c>
+      <c r="E18" s="16">
+        <v>2.7909999999999999</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1878,16 +1888,16 @@
         <v>92</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="12">
-        <v>18.945</v>
-      </c>
-      <c r="E19" s="12">
-        <v>18.945</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>85</v>
+        <v>133</v>
+      </c>
+      <c r="D19" s="16">
+        <v>2.2925</v>
+      </c>
+      <c r="E19" s="16">
+        <v>2.2925</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1898,15 +1908,15 @@
         <v>92</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="12">
-        <v>0.78549999999999998</v>
-      </c>
-      <c r="E20" s="12">
-        <v>0.78549999999999998</v>
-      </c>
-      <c r="F20" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="16">
+        <v>18.945</v>
+      </c>
+      <c r="E20" s="16">
+        <v>18.945</v>
+      </c>
+      <c r="F20" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1918,15 +1928,15 @@
         <v>92</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="12">
-        <v>0.1045</v>
-      </c>
-      <c r="E21" s="12">
-        <v>0.1045</v>
-      </c>
-      <c r="F21" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="16">
+        <v>0.78549999999999998</v>
+      </c>
+      <c r="E21" s="16">
+        <v>0.78549999999999998</v>
+      </c>
+      <c r="F21" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1938,15 +1948,15 @@
         <v>92</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="12">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="E22" s="12">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="F22" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="16">
+        <v>0.1045</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0.1045</v>
+      </c>
+      <c r="F22" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1958,36 +1968,36 @@
         <v>92</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" s="12">
-        <v>0.50024999999999997</v>
-      </c>
-      <c r="E23" s="12">
-        <v>0.50024999999999997</v>
-      </c>
-      <c r="F23" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="16">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="E23" s="16">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="F23" s="17" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="12">
-        <v>0.97139999999999993</v>
-      </c>
-      <c r="E24" s="12">
-        <v>0.97139999999999993</v>
-      </c>
-      <c r="F24" s="13">
-        <v>0</v>
+        <v>147</v>
+      </c>
+      <c r="D24" s="16">
+        <v>0.50024999999999997</v>
+      </c>
+      <c r="E24" s="16">
+        <v>0.50024999999999997</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1998,15 +2008,15 @@
         <v>89</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="12">
-        <v>7.1236000000000006</v>
-      </c>
-      <c r="E25" s="12">
-        <v>7.1236000000000006</v>
-      </c>
-      <c r="F25" s="13">
+        <v>136</v>
+      </c>
+      <c r="D25" s="16">
+        <v>0.97139999999999993</v>
+      </c>
+      <c r="E25" s="16">
+        <v>0.97139999999999993</v>
+      </c>
+      <c r="F25" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2018,15 +2028,15 @@
         <v>89</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D26" s="12">
-        <v>3.4500000000000004E-3</v>
-      </c>
-      <c r="E26" s="12">
-        <v>3.4500000000000004E-3</v>
-      </c>
-      <c r="F26" s="13">
+        <v>137</v>
+      </c>
+      <c r="D26" s="16">
+        <v>7.1236000000000006</v>
+      </c>
+      <c r="E26" s="16">
+        <v>7.1236000000000006</v>
+      </c>
+      <c r="F26" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2038,15 +2048,15 @@
         <v>89</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="12">
-        <v>11.6</v>
-      </c>
-      <c r="E27" s="12">
-        <v>11.6</v>
-      </c>
-      <c r="F27" s="13">
+        <v>138</v>
+      </c>
+      <c r="D27" s="16">
+        <v>3.4500000000000004E-3</v>
+      </c>
+      <c r="E27" s="16">
+        <v>3.4500000000000004E-3</v>
+      </c>
+      <c r="F27" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2055,19 +2065,19 @@
         <v>77</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="12">
-        <v>116.77</v>
-      </c>
-      <c r="E28" s="12">
-        <v>116.77</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>148</v>
+        <v>132</v>
+      </c>
+      <c r="D28" s="16">
+        <v>11.6</v>
+      </c>
+      <c r="E28" s="16">
+        <v>11.6</v>
+      </c>
+      <c r="F28" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2078,16 +2088,16 @@
         <v>90</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D29" s="12">
-        <v>5.5</v>
-      </c>
-      <c r="E29" s="12">
-        <v>5.5</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>149</v>
+        <v>91</v>
+      </c>
+      <c r="D29" s="16">
+        <v>116.77</v>
+      </c>
+      <c r="E29" s="16">
+        <v>116.77</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2095,19 +2105,19 @@
         <v>77</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D30" s="12">
-        <v>1.1259999999999999E-2</v>
-      </c>
-      <c r="E30" s="12">
-        <v>1.1259999999999999E-2</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>85</v>
+        <v>139</v>
+      </c>
+      <c r="D30" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="E30" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2118,15 +2128,15 @@
         <v>92</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="D31" s="12">
-        <v>0.11219</v>
-      </c>
-      <c r="E31" s="12">
-        <v>0.11219</v>
-      </c>
-      <c r="F31" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="16">
+        <v>1.1259999999999999E-2</v>
+      </c>
+      <c r="E31" s="16">
+        <v>1.1259999999999999E-2</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2138,15 +2148,15 @@
         <v>92</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D32" s="12">
-        <v>2.0460000000000002E-2</v>
-      </c>
-      <c r="E32" s="12">
-        <v>2.0460000000000002E-2</v>
-      </c>
-      <c r="F32" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="16">
+        <v>0.11219</v>
+      </c>
+      <c r="E32" s="16">
+        <v>0.11219</v>
+      </c>
+      <c r="F32" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2158,16 +2168,16 @@
         <v>92</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" s="12">
-        <v>4.04</v>
-      </c>
-      <c r="E33" s="12">
-        <v>4.04</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+      <c r="D33" s="16">
+        <v>2.0460000000000002E-2</v>
+      </c>
+      <c r="E33" s="16">
+        <v>2.0460000000000002E-2</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2178,15 +2188,15 @@
         <v>92</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" s="12">
-        <v>3.2574999999999998</v>
-      </c>
-      <c r="E34" s="12">
-        <v>3.2574999999999998</v>
-      </c>
-      <c r="F34" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34" s="16">
+        <v>4.04</v>
+      </c>
+      <c r="E34" s="16">
+        <v>4.04</v>
+      </c>
+      <c r="F34" s="17" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2198,16 +2208,16 @@
         <v>92</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="12">
-        <v>19.89</v>
-      </c>
-      <c r="E35" s="12">
-        <v>19.89</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>85</v>
+        <v>133</v>
+      </c>
+      <c r="D35" s="16">
+        <v>3.2574999999999998</v>
+      </c>
+      <c r="E35" s="16">
+        <v>3.2574999999999998</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2218,15 +2228,15 @@
         <v>92</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" s="12">
-        <v>0.79039999999999999</v>
-      </c>
-      <c r="E36" s="12">
-        <v>0.79039999999999999</v>
-      </c>
-      <c r="F36" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="16">
+        <v>19.89</v>
+      </c>
+      <c r="E36" s="16">
+        <v>19.89</v>
+      </c>
+      <c r="F36" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2238,15 +2248,15 @@
         <v>92</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D37" s="12">
-        <v>0.10940000000000001</v>
-      </c>
-      <c r="E37" s="12">
-        <v>0.10940000000000001</v>
-      </c>
-      <c r="F37" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="16">
+        <v>0.79039999999999999</v>
+      </c>
+      <c r="E37" s="16">
+        <v>0.79039999999999999</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2258,15 +2268,15 @@
         <v>92</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D38" s="12">
-        <v>0.32230000000000003</v>
-      </c>
-      <c r="E38" s="12">
-        <v>0.32230000000000003</v>
-      </c>
-      <c r="F38" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" s="16">
+        <v>0.10940000000000001</v>
+      </c>
+      <c r="E38" s="16">
+        <v>0.10940000000000001</v>
+      </c>
+      <c r="F38" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2278,35 +2288,35 @@
         <v>92</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="16">
+        <v>0.32230000000000003</v>
+      </c>
+      <c r="E39" s="16">
+        <v>0.32230000000000003</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D40" s="16">
         <v>0.5272</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E40" s="16">
         <v>0.5272</v>
       </c>
-      <c r="F39" s="13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" t="s">
-        <v>94</v>
-      </c>
-      <c r="D40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" t="s">
-        <v>95</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="F40" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2318,15 +2328,35 @@
         <v>86</v>
       </c>
       <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" t="s">
         <v>96</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>97</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" t="s">
         <v>97</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F42" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2346,1904 +2376,1904 @@
       <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>57100000</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>58100000</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1961</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>1760000</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4260,82 +4290,82 @@
       <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C2">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E2">
         <v>2484</v>
@@ -4365,10 +4395,10 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O2">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -4393,17 +4423,17 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C3">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E3">
         <v>2484</v>
@@ -4433,10 +4463,10 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O3">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -4461,17 +4491,17 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C4">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E4">
         <v>2484</v>
@@ -4501,10 +4531,10 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O4">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -4529,17 +4559,17 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C5">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E5">
         <v>2484</v>
@@ -4569,10 +4599,10 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O5">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -4597,17 +4627,17 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E6">
         <v>2484</v>
@@ -4637,10 +4667,10 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O6">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -4665,17 +4695,17 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C7">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E7">
         <v>2484</v>
@@ -4705,10 +4735,10 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O7">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -4733,17 +4763,17 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E8">
         <v>2484</v>
@@ -4773,10 +4803,10 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O8">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -4801,17 +4831,17 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E9">
         <v>2484</v>
@@ -4841,10 +4871,10 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O9">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -4869,17 +4899,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E10">
         <v>2484</v>
@@ -4909,10 +4939,10 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O10">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -4937,17 +4967,17 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C11">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E11">
         <v>2484</v>
@@ -4977,10 +5007,10 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O11">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -5005,17 +5035,17 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C12">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E12">
         <v>2484</v>
@@ -5045,10 +5075,10 @@
         <v>1</v>
       </c>
       <c r="N12">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O12">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P12">
         <v>1</v>
@@ -5073,17 +5103,17 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C13">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E13">
         <v>2484</v>
@@ -5113,10 +5143,10 @@
         <v>1</v>
       </c>
       <c r="N13">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O13">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P13">
         <v>1</v>
@@ -5141,17 +5171,17 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C14">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E14">
         <v>2484</v>
@@ -5181,10 +5211,10 @@
         <v>1</v>
       </c>
       <c r="N14">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O14">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P14">
         <v>1</v>
@@ -5209,17 +5239,17 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C15">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E15">
         <v>2484</v>
@@ -5249,10 +5279,10 @@
         <v>1</v>
       </c>
       <c r="N15">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O15">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -5277,17 +5307,17 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C16">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E16">
         <v>2484</v>
@@ -5317,10 +5347,10 @@
         <v>1</v>
       </c>
       <c r="N16">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O16">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -5345,17 +5375,17 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C17">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E17">
         <v>2484</v>
@@ -5385,10 +5415,10 @@
         <v>1</v>
       </c>
       <c r="N17">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O17">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P17">
         <v>1</v>
@@ -5413,17 +5443,17 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C18">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E18">
         <v>2484</v>
@@ -5453,10 +5483,10 @@
         <v>1</v>
       </c>
       <c r="N18">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O18">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P18">
         <v>1</v>
@@ -5481,17 +5511,17 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C19">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E19">
         <v>2484</v>
@@ -5521,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O19">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -5549,17 +5579,17 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C20">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E20">
         <v>2484</v>
@@ -5589,10 +5619,10 @@
         <v>1</v>
       </c>
       <c r="N20">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O20">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P20">
         <v>1</v>
@@ -5617,17 +5647,17 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C21">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E21">
         <v>2484</v>
@@ -5657,10 +5687,10 @@
         <v>1</v>
       </c>
       <c r="N21">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O21">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -5685,17 +5715,17 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C22">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E22">
         <v>2484</v>
@@ -5725,10 +5755,10 @@
         <v>1</v>
       </c>
       <c r="N22">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O22">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P22">
         <v>1</v>
@@ -5753,17 +5783,17 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C23">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E23">
         <v>2484</v>
@@ -5793,10 +5823,10 @@
         <v>1</v>
       </c>
       <c r="N23">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O23">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P23">
         <v>1</v>
@@ -5821,17 +5851,17 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C24">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E24">
         <v>2484</v>
@@ -5861,10 +5891,10 @@
         <v>1</v>
       </c>
       <c r="N24">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O24">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P24">
         <v>1</v>
@@ -5889,17 +5919,17 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C25">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E25">
         <v>2484</v>
@@ -5929,10 +5959,10 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O25">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -5957,17 +5987,17 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C26">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E26">
         <v>2484</v>
@@ -5997,10 +6027,10 @@
         <v>1</v>
       </c>
       <c r="N26">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O26">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -6025,17 +6055,17 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E27">
         <v>2484</v>
@@ -6065,10 +6095,10 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O27">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -6093,17 +6123,17 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C28">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E28">
         <v>2484</v>
@@ -6133,10 +6163,10 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O28">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P28">
         <v>1</v>
@@ -6174,82 +6204,82 @@
       <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C2">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E2">
         <v>2484</v>
@@ -6279,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O2">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -6307,17 +6337,17 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C3">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E3">
         <v>2484</v>
@@ -6347,10 +6377,10 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O3">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -6375,17 +6405,17 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C4">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E4">
         <v>2484</v>
@@ -6415,10 +6445,10 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O4">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -6443,17 +6473,17 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C5">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E5">
         <v>2484</v>
@@ -6483,10 +6513,10 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O5">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -6511,17 +6541,17 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E6">
         <v>2484</v>
@@ -6551,10 +6581,10 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O6">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -6579,17 +6609,17 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C7">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E7">
         <v>2484</v>
@@ -6619,10 +6649,10 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O7">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -6647,17 +6677,17 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E8">
         <v>2484</v>
@@ -6687,10 +6717,10 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O8">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -6715,17 +6745,17 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E9">
         <v>2484</v>
@@ -6755,10 +6785,10 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O9">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -6783,17 +6813,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E10">
         <v>2484</v>
@@ -6823,10 +6853,10 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O10">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -6851,17 +6881,17 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C11">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E11">
         <v>2484</v>
@@ -6891,10 +6921,10 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O11">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -6919,17 +6949,17 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C12">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E12">
         <v>2484</v>
@@ -6959,10 +6989,10 @@
         <v>1</v>
       </c>
       <c r="N12">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O12">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P12">
         <v>1</v>
@@ -6987,17 +7017,17 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C13">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E13">
         <v>2484</v>
@@ -7027,10 +7057,10 @@
         <v>1</v>
       </c>
       <c r="N13">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O13">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P13">
         <v>1</v>
@@ -7055,17 +7085,17 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C14">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E14">
         <v>2484</v>
@@ -7095,10 +7125,10 @@
         <v>1</v>
       </c>
       <c r="N14">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O14">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P14">
         <v>1</v>
@@ -7123,17 +7153,17 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C15">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E15">
         <v>2484</v>
@@ -7163,10 +7193,10 @@
         <v>1</v>
       </c>
       <c r="N15">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O15">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -7191,17 +7221,17 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C16">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E16">
         <v>2484</v>
@@ -7231,10 +7261,10 @@
         <v>1</v>
       </c>
       <c r="N16">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O16">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -7259,17 +7289,17 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C17">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E17">
         <v>2484</v>
@@ -7299,10 +7329,10 @@
         <v>1</v>
       </c>
       <c r="N17">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O17">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P17">
         <v>1</v>
@@ -7327,17 +7357,17 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C18">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E18">
         <v>2484</v>
@@ -7367,10 +7397,10 @@
         <v>1</v>
       </c>
       <c r="N18">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O18">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P18">
         <v>1</v>
@@ -7395,17 +7425,17 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C19">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E19">
         <v>2484</v>
@@ -7435,10 +7465,10 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O19">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -7463,17 +7493,17 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C20">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E20">
         <v>2484</v>
@@ -7503,10 +7533,10 @@
         <v>1</v>
       </c>
       <c r="N20">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O20">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P20">
         <v>1</v>
@@ -7531,17 +7561,17 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C21">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E21">
         <v>2484</v>
@@ -7571,10 +7601,10 @@
         <v>1</v>
       </c>
       <c r="N21">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O21">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -7599,17 +7629,17 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C22">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E22">
         <v>2484</v>
@@ -7639,10 +7669,10 @@
         <v>1</v>
       </c>
       <c r="N22">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O22">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P22">
         <v>1</v>
@@ -7667,17 +7697,17 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C23">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E23">
         <v>2484</v>
@@ -7707,10 +7737,10 @@
         <v>1</v>
       </c>
       <c r="N23">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O23">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P23">
         <v>1</v>
@@ -7735,17 +7765,17 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C24">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E24">
         <v>2484</v>
@@ -7775,10 +7805,10 @@
         <v>1</v>
       </c>
       <c r="N24">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O24">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P24">
         <v>1</v>
@@ -7803,17 +7833,17 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C25">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E25">
         <v>2484</v>
@@ -7843,10 +7873,10 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O25">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -7871,17 +7901,17 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C26">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E26">
         <v>2484</v>
@@ -7911,10 +7941,10 @@
         <v>1</v>
       </c>
       <c r="N26">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O26">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -7939,17 +7969,17 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E27">
         <v>2484</v>
@@ -7979,10 +8009,10 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O27">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -8007,17 +8037,17 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>83.72</v>
+        <v>59</v>
       </c>
       <c r="C28">
-        <v>9.1999999999999993</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>2540000</v>
+        <v>2500000</v>
       </c>
       <c r="E28">
         <v>2484</v>
@@ -8047,10 +8077,10 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <v>1800</v>
+        <v>3135</v>
       </c>
       <c r="O28">
-        <v>6800</v>
+        <v>12905</v>
       </c>
       <c r="P28">
         <v>1</v>
@@ -8088,72 +8118,72 @@
       <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>2024</v>
       </c>
       <c r="B2">
@@ -8221,7 +8251,7 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>2025</v>
       </c>
       <c r="B3">
@@ -8289,7 +8319,7 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>2026</v>
       </c>
       <c r="B4">
@@ -8357,7 +8387,7 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>2027</v>
       </c>
       <c r="B5">
@@ -8425,7 +8455,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>2028</v>
       </c>
       <c r="B6">
@@ -8493,7 +8523,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>2029</v>
       </c>
       <c r="B7">
@@ -8561,7 +8591,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>2030</v>
       </c>
       <c r="B8">
@@ -8629,7 +8659,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>2031</v>
       </c>
       <c r="B9">
@@ -8697,7 +8727,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>2032</v>
       </c>
       <c r="B10">
@@ -8765,7 +8795,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>2033</v>
       </c>
       <c r="B11">
@@ -8833,7 +8863,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>2034</v>
       </c>
       <c r="B12">
@@ -8901,7 +8931,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>2035</v>
       </c>
       <c r="B13">
@@ -8969,7 +8999,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>2036</v>
       </c>
       <c r="B14">
@@ -9037,7 +9067,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>2037</v>
       </c>
       <c r="B15">
@@ -9105,7 +9135,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>2038</v>
       </c>
       <c r="B16">
@@ -9173,7 +9203,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>2039</v>
       </c>
       <c r="B17">
@@ -9241,7 +9271,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>2040</v>
       </c>
       <c r="B18">
@@ -9309,7 +9339,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>2041</v>
       </c>
       <c r="B19">
@@ -9377,7 +9407,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>2042</v>
       </c>
       <c r="B20">
@@ -9445,7 +9475,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>2043</v>
       </c>
       <c r="B21">
@@ -9513,7 +9543,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>2044</v>
       </c>
       <c r="B22">
@@ -9581,7 +9611,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>2045</v>
       </c>
       <c r="B23">
@@ -9649,7 +9679,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>2046</v>
       </c>
       <c r="B24">
@@ -9717,7 +9747,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>2047</v>
       </c>
       <c r="B25">
@@ -9785,7 +9815,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>2048</v>
       </c>
       <c r="B26">
@@ -9853,7 +9883,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>2049</v>
       </c>
       <c r="B27">
@@ -9921,7 +9951,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>2050</v>
       </c>
       <c r="B28">
@@ -10002,72 +10032,72 @@
       <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>2024</v>
       </c>
       <c r="B2">
@@ -10135,7 +10165,7 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>2025</v>
       </c>
       <c r="B3">
@@ -10203,7 +10233,7 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>2026</v>
       </c>
       <c r="B4">
@@ -10271,7 +10301,7 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>2027</v>
       </c>
       <c r="B5">
@@ -10339,7 +10369,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>2028</v>
       </c>
       <c r="B6">
@@ -10407,7 +10437,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>2029</v>
       </c>
       <c r="B7">
@@ -10475,7 +10505,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>2030</v>
       </c>
       <c r="B8">
@@ -10543,7 +10573,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>2031</v>
       </c>
       <c r="B9">
@@ -10611,7 +10641,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>2032</v>
       </c>
       <c r="B10">
@@ -10679,7 +10709,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>2033</v>
       </c>
       <c r="B11">
@@ -10747,7 +10777,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>2034</v>
       </c>
       <c r="B12">
@@ -10815,7 +10845,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>2035</v>
       </c>
       <c r="B13">
@@ -10883,7 +10913,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>2036</v>
       </c>
       <c r="B14">
@@ -10951,7 +10981,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>2037</v>
       </c>
       <c r="B15">
@@ -11019,7 +11049,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>2038</v>
       </c>
       <c r="B16">
@@ -11087,7 +11117,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>2039</v>
       </c>
       <c r="B17">
@@ -11155,7 +11185,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>2040</v>
       </c>
       <c r="B18">
@@ -11223,7 +11253,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>2041</v>
       </c>
       <c r="B19">
@@ -11291,7 +11321,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>2042</v>
       </c>
       <c r="B20">
@@ -11359,7 +11389,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>2043</v>
       </c>
       <c r="B21">
@@ -11427,7 +11457,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>2044</v>
       </c>
       <c r="B22">
@@ -11495,7 +11525,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>2045</v>
       </c>
       <c r="B23">
@@ -11563,7 +11593,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>2046</v>
       </c>
       <c r="B24">
@@ -11631,7 +11661,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>2047</v>
       </c>
       <c r="B25">
@@ -11699,7 +11729,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>2048</v>
       </c>
       <c r="B26">
@@ -11767,7 +11797,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>2049</v>
       </c>
       <c r="B27">
@@ -11835,7 +11865,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>2050</v>
       </c>
       <c r="B28">
@@ -12146,13 +12176,13 @@
         <v>122</v>
       </c>
       <c r="E2" s="12">
-        <v>55200</v>
+        <v>64400.000000000007</v>
       </c>
       <c r="F2" s="12">
         <v>1449.0000000000002</v>
       </c>
       <c r="G2" s="12">
-        <v>3220.0000000000005</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -12237,13 +12267,13 @@
       <c r="D6" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="16">
         <v>73600</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="16">
         <v>20976.000000000007</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="16">
         <v>3680.0000000000009</v>
       </c>
     </row>
@@ -12260,13 +12290,13 @@
       <c r="D7" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="16">
         <v>82800</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="16">
         <v>7866</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="16">
         <v>4140</v>
       </c>
     </row>
@@ -12283,13 +12313,13 @@
       <c r="D8" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="16">
         <v>276000</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="16">
         <v>26220</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="16">
         <v>13800</v>
       </c>
     </row>
@@ -12306,13 +12336,13 @@
       <c r="D9" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="12">
-        <v>1</v>
-      </c>
-      <c r="F9" s="12">
-        <v>1</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="E9" s="16">
+        <v>1</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1</v>
+      </c>
+      <c r="G9" s="16">
         <v>1</v>
       </c>
     </row>
@@ -12329,13 +12359,13 @@
       <c r="D10" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="16">
         <v>165600</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="16">
         <v>47196</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="16">
         <v>8280</v>
       </c>
     </row>
@@ -12352,13 +12382,13 @@
       <c r="D11" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="16">
         <v>202400</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="16">
         <v>19228</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="16">
         <v>10120</v>
       </c>
     </row>
@@ -12375,13 +12405,13 @@
       <c r="D12" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="16">
         <v>202400</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="16">
         <v>19228</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="16">
         <v>10120</v>
       </c>
     </row>
@@ -12398,13 +12428,13 @@
       <c r="D13" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="12">
-        <v>1</v>
-      </c>
-      <c r="F13" s="12">
-        <v>1</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="E13" s="16">
+        <v>1</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
+      <c r="G13" s="16">
         <v>1</v>
       </c>
     </row>
@@ -12421,13 +12451,13 @@
       <c r="D14" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="16">
         <v>92000</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="16">
         <v>13524</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="16">
         <v>4600</v>
       </c>
     </row>
@@ -12444,13 +12474,13 @@
       <c r="D15" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="12">
-        <v>1</v>
-      </c>
-      <c r="F15" s="12">
-        <v>1</v>
-      </c>
-      <c r="G15" s="12">
+      <c r="E15" s="16">
+        <v>1</v>
+      </c>
+      <c r="F15" s="16">
+        <v>1</v>
+      </c>
+      <c r="G15" s="16">
         <v>1</v>
       </c>
     </row>
@@ -12526,7 +12556,7 @@
         <v>82800</v>
       </c>
       <c r="E2">
-        <v>165600</v>
+        <v>170200</v>
       </c>
       <c r="F2">
         <v>9999999</v>
@@ -12564,16 +12594,16 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>38640</v>
+        <v>38060.400000000001</v>
       </c>
       <c r="C3">
-        <v>55200</v>
+        <v>54372</v>
       </c>
       <c r="D3">
-        <v>82800</v>
+        <v>81558</v>
       </c>
       <c r="E3">
-        <v>165600</v>
+        <v>167647</v>
       </c>
       <c r="F3">
         <v>9999999</v>
@@ -12611,16 +12641,16 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>38640</v>
+        <v>37489.493999999999</v>
       </c>
       <c r="C4">
-        <v>55200</v>
+        <v>53556.42</v>
       </c>
       <c r="D4">
-        <v>82800</v>
+        <v>80334.63</v>
       </c>
       <c r="E4">
-        <v>165600</v>
+        <v>165132.29499999998</v>
       </c>
       <c r="F4">
         <v>9999999</v>
@@ -12658,16 +12688,16 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>38640</v>
+        <v>36927.151590000001</v>
       </c>
       <c r="C5">
-        <v>55200</v>
+        <v>52753.073700000001</v>
       </c>
       <c r="D5">
-        <v>82800</v>
+        <v>79129.610549999998</v>
       </c>
       <c r="E5">
-        <v>165600</v>
+        <v>162655.31057499998</v>
       </c>
       <c r="F5">
         <v>9999999</v>
@@ -12705,16 +12735,16 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>38640</v>
+        <v>36373.244316149998</v>
       </c>
       <c r="C6">
-        <v>55200</v>
+        <v>51961.777594500003</v>
       </c>
       <c r="D6">
-        <v>82800</v>
+        <v>77942.666391749997</v>
       </c>
       <c r="E6">
-        <v>165600</v>
+        <v>160215.48091637497</v>
       </c>
       <c r="F6">
         <v>9999999</v>
@@ -12752,16 +12782,16 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>38640</v>
+        <v>35827.645651407751</v>
       </c>
       <c r="C7">
-        <v>55200</v>
+        <v>51182.350930582499</v>
       </c>
       <c r="D7">
-        <v>82800</v>
+        <v>76773.526395873749</v>
       </c>
       <c r="E7">
-        <v>165600</v>
+        <v>157812.24870262935</v>
       </c>
       <c r="F7">
         <v>9999999</v>
@@ -12799,16 +12829,16 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>38640</v>
+        <v>35290.230966636635</v>
       </c>
       <c r="C8">
-        <v>55200</v>
+        <v>50414.615666623758</v>
       </c>
       <c r="D8">
-        <v>82800</v>
+        <v>75621.923499935641</v>
       </c>
       <c r="E8">
-        <v>165600</v>
+        <v>155445.06497208992</v>
       </c>
       <c r="F8">
         <v>9999999</v>
@@ -12846,16 +12876,16 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>38640</v>
+        <v>34760.877502137082</v>
       </c>
       <c r="C9">
-        <v>55200</v>
+        <v>49658.396431624402</v>
       </c>
       <c r="D9">
-        <v>82800</v>
+        <v>74487.594647436606</v>
       </c>
       <c r="E9">
-        <v>165600</v>
+        <v>153113.38899750856</v>
       </c>
       <c r="F9">
         <v>9999999</v>
@@ -12893,16 +12923,16 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>38640</v>
+        <v>34239.464339605023</v>
       </c>
       <c r="C10">
-        <v>55200</v>
+        <v>48913.520485150038</v>
       </c>
       <c r="D10">
-        <v>82800</v>
+        <v>73370.280727725054</v>
       </c>
       <c r="E10">
-        <v>165600</v>
+        <v>150816.68816254594</v>
       </c>
       <c r="F10">
         <v>9999999</v>
@@ -12940,16 +12970,16 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>38640</v>
+        <v>33725.872374510946</v>
       </c>
       <c r="C11">
-        <v>55200</v>
+        <v>48179.817677872787</v>
       </c>
       <c r="D11">
-        <v>82800</v>
+        <v>72269.726516809184</v>
       </c>
       <c r="E11">
-        <v>165600</v>
+        <v>148554.43784010774</v>
       </c>
       <c r="F11">
         <v>9999999</v>
@@ -12987,16 +13017,16 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>38640</v>
+        <v>33219.984288893284</v>
       </c>
       <c r="C12">
-        <v>55200</v>
+        <v>47457.120412704695</v>
       </c>
       <c r="D12">
-        <v>82800</v>
+        <v>71185.68061905705</v>
       </c>
       <c r="E12">
-        <v>165600</v>
+        <v>146326.12127250613</v>
       </c>
       <c r="F12">
         <v>9999999</v>
@@ -13034,16 +13064,16 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>38640</v>
+        <v>32721.684524559885</v>
       </c>
       <c r="C13">
-        <v>55200</v>
+        <v>46745.263606514127</v>
       </c>
       <c r="D13">
-        <v>82800</v>
+        <v>70117.895409771198</v>
       </c>
       <c r="E13">
-        <v>165600</v>
+        <v>144131.22945341855</v>
       </c>
       <c r="F13">
         <v>9999999</v>
@@ -13081,16 +13111,16 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>38640</v>
+        <v>32230.859256691485</v>
       </c>
       <c r="C14">
-        <v>55200</v>
+        <v>46044.084652416415</v>
       </c>
       <c r="D14">
-        <v>82800</v>
+        <v>69066.126978624627</v>
       </c>
       <c r="E14">
-        <v>165600</v>
+        <v>141969.26101161726</v>
       </c>
       <c r="F14">
         <v>9999999</v>
@@ -13128,16 +13158,16 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>38640</v>
+        <v>31747.396367841113</v>
       </c>
       <c r="C15">
-        <v>55200</v>
+        <v>45353.423382630172</v>
       </c>
       <c r="D15">
-        <v>82800</v>
+        <v>68030.135073945261</v>
       </c>
       <c r="E15">
-        <v>165600</v>
+        <v>139839.722096443</v>
       </c>
       <c r="F15">
         <v>9999999</v>
@@ -13175,16 +13205,16 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>38640</v>
+        <v>31271.185422323495</v>
       </c>
       <c r="C16">
-        <v>55200</v>
+        <v>44673.122031890722</v>
       </c>
       <c r="D16">
-        <v>82800</v>
+        <v>67009.683047836079</v>
       </c>
       <c r="E16">
-        <v>165600</v>
+        <v>137742.12626499636</v>
       </c>
       <c r="F16">
         <v>9999999</v>
@@ -13222,16 +13252,16 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>38640</v>
+        <v>30802.117640988643</v>
       </c>
       <c r="C17">
-        <v>55200</v>
+        <v>44003.025201412362</v>
       </c>
       <c r="D17">
-        <v>82800</v>
+        <v>66004.537802118532</v>
       </c>
       <c r="E17">
-        <v>165600</v>
+        <v>135675.9943710214</v>
       </c>
       <c r="F17">
         <v>9999999</v>
@@ -13269,16 +13299,16 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>38640</v>
+        <v>30340.085876373814</v>
       </c>
       <c r="C18">
-        <v>55200</v>
+        <v>43342.979823391179</v>
       </c>
       <c r="D18">
-        <v>82800</v>
+        <v>65014.46973508675</v>
       </c>
       <c r="E18">
-        <v>165600</v>
+        <v>133640.85445545608</v>
       </c>
       <c r="F18">
         <v>9999999</v>
@@ -13316,16 +13346,16 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>38640</v>
+        <v>29884.984588228206</v>
       </c>
       <c r="C19">
-        <v>55200</v>
+        <v>42692.835126040307</v>
       </c>
       <c r="D19">
-        <v>82800</v>
+        <v>64039.252689060449</v>
       </c>
       <c r="E19">
-        <v>165600</v>
+        <v>131636.24163862423</v>
       </c>
       <c r="F19">
         <v>9999999</v>
@@ -13363,16 +13393,16 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>38640</v>
+        <v>29436.709819404783</v>
       </c>
       <c r="C20">
-        <v>55200</v>
+        <v>42052.442599149705</v>
       </c>
       <c r="D20">
-        <v>82800</v>
+        <v>63078.663898724539</v>
       </c>
       <c r="E20">
-        <v>165600</v>
+        <v>129661.69801404486</v>
       </c>
       <c r="F20">
         <v>9999999</v>
@@ -13410,16 +13440,16 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>38640</v>
+        <v>28995.159172113712</v>
       </c>
       <c r="C21">
-        <v>55200</v>
+        <v>41421.655960162461</v>
       </c>
       <c r="D21">
-        <v>82800</v>
+        <v>62132.48394024367</v>
       </c>
       <c r="E21">
-        <v>165600</v>
+        <v>127716.77254383419</v>
       </c>
       <c r="F21">
         <v>9999999</v>
@@ -13457,16 +13487,16 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>38640</v>
+        <v>28560.231784532007</v>
       </c>
       <c r="C22">
-        <v>55200</v>
+        <v>40800.331120760027</v>
       </c>
       <c r="D22">
-        <v>82800</v>
+        <v>61200.496681140015</v>
       </c>
       <c r="E22">
-        <v>165600</v>
+        <v>125801.02095567668</v>
       </c>
       <c r="F22">
         <v>9999999</v>
@@ -13504,16 +13534,16 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>38640</v>
+        <v>28131.828307764026</v>
       </c>
       <c r="C23">
-        <v>55200</v>
+        <v>40188.326153948627</v>
       </c>
       <c r="D23">
-        <v>82800</v>
+        <v>60282.489230922911</v>
       </c>
       <c r="E23">
-        <v>165600</v>
+        <v>123914.00564134153</v>
       </c>
       <c r="F23">
         <v>9999999</v>
@@ -13551,16 +13581,16 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>38640</v>
+        <v>27709.850883147566</v>
       </c>
       <c r="C24">
-        <v>55200</v>
+        <v>39585.501261639394</v>
       </c>
       <c r="D24">
-        <v>82800</v>
+        <v>59378.251892459069</v>
       </c>
       <c r="E24">
-        <v>165600</v>
+        <v>122055.29555672141</v>
       </c>
       <c r="F24">
         <v>9999999</v>
@@ -13598,16 +13628,16 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>38640</v>
+        <v>27294.203119900354</v>
       </c>
       <c r="C25">
-        <v>55200</v>
+        <v>38991.718742714802</v>
       </c>
       <c r="D25">
-        <v>82800</v>
+        <v>58487.578114072181</v>
       </c>
       <c r="E25">
-        <v>165600</v>
+        <v>120224.46612337058</v>
       </c>
       <c r="F25">
         <v>9999999</v>
@@ -13645,16 +13675,16 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>38640</v>
+        <v>26884.790073101849</v>
       </c>
       <c r="C26">
-        <v>55200</v>
+        <v>38406.842961574082</v>
       </c>
       <c r="D26">
-        <v>82800</v>
+        <v>57610.264442361098</v>
       </c>
       <c r="E26">
-        <v>165600</v>
+        <v>118421.09913152002</v>
       </c>
       <c r="F26">
         <v>9999999</v>
@@ -13692,16 +13722,16 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>38640</v>
+        <v>26481.518222005321</v>
       </c>
       <c r="C27">
-        <v>55200</v>
+        <v>37830.74031715047</v>
       </c>
       <c r="D27">
-        <v>82800</v>
+        <v>56746.110475725684</v>
       </c>
       <c r="E27">
-        <v>165600</v>
+        <v>116644.78264454722</v>
       </c>
       <c r="F27">
         <v>9999999</v>
@@ -13739,16 +13769,16 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>38640</v>
+        <v>26084.295448675242</v>
       </c>
       <c r="C28">
-        <v>55200</v>
+        <v>37263.279212393216</v>
       </c>
       <c r="D28">
-        <v>82800</v>
+        <v>55894.918818589795</v>
       </c>
       <c r="E28">
-        <v>165600</v>
+        <v>114895.11090487901</v>
       </c>
       <c r="F28">
         <v>9999999</v>
@@ -22366,7 +22396,7 @@
       <c r="Q2" s="6">
         <v>70.922028124999997</v>
       </c>
-      <c r="R2" s="14">
+      <c r="R2" s="13">
         <v>0.85</v>
       </c>
       <c r="S2" s="6">
@@ -22449,7 +22479,7 @@
       <c r="Q3" s="6">
         <v>171.04915999999997</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="13">
         <v>0.95</v>
       </c>
       <c r="S3" s="6">
@@ -22532,7 +22562,7 @@
       <c r="Q4" s="6">
         <v>162.10234999999997</v>
       </c>
-      <c r="R4" s="14">
+      <c r="R4" s="13">
         <v>0.95</v>
       </c>
       <c r="S4" s="6">
@@ -22615,7 +22645,7 @@
       <c r="Q5" s="6">
         <v>20</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="13">
         <v>0.7</v>
       </c>
       <c r="S5" s="6">
@@ -24174,7 +24204,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="15">
         <v>2024</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -24188,7 +24218,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
+      <c r="A3" s="15"/>
       <c r="B3" s="11" t="s">
         <v>70</v>
       </c>
@@ -24201,7 +24231,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -24213,7 +24243,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
+      <c r="A5" s="15"/>
       <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
@@ -24225,7 +24255,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="15">
         <v>2025</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -24239,7 +24269,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
@@ -24251,7 +24281,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
@@ -24263,7 +24293,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="11" t="s">
         <v>68</v>
       </c>
@@ -24276,7 +24306,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+      <c r="A10" s="15">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -24290,7 +24320,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
@@ -24302,7 +24332,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -24314,7 +24344,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -24327,7 +24357,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
+      <c r="A14" s="15">
         <v>2027</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -24341,7 +24371,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
@@ -24353,7 +24383,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
@@ -24365,7 +24395,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
@@ -24378,7 +24408,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="A18" s="15">
         <v>2028</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -24392,7 +24422,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
@@ -24404,7 +24434,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
@@ -24416,7 +24446,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="11" t="s">
         <v>68</v>
       </c>
@@ -24429,7 +24459,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="A22" s="15">
         <v>2029</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -24443,7 +24473,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="11" t="s">
         <v>70</v>
       </c>
@@ -24455,7 +24485,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="11" t="s">
         <v>71</v>
       </c>
@@ -24467,7 +24497,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="11" t="s">
         <v>68</v>
       </c>
@@ -24480,7 +24510,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
+      <c r="A26" s="15">
         <v>2030</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -24494,7 +24524,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="11" t="s">
         <v>70</v>
       </c>
@@ -24506,7 +24536,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="11" t="s">
         <v>71</v>
       </c>
@@ -24518,7 +24548,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="11" t="s">
         <v>68</v>
       </c>
@@ -24531,7 +24561,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
+      <c r="A30" s="15">
         <v>2031</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -24545,7 +24575,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
@@ -24557,7 +24587,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="11" t="s">
         <v>71</v>
       </c>
@@ -24569,7 +24599,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
@@ -24582,7 +24612,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
+      <c r="A34" s="15">
         <v>2032</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -24596,7 +24626,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="11" t="s">
         <v>70</v>
       </c>
@@ -24608,7 +24638,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
+      <c r="A36" s="15"/>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
@@ -24620,7 +24650,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
+      <c r="A37" s="15"/>
       <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
@@ -24633,7 +24663,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="16">
+      <c r="A38" s="15">
         <v>2033</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -24647,7 +24677,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
+      <c r="A39" s="15"/>
       <c r="B39" s="11" t="s">
         <v>70</v>
       </c>
@@ -24659,7 +24689,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
+      <c r="A40" s="15"/>
       <c r="B40" s="11" t="s">
         <v>71</v>
       </c>
@@ -24671,7 +24701,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
+      <c r="A41" s="15"/>
       <c r="B41" s="11" t="s">
         <v>68</v>
       </c>
@@ -24684,7 +24714,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="16">
+      <c r="A42" s="15">
         <v>2034</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -24698,7 +24728,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
+      <c r="A43" s="15"/>
       <c r="B43" s="11" t="s">
         <v>70</v>
       </c>
@@ -24710,7 +24740,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
+      <c r="A44" s="15"/>
       <c r="B44" s="11" t="s">
         <v>71</v>
       </c>
@@ -24722,7 +24752,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
+      <c r="A45" s="15"/>
       <c r="B45" s="11" t="s">
         <v>68</v>
       </c>
@@ -24735,7 +24765,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="16">
+      <c r="A46" s="15">
         <v>2035</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -24749,7 +24779,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="16"/>
+      <c r="A47" s="15"/>
       <c r="B47" s="11" t="s">
         <v>70</v>
       </c>
@@ -24761,7 +24791,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
+      <c r="A48" s="15"/>
       <c r="B48" s="11" t="s">
         <v>71</v>
       </c>
@@ -24773,7 +24803,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
+      <c r="A49" s="15"/>
       <c r="B49" s="11" t="s">
         <v>68</v>
       </c>
@@ -24786,7 +24816,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="16">
+      <c r="A50" s="15">
         <v>2036</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -24800,7 +24830,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
+      <c r="A51" s="15"/>
       <c r="B51" s="11" t="s">
         <v>70</v>
       </c>
@@ -24812,7 +24842,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="16"/>
+      <c r="A52" s="15"/>
       <c r="B52" s="11" t="s">
         <v>71</v>
       </c>
@@ -24824,7 +24854,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="16"/>
+      <c r="A53" s="15"/>
       <c r="B53" s="11" t="s">
         <v>68</v>
       </c>
@@ -24837,7 +24867,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="16">
+      <c r="A54" s="15">
         <v>2037</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -24851,7 +24881,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="16"/>
+      <c r="A55" s="15"/>
       <c r="B55" s="11" t="s">
         <v>70</v>
       </c>
@@ -24863,7 +24893,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="16"/>
+      <c r="A56" s="15"/>
       <c r="B56" s="11" t="s">
         <v>71</v>
       </c>
@@ -24875,7 +24905,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="16"/>
+      <c r="A57" s="15"/>
       <c r="B57" s="11" t="s">
         <v>68</v>
       </c>
@@ -24888,7 +24918,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="16">
+      <c r="A58" s="15">
         <v>2038</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -24902,7 +24932,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="16"/>
+      <c r="A59" s="15"/>
       <c r="B59" s="11" t="s">
         <v>70</v>
       </c>
@@ -24914,7 +24944,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="16"/>
+      <c r="A60" s="15"/>
       <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
@@ -24926,7 +24956,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="16"/>
+      <c r="A61" s="15"/>
       <c r="B61" s="11" t="s">
         <v>68</v>
       </c>
@@ -24939,7 +24969,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="16">
+      <c r="A62" s="15">
         <v>2039</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -24953,7 +24983,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="16"/>
+      <c r="A63" s="15"/>
       <c r="B63" s="11" t="s">
         <v>70</v>
       </c>
@@ -24965,7 +24995,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="16"/>
+      <c r="A64" s="15"/>
       <c r="B64" s="11" t="s">
         <v>71</v>
       </c>
@@ -24977,7 +25007,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="16"/>
+      <c r="A65" s="15"/>
       <c r="B65" s="11" t="s">
         <v>68</v>
       </c>
@@ -24990,7 +25020,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="16">
+      <c r="A66" s="15">
         <v>2040</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -25004,7 +25034,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="16"/>
+      <c r="A67" s="15"/>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
@@ -25016,7 +25046,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="16"/>
+      <c r="A68" s="15"/>
       <c r="B68" s="11" t="s">
         <v>71</v>
       </c>
@@ -25028,7 +25058,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="16"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="11" t="s">
         <v>68</v>
       </c>
@@ -25041,7 +25071,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="16">
+      <c r="A70" s="15">
         <v>2041</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -25055,7 +25085,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="16"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="11" t="s">
         <v>70</v>
       </c>
@@ -25067,7 +25097,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="16"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="11" t="s">
         <v>71</v>
       </c>
@@ -25079,7 +25109,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="16"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="11" t="s">
         <v>68</v>
       </c>
@@ -25092,7 +25122,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="16">
+      <c r="A74" s="15">
         <v>2042</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -25106,7 +25136,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="16"/>
+      <c r="A75" s="15"/>
       <c r="B75" s="11" t="s">
         <v>70</v>
       </c>
@@ -25118,7 +25148,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="16"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
@@ -25130,7 +25160,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="16"/>
+      <c r="A77" s="15"/>
       <c r="B77" s="11" t="s">
         <v>68</v>
       </c>
@@ -25143,7 +25173,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="16">
+      <c r="A78" s="15">
         <v>2043</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -25157,7 +25187,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="16"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="11" t="s">
         <v>70</v>
       </c>
@@ -25169,7 +25199,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="16"/>
+      <c r="A80" s="15"/>
       <c r="B80" s="11" t="s">
         <v>71</v>
       </c>
@@ -25181,7 +25211,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="16"/>
+      <c r="A81" s="15"/>
       <c r="B81" s="11" t="s">
         <v>68</v>
       </c>
@@ -25194,7 +25224,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="16">
+      <c r="A82" s="15">
         <v>2044</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -25208,7 +25238,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="16"/>
+      <c r="A83" s="15"/>
       <c r="B83" s="11" t="s">
         <v>70</v>
       </c>
@@ -25220,7 +25250,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="16"/>
+      <c r="A84" s="15"/>
       <c r="B84" s="11" t="s">
         <v>71</v>
       </c>
@@ -25232,7 +25262,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="16"/>
+      <c r="A85" s="15"/>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
@@ -25245,7 +25275,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="16">
+      <c r="A86" s="15">
         <v>2045</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -25259,7 +25289,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="16"/>
+      <c r="A87" s="15"/>
       <c r="B87" s="11" t="s">
         <v>70</v>
       </c>
@@ -25271,7 +25301,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="16"/>
+      <c r="A88" s="15"/>
       <c r="B88" s="11" t="s">
         <v>71</v>
       </c>
@@ -25283,7 +25313,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="16"/>
+      <c r="A89" s="15"/>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
@@ -25296,7 +25326,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="16">
+      <c r="A90" s="15">
         <v>2046</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -25310,7 +25340,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="16"/>
+      <c r="A91" s="15"/>
       <c r="B91" s="11" t="s">
         <v>70</v>
       </c>
@@ -25322,7 +25352,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="16"/>
+      <c r="A92" s="15"/>
       <c r="B92" s="11" t="s">
         <v>71</v>
       </c>
@@ -25334,7 +25364,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="16"/>
+      <c r="A93" s="15"/>
       <c r="B93" s="11" t="s">
         <v>68</v>
       </c>
@@ -25347,7 +25377,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="16">
+      <c r="A94" s="15">
         <v>2047</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -25361,7 +25391,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="16"/>
+      <c r="A95" s="15"/>
       <c r="B95" s="11" t="s">
         <v>70</v>
       </c>
@@ -25373,7 +25403,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="16"/>
+      <c r="A96" s="15"/>
       <c r="B96" s="11" t="s">
         <v>71</v>
       </c>
@@ -25385,7 +25415,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="16"/>
+      <c r="A97" s="15"/>
       <c r="B97" s="11" t="s">
         <v>68</v>
       </c>
@@ -25398,7 +25428,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="16">
+      <c r="A98" s="15">
         <v>2048</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -25412,7 +25442,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="16"/>
+      <c r="A99" s="15"/>
       <c r="B99" s="11" t="s">
         <v>70</v>
       </c>
@@ -25424,7 +25454,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="16"/>
+      <c r="A100" s="15"/>
       <c r="B100" s="11" t="s">
         <v>71</v>
       </c>
@@ -25436,7 +25466,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="16"/>
+      <c r="A101" s="15"/>
       <c r="B101" s="11" t="s">
         <v>68</v>
       </c>
@@ -25449,7 +25479,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="16">
+      <c r="A102" s="15">
         <v>2049</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -25463,7 +25493,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="16"/>
+      <c r="A103" s="15"/>
       <c r="B103" s="11" t="s">
         <v>70</v>
       </c>
@@ -25475,7 +25505,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="16"/>
+      <c r="A104" s="15"/>
       <c r="B104" s="11" t="s">
         <v>71</v>
       </c>
@@ -25487,7 +25517,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="16"/>
+      <c r="A105" s="15"/>
       <c r="B105" s="11" t="s">
         <v>68</v>
       </c>
@@ -25500,7 +25530,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="16">
+      <c r="A106" s="15">
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -25514,7 +25544,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="16"/>
+      <c r="A107" s="15"/>
       <c r="B107" s="11" t="s">
         <v>70</v>
       </c>
@@ -25526,7 +25556,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="16"/>
+      <c r="A108" s="15"/>
       <c r="B108" s="11" t="s">
         <v>71</v>
       </c>
@@ -25538,7 +25568,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="16"/>
+      <c r="A109" s="15"/>
       <c r="B109" s="11" t="s">
         <v>68</v>
       </c>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="688" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF99B2D8-6013-44D2-BC0C-7C6E7DC34F3E}"/>
+  <xr:revisionPtr revIDLastSave="693" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AD85F33-426E-44BB-A093-4FD93EDE6565}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="7" activeTab="13" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="38280" yWindow="-1710" windowWidth="38640" windowHeight="21120" firstSheet="7" activeTab="12" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -707,7 +707,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -743,10 +743,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -1690,13 +1686,13 @@
       <c r="C9" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9">
         <v>0.94859999999999989</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9">
         <v>0.94859999999999989</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1710,13 +1706,13 @@
       <c r="C10" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10">
         <v>6.9563999999999995</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10">
         <v>6.9563999999999995</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1730,13 +1726,13 @@
       <c r="C11" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11">
         <v>1.17E-3</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11">
         <v>1.17E-3</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1750,13 +1746,13 @@
       <c r="C12" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12">
         <v>8.1</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12">
         <v>8.1</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1770,13 +1766,13 @@
       <c r="C13" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13">
         <v>114.72499999999999</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13">
         <v>114.72499999999999</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="9" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1790,13 +1786,13 @@
       <c r="C14" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14">
         <v>5.5</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14">
         <v>5.5</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="9" t="s">
         <v>149</v>
       </c>
     </row>
@@ -1810,13 +1806,13 @@
       <c r="C15" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15">
         <v>5.47E-3</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15">
         <v>5.47E-3</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1830,13 +1826,13 @@
       <c r="C16" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16">
         <v>4.7689999999999996E-2</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16">
         <v>4.7689999999999996E-2</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1850,13 +1846,13 @@
       <c r="C17" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17">
         <v>7.2699999999999996E-3</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17">
         <v>7.2699999999999996E-3</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1870,13 +1866,13 @@
       <c r="C18" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18">
         <v>2.7909999999999999</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18">
         <v>2.7909999999999999</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="9" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1890,13 +1886,13 @@
       <c r="C19" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19">
         <v>2.2925</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19">
         <v>2.2925</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="9" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1910,13 +1906,13 @@
       <c r="C20" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20">
         <v>18.945</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20">
         <v>18.945</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1930,13 +1926,13 @@
       <c r="C21" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21">
         <v>0.78549999999999998</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21">
         <v>0.78549999999999998</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1950,13 +1946,13 @@
       <c r="C22" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22">
         <v>0.1045</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22">
         <v>0.1045</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1970,13 +1966,13 @@
       <c r="C23" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1990,13 +1986,13 @@
       <c r="C24" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24">
         <v>0.50024999999999997</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24">
         <v>0.50024999999999997</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2010,13 +2006,13 @@
       <c r="C25" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25">
         <v>0.97139999999999993</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25">
         <v>0.97139999999999993</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2030,13 +2026,13 @@
       <c r="C26" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26">
         <v>7.1236000000000006</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26">
         <v>7.1236000000000006</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2050,13 +2046,13 @@
       <c r="C27" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27">
         <v>3.4500000000000004E-3</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27">
         <v>3.4500000000000004E-3</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2070,13 +2066,13 @@
       <c r="C28" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28">
         <v>11.6</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28">
         <v>11.6</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2090,13 +2086,13 @@
       <c r="C29" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29">
         <v>116.77</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29">
         <v>116.77</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="9" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2110,13 +2106,13 @@
       <c r="C30" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30">
         <v>5.5</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30">
         <v>5.5</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="9" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2130,13 +2126,13 @@
       <c r="C31" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31">
         <v>1.1259999999999999E-2</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31">
         <v>1.1259999999999999E-2</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2150,13 +2146,13 @@
       <c r="C32" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32">
         <v>0.11219</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32">
         <v>0.11219</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2170,13 +2166,13 @@
       <c r="C33" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33">
         <v>2.0460000000000002E-2</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33">
         <v>2.0460000000000002E-2</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2190,13 +2186,13 @@
       <c r="C34" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34">
         <v>4.04</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34">
         <v>4.04</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="9" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2210,13 +2206,13 @@
       <c r="C35" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35">
         <v>3.2574999999999998</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35">
         <v>3.2574999999999998</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="9" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2230,13 +2226,13 @@
       <c r="C36" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36">
         <v>19.89</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36">
         <v>19.89</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2250,13 +2246,13 @@
       <c r="C37" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37">
         <v>0.79039999999999999</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37">
         <v>0.79039999999999999</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2270,13 +2266,13 @@
       <c r="C38" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38">
         <v>0.10940000000000001</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38">
         <v>0.10940000000000001</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2290,13 +2286,13 @@
       <c r="C39" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39">
         <v>0.32230000000000003</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39">
         <v>0.32230000000000003</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2310,13 +2306,13 @@
       <c r="C40" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40">
         <v>0.5272</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40">
         <v>0.5272</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -6285,28 +6281,28 @@
         <v>2484</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N2">
         <v>3135</v>
@@ -6315,25 +6311,25 @@
         <v>12905</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -6353,28 +6349,28 @@
         <v>2484</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N3">
         <v>3135</v>
@@ -6383,25 +6379,25 @@
         <v>12905</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -6421,28 +6417,28 @@
         <v>2484</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N4">
         <v>3135</v>
@@ -6451,25 +6447,25 @@
         <v>12905</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -6489,28 +6485,28 @@
         <v>2484</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N5">
         <v>3135</v>
@@ -6519,25 +6515,25 @@
         <v>12905</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -6557,28 +6553,28 @@
         <v>2484</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N6">
         <v>3135</v>
@@ -6587,25 +6583,25 @@
         <v>12905</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -6625,28 +6621,28 @@
         <v>2484</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N7">
         <v>3135</v>
@@ -6655,25 +6651,25 @@
         <v>12905</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -6693,28 +6689,28 @@
         <v>2484</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N8">
         <v>3135</v>
@@ -6723,25 +6719,25 @@
         <v>12905</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -6761,28 +6757,28 @@
         <v>2484</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N9">
         <v>3135</v>
@@ -6791,25 +6787,25 @@
         <v>12905</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -6829,28 +6825,28 @@
         <v>2484</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N10">
         <v>3135</v>
@@ -6859,25 +6855,25 @@
         <v>12905</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -6897,28 +6893,28 @@
         <v>2484</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N11">
         <v>3135</v>
@@ -6927,25 +6923,25 @@
         <v>12905</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -6965,28 +6961,28 @@
         <v>2484</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N12">
         <v>3135</v>
@@ -6995,25 +6991,25 @@
         <v>12905</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -7033,28 +7029,28 @@
         <v>2484</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N13">
         <v>3135</v>
@@ -7063,25 +7059,25 @@
         <v>12905</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -7101,28 +7097,28 @@
         <v>2484</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N14">
         <v>3135</v>
@@ -7131,25 +7127,25 @@
         <v>12905</v>
       </c>
       <c r="P14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -7169,28 +7165,28 @@
         <v>2484</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N15">
         <v>3135</v>
@@ -7199,25 +7195,25 @@
         <v>12905</v>
       </c>
       <c r="P15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -7237,28 +7233,28 @@
         <v>2484</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N16">
         <v>3135</v>
@@ -7267,25 +7263,25 @@
         <v>12905</v>
       </c>
       <c r="P16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -7305,28 +7301,28 @@
         <v>2484</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N17">
         <v>3135</v>
@@ -7335,25 +7331,25 @@
         <v>12905</v>
       </c>
       <c r="P17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -7373,28 +7369,28 @@
         <v>2484</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N18">
         <v>3135</v>
@@ -7403,25 +7399,25 @@
         <v>12905</v>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -7441,28 +7437,28 @@
         <v>2484</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N19">
         <v>3135</v>
@@ -7471,25 +7467,25 @@
         <v>12905</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -7509,28 +7505,28 @@
         <v>2484</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N20">
         <v>3135</v>
@@ -7539,25 +7535,25 @@
         <v>12905</v>
       </c>
       <c r="P20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -7577,28 +7573,28 @@
         <v>2484</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N21">
         <v>3135</v>
@@ -7607,25 +7603,25 @@
         <v>12905</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
@@ -7645,28 +7641,28 @@
         <v>2484</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N22">
         <v>3135</v>
@@ -7675,25 +7671,25 @@
         <v>12905</v>
       </c>
       <c r="P22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -7713,28 +7709,28 @@
         <v>2484</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N23">
         <v>3135</v>
@@ -7743,25 +7739,25 @@
         <v>12905</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -7781,28 +7777,28 @@
         <v>2484</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N24">
         <v>3135</v>
@@ -7811,25 +7807,25 @@
         <v>12905</v>
       </c>
       <c r="P24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -7849,28 +7845,28 @@
         <v>2484</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N25">
         <v>3135</v>
@@ -7879,25 +7875,25 @@
         <v>12905</v>
       </c>
       <c r="P25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
@@ -7917,28 +7913,28 @@
         <v>2484</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N26">
         <v>3135</v>
@@ -7947,25 +7943,25 @@
         <v>12905</v>
       </c>
       <c r="P26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
@@ -7985,28 +7981,28 @@
         <v>2484</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N27">
         <v>3135</v>
@@ -8015,25 +8011,25 @@
         <v>12905</v>
       </c>
       <c r="P27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
@@ -8053,28 +8049,28 @@
         <v>2484</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="M28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="N28">
         <v>3135</v>
@@ -8083,25 +8079,25 @@
         <v>12905</v>
       </c>
       <c r="P28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="R28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="S28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="T28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="U28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
   </sheetData>
@@ -12267,13 +12263,13 @@
       <c r="D6" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6">
         <v>73600</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6">
         <v>20976.000000000007</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6">
         <v>3680.0000000000009</v>
       </c>
     </row>
@@ -12290,13 +12286,13 @@
       <c r="D7" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7">
         <v>82800</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7">
         <v>7866</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7">
         <v>4140</v>
       </c>
     </row>
@@ -12313,13 +12309,13 @@
       <c r="D8" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8">
         <v>276000</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8">
         <v>26220</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8">
         <v>13800</v>
       </c>
     </row>
@@ -12336,13 +12332,13 @@
       <c r="D9" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="16">
-        <v>1</v>
-      </c>
-      <c r="F9" s="16">
-        <v>1</v>
-      </c>
-      <c r="G9" s="16">
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
@@ -12359,13 +12355,13 @@
       <c r="D10" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10">
         <v>165600</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10">
         <v>47196</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10">
         <v>8280</v>
       </c>
     </row>
@@ -12382,13 +12378,13 @@
       <c r="D11" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11">
         <v>202400</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11">
         <v>19228</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11">
         <v>10120</v>
       </c>
     </row>
@@ -12405,13 +12401,13 @@
       <c r="D12" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12">
         <v>202400</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12">
         <v>19228</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12">
         <v>10120</v>
       </c>
     </row>
@@ -12428,13 +12424,13 @@
       <c r="D13" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="16">
-        <v>1</v>
-      </c>
-      <c r="F13" s="16">
-        <v>1</v>
-      </c>
-      <c r="G13" s="16">
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>
@@ -12451,13 +12447,13 @@
       <c r="D14" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14">
         <v>92000</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14">
         <v>13524</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14">
         <v>4600</v>
       </c>
     </row>
@@ -12474,13 +12470,13 @@
       <c r="D15" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="16">
-        <v>1</v>
-      </c>
-      <c r="F15" s="16">
-        <v>1</v>
-      </c>
-      <c r="G15" s="16">
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>
@@ -25583,26 +25579,6 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -25610,6 +25586,26 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="693" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AD85F33-426E-44BB-A093-4FD93EDE6565}"/>
+  <xr:revisionPtr revIDLastSave="760" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96A33976-E88E-486A-A956-3C537D48B947}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-1710" windowWidth="38640" windowHeight="21120" firstSheet="7" activeTab="12" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="12" activeTab="18" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="152">
   <si>
     <t>Value</t>
   </si>
@@ -344,13 +344,7 @@
     <t>Lithium</t>
   </si>
   <si>
-    <t>0.8</t>
-  </si>
-  <si>
     <t>Cobalt</t>
-  </si>
-  <si>
-    <t>0.2</t>
   </si>
   <si>
     <t>Year</t>
@@ -434,9 +428,6 @@
     <t>Batteries_Assembly</t>
   </si>
   <si>
-    <t>Batteries_Cell</t>
-  </si>
-  <si>
     <t>finished, happens on-site so no limitation, will be limited by installable capacity</t>
   </si>
   <si>
@@ -516,6 +507,12 @@
   </si>
   <si>
     <t>0.94</t>
+  </si>
+  <si>
+    <t>CellBatt</t>
+  </si>
+  <si>
+    <t>Batteries_CellBatt</t>
   </si>
 </sst>
 </file>
@@ -707,7 +704,7 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -741,8 +738,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -1138,7 +1140,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s">
         <v>82</v>
@@ -1153,7 +1155,7 @@
         <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G1" t="s">
         <v>74</v>
@@ -1170,7 +1172,7 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1193,7 +1195,7 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1343,7 +1345,7 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1358,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1420,6 +1422,9 @@
       <c r="C12" t="s">
         <v>92</v>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
       <c r="E12" s="12">
         <v>35</v>
       </c>
@@ -1438,7 +1443,7 @@
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1461,16 +1466,16 @@
         <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" s="12">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1484,7 +1489,7 @@
         <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1493,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="12">
-        <v>999999</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1527,13 +1532,13 @@
         <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1544,7 +1549,7 @@
         <v>87</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D2" s="12">
         <v>11.080597014925374</v>
@@ -1553,7 +1558,7 @@
         <v>11.080597014925374</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1573,7 +1578,7 @@
         <v>46.4</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1584,7 +1589,7 @@
         <v>87</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D4" s="12">
         <v>7.6179104477611936</v>
@@ -1604,7 +1609,7 @@
         <v>87</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D5" s="12">
         <v>0.62328358208955215</v>
@@ -1613,7 +1618,7 @@
         <v>0.62328358208955215</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,7 +1629,7 @@
         <v>86</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D6" s="12">
         <v>2.0776119402985072E-2</v>
@@ -1633,7 +1638,7 @@
         <v>2.0776119402985072E-2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1641,10 +1646,10 @@
         <v>75</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D7" s="12">
         <v>3.047164179104477</v>
@@ -1653,7 +1658,7 @@
         <v>3.047164179104477</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,7 +1669,7 @@
         <v>86</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D8" s="12">
         <v>0.20776119402985074</v>
@@ -1673,7 +1678,7 @@
         <v>0.20776119402985074</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1684,7 +1689,7 @@
         <v>89</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D9">
         <v>0.94859999999999989</v>
@@ -1704,7 +1709,7 @@
         <v>89</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D10">
         <v>6.9563999999999995</v>
@@ -1724,7 +1729,7 @@
         <v>89</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D11">
         <v>1.17E-3</v>
@@ -1744,7 +1749,7 @@
         <v>89</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D12">
         <v>8.1</v>
@@ -1773,7 +1778,7 @@
         <v>114.72499999999999</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,7 +1789,7 @@
         <v>90</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D14">
         <v>5.5</v>
@@ -1793,7 +1798,7 @@
         <v>5.5</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1804,7 +1809,7 @@
         <v>92</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D15">
         <v>5.47E-3</v>
@@ -1824,7 +1829,7 @@
         <v>92</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D16">
         <v>4.7689999999999996E-2</v>
@@ -1844,7 +1849,7 @@
         <v>92</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D17">
         <v>7.2699999999999996E-3</v>
@@ -1864,7 +1869,7 @@
         <v>92</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D18">
         <v>2.7909999999999999</v>
@@ -1873,7 +1878,7 @@
         <v>2.7909999999999999</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1884,7 +1889,7 @@
         <v>92</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D19">
         <v>2.2925</v>
@@ -1893,7 +1898,7 @@
         <v>2.2925</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,7 +1909,7 @@
         <v>92</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D20">
         <v>18.945</v>
@@ -1924,7 +1929,7 @@
         <v>92</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D21">
         <v>0.78549999999999998</v>
@@ -1944,7 +1949,7 @@
         <v>92</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D22">
         <v>0.1045</v>
@@ -1964,7 +1969,7 @@
         <v>92</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D23">
         <v>0.39200000000000002</v>
@@ -1984,7 +1989,7 @@
         <v>92</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D24">
         <v>0.50024999999999997</v>
@@ -2004,7 +2009,7 @@
         <v>89</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D25">
         <v>0.97139999999999993</v>
@@ -2024,7 +2029,7 @@
         <v>89</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D26">
         <v>7.1236000000000006</v>
@@ -2044,7 +2049,7 @@
         <v>89</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D27">
         <v>3.4500000000000004E-3</v>
@@ -2064,7 +2069,7 @@
         <v>89</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D28">
         <v>11.6</v>
@@ -2093,7 +2098,7 @@
         <v>116.77</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2104,7 +2109,7 @@
         <v>90</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D30">
         <v>5.5</v>
@@ -2113,7 +2118,7 @@
         <v>5.5</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,7 +2129,7 @@
         <v>92</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D31">
         <v>1.1259999999999999E-2</v>
@@ -2144,7 +2149,7 @@
         <v>92</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D32">
         <v>0.11219</v>
@@ -2164,7 +2169,7 @@
         <v>92</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D33">
         <v>2.0460000000000002E-2</v>
@@ -2184,7 +2189,7 @@
         <v>92</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D34">
         <v>4.04</v>
@@ -2193,7 +2198,7 @@
         <v>4.04</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2204,7 +2209,7 @@
         <v>92</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D35">
         <v>3.2574999999999998</v>
@@ -2213,7 +2218,7 @@
         <v>3.2574999999999998</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2224,7 +2229,7 @@
         <v>92</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D36">
         <v>19.89</v>
@@ -2244,7 +2249,7 @@
         <v>92</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D37">
         <v>0.79039999999999999</v>
@@ -2264,7 +2269,7 @@
         <v>92</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D38">
         <v>0.10940000000000001</v>
@@ -2284,7 +2289,7 @@
         <v>92</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D39">
         <v>0.32230000000000003</v>
@@ -2304,7 +2309,7 @@
         <v>92</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D40">
         <v>0.5272</v>
@@ -2321,19 +2326,19 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="C41" t="s">
         <v>94</v>
       </c>
-      <c r="D41" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" t="s">
-        <v>95</v>
-      </c>
-      <c r="F41" t="s">
-        <v>85</v>
+      <c r="D41">
+        <v>50</v>
+      </c>
+      <c r="E41">
+        <v>50</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2341,19 +2346,19 @@
         <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" t="s">
-        <v>97</v>
-      </c>
-      <c r="E42" t="s">
-        <v>97</v>
-      </c>
-      <c r="F42" t="s">
-        <v>85</v>
+        <v>95</v>
+      </c>
+      <c r="D42">
+        <v>50</v>
+      </c>
+      <c r="E42">
+        <v>50</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2376,81 +2381,81 @@
         <v>88</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="F1" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
       <c r="J1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="N1" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="P1" s="14" t="s">
+      <c r="S1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
+      <c r="B2" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C2" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D2" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E2" s="15">
+        <v>167000</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2476,11 +2481,11 @@
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
+      <c r="N2" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O2" s="15">
+        <v>960000</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2508,17 +2513,17 @@
       <c r="A3" s="14">
         <v>2025</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
+      <c r="B3" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C3" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D3" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E3" s="15">
+        <v>167000</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2544,11 +2549,11 @@
       <c r="M3">
         <v>0</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
+      <c r="N3" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O3" s="15">
+        <v>960000</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2576,17 +2581,17 @@
       <c r="A4" s="14">
         <v>2026</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+      <c r="B4" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C4" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D4" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E4" s="15">
+        <v>167000</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -2612,11 +2617,11 @@
       <c r="M4">
         <v>0</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
+      <c r="N4" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O4" s="15">
+        <v>960000</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2644,17 +2649,17 @@
       <c r="A5" s="14">
         <v>2027</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
+      <c r="B5" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C5" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E5" s="15">
+        <v>167000</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -2680,11 +2685,11 @@
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
+      <c r="N5" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O5" s="15">
+        <v>960000</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -2712,17 +2717,17 @@
       <c r="A6" s="14">
         <v>2028</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+      <c r="B6" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C6" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D6" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E6" s="15">
+        <v>167000</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2748,11 +2753,11 @@
       <c r="M6">
         <v>0</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
+      <c r="N6" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O6" s="15">
+        <v>960000</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2780,17 +2785,17 @@
       <c r="A7" s="14">
         <v>2029</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
+      <c r="B7" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C7" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D7" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E7" s="15">
+        <v>167000</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2816,11 +2821,11 @@
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
+      <c r="N7" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O7" s="15">
+        <v>960000</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2848,17 +2853,17 @@
       <c r="A8" s="14">
         <v>2030</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+      <c r="B8" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C8" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D8" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E8" s="15">
+        <v>167000</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2884,11 +2889,11 @@
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
+      <c r="N8" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O8" s="15">
+        <v>960000</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2916,17 +2921,17 @@
       <c r="A9" s="14">
         <v>2031</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
+      <c r="B9" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C9" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D9" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E9" s="15">
+        <v>167000</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2952,11 +2957,11 @@
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
+      <c r="N9" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O9" s="15">
+        <v>960000</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -2984,17 +2989,17 @@
       <c r="A10" s="14">
         <v>2032</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
+      <c r="B10" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C10" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D10" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E10" s="15">
+        <v>167000</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -3020,11 +3025,11 @@
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
+      <c r="N10" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O10" s="15">
+        <v>960000</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3052,17 +3057,17 @@
       <c r="A11" s="14">
         <v>2033</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
+      <c r="B11" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C11" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E11" s="15">
+        <v>167000</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -3088,11 +3093,11 @@
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
+      <c r="N11" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O11" s="15">
+        <v>960000</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3120,17 +3125,17 @@
       <c r="A12" s="14">
         <v>2034</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
+      <c r="B12" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C12" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E12" s="15">
+        <v>167000</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -3156,11 +3161,11 @@
       <c r="M12">
         <v>0</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
+      <c r="N12" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O12" s="15">
+        <v>960000</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3188,17 +3193,17 @@
       <c r="A13" s="14">
         <v>2035</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
+      <c r="B13" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C13" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D13" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E13" s="15">
+        <v>167000</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -3224,11 +3229,11 @@
       <c r="M13">
         <v>0</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
+      <c r="N13" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O13" s="15">
+        <v>960000</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3256,17 +3261,17 @@
       <c r="A14" s="14">
         <v>2036</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
+      <c r="B14" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C14" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D14" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E14" s="15">
+        <v>167000</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -3292,11 +3297,11 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
+      <c r="N14" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O14" s="15">
+        <v>960000</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3324,17 +3329,17 @@
       <c r="A15" s="14">
         <v>2037</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
+      <c r="B15" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C15" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E15" s="15">
+        <v>167000</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -3360,11 +3365,11 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
+      <c r="N15" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O15" s="15">
+        <v>960000</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3392,17 +3397,17 @@
       <c r="A16" s="14">
         <v>2038</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
+      <c r="B16" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C16" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E16" s="15">
+        <v>167000</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -3428,11 +3433,11 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
+      <c r="N16" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O16" s="15">
+        <v>960000</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3460,17 +3465,17 @@
       <c r="A17" s="14">
         <v>2039</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
+      <c r="B17" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C17" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E17" s="15">
+        <v>167000</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -3496,11 +3501,11 @@
       <c r="M17">
         <v>0</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
+      <c r="N17" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O17" s="15">
+        <v>960000</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3528,17 +3533,17 @@
       <c r="A18" s="14">
         <v>2040</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
+      <c r="B18" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C18" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E18" s="15">
+        <v>167000</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -3564,11 +3569,11 @@
       <c r="M18">
         <v>0</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
+      <c r="N18" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O18" s="15">
+        <v>960000</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -3596,17 +3601,17 @@
       <c r="A19" s="14">
         <v>2041</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
+      <c r="B19" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C19" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E19" s="15">
+        <v>167000</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -3632,11 +3637,11 @@
       <c r="M19">
         <v>0</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
+      <c r="N19" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O19" s="15">
+        <v>960000</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -3664,17 +3669,17 @@
       <c r="A20" s="14">
         <v>2042</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
+      <c r="B20" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C20" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E20" s="15">
+        <v>167000</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -3700,11 +3705,11 @@
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
+      <c r="N20" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O20" s="15">
+        <v>960000</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -3732,17 +3737,17 @@
       <c r="A21" s="14">
         <v>2043</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
+      <c r="B21" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C21" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D21" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E21" s="15">
+        <v>167000</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -3768,11 +3773,11 @@
       <c r="M21">
         <v>0</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
+      <c r="N21" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O21" s="15">
+        <v>960000</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -3800,17 +3805,17 @@
       <c r="A22" s="14">
         <v>2044</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
+      <c r="B22" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C22" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E22" s="15">
+        <v>167000</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -3836,11 +3841,11 @@
       <c r="M22">
         <v>0</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
+      <c r="N22" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O22" s="15">
+        <v>960000</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -3868,17 +3873,17 @@
       <c r="A23" s="14">
         <v>2045</v>
       </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
+      <c r="B23" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C23" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E23" s="15">
+        <v>167000</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -3904,11 +3909,11 @@
       <c r="M23">
         <v>0</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
+      <c r="N23" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O23" s="15">
+        <v>960000</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -3936,17 +3941,17 @@
       <c r="A24" s="14">
         <v>2046</v>
       </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
+      <c r="B24" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C24" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D24" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E24" s="15">
+        <v>167000</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -3972,11 +3977,11 @@
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
+      <c r="N24" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O24" s="15">
+        <v>960000</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -4004,17 +4009,17 @@
       <c r="A25" s="14">
         <v>2047</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
+      <c r="B25" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C25" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D25" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E25" s="15">
+        <v>167000</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -4040,11 +4045,11 @@
       <c r="M25">
         <v>0</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
+      <c r="N25" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O25" s="15">
+        <v>960000</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -4072,17 +4077,17 @@
       <c r="A26" s="14">
         <v>2048</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
+      <c r="B26" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C26" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D26" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E26" s="15">
+        <v>167000</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -4108,11 +4113,11 @@
       <c r="M26">
         <v>0</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
+      <c r="N26" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O26" s="15">
+        <v>960000</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -4140,17 +4145,17 @@
       <c r="A27" s="14">
         <v>2049</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
+      <c r="B27" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C27" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E27" s="15">
+        <v>167000</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -4176,11 +4181,11 @@
       <c r="M27">
         <v>0</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
+      <c r="N27" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O27" s="15">
+        <v>960000</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -4208,17 +4213,17 @@
       <c r="A28" s="14">
         <v>2050</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
+      <c r="B28" s="15">
+        <v>57100000</v>
+      </c>
+      <c r="C28" s="15">
+        <v>58100000</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1961</v>
+      </c>
+      <c r="E28" s="15">
+        <v>167000</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -4244,11 +4249,11 @@
       <c r="M28">
         <v>0</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
+      <c r="N28" s="15">
+        <v>1760000</v>
+      </c>
+      <c r="O28" s="15">
+        <v>960000</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -4290,64 +4295,64 @@
         <v>88</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="F1" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
       <c r="J1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="N1" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="P1" s="14" t="s">
+      <c r="S1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -4355,10 +4360,10 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D2">
         <v>2500000</v>
@@ -4412,10 +4417,10 @@
         <v>1</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -4423,10 +4428,10 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D3">
         <v>2500000</v>
@@ -4480,10 +4485,10 @@
         <v>1</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -4491,10 +4496,10 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D4">
         <v>2500000</v>
@@ -4548,10 +4553,10 @@
         <v>1</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -4559,10 +4564,10 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D5">
         <v>2500000</v>
@@ -4616,10 +4621,10 @@
         <v>1</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -4627,10 +4632,10 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D6">
         <v>2500000</v>
@@ -4684,10 +4689,10 @@
         <v>1</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -4695,10 +4700,10 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D7">
         <v>2500000</v>
@@ -4752,10 +4757,10 @@
         <v>1</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -4763,10 +4768,10 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D8">
         <v>2500000</v>
@@ -4820,10 +4825,10 @@
         <v>1</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -4831,10 +4836,10 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D9">
         <v>2500000</v>
@@ -4888,10 +4893,10 @@
         <v>1</v>
       </c>
       <c r="U9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V9">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -4899,10 +4904,10 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D10">
         <v>2500000</v>
@@ -4956,10 +4961,10 @@
         <v>1</v>
       </c>
       <c r="U10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -4967,10 +4972,10 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D11">
         <v>2500000</v>
@@ -5024,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -5035,10 +5040,10 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D12">
         <v>2500000</v>
@@ -5092,10 +5097,10 @@
         <v>1</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -5103,10 +5108,10 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D13">
         <v>2500000</v>
@@ -5160,10 +5165,10 @@
         <v>1</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -5171,10 +5176,10 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D14">
         <v>2500000</v>
@@ -5228,10 +5233,10 @@
         <v>1</v>
       </c>
       <c r="U14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V14">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -5239,10 +5244,10 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D15">
         <v>2500000</v>
@@ -5296,10 +5301,10 @@
         <v>1</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V15">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -5307,10 +5312,10 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D16">
         <v>2500000</v>
@@ -5364,10 +5369,10 @@
         <v>1</v>
       </c>
       <c r="U16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V16">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -5375,10 +5380,10 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D17">
         <v>2500000</v>
@@ -5432,10 +5437,10 @@
         <v>1</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V17">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -5443,10 +5448,10 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D18">
         <v>2500000</v>
@@ -5500,10 +5505,10 @@
         <v>1</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -5511,10 +5516,10 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D19">
         <v>2500000</v>
@@ -5568,10 +5573,10 @@
         <v>1</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -5579,10 +5584,10 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D20">
         <v>2500000</v>
@@ -5636,10 +5641,10 @@
         <v>1</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V20">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -5647,10 +5652,10 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D21">
         <v>2500000</v>
@@ -5704,10 +5709,10 @@
         <v>1</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
@@ -5715,10 +5720,10 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D22">
         <v>2500000</v>
@@ -5772,10 +5777,10 @@
         <v>1</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V22">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -5783,10 +5788,10 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D23">
         <v>2500000</v>
@@ -5840,10 +5845,10 @@
         <v>1</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V23">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -5851,10 +5856,10 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D24">
         <v>2500000</v>
@@ -5908,10 +5913,10 @@
         <v>1</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V24">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -5919,10 +5924,10 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D25">
         <v>2500000</v>
@@ -5976,10 +5981,10 @@
         <v>1</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V25">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
@@ -5987,10 +5992,10 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D26">
         <v>2500000</v>
@@ -6044,10 +6049,10 @@
         <v>1</v>
       </c>
       <c r="U26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V26">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
@@ -6055,10 +6060,10 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D27">
         <v>2500000</v>
@@ -6112,10 +6117,10 @@
         <v>1</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V27">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
@@ -6123,10 +6128,10 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D28">
         <v>2500000</v>
@@ -6180,10 +6185,10 @@
         <v>1</v>
       </c>
       <c r="U28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="V28">
-        <v>1</v>
+        <v>9999999</v>
       </c>
     </row>
   </sheetData>
@@ -6204,64 +6209,64 @@
         <v>88</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="F1" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
       <c r="J1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="N1" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="P1" s="14" t="s">
+      <c r="S1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -6269,10 +6274,10 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D2">
         <v>2500000</v>
@@ -6337,10 +6342,10 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D3">
         <v>2500000</v>
@@ -6405,10 +6410,10 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D4">
         <v>2500000</v>
@@ -6473,10 +6478,10 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D5">
         <v>2500000</v>
@@ -6541,10 +6546,10 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D6">
         <v>2500000</v>
@@ -6609,10 +6614,10 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D7">
         <v>2500000</v>
@@ -6677,10 +6682,10 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D8">
         <v>2500000</v>
@@ -6745,10 +6750,10 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D9">
         <v>2500000</v>
@@ -6813,10 +6818,10 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D10">
         <v>2500000</v>
@@ -6881,10 +6886,10 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D11">
         <v>2500000</v>
@@ -6949,10 +6954,10 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D12">
         <v>2500000</v>
@@ -7017,10 +7022,10 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D13">
         <v>2500000</v>
@@ -7085,10 +7090,10 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D14">
         <v>2500000</v>
@@ -7153,10 +7158,10 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D15">
         <v>2500000</v>
@@ -7221,10 +7226,10 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D16">
         <v>2500000</v>
@@ -7289,10 +7294,10 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D17">
         <v>2500000</v>
@@ -7357,10 +7362,10 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D18">
         <v>2500000</v>
@@ -7425,10 +7430,10 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D19">
         <v>2500000</v>
@@ -7493,10 +7498,10 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D20">
         <v>2500000</v>
@@ -7561,10 +7566,10 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D21">
         <v>2500000</v>
@@ -7629,10 +7634,10 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D22">
         <v>2500000</v>
@@ -7697,10 +7702,10 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D23">
         <v>2500000</v>
@@ -7765,10 +7770,10 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D24">
         <v>2500000</v>
@@ -7833,10 +7838,10 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D25">
         <v>2500000</v>
@@ -7901,10 +7906,10 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D26">
         <v>2500000</v>
@@ -7969,10 +7974,10 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D27">
         <v>2500000</v>
@@ -8037,10 +8042,10 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>1760</v>
       </c>
       <c r="D28">
         <v>2500000</v>
@@ -8118,64 +8123,64 @@
         <v>88</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="F1" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
       <c r="J1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="N1" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="P1" s="14" t="s">
+      <c r="S1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -10032,64 +10037,64 @@
         <v>88</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="F1" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>91</v>
       </c>
       <c r="J1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="N1" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="P1" s="14" t="s">
+      <c r="S1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="U1" s="14" t="s">
         <v>94</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -11940,19 +11945,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>104</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>105</v>
-      </c>
-      <c r="D1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -11960,16 +11965,16 @@
         <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -11983,10 +11988,10 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -12003,7 +12008,7 @@
         <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -12011,16 +12016,16 @@
         <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -12028,7 +12033,7 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
         <v>76</v>
@@ -12037,7 +12042,7 @@
         <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -12045,7 +12050,7 @@
         <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>76</v>
@@ -12054,7 +12059,7 @@
         <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -12062,7 +12067,7 @@
         <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
         <v>76</v>
@@ -12071,7 +12076,7 @@
         <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -12079,7 +12084,7 @@
         <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
         <v>77</v>
@@ -12088,7 +12093,7 @@
         <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -12096,7 +12101,7 @@
         <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
         <v>77</v>
@@ -12105,7 +12110,7 @@
         <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -12113,7 +12118,7 @@
         <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
         <v>77</v>
@@ -12122,7 +12127,7 @@
         <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -12137,10 +12142,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C1" t="s">
         <v>82</v>
@@ -12149,13 +12154,13 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -12169,7 +12174,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E2" s="12">
         <v>64400.000000000007</v>
@@ -12192,7 +12197,7 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" s="12">
         <v>92000</v>
@@ -12330,7 +12335,7 @@
         <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -12422,7 +12427,7 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -12445,16 +12450,16 @@
         <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="E14">
-        <v>92000</v>
+        <v>999999</v>
       </c>
       <c r="F14">
-        <v>13524</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>4600</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -12468,7 +12473,7 @@
         <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -12488,7 +12493,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B74DFEF-01D9-4B2D-A936-BF616F091054}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -12496,46 +12501,46 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" t="s">
         <v>114</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>115</v>
       </c>
-      <c r="E1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>116</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>117</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1" t="s">
+        <v>125</v>
+      </c>
+      <c r="L1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M1" t="s">
         <v>118</v>
       </c>
-      <c r="I1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K1" t="s">
-        <v>128</v>
-      </c>
-      <c r="L1" t="s">
-        <v>129</v>
-      </c>
-      <c r="M1" t="s">
-        <v>120</v>
-      </c>
       <c r="N1" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="O1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -12552,7 +12557,7 @@
         <v>82800</v>
       </c>
       <c r="E2">
-        <v>170200</v>
+        <v>149960</v>
       </c>
       <c r="F2">
         <v>9999999</v>
@@ -12599,7 +12604,7 @@
         <v>81558</v>
       </c>
       <c r="E3">
-        <v>167647</v>
+        <v>148580</v>
       </c>
       <c r="F3">
         <v>9999999</v>
@@ -12646,7 +12651,7 @@
         <v>80334.63</v>
       </c>
       <c r="E4">
-        <v>165132.29499999998</v>
+        <v>147200</v>
       </c>
       <c r="F4">
         <v>9999999</v>
@@ -12693,7 +12698,7 @@
         <v>79129.610549999998</v>
       </c>
       <c r="E5">
-        <v>162655.31057499998</v>
+        <v>145820</v>
       </c>
       <c r="F5">
         <v>9999999</v>
@@ -12740,7 +12745,7 @@
         <v>77942.666391749997</v>
       </c>
       <c r="E6">
-        <v>160215.48091637497</v>
+        <v>144440</v>
       </c>
       <c r="F6">
         <v>9999999</v>
@@ -12787,7 +12792,7 @@
         <v>76773.526395873749</v>
       </c>
       <c r="E7">
-        <v>157812.24870262935</v>
+        <v>143060</v>
       </c>
       <c r="F7">
         <v>9999999</v>
@@ -12834,7 +12839,7 @@
         <v>75621.923499935641</v>
       </c>
       <c r="E8">
-        <v>155445.06497208992</v>
+        <v>141680</v>
       </c>
       <c r="F8">
         <v>9999999</v>
@@ -12881,7 +12886,7 @@
         <v>74487.594647436606</v>
       </c>
       <c r="E9">
-        <v>153113.38899750856</v>
+        <v>140300</v>
       </c>
       <c r="F9">
         <v>9999999</v>
@@ -12928,7 +12933,7 @@
         <v>73370.280727725054</v>
       </c>
       <c r="E10">
-        <v>150816.68816254594</v>
+        <v>138920</v>
       </c>
       <c r="F10">
         <v>9999999</v>
@@ -12975,7 +12980,7 @@
         <v>72269.726516809184</v>
       </c>
       <c r="E11">
-        <v>148554.43784010774</v>
+        <v>137540</v>
       </c>
       <c r="F11">
         <v>9999999</v>
@@ -13022,7 +13027,7 @@
         <v>71185.68061905705</v>
       </c>
       <c r="E12">
-        <v>146326.12127250613</v>
+        <v>136160</v>
       </c>
       <c r="F12">
         <v>9999999</v>
@@ -13069,7 +13074,7 @@
         <v>70117.895409771198</v>
       </c>
       <c r="E13">
-        <v>144131.22945341855</v>
+        <v>134780</v>
       </c>
       <c r="F13">
         <v>9999999</v>
@@ -13116,7 +13121,7 @@
         <v>69066.126978624627</v>
       </c>
       <c r="E14">
-        <v>141969.26101161726</v>
+        <v>133400</v>
       </c>
       <c r="F14">
         <v>9999999</v>
@@ -13163,7 +13168,7 @@
         <v>68030.135073945261</v>
       </c>
       <c r="E15">
-        <v>139839.722096443</v>
+        <v>132020</v>
       </c>
       <c r="F15">
         <v>9999999</v>
@@ -13210,7 +13215,7 @@
         <v>67009.683047836079</v>
       </c>
       <c r="E16">
-        <v>137742.12626499636</v>
+        <v>130640</v>
       </c>
       <c r="F16">
         <v>9999999</v>
@@ -13257,7 +13262,7 @@
         <v>66004.537802118532</v>
       </c>
       <c r="E17">
-        <v>135675.9943710214</v>
+        <v>129260</v>
       </c>
       <c r="F17">
         <v>9999999</v>
@@ -13304,7 +13309,7 @@
         <v>65014.46973508675</v>
       </c>
       <c r="E18">
-        <v>133640.85445545608</v>
+        <v>127880</v>
       </c>
       <c r="F18">
         <v>9999999</v>
@@ -13351,7 +13356,7 @@
         <v>64039.252689060449</v>
       </c>
       <c r="E19">
-        <v>131636.24163862423</v>
+        <v>126500</v>
       </c>
       <c r="F19">
         <v>9999999</v>
@@ -13398,7 +13403,7 @@
         <v>63078.663898724539</v>
       </c>
       <c r="E20">
-        <v>129661.69801404486</v>
+        <v>125120</v>
       </c>
       <c r="F20">
         <v>9999999</v>
@@ -13445,7 +13450,7 @@
         <v>62132.48394024367</v>
       </c>
       <c r="E21">
-        <v>127716.77254383419</v>
+        <v>123740</v>
       </c>
       <c r="F21">
         <v>9999999</v>
@@ -13492,7 +13497,7 @@
         <v>61200.496681140015</v>
       </c>
       <c r="E22">
-        <v>125801.02095567668</v>
+        <v>122360</v>
       </c>
       <c r="F22">
         <v>9999999</v>
@@ -13539,7 +13544,7 @@
         <v>60282.489230922911</v>
       </c>
       <c r="E23">
-        <v>123914.00564134153</v>
+        <v>120980</v>
       </c>
       <c r="F23">
         <v>9999999</v>
@@ -13586,7 +13591,7 @@
         <v>59378.251892459069</v>
       </c>
       <c r="E24">
-        <v>122055.29555672141</v>
+        <v>119600</v>
       </c>
       <c r="F24">
         <v>9999999</v>
@@ -13633,7 +13638,7 @@
         <v>58487.578114072181</v>
       </c>
       <c r="E25">
-        <v>120224.46612337058</v>
+        <v>118220</v>
       </c>
       <c r="F25">
         <v>9999999</v>
@@ -13680,7 +13685,7 @@
         <v>57610.264442361098</v>
       </c>
       <c r="E26">
-        <v>118421.09913152002</v>
+        <v>116840</v>
       </c>
       <c r="F26">
         <v>9999999</v>
@@ -13727,7 +13732,7 @@
         <v>56746.110475725684</v>
       </c>
       <c r="E27">
-        <v>116644.78264454722</v>
+        <v>115460</v>
       </c>
       <c r="F27">
         <v>9999999</v>
@@ -13774,7 +13779,7 @@
         <v>55894.918818589795</v>
       </c>
       <c r="E28">
-        <v>114895.11090487901</v>
+        <v>114080</v>
       </c>
       <c r="F28">
         <v>9999999</v>
@@ -13806,6 +13811,12 @@
       <c r="O28">
         <v>164356.51999999999</v>
       </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="18"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G34" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -24200,7 +24211,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="16">
         <v>2024</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -24214,7 +24225,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="11" t="s">
         <v>70</v>
       </c>
@@ -24227,7 +24238,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -24239,7 +24250,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
@@ -24251,7 +24262,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <v>2025</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -24265,7 +24276,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
@@ -24277,7 +24288,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
@@ -24289,7 +24300,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="11" t="s">
         <v>68</v>
       </c>
@@ -24302,7 +24313,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="16">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -24316,7 +24327,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
@@ -24328,7 +24339,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -24340,7 +24351,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -24353,7 +24364,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="16">
         <v>2027</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -24367,7 +24378,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
@@ -24379,7 +24390,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
@@ -24391,7 +24402,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="16"/>
       <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
@@ -24404,7 +24415,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="16">
         <v>2028</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -24418,7 +24429,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
@@ -24430,7 +24441,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="15"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
@@ -24442,7 +24453,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="11" t="s">
         <v>68</v>
       </c>
@@ -24455,7 +24466,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="16">
         <v>2029</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -24469,7 +24480,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="11" t="s">
         <v>70</v>
       </c>
@@ -24481,7 +24492,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="11" t="s">
         <v>71</v>
       </c>
@@ -24493,7 +24504,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="16"/>
       <c r="B25" s="11" t="s">
         <v>68</v>
       </c>
@@ -24506,7 +24517,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="16">
         <v>2030</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -24520,7 +24531,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="16"/>
       <c r="B27" s="11" t="s">
         <v>70</v>
       </c>
@@ -24532,7 +24543,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="11" t="s">
         <v>71</v>
       </c>
@@ -24544,7 +24555,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="11" t="s">
         <v>68</v>
       </c>
@@ -24557,7 +24568,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="15">
+      <c r="A30" s="16">
         <v>2031</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -24571,7 +24582,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
@@ -24583,7 +24594,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
+      <c r="A32" s="16"/>
       <c r="B32" s="11" t="s">
         <v>71</v>
       </c>
@@ -24595,7 +24606,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="16"/>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
@@ -24608,7 +24619,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="15">
+      <c r="A34" s="16">
         <v>2032</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -24622,7 +24633,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="16"/>
       <c r="B35" s="11" t="s">
         <v>70</v>
       </c>
@@ -24634,7 +24645,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
+      <c r="A36" s="16"/>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
@@ -24646,7 +24657,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="16"/>
       <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
@@ -24659,7 +24670,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="15">
+      <c r="A38" s="16">
         <v>2033</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -24673,7 +24684,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="16"/>
       <c r="B39" s="11" t="s">
         <v>70</v>
       </c>
@@ -24685,7 +24696,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
+      <c r="A40" s="16"/>
       <c r="B40" s="11" t="s">
         <v>71</v>
       </c>
@@ -24697,7 +24708,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
+      <c r="A41" s="16"/>
       <c r="B41" s="11" t="s">
         <v>68</v>
       </c>
@@ -24710,7 +24721,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
+      <c r="A42" s="16">
         <v>2034</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -24724,7 +24735,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
+      <c r="A43" s="16"/>
       <c r="B43" s="11" t="s">
         <v>70</v>
       </c>
@@ -24736,7 +24747,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
+      <c r="A44" s="16"/>
       <c r="B44" s="11" t="s">
         <v>71</v>
       </c>
@@ -24748,7 +24759,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="16"/>
       <c r="B45" s="11" t="s">
         <v>68</v>
       </c>
@@ -24761,7 +24772,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="15">
+      <c r="A46" s="16">
         <v>2035</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -24775,7 +24786,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="16"/>
       <c r="B47" s="11" t="s">
         <v>70</v>
       </c>
@@ -24787,7 +24798,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
+      <c r="A48" s="16"/>
       <c r="B48" s="11" t="s">
         <v>71</v>
       </c>
@@ -24799,7 +24810,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="16"/>
       <c r="B49" s="11" t="s">
         <v>68</v>
       </c>
@@ -24812,7 +24823,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
+      <c r="A50" s="16">
         <v>2036</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -24826,7 +24837,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="16"/>
       <c r="B51" s="11" t="s">
         <v>70</v>
       </c>
@@ -24838,7 +24849,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="15"/>
+      <c r="A52" s="16"/>
       <c r="B52" s="11" t="s">
         <v>71</v>
       </c>
@@ -24850,7 +24861,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="16"/>
       <c r="B53" s="11" t="s">
         <v>68</v>
       </c>
@@ -24863,7 +24874,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="15">
+      <c r="A54" s="16">
         <v>2037</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -24877,7 +24888,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="11" t="s">
         <v>70</v>
       </c>
@@ -24889,7 +24900,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="11" t="s">
         <v>71</v>
       </c>
@@ -24901,7 +24912,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="11" t="s">
         <v>68</v>
       </c>
@@ -24914,7 +24925,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="15">
+      <c r="A58" s="16">
         <v>2038</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -24928,7 +24939,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="11" t="s">
         <v>70</v>
       </c>
@@ -24940,7 +24951,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="15"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
@@ -24952,7 +24963,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="11" t="s">
         <v>68</v>
       </c>
@@ -24965,7 +24976,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="15">
+      <c r="A62" s="16">
         <v>2039</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -24979,7 +24990,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="11" t="s">
         <v>70</v>
       </c>
@@ -24991,7 +25002,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="15"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="11" t="s">
         <v>71</v>
       </c>
@@ -25003,7 +25014,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="11" t="s">
         <v>68</v>
       </c>
@@ -25016,7 +25027,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="15">
+      <c r="A66" s="16">
         <v>2040</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -25030,7 +25041,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
@@ -25042,7 +25053,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="15"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="11" t="s">
         <v>71</v>
       </c>
@@ -25054,7 +25065,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="11" t="s">
         <v>68</v>
       </c>
@@ -25067,7 +25078,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="15">
+      <c r="A70" s="16">
         <v>2041</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -25081,7 +25092,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="11" t="s">
         <v>70</v>
       </c>
@@ -25093,7 +25104,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="15"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="11" t="s">
         <v>71</v>
       </c>
@@ -25105,7 +25116,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="11" t="s">
         <v>68</v>
       </c>
@@ -25118,7 +25129,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="15">
+      <c r="A74" s="16">
         <v>2042</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -25132,7 +25143,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="11" t="s">
         <v>70</v>
       </c>
@@ -25144,7 +25155,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="15"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
@@ -25156,7 +25167,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="11" t="s">
         <v>68</v>
       </c>
@@ -25169,7 +25180,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="15">
+      <c r="A78" s="16">
         <v>2043</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -25183,7 +25194,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="11" t="s">
         <v>70</v>
       </c>
@@ -25195,7 +25206,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="15"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="11" t="s">
         <v>71</v>
       </c>
@@ -25207,7 +25218,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="16"/>
       <c r="B81" s="11" t="s">
         <v>68</v>
       </c>
@@ -25220,7 +25231,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="15">
+      <c r="A82" s="16">
         <v>2044</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -25234,7 +25245,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="16"/>
       <c r="B83" s="11" t="s">
         <v>70</v>
       </c>
@@ -25246,7 +25257,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="15"/>
+      <c r="A84" s="16"/>
       <c r="B84" s="11" t="s">
         <v>71</v>
       </c>
@@ -25258,7 +25269,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="16"/>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
@@ -25271,7 +25282,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="15">
+      <c r="A86" s="16">
         <v>2045</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -25285,7 +25296,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="16"/>
       <c r="B87" s="11" t="s">
         <v>70</v>
       </c>
@@ -25297,7 +25308,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="15"/>
+      <c r="A88" s="16"/>
       <c r="B88" s="11" t="s">
         <v>71</v>
       </c>
@@ -25309,7 +25320,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="16"/>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
@@ -25322,7 +25333,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="15">
+      <c r="A90" s="16">
         <v>2046</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -25336,7 +25347,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="16"/>
       <c r="B91" s="11" t="s">
         <v>70</v>
       </c>
@@ -25348,7 +25359,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
+      <c r="A92" s="16"/>
       <c r="B92" s="11" t="s">
         <v>71</v>
       </c>
@@ -25360,7 +25371,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="16"/>
       <c r="B93" s="11" t="s">
         <v>68</v>
       </c>
@@ -25373,7 +25384,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="15">
+      <c r="A94" s="16">
         <v>2047</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -25387,7 +25398,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="16"/>
       <c r="B95" s="11" t="s">
         <v>70</v>
       </c>
@@ -25399,7 +25410,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="15"/>
+      <c r="A96" s="16"/>
       <c r="B96" s="11" t="s">
         <v>71</v>
       </c>
@@ -25411,7 +25422,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="16"/>
       <c r="B97" s="11" t="s">
         <v>68</v>
       </c>
@@ -25424,7 +25435,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="15">
+      <c r="A98" s="16">
         <v>2048</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -25438,7 +25449,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="16"/>
       <c r="B99" s="11" t="s">
         <v>70</v>
       </c>
@@ -25450,7 +25461,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="15"/>
+      <c r="A100" s="16"/>
       <c r="B100" s="11" t="s">
         <v>71</v>
       </c>
@@ -25462,7 +25473,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="16"/>
       <c r="B101" s="11" t="s">
         <v>68</v>
       </c>
@@ -25475,7 +25486,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="15">
+      <c r="A102" s="16">
         <v>2049</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -25489,7 +25500,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
+      <c r="A103" s="16"/>
       <c r="B103" s="11" t="s">
         <v>70</v>
       </c>
@@ -25501,7 +25512,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="15"/>
+      <c r="A104" s="16"/>
       <c r="B104" s="11" t="s">
         <v>71</v>
       </c>
@@ -25513,7 +25524,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
+      <c r="A105" s="16"/>
       <c r="B105" s="11" t="s">
         <v>68</v>
       </c>
@@ -25526,7 +25537,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="15">
+      <c r="A106" s="16">
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -25540,7 +25551,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="16"/>
       <c r="B107" s="11" t="s">
         <v>70</v>
       </c>
@@ -25552,7 +25563,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="15"/>
+      <c r="A108" s="16"/>
       <c r="B108" s="11" t="s">
         <v>71</v>
       </c>
@@ -25564,7 +25575,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="16"/>
       <c r="B109" s="11" t="s">
         <v>68</v>
       </c>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-extension/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="760" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96A33976-E88E-486A-A956-3C537D48B947}"/>
+  <xr:revisionPtr revIDLastSave="762" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F15EF054-2427-4D2D-BE91-3CB9DFE66F3B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="12" activeTab="18" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="7" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -739,12 +739,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -770,10 +770,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1354,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="12">
-        <v>999999</v>
+        <v>100000</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1452,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="12">
-        <v>999999</v>
+        <v>100000</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -13813,10 +13809,10 @@
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="18"/>
+      <c r="B33" s="17"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G34" s="17"/>
+      <c r="G34" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -24211,7 +24207,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>2024</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -24225,7 +24221,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="11" t="s">
         <v>70</v>
       </c>
@@ -24238,7 +24234,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -24250,7 +24246,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
@@ -24262,7 +24258,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="18">
         <v>2025</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -24276,7 +24272,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
@@ -24288,7 +24284,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
@@ -24300,7 +24296,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="11" t="s">
         <v>68</v>
       </c>
@@ -24313,7 +24309,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+      <c r="A10" s="18">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -24327,7 +24323,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
@@ -24339,7 +24335,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -24351,7 +24347,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -24364,7 +24360,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
+      <c r="A14" s="18">
         <v>2027</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -24378,7 +24374,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
@@ -24390,7 +24386,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
@@ -24402,7 +24398,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
@@ -24415,7 +24411,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="A18" s="18">
         <v>2028</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -24429,7 +24425,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
@@ -24441,7 +24437,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
@@ -24453,7 +24449,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="11" t="s">
         <v>68</v>
       </c>
@@ -24466,7 +24462,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="A22" s="18">
         <v>2029</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -24480,7 +24476,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="11" t="s">
         <v>70</v>
       </c>
@@ -24492,7 +24488,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="11" t="s">
         <v>71</v>
       </c>
@@ -24504,7 +24500,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="11" t="s">
         <v>68</v>
       </c>
@@ -24517,7 +24513,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
+      <c r="A26" s="18">
         <v>2030</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -24531,7 +24527,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="11" t="s">
         <v>70</v>
       </c>
@@ -24543,7 +24539,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
+      <c r="A28" s="18"/>
       <c r="B28" s="11" t="s">
         <v>71</v>
       </c>
@@ -24555,7 +24551,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="11" t="s">
         <v>68</v>
       </c>
@@ -24568,7 +24564,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
+      <c r="A30" s="18">
         <v>2031</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -24582,7 +24578,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
@@ -24594,7 +24590,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="11" t="s">
         <v>71</v>
       </c>
@@ -24606,7 +24602,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
@@ -24619,7 +24615,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
+      <c r="A34" s="18">
         <v>2032</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -24633,7 +24629,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
+      <c r="A35" s="18"/>
       <c r="B35" s="11" t="s">
         <v>70</v>
       </c>
@@ -24645,7 +24641,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
@@ -24657,7 +24653,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
@@ -24670,7 +24666,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="16">
+      <c r="A38" s="18">
         <v>2033</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -24684,7 +24680,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
+      <c r="A39" s="18"/>
       <c r="B39" s="11" t="s">
         <v>70</v>
       </c>
@@ -24696,7 +24692,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
+      <c r="A40" s="18"/>
       <c r="B40" s="11" t="s">
         <v>71</v>
       </c>
@@ -24708,7 +24704,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
+      <c r="A41" s="18"/>
       <c r="B41" s="11" t="s">
         <v>68</v>
       </c>
@@ -24721,7 +24717,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="16">
+      <c r="A42" s="18">
         <v>2034</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -24735,7 +24731,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="11" t="s">
         <v>70</v>
       </c>
@@ -24747,7 +24743,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="11" t="s">
         <v>71</v>
       </c>
@@ -24759,7 +24755,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="11" t="s">
         <v>68</v>
       </c>
@@ -24772,7 +24768,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="16">
+      <c r="A46" s="18">
         <v>2035</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -24786,7 +24782,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="16"/>
+      <c r="A47" s="18"/>
       <c r="B47" s="11" t="s">
         <v>70</v>
       </c>
@@ -24798,7 +24794,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
+      <c r="A48" s="18"/>
       <c r="B48" s="11" t="s">
         <v>71</v>
       </c>
@@ -24810,7 +24806,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
+      <c r="A49" s="18"/>
       <c r="B49" s="11" t="s">
         <v>68</v>
       </c>
@@ -24823,7 +24819,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="16">
+      <c r="A50" s="18">
         <v>2036</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -24837,7 +24833,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
+      <c r="A51" s="18"/>
       <c r="B51" s="11" t="s">
         <v>70</v>
       </c>
@@ -24849,7 +24845,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="16"/>
+      <c r="A52" s="18"/>
       <c r="B52" s="11" t="s">
         <v>71</v>
       </c>
@@ -24861,7 +24857,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="16"/>
+      <c r="A53" s="18"/>
       <c r="B53" s="11" t="s">
         <v>68</v>
       </c>
@@ -24874,7 +24870,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="16">
+      <c r="A54" s="18">
         <v>2037</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -24888,7 +24884,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="16"/>
+      <c r="A55" s="18"/>
       <c r="B55" s="11" t="s">
         <v>70</v>
       </c>
@@ -24900,7 +24896,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="16"/>
+      <c r="A56" s="18"/>
       <c r="B56" s="11" t="s">
         <v>71</v>
       </c>
@@ -24912,7 +24908,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="16"/>
+      <c r="A57" s="18"/>
       <c r="B57" s="11" t="s">
         <v>68</v>
       </c>
@@ -24925,7 +24921,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="16">
+      <c r="A58" s="18">
         <v>2038</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -24939,7 +24935,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="16"/>
+      <c r="A59" s="18"/>
       <c r="B59" s="11" t="s">
         <v>70</v>
       </c>
@@ -24951,7 +24947,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="16"/>
+      <c r="A60" s="18"/>
       <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
@@ -24963,7 +24959,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="16"/>
+      <c r="A61" s="18"/>
       <c r="B61" s="11" t="s">
         <v>68</v>
       </c>
@@ -24976,7 +24972,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="16">
+      <c r="A62" s="18">
         <v>2039</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -24990,7 +24986,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="16"/>
+      <c r="A63" s="18"/>
       <c r="B63" s="11" t="s">
         <v>70</v>
       </c>
@@ -25002,7 +24998,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="16"/>
+      <c r="A64" s="18"/>
       <c r="B64" s="11" t="s">
         <v>71</v>
       </c>
@@ -25014,7 +25010,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="16"/>
+      <c r="A65" s="18"/>
       <c r="B65" s="11" t="s">
         <v>68</v>
       </c>
@@ -25027,7 +25023,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="16">
+      <c r="A66" s="18">
         <v>2040</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -25041,7 +25037,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="16"/>
+      <c r="A67" s="18"/>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
@@ -25053,7 +25049,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="16"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="11" t="s">
         <v>71</v>
       </c>
@@ -25065,7 +25061,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="16"/>
+      <c r="A69" s="18"/>
       <c r="B69" s="11" t="s">
         <v>68</v>
       </c>
@@ -25078,7 +25074,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="16">
+      <c r="A70" s="18">
         <v>2041</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -25092,7 +25088,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="16"/>
+      <c r="A71" s="18"/>
       <c r="B71" s="11" t="s">
         <v>70</v>
       </c>
@@ -25104,7 +25100,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="16"/>
+      <c r="A72" s="18"/>
       <c r="B72" s="11" t="s">
         <v>71</v>
       </c>
@@ -25116,7 +25112,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="16"/>
+      <c r="A73" s="18"/>
       <c r="B73" s="11" t="s">
         <v>68</v>
       </c>
@@ -25129,7 +25125,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="16">
+      <c r="A74" s="18">
         <v>2042</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -25143,7 +25139,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="16"/>
+      <c r="A75" s="18"/>
       <c r="B75" s="11" t="s">
         <v>70</v>
       </c>
@@ -25155,7 +25151,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="16"/>
+      <c r="A76" s="18"/>
       <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
@@ -25167,7 +25163,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="16"/>
+      <c r="A77" s="18"/>
       <c r="B77" s="11" t="s">
         <v>68</v>
       </c>
@@ -25180,7 +25176,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="16">
+      <c r="A78" s="18">
         <v>2043</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -25194,7 +25190,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="16"/>
+      <c r="A79" s="18"/>
       <c r="B79" s="11" t="s">
         <v>70</v>
       </c>
@@ -25206,7 +25202,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="16"/>
+      <c r="A80" s="18"/>
       <c r="B80" s="11" t="s">
         <v>71</v>
       </c>
@@ -25218,7 +25214,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="16"/>
+      <c r="A81" s="18"/>
       <c r="B81" s="11" t="s">
         <v>68</v>
       </c>
@@ -25231,7 +25227,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="16">
+      <c r="A82" s="18">
         <v>2044</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -25245,7 +25241,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="16"/>
+      <c r="A83" s="18"/>
       <c r="B83" s="11" t="s">
         <v>70</v>
       </c>
@@ -25257,7 +25253,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="16"/>
+      <c r="A84" s="18"/>
       <c r="B84" s="11" t="s">
         <v>71</v>
       </c>
@@ -25269,7 +25265,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="16"/>
+      <c r="A85" s="18"/>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
@@ -25282,7 +25278,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="16">
+      <c r="A86" s="18">
         <v>2045</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -25296,7 +25292,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="16"/>
+      <c r="A87" s="18"/>
       <c r="B87" s="11" t="s">
         <v>70</v>
       </c>
@@ -25308,7 +25304,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="16"/>
+      <c r="A88" s="18"/>
       <c r="B88" s="11" t="s">
         <v>71</v>
       </c>
@@ -25320,7 +25316,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="16"/>
+      <c r="A89" s="18"/>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
@@ -25333,7 +25329,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="16">
+      <c r="A90" s="18">
         <v>2046</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -25347,7 +25343,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="16"/>
+      <c r="A91" s="18"/>
       <c r="B91" s="11" t="s">
         <v>70</v>
       </c>
@@ -25359,7 +25355,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="16"/>
+      <c r="A92" s="18"/>
       <c r="B92" s="11" t="s">
         <v>71</v>
       </c>
@@ -25371,7 +25367,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="16"/>
+      <c r="A93" s="18"/>
       <c r="B93" s="11" t="s">
         <v>68</v>
       </c>
@@ -25384,7 +25380,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="16">
+      <c r="A94" s="18">
         <v>2047</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -25398,7 +25394,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="16"/>
+      <c r="A95" s="18"/>
       <c r="B95" s="11" t="s">
         <v>70</v>
       </c>
@@ -25410,7 +25406,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="16"/>
+      <c r="A96" s="18"/>
       <c r="B96" s="11" t="s">
         <v>71</v>
       </c>
@@ -25422,7 +25418,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="16"/>
+      <c r="A97" s="18"/>
       <c r="B97" s="11" t="s">
         <v>68</v>
       </c>
@@ -25435,7 +25431,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="16">
+      <c r="A98" s="18">
         <v>2048</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -25449,7 +25445,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="16"/>
+      <c r="A99" s="18"/>
       <c r="B99" s="11" t="s">
         <v>70</v>
       </c>
@@ -25461,7 +25457,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="16"/>
+      <c r="A100" s="18"/>
       <c r="B100" s="11" t="s">
         <v>71</v>
       </c>
@@ -25473,7 +25469,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="16"/>
+      <c r="A101" s="18"/>
       <c r="B101" s="11" t="s">
         <v>68</v>
       </c>
@@ -25486,7 +25482,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="16">
+      <c r="A102" s="18">
         <v>2049</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -25500,7 +25496,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="16"/>
+      <c r="A103" s="18"/>
       <c r="B103" s="11" t="s">
         <v>70</v>
       </c>
@@ -25512,7 +25508,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="16"/>
+      <c r="A104" s="18"/>
       <c r="B104" s="11" t="s">
         <v>71</v>
       </c>
@@ -25524,7 +25520,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="16"/>
+      <c r="A105" s="18"/>
       <c r="B105" s="11" t="s">
         <v>68</v>
       </c>
@@ -25537,7 +25533,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="16">
+      <c r="A106" s="18">
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -25551,7 +25547,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="16"/>
+      <c r="A107" s="18"/>
       <c r="B107" s="11" t="s">
         <v>70</v>
       </c>
@@ -25563,7 +25559,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="16"/>
+      <c r="A108" s="18"/>
       <c r="B108" s="11" t="s">
         <v>71</v>
       </c>
@@ -25575,7 +25571,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="16"/>
+      <c r="A109" s="18"/>
       <c r="B109" s="11" t="s">
         <v>68</v>
       </c>
@@ -25590,6 +25586,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -25597,26 +25613,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="762" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F15EF054-2427-4D2D-BE91-3CB9DFE66F3B}"/>
+  <xr:revisionPtr revIDLastSave="778" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09613109-F906-46D9-B1AE-A17BDBE63962}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="7" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="12" activeTab="17" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="153">
   <si>
     <t>Value</t>
   </si>
@@ -514,6 +514,9 @@
   <si>
     <t>Batteries_CellBatt</t>
   </si>
+  <si>
+    <t>material_downstream_manufacturing</t>
+  </si>
 </sst>
 </file>
 
@@ -580,6 +583,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -12133,10 +12137,10 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE844EE-882F-4833-8B87-00A8BB665263}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>96</v>
       </c>
@@ -12158,8 +12162,11 @@
       <c r="G1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -12181,8 +12188,11 @@
       <c r="G2" s="12">
         <v>3220</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -12204,8 +12214,11 @@
       <c r="G3" s="12">
         <v>4600</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -12227,8 +12240,11 @@
       <c r="G4" s="12">
         <v>8280</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -12250,8 +12266,11 @@
       <c r="G5" s="12">
         <v>2300</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2024</v>
       </c>
@@ -12264,17 +12283,20 @@
       <c r="D6" t="s">
         <v>89</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="12">
         <v>73600</v>
       </c>
-      <c r="F6">
-        <v>20976.000000000007</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="12">
+        <v>40142</v>
+      </c>
+      <c r="G6" s="12">
         <v>3680.0000000000009</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="12">
+        <v>74006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2024</v>
       </c>
@@ -12287,17 +12309,20 @@
       <c r="D7" t="s">
         <v>90</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="12">
         <v>82800</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="12">
         <v>7866</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="12">
         <v>4140</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="12">
+        <v>264948.33858154103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -12310,17 +12335,20 @@
       <c r="D8" t="s">
         <v>92</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="12">
         <v>276000</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="12">
         <v>26220</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="12">
         <v>13800</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="12">
+        <v>493032.21042160509</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2024</v>
       </c>
@@ -12333,17 +12361,18 @@
       <c r="D9" t="s">
         <v>100</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12">
+        <v>1</v>
+      </c>
+      <c r="G9" s="12">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -12356,17 +12385,20 @@
       <c r="D10" t="s">
         <v>89</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="12">
         <v>165600</v>
       </c>
-      <c r="F10">
-        <v>47196</v>
-      </c>
-      <c r="G10">
+      <c r="F10" s="12">
+        <v>120522</v>
+      </c>
+      <c r="G10" s="12">
         <v>8280</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="12">
+        <v>229760</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -12379,17 +12411,20 @@
       <c r="D11" t="s">
         <v>90</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="12">
         <v>202400</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="12">
         <v>19228</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="12">
         <v>10120</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="12">
+        <v>231566.55902280001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -12402,17 +12437,20 @@
       <c r="D12" t="s">
         <v>92</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="12">
         <v>202400</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="12">
         <v>19228</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="12">
         <v>10120</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="12">
+        <v>901215.14350847807</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2024</v>
       </c>
@@ -12435,7 +12473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2024</v>
       </c>
@@ -12458,7 +12496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2024</v>
       </c>
@@ -25586,26 +25624,6 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -25613,6 +25631,26 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="778" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09613109-F906-46D9-B1AE-A17BDBE63962}"/>
+  <xr:revisionPtr revIDLastSave="806" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FC4A7EF-48AA-4ADE-81C0-85A7670B0A6F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="12" activeTab="17" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" activeTab="9" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -36,7 +36,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="165">
   <si>
     <t>Value</t>
   </si>
@@ -517,6 +517,42 @@
   <si>
     <t>material_downstream_manufacturing</t>
   </si>
+  <si>
+    <t>blade_bulk_on</t>
+  </si>
+  <si>
+    <t>blade_bulk_off</t>
+  </si>
+  <si>
+    <t>tower_bulk_on</t>
+  </si>
+  <si>
+    <t>tower_bulk_off</t>
+  </si>
+  <si>
+    <t>BladeOn</t>
+  </si>
+  <si>
+    <t>TowerOn</t>
+  </si>
+  <si>
+    <t>NacelleOn</t>
+  </si>
+  <si>
+    <t>AssemblyOn</t>
+  </si>
+  <si>
+    <t>BladeOff</t>
+  </si>
+  <si>
+    <t>TowerOff</t>
+  </si>
+  <si>
+    <t>NacelleOff</t>
+  </si>
+  <si>
+    <t>AssemblyOff</t>
+  </si>
 </sst>
 </file>
 
@@ -774,6 +810,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1267,7 +1307,7 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1293,7 +1333,7 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1319,7 +1359,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1345,7 +1385,7 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1371,7 +1411,7 @@
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1397,7 +1437,7 @@
         <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1420,7 +1460,7 @@
         <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1443,7 +1483,7 @@
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1515,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA1A697-84AA-4F97-BE70-81695B57512E}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -1689,13 +1729,13 @@
         <v>89</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D9">
-        <v>0.94859999999999989</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0.94859999999999989</v>
+        <v>1</v>
       </c>
       <c r="F9" s="9">
         <v>0</v>
@@ -1706,16 +1746,16 @@
         <v>76</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="D10">
-        <v>6.9563999999999995</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>6.9563999999999995</v>
+        <v>1</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -1726,19 +1766,19 @@
         <v>76</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D11">
-        <v>1.17E-3</v>
+        <v>5.5</v>
       </c>
       <c r="E11">
-        <v>1.17E-3</v>
-      </c>
-      <c r="F11" s="9">
-        <v>0</v>
+        <v>5.5</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1746,19 +1786,19 @@
         <v>76</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D12">
-        <v>8.1</v>
+        <v>5.47E-3</v>
       </c>
       <c r="E12">
-        <v>8.1</v>
-      </c>
-      <c r="F12" s="9">
-        <v>0</v>
+        <v>5.47E-3</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1766,19 +1806,19 @@
         <v>76</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="D13">
-        <v>114.72499999999999</v>
+        <v>4.7689999999999996E-2</v>
       </c>
       <c r="E13">
-        <v>114.72499999999999</v>
+        <v>4.7689999999999996E-2</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,19 +1826,19 @@
         <v>76</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D14">
-        <v>5.5</v>
+        <v>7.2699999999999996E-3</v>
       </c>
       <c r="E14">
-        <v>5.5</v>
+        <v>7.2699999999999996E-3</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>146</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1809,16 +1849,16 @@
         <v>92</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D15">
-        <v>5.47E-3</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="E15">
-        <v>5.47E-3</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1829,16 +1869,16 @@
         <v>92</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D16">
-        <v>4.7689999999999996E-2</v>
+        <v>2.2925</v>
       </c>
       <c r="E16">
-        <v>4.7689999999999996E-2</v>
+        <v>2.2925</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1849,13 +1889,13 @@
         <v>92</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D17">
-        <v>7.2699999999999996E-3</v>
+        <v>18.945</v>
       </c>
       <c r="E17">
-        <v>7.2699999999999996E-3</v>
+        <v>18.945</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>85</v>
@@ -1869,16 +1909,16 @@
         <v>92</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D18">
-        <v>2.7909999999999999</v>
+        <v>0.78549999999999998</v>
       </c>
       <c r="E18">
-        <v>2.7909999999999999</v>
+        <v>0.78549999999999998</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1889,16 +1929,16 @@
         <v>92</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D19">
-        <v>2.2925</v>
+        <v>0.1045</v>
       </c>
       <c r="E19">
-        <v>2.2925</v>
+        <v>0.1045</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1909,13 +1949,13 @@
         <v>92</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D20">
-        <v>18.945</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="E20">
-        <v>18.945</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>85</v>
@@ -1929,13 +1969,13 @@
         <v>92</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D21">
-        <v>0.78549999999999998</v>
+        <v>0.50024999999999997</v>
       </c>
       <c r="E21">
-        <v>0.78549999999999998</v>
+        <v>0.50024999999999997</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>85</v>
@@ -1943,62 +1983,62 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D22">
-        <v>0.1045</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0.1045</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>85</v>
+        <v>1</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D23">
-        <v>0.39200000000000002</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>85</v>
+        <v>1</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D24">
-        <v>0.50024999999999997</v>
+        <v>5.5</v>
       </c>
       <c r="E24">
-        <v>0.50024999999999997</v>
+        <v>5.5</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2006,19 +2046,19 @@
         <v>77</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D25">
-        <v>0.97139999999999993</v>
+        <v>1.1259999999999999E-2</v>
       </c>
       <c r="E25">
-        <v>0.97139999999999993</v>
-      </c>
-      <c r="F25" s="9">
-        <v>0</v>
+        <v>1.1259999999999999E-2</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2026,19 +2066,19 @@
         <v>77</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D26">
-        <v>7.1236000000000006</v>
+        <v>0.11219</v>
       </c>
       <c r="E26">
-        <v>7.1236000000000006</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0</v>
+        <v>0.11219</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2046,19 +2086,19 @@
         <v>77</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D27">
-        <v>3.4500000000000004E-3</v>
+        <v>2.0460000000000002E-2</v>
       </c>
       <c r="E27">
-        <v>3.4500000000000004E-3</v>
-      </c>
-      <c r="F27" s="9">
-        <v>0</v>
+        <v>2.0460000000000002E-2</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2066,19 +2106,19 @@
         <v>77</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D28">
-        <v>11.6</v>
+        <v>4.04</v>
       </c>
       <c r="E28">
-        <v>11.6</v>
-      </c>
-      <c r="F28" s="9">
-        <v>0</v>
+        <v>4.04</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2086,16 +2126,16 @@
         <v>77</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D29">
-        <v>116.77</v>
+        <v>3.2574999999999998</v>
       </c>
       <c r="E29">
-        <v>116.77</v>
+        <v>3.2574999999999998</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>145</v>
@@ -2106,19 +2146,19 @@
         <v>77</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D30">
-        <v>5.5</v>
+        <v>19.89</v>
       </c>
       <c r="E30">
-        <v>5.5</v>
+        <v>19.89</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>146</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2129,13 +2169,13 @@
         <v>92</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D31">
-        <v>1.1259999999999999E-2</v>
+        <v>0.79039999999999999</v>
       </c>
       <c r="E31">
-        <v>1.1259999999999999E-2</v>
+        <v>0.79039999999999999</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>85</v>
@@ -2149,13 +2189,13 @@
         <v>92</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D32">
-        <v>0.11219</v>
+        <v>0.10940000000000001</v>
       </c>
       <c r="E32">
-        <v>0.11219</v>
+        <v>0.10940000000000001</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>85</v>
@@ -2169,13 +2209,13 @@
         <v>92</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D33">
-        <v>2.0460000000000002E-2</v>
+        <v>0.32230000000000003</v>
       </c>
       <c r="E33">
-        <v>2.0460000000000002E-2</v>
+        <v>0.32230000000000003</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>85</v>
@@ -2189,175 +2229,55 @@
         <v>92</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="D34">
-        <v>4.04</v>
+        <v>0.5272</v>
       </c>
       <c r="E34">
-        <v>4.04</v>
+        <v>0.5272</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>130</v>
+      <c r="A35" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
       </c>
       <c r="D35">
-        <v>3.2574999999999998</v>
+        <v>50</v>
       </c>
       <c r="E35">
-        <v>3.2574999999999998</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>145</v>
+        <v>50</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>140</v>
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" t="s">
+        <v>95</v>
       </c>
       <c r="D36">
-        <v>19.89</v>
+        <v>50</v>
       </c>
       <c r="E36">
-        <v>19.89</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="D37">
-        <v>0.79039999999999999</v>
-      </c>
-      <c r="E37">
-        <v>0.79039999999999999</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38">
-        <v>0.10940000000000001</v>
-      </c>
-      <c r="E38">
-        <v>0.10940000000000001</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D39">
-        <v>0.32230000000000003</v>
-      </c>
-      <c r="E39">
-        <v>0.32230000000000003</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40">
-        <v>0.5272</v>
-      </c>
-      <c r="E40">
-        <v>0.5272</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" t="s">
-        <v>150</v>
-      </c>
-      <c r="C41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D41">
         <v>50</v>
       </c>
-      <c r="E41">
-        <v>50</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" t="s">
-        <v>150</v>
-      </c>
-      <c r="C42" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42">
-        <v>50</v>
-      </c>
-      <c r="E42">
-        <v>50</v>
-      </c>
-      <c r="F42">
+      <c r="F36">
         <v>0</v>
       </c>
     </row>
@@ -25624,6 +25544,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -25631,26 +25571,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1096" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F95914E4-E465-4F60-BC82-3474F0D31125}"/>
+  <xr:revisionPtr revIDLastSave="1098" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{280D284B-9121-4E13-AEAE-5874AF8D5C6E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" firstSheet="12" activeTab="18" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="17" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -36,7 +36,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -866,11 +866,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
@@ -1305,7 +1305,7 @@
       <c r="E2" s="12">
         <v>150</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="20">
         <v>24000</v>
       </c>
       <c r="G2">
@@ -1328,7 +1328,7 @@
       <c r="E3" s="12">
         <v>125</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="20">
         <v>2000</v>
       </c>
       <c r="G3">
@@ -1351,7 +1351,7 @@
       <c r="E4" s="12">
         <v>76</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="20">
         <v>7000</v>
       </c>
       <c r="G4">
@@ -1400,7 +1400,7 @@
       <c r="E6" s="12">
         <v>60</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>18000</v>
       </c>
       <c r="G6">
@@ -1426,7 +1426,7 @@
       <c r="E7" s="12">
         <v>55</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="20">
         <v>14000</v>
       </c>
       <c r="G7">
@@ -1452,7 +1452,7 @@
       <c r="E8" s="12">
         <v>35</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <v>13000</v>
       </c>
       <c r="G8">
@@ -1504,7 +1504,7 @@
       <c r="E10" s="12">
         <v>60</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <v>5000</v>
       </c>
       <c r="G10">
@@ -1530,7 +1530,7 @@
       <c r="E11" s="12">
         <v>55</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="20">
         <v>9000</v>
       </c>
       <c r="G11">
@@ -1553,7 +1553,7 @@
       <c r="E12" s="12">
         <v>35</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <v>7000</v>
       </c>
       <c r="G12">
@@ -1844,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="9">
-        <v>0</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="9">
-        <v>0</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4946,10 +4946,10 @@
       <c r="L2" s="12">
         <v>450000</v>
       </c>
-      <c r="M2" s="22">
+      <c r="M2" s="21">
         <v>1200</v>
       </c>
-      <c r="N2" s="22">
+      <c r="N2" s="21">
         <v>5000</v>
       </c>
       <c r="O2" s="12">
@@ -5026,10 +5026,10 @@
       <c r="L3" s="12">
         <v>450000</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="21">
         <v>1200</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="21">
         <v>5000</v>
       </c>
       <c r="O3" s="12">
@@ -5106,10 +5106,10 @@
       <c r="L4" s="12">
         <v>450000</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="21">
         <v>1200</v>
       </c>
-      <c r="N4" s="22">
+      <c r="N4" s="21">
         <v>5000</v>
       </c>
       <c r="O4" s="12">
@@ -5186,10 +5186,10 @@
       <c r="L5" s="12">
         <v>450000</v>
       </c>
-      <c r="M5" s="22">
+      <c r="M5" s="21">
         <v>1200</v>
       </c>
-      <c r="N5" s="22">
+      <c r="N5" s="21">
         <v>5000</v>
       </c>
       <c r="O5" s="12">
@@ -5266,10 +5266,10 @@
       <c r="L6" s="12">
         <v>450000</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="21">
         <v>1200</v>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="21">
         <v>5000</v>
       </c>
       <c r="O6" s="12">
@@ -5346,10 +5346,10 @@
       <c r="L7" s="12">
         <v>450000</v>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="21">
         <v>1200</v>
       </c>
-      <c r="N7" s="22">
+      <c r="N7" s="21">
         <v>5000</v>
       </c>
       <c r="O7" s="12">
@@ -5426,10 +5426,10 @@
       <c r="L8" s="12">
         <v>450000</v>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="21">
         <v>1200</v>
       </c>
-      <c r="N8" s="22">
+      <c r="N8" s="21">
         <v>5000</v>
       </c>
       <c r="O8" s="12">
@@ -5506,10 +5506,10 @@
       <c r="L9" s="12">
         <v>450000</v>
       </c>
-      <c r="M9" s="22">
+      <c r="M9" s="21">
         <v>1200</v>
       </c>
-      <c r="N9" s="22">
+      <c r="N9" s="21">
         <v>5000</v>
       </c>
       <c r="O9" s="12">
@@ -5586,10 +5586,10 @@
       <c r="L10" s="12">
         <v>450000</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="21">
         <v>1200</v>
       </c>
-      <c r="N10" s="22">
+      <c r="N10" s="21">
         <v>5000</v>
       </c>
       <c r="O10" s="12">
@@ -5666,10 +5666,10 @@
       <c r="L11" s="12">
         <v>450000</v>
       </c>
-      <c r="M11" s="22">
+      <c r="M11" s="21">
         <v>1200</v>
       </c>
-      <c r="N11" s="22">
+      <c r="N11" s="21">
         <v>5000</v>
       </c>
       <c r="O11" s="12">
@@ -5746,10 +5746,10 @@
       <c r="L12" s="12">
         <v>450000</v>
       </c>
-      <c r="M12" s="22">
+      <c r="M12" s="21">
         <v>1200</v>
       </c>
-      <c r="N12" s="22">
+      <c r="N12" s="21">
         <v>5000</v>
       </c>
       <c r="O12" s="12">
@@ -5826,10 +5826,10 @@
       <c r="L13" s="12">
         <v>450000</v>
       </c>
-      <c r="M13" s="22">
+      <c r="M13" s="21">
         <v>1200</v>
       </c>
-      <c r="N13" s="22">
+      <c r="N13" s="21">
         <v>5000</v>
       </c>
       <c r="O13" s="12">
@@ -5906,10 +5906,10 @@
       <c r="L14" s="12">
         <v>450000</v>
       </c>
-      <c r="M14" s="22">
+      <c r="M14" s="21">
         <v>1200</v>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="21">
         <v>5000</v>
       </c>
       <c r="O14" s="12">
@@ -5986,10 +5986,10 @@
       <c r="L15" s="12">
         <v>450000</v>
       </c>
-      <c r="M15" s="22">
+      <c r="M15" s="21">
         <v>1200</v>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="21">
         <v>5000</v>
       </c>
       <c r="O15" s="12">
@@ -6066,10 +6066,10 @@
       <c r="L16" s="12">
         <v>450000</v>
       </c>
-      <c r="M16" s="22">
+      <c r="M16" s="21">
         <v>1200</v>
       </c>
-      <c r="N16" s="22">
+      <c r="N16" s="21">
         <v>5000</v>
       </c>
       <c r="O16" s="12">
@@ -6146,10 +6146,10 @@
       <c r="L17" s="12">
         <v>450000</v>
       </c>
-      <c r="M17" s="22">
+      <c r="M17" s="21">
         <v>1200</v>
       </c>
-      <c r="N17" s="22">
+      <c r="N17" s="21">
         <v>5000</v>
       </c>
       <c r="O17" s="12">
@@ -6226,10 +6226,10 @@
       <c r="L18" s="12">
         <v>450000</v>
       </c>
-      <c r="M18" s="22">
+      <c r="M18" s="21">
         <v>1200</v>
       </c>
-      <c r="N18" s="22">
+      <c r="N18" s="21">
         <v>5000</v>
       </c>
       <c r="O18" s="12">
@@ -6306,10 +6306,10 @@
       <c r="L19" s="12">
         <v>450000</v>
       </c>
-      <c r="M19" s="22">
+      <c r="M19" s="21">
         <v>1200</v>
       </c>
-      <c r="N19" s="22">
+      <c r="N19" s="21">
         <v>5000</v>
       </c>
       <c r="O19" s="12">
@@ -6386,10 +6386,10 @@
       <c r="L20" s="12">
         <v>450000</v>
       </c>
-      <c r="M20" s="22">
+      <c r="M20" s="21">
         <v>1200</v>
       </c>
-      <c r="N20" s="22">
+      <c r="N20" s="21">
         <v>5000</v>
       </c>
       <c r="O20" s="12">
@@ -6466,10 +6466,10 @@
       <c r="L21" s="12">
         <v>450000</v>
       </c>
-      <c r="M21" s="22">
+      <c r="M21" s="21">
         <v>1200</v>
       </c>
-      <c r="N21" s="22">
+      <c r="N21" s="21">
         <v>5000</v>
       </c>
       <c r="O21" s="12">
@@ -6546,10 +6546,10 @@
       <c r="L22" s="12">
         <v>450000</v>
       </c>
-      <c r="M22" s="22">
+      <c r="M22" s="21">
         <v>1200</v>
       </c>
-      <c r="N22" s="22">
+      <c r="N22" s="21">
         <v>5000</v>
       </c>
       <c r="O22" s="12">
@@ -6626,10 +6626,10 @@
       <c r="L23" s="12">
         <v>450000</v>
       </c>
-      <c r="M23" s="22">
+      <c r="M23" s="21">
         <v>1200</v>
       </c>
-      <c r="N23" s="22">
+      <c r="N23" s="21">
         <v>5000</v>
       </c>
       <c r="O23" s="12">
@@ -6706,10 +6706,10 @@
       <c r="L24" s="12">
         <v>450000</v>
       </c>
-      <c r="M24" s="22">
+      <c r="M24" s="21">
         <v>1200</v>
       </c>
-      <c r="N24" s="22">
+      <c r="N24" s="21">
         <v>5000</v>
       </c>
       <c r="O24" s="12">
@@ -6786,10 +6786,10 @@
       <c r="L25" s="12">
         <v>450000</v>
       </c>
-      <c r="M25" s="22">
+      <c r="M25" s="21">
         <v>1200</v>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="21">
         <v>5000</v>
       </c>
       <c r="O25" s="12">
@@ -6866,10 +6866,10 @@
       <c r="L26" s="12">
         <v>450000</v>
       </c>
-      <c r="M26" s="22">
+      <c r="M26" s="21">
         <v>1200</v>
       </c>
-      <c r="N26" s="22">
+      <c r="N26" s="21">
         <v>5000</v>
       </c>
       <c r="O26" s="12">
@@ -6946,10 +6946,10 @@
       <c r="L27" s="12">
         <v>450000</v>
       </c>
-      <c r="M27" s="22">
+      <c r="M27" s="21">
         <v>1200</v>
       </c>
-      <c r="N27" s="22">
+      <c r="N27" s="21">
         <v>5000</v>
       </c>
       <c r="O27" s="12">
@@ -7026,10 +7026,10 @@
       <c r="L28" s="12">
         <v>450000</v>
       </c>
-      <c r="M28" s="22">
+      <c r="M28" s="21">
         <v>1200</v>
       </c>
-      <c r="N28" s="22">
+      <c r="N28" s="21">
         <v>5000</v>
       </c>
       <c r="O28" s="12">
@@ -7196,10 +7196,10 @@
       <c r="L2" s="12">
         <v>450000</v>
       </c>
-      <c r="M2" s="22">
+      <c r="M2" s="21">
         <v>1200</v>
       </c>
-      <c r="N2" s="22">
+      <c r="N2" s="21">
         <v>5000</v>
       </c>
       <c r="O2" s="12">
@@ -7276,10 +7276,10 @@
       <c r="L3" s="12">
         <v>450000</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="21">
         <v>1200</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="21">
         <v>5000</v>
       </c>
       <c r="O3" s="12">
@@ -7356,10 +7356,10 @@
       <c r="L4" s="12">
         <v>450000</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="21">
         <v>1200</v>
       </c>
-      <c r="N4" s="22">
+      <c r="N4" s="21">
         <v>5000</v>
       </c>
       <c r="O4" s="12">
@@ -7436,10 +7436,10 @@
       <c r="L5" s="12">
         <v>450000</v>
       </c>
-      <c r="M5" s="22">
+      <c r="M5" s="21">
         <v>1200</v>
       </c>
-      <c r="N5" s="22">
+      <c r="N5" s="21">
         <v>5000</v>
       </c>
       <c r="O5" s="12">
@@ -7516,10 +7516,10 @@
       <c r="L6" s="12">
         <v>450000</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="21">
         <v>1200</v>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="21">
         <v>5000</v>
       </c>
       <c r="O6" s="12">
@@ -7596,10 +7596,10 @@
       <c r="L7" s="12">
         <v>450000</v>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="21">
         <v>1200</v>
       </c>
-      <c r="N7" s="22">
+      <c r="N7" s="21">
         <v>5000</v>
       </c>
       <c r="O7" s="12">
@@ -7676,10 +7676,10 @@
       <c r="L8" s="12">
         <v>450000</v>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="21">
         <v>1200</v>
       </c>
-      <c r="N8" s="22">
+      <c r="N8" s="21">
         <v>5000</v>
       </c>
       <c r="O8" s="12">
@@ -7756,10 +7756,10 @@
       <c r="L9" s="12">
         <v>450000</v>
       </c>
-      <c r="M9" s="22">
+      <c r="M9" s="21">
         <v>1200</v>
       </c>
-      <c r="N9" s="22">
+      <c r="N9" s="21">
         <v>5000</v>
       </c>
       <c r="O9" s="12">
@@ -7836,10 +7836,10 @@
       <c r="L10" s="12">
         <v>450000</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="21">
         <v>1200</v>
       </c>
-      <c r="N10" s="22">
+      <c r="N10" s="21">
         <v>5000</v>
       </c>
       <c r="O10" s="12">
@@ -7916,10 +7916,10 @@
       <c r="L11" s="12">
         <v>450000</v>
       </c>
-      <c r="M11" s="22">
+      <c r="M11" s="21">
         <v>1200</v>
       </c>
-      <c r="N11" s="22">
+      <c r="N11" s="21">
         <v>5000</v>
       </c>
       <c r="O11" s="12">
@@ -7996,10 +7996,10 @@
       <c r="L12" s="12">
         <v>450000</v>
       </c>
-      <c r="M12" s="22">
+      <c r="M12" s="21">
         <v>1200</v>
       </c>
-      <c r="N12" s="22">
+      <c r="N12" s="21">
         <v>5000</v>
       </c>
       <c r="O12" s="12">
@@ -8076,10 +8076,10 @@
       <c r="L13" s="12">
         <v>450000</v>
       </c>
-      <c r="M13" s="22">
+      <c r="M13" s="21">
         <v>1200</v>
       </c>
-      <c r="N13" s="22">
+      <c r="N13" s="21">
         <v>5000</v>
       </c>
       <c r="O13" s="12">
@@ -8156,10 +8156,10 @@
       <c r="L14" s="12">
         <v>450000</v>
       </c>
-      <c r="M14" s="22">
+      <c r="M14" s="21">
         <v>1200</v>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="21">
         <v>5000</v>
       </c>
       <c r="O14" s="12">
@@ -8236,10 +8236,10 @@
       <c r="L15" s="12">
         <v>450000</v>
       </c>
-      <c r="M15" s="22">
+      <c r="M15" s="21">
         <v>1200</v>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="21">
         <v>5000</v>
       </c>
       <c r="O15" s="12">
@@ -8316,10 +8316,10 @@
       <c r="L16" s="12">
         <v>450000</v>
       </c>
-      <c r="M16" s="22">
+      <c r="M16" s="21">
         <v>1200</v>
       </c>
-      <c r="N16" s="22">
+      <c r="N16" s="21">
         <v>5000</v>
       </c>
       <c r="O16" s="12">
@@ -8396,10 +8396,10 @@
       <c r="L17" s="12">
         <v>450000</v>
       </c>
-      <c r="M17" s="22">
+      <c r="M17" s="21">
         <v>1200</v>
       </c>
-      <c r="N17" s="22">
+      <c r="N17" s="21">
         <v>5000</v>
       </c>
       <c r="O17" s="12">
@@ -8476,10 +8476,10 @@
       <c r="L18" s="12">
         <v>450000</v>
       </c>
-      <c r="M18" s="22">
+      <c r="M18" s="21">
         <v>1200</v>
       </c>
-      <c r="N18" s="22">
+      <c r="N18" s="21">
         <v>5000</v>
       </c>
       <c r="O18" s="12">
@@ -8556,10 +8556,10 @@
       <c r="L19" s="12">
         <v>450000</v>
       </c>
-      <c r="M19" s="22">
+      <c r="M19" s="21">
         <v>1200</v>
       </c>
-      <c r="N19" s="22">
+      <c r="N19" s="21">
         <v>5000</v>
       </c>
       <c r="O19" s="12">
@@ -8636,10 +8636,10 @@
       <c r="L20" s="12">
         <v>450000</v>
       </c>
-      <c r="M20" s="22">
+      <c r="M20" s="21">
         <v>1200</v>
       </c>
-      <c r="N20" s="22">
+      <c r="N20" s="21">
         <v>5000</v>
       </c>
       <c r="O20" s="12">
@@ -8716,10 +8716,10 @@
       <c r="L21" s="12">
         <v>450000</v>
       </c>
-      <c r="M21" s="22">
+      <c r="M21" s="21">
         <v>1200</v>
       </c>
-      <c r="N21" s="22">
+      <c r="N21" s="21">
         <v>5000</v>
       </c>
       <c r="O21" s="12">
@@ -8796,10 +8796,10 @@
       <c r="L22" s="12">
         <v>450000</v>
       </c>
-      <c r="M22" s="22">
+      <c r="M22" s="21">
         <v>1200</v>
       </c>
-      <c r="N22" s="22">
+      <c r="N22" s="21">
         <v>5000</v>
       </c>
       <c r="O22" s="12">
@@ -8876,10 +8876,10 @@
       <c r="L23" s="12">
         <v>450000</v>
       </c>
-      <c r="M23" s="22">
+      <c r="M23" s="21">
         <v>1200</v>
       </c>
-      <c r="N23" s="22">
+      <c r="N23" s="21">
         <v>5000</v>
       </c>
       <c r="O23" s="12">
@@ -8956,10 +8956,10 @@
       <c r="L24" s="12">
         <v>450000</v>
       </c>
-      <c r="M24" s="22">
+      <c r="M24" s="21">
         <v>1200</v>
       </c>
-      <c r="N24" s="22">
+      <c r="N24" s="21">
         <v>5000</v>
       </c>
       <c r="O24" s="12">
@@ -9036,10 +9036,10 @@
       <c r="L25" s="12">
         <v>450000</v>
       </c>
-      <c r="M25" s="22">
+      <c r="M25" s="21">
         <v>1200</v>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="21">
         <v>5000</v>
       </c>
       <c r="O25" s="12">
@@ -9116,10 +9116,10 @@
       <c r="L26" s="12">
         <v>450000</v>
       </c>
-      <c r="M26" s="22">
+      <c r="M26" s="21">
         <v>1200</v>
       </c>
-      <c r="N26" s="22">
+      <c r="N26" s="21">
         <v>5000</v>
       </c>
       <c r="O26" s="12">
@@ -9196,10 +9196,10 @@
       <c r="L27" s="12">
         <v>450000</v>
       </c>
-      <c r="M27" s="22">
+      <c r="M27" s="21">
         <v>1200</v>
       </c>
-      <c r="N27" s="22">
+      <c r="N27" s="21">
         <v>5000</v>
       </c>
       <c r="O27" s="12">
@@ -9276,10 +9276,10 @@
       <c r="L28" s="12">
         <v>450000</v>
       </c>
-      <c r="M28" s="22">
+      <c r="M28" s="21">
         <v>1200</v>
       </c>
-      <c r="N28" s="22">
+      <c r="N28" s="21">
         <v>5000</v>
       </c>
       <c r="O28" s="12">
@@ -26142,7 +26142,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+      <c r="A2" s="22">
         <v>2024</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -26156,7 +26156,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
+      <c r="A3" s="22"/>
       <c r="B3" s="11" t="s">
         <v>70</v>
       </c>
@@ -26169,7 +26169,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
+      <c r="A4" s="22"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -26181,7 +26181,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
@@ -26193,7 +26193,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="22">
         <v>2025</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -26207,7 +26207,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
@@ -26219,7 +26219,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
@@ -26231,7 +26231,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="11" t="s">
         <v>68</v>
       </c>
@@ -26244,7 +26244,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+      <c r="A10" s="22">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -26258,7 +26258,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
@@ -26270,7 +26270,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -26282,7 +26282,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -26295,7 +26295,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="A14" s="22">
         <v>2027</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -26309,7 +26309,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
@@ -26321,7 +26321,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
+      <c r="A16" s="22"/>
       <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
@@ -26333,7 +26333,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
@@ -26346,7 +26346,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+      <c r="A18" s="22">
         <v>2028</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -26360,7 +26360,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
@@ -26372,7 +26372,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
@@ -26384,7 +26384,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="11" t="s">
         <v>68</v>
       </c>
@@ -26397,7 +26397,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="20">
+      <c r="A22" s="22">
         <v>2029</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -26411,7 +26411,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="11" t="s">
         <v>70</v>
       </c>
@@ -26423,7 +26423,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="20"/>
+      <c r="A24" s="22"/>
       <c r="B24" s="11" t="s">
         <v>71</v>
       </c>
@@ -26435,7 +26435,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="20"/>
+      <c r="A25" s="22"/>
       <c r="B25" s="11" t="s">
         <v>68</v>
       </c>
@@ -26448,7 +26448,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="20">
+      <c r="A26" s="22">
         <v>2030</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -26462,7 +26462,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="20"/>
+      <c r="A27" s="22"/>
       <c r="B27" s="11" t="s">
         <v>70</v>
       </c>
@@ -26474,7 +26474,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="20"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="11" t="s">
         <v>71</v>
       </c>
@@ -26486,7 +26486,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="20"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="11" t="s">
         <v>68</v>
       </c>
@@ -26499,7 +26499,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="20">
+      <c r="A30" s="22">
         <v>2031</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -26513,7 +26513,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
@@ -26525,7 +26525,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="20"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="11" t="s">
         <v>71</v>
       </c>
@@ -26537,7 +26537,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="20"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
@@ -26550,7 +26550,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
+      <c r="A34" s="22">
         <v>2032</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -26564,7 +26564,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="20"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="11" t="s">
         <v>70</v>
       </c>
@@ -26576,7 +26576,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="20"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="11" t="s">
         <v>71</v>
       </c>
@@ -26588,7 +26588,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="20"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="11" t="s">
         <v>68</v>
       </c>
@@ -26601,7 +26601,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="20">
+      <c r="A38" s="22">
         <v>2033</v>
       </c>
       <c r="B38" s="11" t="s">
@@ -26615,7 +26615,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="20"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="11" t="s">
         <v>70</v>
       </c>
@@ -26627,7 +26627,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="20"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="11" t="s">
         <v>71</v>
       </c>
@@ -26639,7 +26639,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="20"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="11" t="s">
         <v>68</v>
       </c>
@@ -26652,7 +26652,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="20">
+      <c r="A42" s="22">
         <v>2034</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -26666,7 +26666,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="20"/>
+      <c r="A43" s="22"/>
       <c r="B43" s="11" t="s">
         <v>70</v>
       </c>
@@ -26678,7 +26678,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="20"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="11" t="s">
         <v>71</v>
       </c>
@@ -26690,7 +26690,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="20"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="11" t="s">
         <v>68</v>
       </c>
@@ -26703,7 +26703,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
+      <c r="A46" s="22">
         <v>2035</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -26717,7 +26717,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="20"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="11" t="s">
         <v>70</v>
       </c>
@@ -26729,7 +26729,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="20"/>
+      <c r="A48" s="22"/>
       <c r="B48" s="11" t="s">
         <v>71</v>
       </c>
@@ -26741,7 +26741,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="20"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="11" t="s">
         <v>68</v>
       </c>
@@ -26754,7 +26754,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="20">
+      <c r="A50" s="22">
         <v>2036</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -26768,7 +26768,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="20"/>
+      <c r="A51" s="22"/>
       <c r="B51" s="11" t="s">
         <v>70</v>
       </c>
@@ -26780,7 +26780,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="20"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="11" t="s">
         <v>71</v>
       </c>
@@ -26792,7 +26792,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="20"/>
+      <c r="A53" s="22"/>
       <c r="B53" s="11" t="s">
         <v>68</v>
       </c>
@@ -26805,7 +26805,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="20">
+      <c r="A54" s="22">
         <v>2037</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -26819,7 +26819,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="20"/>
+      <c r="A55" s="22"/>
       <c r="B55" s="11" t="s">
         <v>70</v>
       </c>
@@ -26831,7 +26831,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="20"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="11" t="s">
         <v>71</v>
       </c>
@@ -26843,7 +26843,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="20"/>
+      <c r="A57" s="22"/>
       <c r="B57" s="11" t="s">
         <v>68</v>
       </c>
@@ -26856,7 +26856,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="20">
+      <c r="A58" s="22">
         <v>2038</v>
       </c>
       <c r="B58" s="11" t="s">
@@ -26870,7 +26870,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="20"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="11" t="s">
         <v>70</v>
       </c>
@@ -26882,7 +26882,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="20"/>
+      <c r="A60" s="22"/>
       <c r="B60" s="11" t="s">
         <v>71</v>
       </c>
@@ -26894,7 +26894,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="20"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="11" t="s">
         <v>68</v>
       </c>
@@ -26907,7 +26907,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="20">
+      <c r="A62" s="22">
         <v>2039</v>
       </c>
       <c r="B62" s="11" t="s">
@@ -26921,7 +26921,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="20"/>
+      <c r="A63" s="22"/>
       <c r="B63" s="11" t="s">
         <v>70</v>
       </c>
@@ -26933,7 +26933,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="20"/>
+      <c r="A64" s="22"/>
       <c r="B64" s="11" t="s">
         <v>71</v>
       </c>
@@ -26945,7 +26945,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="20"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="11" t="s">
         <v>68</v>
       </c>
@@ -26958,7 +26958,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="20">
+      <c r="A66" s="22">
         <v>2040</v>
       </c>
       <c r="B66" s="11" t="s">
@@ -26972,7 +26972,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="20"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
@@ -26984,7 +26984,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="20"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="11" t="s">
         <v>71</v>
       </c>
@@ -26996,7 +26996,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="20"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="11" t="s">
         <v>68</v>
       </c>
@@ -27009,7 +27009,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="20">
+      <c r="A70" s="22">
         <v>2041</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -27023,7 +27023,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="20"/>
+      <c r="A71" s="22"/>
       <c r="B71" s="11" t="s">
         <v>70</v>
       </c>
@@ -27035,7 +27035,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="20"/>
+      <c r="A72" s="22"/>
       <c r="B72" s="11" t="s">
         <v>71</v>
       </c>
@@ -27047,7 +27047,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="20"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="11" t="s">
         <v>68</v>
       </c>
@@ -27060,7 +27060,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="20">
+      <c r="A74" s="22">
         <v>2042</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -27074,7 +27074,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="20"/>
+      <c r="A75" s="22"/>
       <c r="B75" s="11" t="s">
         <v>70</v>
       </c>
@@ -27086,7 +27086,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="20"/>
+      <c r="A76" s="22"/>
       <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
@@ -27098,7 +27098,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="20"/>
+      <c r="A77" s="22"/>
       <c r="B77" s="11" t="s">
         <v>68</v>
       </c>
@@ -27111,7 +27111,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="20">
+      <c r="A78" s="22">
         <v>2043</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -27125,7 +27125,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="20"/>
+      <c r="A79" s="22"/>
       <c r="B79" s="11" t="s">
         <v>70</v>
       </c>
@@ -27137,7 +27137,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="20"/>
+      <c r="A80" s="22"/>
       <c r="B80" s="11" t="s">
         <v>71</v>
       </c>
@@ -27149,7 +27149,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="20"/>
+      <c r="A81" s="22"/>
       <c r="B81" s="11" t="s">
         <v>68</v>
       </c>
@@ -27162,7 +27162,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="20">
+      <c r="A82" s="22">
         <v>2044</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -27176,7 +27176,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="20"/>
+      <c r="A83" s="22"/>
       <c r="B83" s="11" t="s">
         <v>70</v>
       </c>
@@ -27188,7 +27188,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="20"/>
+      <c r="A84" s="22"/>
       <c r="B84" s="11" t="s">
         <v>71</v>
       </c>
@@ -27200,7 +27200,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="20"/>
+      <c r="A85" s="22"/>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
@@ -27213,7 +27213,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="20">
+      <c r="A86" s="22">
         <v>2045</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -27227,7 +27227,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="20"/>
+      <c r="A87" s="22"/>
       <c r="B87" s="11" t="s">
         <v>70</v>
       </c>
@@ -27239,7 +27239,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="20"/>
+      <c r="A88" s="22"/>
       <c r="B88" s="11" t="s">
         <v>71</v>
       </c>
@@ -27251,7 +27251,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="20"/>
+      <c r="A89" s="22"/>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
@@ -27264,7 +27264,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="20">
+      <c r="A90" s="22">
         <v>2046</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -27278,7 +27278,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="20"/>
+      <c r="A91" s="22"/>
       <c r="B91" s="11" t="s">
         <v>70</v>
       </c>
@@ -27290,7 +27290,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="20"/>
+      <c r="A92" s="22"/>
       <c r="B92" s="11" t="s">
         <v>71</v>
       </c>
@@ -27302,7 +27302,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="20"/>
+      <c r="A93" s="22"/>
       <c r="B93" s="11" t="s">
         <v>68</v>
       </c>
@@ -27315,7 +27315,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="20">
+      <c r="A94" s="22">
         <v>2047</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -27329,7 +27329,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="20"/>
+      <c r="A95" s="22"/>
       <c r="B95" s="11" t="s">
         <v>70</v>
       </c>
@@ -27341,7 +27341,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="20"/>
+      <c r="A96" s="22"/>
       <c r="B96" s="11" t="s">
         <v>71</v>
       </c>
@@ -27353,7 +27353,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="20"/>
+      <c r="A97" s="22"/>
       <c r="B97" s="11" t="s">
         <v>68</v>
       </c>
@@ -27366,7 +27366,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="20">
+      <c r="A98" s="22">
         <v>2048</v>
       </c>
       <c r="B98" s="11" t="s">
@@ -27380,7 +27380,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="20"/>
+      <c r="A99" s="22"/>
       <c r="B99" s="11" t="s">
         <v>70</v>
       </c>
@@ -27392,7 +27392,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="20"/>
+      <c r="A100" s="22"/>
       <c r="B100" s="11" t="s">
         <v>71</v>
       </c>
@@ -27404,7 +27404,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="20"/>
+      <c r="A101" s="22"/>
       <c r="B101" s="11" t="s">
         <v>68</v>
       </c>
@@ -27417,7 +27417,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="20">
+      <c r="A102" s="22">
         <v>2049</v>
       </c>
       <c r="B102" s="11" t="s">
@@ -27431,7 +27431,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="20"/>
+      <c r="A103" s="22"/>
       <c r="B103" s="11" t="s">
         <v>70</v>
       </c>
@@ -27443,7 +27443,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="20"/>
+      <c r="A104" s="22"/>
       <c r="B104" s="11" t="s">
         <v>71</v>
       </c>
@@ -27455,7 +27455,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="20"/>
+      <c r="A105" s="22"/>
       <c r="B105" s="11" t="s">
         <v>68</v>
       </c>
@@ -27468,7 +27468,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="20">
+      <c r="A106" s="22">
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
@@ -27482,7 +27482,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="20"/>
+      <c r="A107" s="22"/>
       <c r="B107" s="11" t="s">
         <v>70</v>
       </c>
@@ -27494,7 +27494,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="20"/>
+      <c r="A108" s="22"/>
       <c r="B108" s="11" t="s">
         <v>71</v>
       </c>
@@ -27506,7 +27506,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="20"/>
+      <c r="A109" s="22"/>
       <c r="B109" s="11" t="s">
         <v>68</v>
       </c>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/urbs-materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1098" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{280D284B-9121-4E13-AEAE-5874AF8D5C6E}"/>
+  <xr:revisionPtr revIDLastSave="1155" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{898C7E9C-83DA-4DD8-8EF3-751FB916CEA0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="17" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="10" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -36,7 +36,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -622,7 +623,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -681,8 +682,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -743,8 +750,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="1">
+          <color theme="0"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -800,8 +823,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8F1D2E"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF8F1D2E"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -824,8 +873,11 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="5">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -871,8 +923,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="10">
+  <cellStyles count="11">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{1C1ADB5D-62B2-4A88-A962-14B0B3D457AA}"/>
     <cellStyle name="Comma 3" xfId="9" xr:uid="{9997F304-5A38-4E5F-B1DE-7811E5D8CE60}"/>
     <cellStyle name="Komma 2" xfId="1" xr:uid="{9730D791-2C32-423B-BFCB-9BD5E54695C9}"/>
@@ -883,6 +938,7 @@
     <cellStyle name="N_InputWhite" xfId="3" xr:uid="{C070A988-14E9-487E-BD2B-E0CB280DDD88}"/>
     <cellStyle name="N_Table1_Header" xfId="6" xr:uid="{5B945886-E1B9-4000-BFBC-F4E856A0CA51}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Tabelle allgemein" xfId="10" xr:uid="{23500D89-14AD-4025-B76C-4803D9910AA2}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2663,8 +2719,8 @@
       <c r="A2" s="14">
         <v>2024</v>
       </c>
-      <c r="B2" s="15">
-        <v>1760000</v>
+      <c r="B2" s="23">
+        <v>2024431</v>
       </c>
       <c r="C2" s="15">
         <v>57100000</v>
@@ -2672,79 +2728,79 @@
       <c r="D2" s="15">
         <v>58100000</v>
       </c>
-      <c r="E2" s="15">
-        <v>960000</v>
+      <c r="E2" s="23">
+        <v>860748</v>
       </c>
       <c r="F2" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G2" s="15">
         <v>167000</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J2" s="23">
+        <v>1235</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M2" s="23">
+        <v>485</v>
+      </c>
+      <c r="N2" s="23">
+        <v>280</v>
+      </c>
+      <c r="O2" s="23">
+        <v>15000</v>
       </c>
       <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="23">
+        <v>47673</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>2025</v>
       </c>
-      <c r="B3" s="15">
-        <v>1760000</v>
+      <c r="B3" s="23">
+        <v>2024431</v>
       </c>
       <c r="C3" s="15">
         <v>57100000</v>
@@ -2752,79 +2808,79 @@
       <c r="D3" s="15">
         <v>58100000</v>
       </c>
-      <c r="E3" s="15">
-        <v>960000</v>
+      <c r="E3" s="23">
+        <v>860748</v>
       </c>
       <c r="F3" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G3" s="15">
         <v>167000</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J3" s="23">
+        <v>1235</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M3" s="23">
+        <v>485</v>
+      </c>
+      <c r="N3" s="23">
+        <v>280</v>
+      </c>
+      <c r="O3" s="23">
+        <v>15000</v>
       </c>
       <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="23">
+        <v>47673</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>2026</v>
       </c>
-      <c r="B4" s="15">
-        <v>1760000</v>
+      <c r="B4" s="23">
+        <v>2024431</v>
       </c>
       <c r="C4" s="15">
         <v>57100000</v>
@@ -2832,79 +2888,79 @@
       <c r="D4" s="15">
         <v>58100000</v>
       </c>
-      <c r="E4" s="15">
-        <v>960000</v>
+      <c r="E4" s="23">
+        <v>860748</v>
       </c>
       <c r="F4" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G4" s="15">
         <v>167000</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J4" s="23">
+        <v>1235</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M4" s="23">
+        <v>485</v>
+      </c>
+      <c r="N4" s="23">
+        <v>280</v>
+      </c>
+      <c r="O4" s="23">
+        <v>15000</v>
       </c>
       <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>47673</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>2027</v>
       </c>
-      <c r="B5" s="15">
-        <v>1760000</v>
+      <c r="B5" s="23">
+        <v>2024431</v>
       </c>
       <c r="C5" s="15">
         <v>57100000</v>
@@ -2912,79 +2968,79 @@
       <c r="D5" s="15">
         <v>58100000</v>
       </c>
-      <c r="E5" s="15">
-        <v>960000</v>
+      <c r="E5" s="23">
+        <v>860748</v>
       </c>
       <c r="F5" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G5" s="15">
         <v>167000</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J5" s="23">
+        <v>1235</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M5" s="23">
+        <v>485</v>
+      </c>
+      <c r="N5" s="23">
+        <v>280</v>
+      </c>
+      <c r="O5" s="23">
+        <v>15000</v>
       </c>
       <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="23">
+        <v>47673</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>2028</v>
       </c>
-      <c r="B6" s="15">
-        <v>1760000</v>
+      <c r="B6" s="23">
+        <v>2024431</v>
       </c>
       <c r="C6" s="15">
         <v>57100000</v>
@@ -2992,79 +3048,79 @@
       <c r="D6" s="15">
         <v>58100000</v>
       </c>
-      <c r="E6" s="15">
-        <v>960000</v>
+      <c r="E6" s="23">
+        <v>860748</v>
       </c>
       <c r="F6" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G6" s="15">
         <v>167000</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J6" s="23">
+        <v>1235</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M6" s="23">
+        <v>485</v>
+      </c>
+      <c r="N6" s="23">
+        <v>280</v>
+      </c>
+      <c r="O6" s="23">
+        <v>15000</v>
       </c>
       <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>47673</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>2029</v>
       </c>
-      <c r="B7" s="15">
-        <v>1760000</v>
+      <c r="B7" s="23">
+        <v>2024431</v>
       </c>
       <c r="C7" s="15">
         <v>57100000</v>
@@ -3072,79 +3128,79 @@
       <c r="D7" s="15">
         <v>58100000</v>
       </c>
-      <c r="E7" s="15">
-        <v>960000</v>
+      <c r="E7" s="23">
+        <v>860748</v>
       </c>
       <c r="F7" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G7" s="15">
         <v>167000</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J7" s="23">
+        <v>1235</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M7" s="23">
+        <v>485</v>
+      </c>
+      <c r="N7" s="23">
+        <v>280</v>
+      </c>
+      <c r="O7" s="23">
+        <v>15000</v>
       </c>
       <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="23">
+        <v>47673</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>2030</v>
       </c>
-      <c r="B8" s="15">
-        <v>1760000</v>
+      <c r="B8" s="23">
+        <v>2024431</v>
       </c>
       <c r="C8" s="15">
         <v>57100000</v>
@@ -3152,79 +3208,79 @@
       <c r="D8" s="15">
         <v>58100000</v>
       </c>
-      <c r="E8" s="15">
-        <v>960000</v>
+      <c r="E8" s="23">
+        <v>860748</v>
       </c>
       <c r="F8" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G8" s="15">
         <v>167000</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J8" s="23">
+        <v>1235</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M8" s="23">
+        <v>485</v>
+      </c>
+      <c r="N8" s="23">
+        <v>280</v>
+      </c>
+      <c r="O8" s="23">
+        <v>15000</v>
       </c>
       <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="23">
+        <v>47673</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>2031</v>
       </c>
-      <c r="B9" s="15">
-        <v>1760000</v>
+      <c r="B9" s="23">
+        <v>2024431</v>
       </c>
       <c r="C9" s="15">
         <v>57100000</v>
@@ -3232,79 +3288,79 @@
       <c r="D9" s="15">
         <v>58100000</v>
       </c>
-      <c r="E9" s="15">
-        <v>960000</v>
+      <c r="E9" s="23">
+        <v>860748</v>
       </c>
       <c r="F9" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G9" s="15">
         <v>167000</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J9" s="23">
+        <v>1235</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M9" s="23">
+        <v>485</v>
+      </c>
+      <c r="N9" s="23">
+        <v>280</v>
+      </c>
+      <c r="O9" s="23">
+        <v>15000</v>
       </c>
       <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="23">
+        <v>47673</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>2032</v>
       </c>
-      <c r="B10" s="15">
-        <v>1760000</v>
+      <c r="B10" s="23">
+        <v>2024431</v>
       </c>
       <c r="C10" s="15">
         <v>57100000</v>
@@ -3312,79 +3368,79 @@
       <c r="D10" s="15">
         <v>58100000</v>
       </c>
-      <c r="E10" s="15">
-        <v>960000</v>
+      <c r="E10" s="23">
+        <v>860748</v>
       </c>
       <c r="F10" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G10" s="15">
         <v>167000</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J10" s="23">
+        <v>1235</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M10" s="23">
+        <v>485</v>
+      </c>
+      <c r="N10" s="23">
+        <v>280</v>
+      </c>
+      <c r="O10" s="23">
+        <v>15000</v>
       </c>
       <c r="P10">
-        <v>1</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>47673</v>
       </c>
       <c r="R10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>2033</v>
       </c>
-      <c r="B11" s="15">
-        <v>1760000</v>
+      <c r="B11" s="23">
+        <v>2024431</v>
       </c>
       <c r="C11" s="15">
         <v>57100000</v>
@@ -3392,79 +3448,79 @@
       <c r="D11" s="15">
         <v>58100000</v>
       </c>
-      <c r="E11" s="15">
-        <v>960000</v>
+      <c r="E11" s="23">
+        <v>860748</v>
       </c>
       <c r="F11" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G11" s="15">
         <v>167000</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J11" s="23">
+        <v>1235</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M11" s="23">
+        <v>485</v>
+      </c>
+      <c r="N11" s="23">
+        <v>280</v>
+      </c>
+      <c r="O11" s="23">
+        <v>15000</v>
       </c>
       <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="23">
+        <v>47673</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>2034</v>
       </c>
-      <c r="B12" s="15">
-        <v>1760000</v>
+      <c r="B12" s="23">
+        <v>2024431</v>
       </c>
       <c r="C12" s="15">
         <v>57100000</v>
@@ -3472,79 +3528,79 @@
       <c r="D12" s="15">
         <v>58100000</v>
       </c>
-      <c r="E12" s="15">
-        <v>960000</v>
+      <c r="E12" s="23">
+        <v>860748</v>
       </c>
       <c r="F12" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G12" s="15">
         <v>167000</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J12" s="23">
+        <v>1235</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M12" s="23">
+        <v>485</v>
+      </c>
+      <c r="N12" s="23">
+        <v>280</v>
+      </c>
+      <c r="O12" s="23">
+        <v>15000</v>
       </c>
       <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="23">
+        <v>47673</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>2035</v>
       </c>
-      <c r="B13" s="15">
-        <v>1760000</v>
+      <c r="B13" s="23">
+        <v>2024431</v>
       </c>
       <c r="C13" s="15">
         <v>57100000</v>
@@ -3552,79 +3608,79 @@
       <c r="D13" s="15">
         <v>58100000</v>
       </c>
-      <c r="E13" s="15">
-        <v>960000</v>
+      <c r="E13" s="23">
+        <v>860748</v>
       </c>
       <c r="F13" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G13" s="15">
         <v>167000</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J13" s="23">
+        <v>1235</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M13" s="23">
+        <v>485</v>
+      </c>
+      <c r="N13" s="23">
+        <v>280</v>
+      </c>
+      <c r="O13" s="23">
+        <v>15000</v>
       </c>
       <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="23">
+        <v>47673</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>2036</v>
       </c>
-      <c r="B14" s="15">
-        <v>1760000</v>
+      <c r="B14" s="23">
+        <v>2024431</v>
       </c>
       <c r="C14" s="15">
         <v>57100000</v>
@@ -3632,79 +3688,79 @@
       <c r="D14" s="15">
         <v>58100000</v>
       </c>
-      <c r="E14" s="15">
-        <v>960000</v>
+      <c r="E14" s="23">
+        <v>860748</v>
       </c>
       <c r="F14" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G14" s="15">
         <v>167000</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J14" s="23">
+        <v>1235</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M14" s="23">
+        <v>485</v>
+      </c>
+      <c r="N14" s="23">
+        <v>280</v>
+      </c>
+      <c r="O14" s="23">
+        <v>15000</v>
       </c>
       <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="23">
+        <v>47673</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>2037</v>
       </c>
-      <c r="B15" s="15">
-        <v>1760000</v>
+      <c r="B15" s="23">
+        <v>2024431</v>
       </c>
       <c r="C15" s="15">
         <v>57100000</v>
@@ -3712,79 +3768,79 @@
       <c r="D15" s="15">
         <v>58100000</v>
       </c>
-      <c r="E15" s="15">
-        <v>960000</v>
+      <c r="E15" s="23">
+        <v>860748</v>
       </c>
       <c r="F15" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G15" s="15">
         <v>167000</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J15" s="23">
+        <v>1235</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M15" s="23">
+        <v>485</v>
+      </c>
+      <c r="N15" s="23">
+        <v>280</v>
+      </c>
+      <c r="O15" s="23">
+        <v>15000</v>
       </c>
       <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="Q15">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="23">
+        <v>47673</v>
       </c>
       <c r="R15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>2038</v>
       </c>
-      <c r="B16" s="15">
-        <v>1760000</v>
+      <c r="B16" s="23">
+        <v>2024431</v>
       </c>
       <c r="C16" s="15">
         <v>57100000</v>
@@ -3792,79 +3848,79 @@
       <c r="D16" s="15">
         <v>58100000</v>
       </c>
-      <c r="E16" s="15">
-        <v>960000</v>
+      <c r="E16" s="23">
+        <v>860748</v>
       </c>
       <c r="F16" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G16" s="15">
         <v>167000</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J16" s="23">
+        <v>1235</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M16" s="23">
+        <v>485</v>
+      </c>
+      <c r="N16" s="23">
+        <v>280</v>
+      </c>
+      <c r="O16" s="23">
+        <v>15000</v>
       </c>
       <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="23">
+        <v>47673</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>2039</v>
       </c>
-      <c r="B17" s="15">
-        <v>1760000</v>
+      <c r="B17" s="23">
+        <v>2024431</v>
       </c>
       <c r="C17" s="15">
         <v>57100000</v>
@@ -3872,79 +3928,79 @@
       <c r="D17" s="15">
         <v>58100000</v>
       </c>
-      <c r="E17" s="15">
-        <v>960000</v>
+      <c r="E17" s="23">
+        <v>860748</v>
       </c>
       <c r="F17" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G17" s="15">
         <v>167000</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J17" s="23">
+        <v>1235</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M17" s="23">
+        <v>485</v>
+      </c>
+      <c r="N17" s="23">
+        <v>280</v>
+      </c>
+      <c r="O17" s="23">
+        <v>15000</v>
       </c>
       <c r="P17">
-        <v>1</v>
-      </c>
-      <c r="Q17">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="23">
+        <v>47673</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>2040</v>
       </c>
-      <c r="B18" s="15">
-        <v>1760000</v>
+      <c r="B18" s="23">
+        <v>2024431</v>
       </c>
       <c r="C18" s="15">
         <v>57100000</v>
@@ -3952,79 +4008,79 @@
       <c r="D18" s="15">
         <v>58100000</v>
       </c>
-      <c r="E18" s="15">
-        <v>960000</v>
+      <c r="E18" s="23">
+        <v>860748</v>
       </c>
       <c r="F18" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G18" s="15">
         <v>167000</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J18" s="23">
+        <v>1235</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M18" s="23">
+        <v>485</v>
+      </c>
+      <c r="N18" s="23">
+        <v>280</v>
+      </c>
+      <c r="O18" s="23">
+        <v>15000</v>
       </c>
       <c r="P18">
-        <v>1</v>
-      </c>
-      <c r="Q18">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="23">
+        <v>47673</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>2041</v>
       </c>
-      <c r="B19" s="15">
-        <v>1760000</v>
+      <c r="B19" s="23">
+        <v>2024431</v>
       </c>
       <c r="C19" s="15">
         <v>57100000</v>
@@ -4032,79 +4088,79 @@
       <c r="D19" s="15">
         <v>58100000</v>
       </c>
-      <c r="E19" s="15">
-        <v>960000</v>
+      <c r="E19" s="23">
+        <v>860748</v>
       </c>
       <c r="F19" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G19" s="15">
         <v>167000</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J19" s="23">
+        <v>1235</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M19" s="23">
+        <v>485</v>
+      </c>
+      <c r="N19" s="23">
+        <v>280</v>
+      </c>
+      <c r="O19" s="23">
+        <v>15000</v>
       </c>
       <c r="P19">
-        <v>1</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="23">
+        <v>47673</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>2042</v>
       </c>
-      <c r="B20" s="15">
-        <v>1760000</v>
+      <c r="B20" s="23">
+        <v>2024431</v>
       </c>
       <c r="C20" s="15">
         <v>57100000</v>
@@ -4112,79 +4168,79 @@
       <c r="D20" s="15">
         <v>58100000</v>
       </c>
-      <c r="E20" s="15">
-        <v>960000</v>
+      <c r="E20" s="23">
+        <v>860748</v>
       </c>
       <c r="F20" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G20" s="15">
         <v>167000</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J20" s="23">
+        <v>1235</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M20" s="23">
+        <v>485</v>
+      </c>
+      <c r="N20" s="23">
+        <v>280</v>
+      </c>
+      <c r="O20" s="23">
+        <v>15000</v>
       </c>
       <c r="P20">
-        <v>1</v>
-      </c>
-      <c r="Q20">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="23">
+        <v>47673</v>
       </c>
       <c r="R20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>2043</v>
       </c>
-      <c r="B21" s="15">
-        <v>1760000</v>
+      <c r="B21" s="23">
+        <v>2024431</v>
       </c>
       <c r="C21" s="15">
         <v>57100000</v>
@@ -4192,79 +4248,79 @@
       <c r="D21" s="15">
         <v>58100000</v>
       </c>
-      <c r="E21" s="15">
-        <v>960000</v>
+      <c r="E21" s="23">
+        <v>860748</v>
       </c>
       <c r="F21" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G21" s="15">
         <v>167000</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J21" s="23">
+        <v>1235</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M21" s="23">
+        <v>485</v>
+      </c>
+      <c r="N21" s="23">
+        <v>280</v>
+      </c>
+      <c r="O21" s="23">
+        <v>15000</v>
       </c>
       <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>47673</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>2044</v>
       </c>
-      <c r="B22" s="15">
-        <v>1760000</v>
+      <c r="B22" s="23">
+        <v>2024431</v>
       </c>
       <c r="C22" s="15">
         <v>57100000</v>
@@ -4272,79 +4328,79 @@
       <c r="D22" s="15">
         <v>58100000</v>
       </c>
-      <c r="E22" s="15">
-        <v>960000</v>
+      <c r="E22" s="23">
+        <v>860748</v>
       </c>
       <c r="F22" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G22" s="15">
         <v>167000</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J22" s="23">
+        <v>1235</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M22" s="23">
+        <v>485</v>
+      </c>
+      <c r="N22" s="23">
+        <v>280</v>
+      </c>
+      <c r="O22" s="23">
+        <v>15000</v>
       </c>
       <c r="P22">
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="23">
+        <v>47673</v>
       </c>
       <c r="R22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>2045</v>
       </c>
-      <c r="B23" s="15">
-        <v>1760000</v>
+      <c r="B23" s="23">
+        <v>2024431</v>
       </c>
       <c r="C23" s="15">
         <v>57100000</v>
@@ -4352,79 +4408,79 @@
       <c r="D23" s="15">
         <v>58100000</v>
       </c>
-      <c r="E23" s="15">
-        <v>960000</v>
+      <c r="E23" s="23">
+        <v>860748</v>
       </c>
       <c r="F23" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G23" s="15">
         <v>167000</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J23" s="23">
+        <v>1235</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M23" s="23">
+        <v>485</v>
+      </c>
+      <c r="N23" s="23">
+        <v>280</v>
+      </c>
+      <c r="O23" s="23">
+        <v>15000</v>
       </c>
       <c r="P23">
-        <v>1</v>
-      </c>
-      <c r="Q23">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="23">
+        <v>47673</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>2046</v>
       </c>
-      <c r="B24" s="15">
-        <v>1760000</v>
+      <c r="B24" s="23">
+        <v>2024431</v>
       </c>
       <c r="C24" s="15">
         <v>57100000</v>
@@ -4432,79 +4488,79 @@
       <c r="D24" s="15">
         <v>58100000</v>
       </c>
-      <c r="E24" s="15">
-        <v>960000</v>
+      <c r="E24" s="23">
+        <v>860748</v>
       </c>
       <c r="F24" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G24" s="15">
         <v>167000</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J24" s="23">
+        <v>1235</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M24" s="23">
+        <v>485</v>
+      </c>
+      <c r="N24" s="23">
+        <v>280</v>
+      </c>
+      <c r="O24" s="23">
+        <v>15000</v>
       </c>
       <c r="P24">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="23">
+        <v>47673</v>
       </c>
       <c r="R24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>2047</v>
       </c>
-      <c r="B25" s="15">
-        <v>1760000</v>
+      <c r="B25" s="23">
+        <v>2024431</v>
       </c>
       <c r="C25" s="15">
         <v>57100000</v>
@@ -4512,79 +4568,79 @@
       <c r="D25" s="15">
         <v>58100000</v>
       </c>
-      <c r="E25" s="15">
-        <v>960000</v>
+      <c r="E25" s="23">
+        <v>860748</v>
       </c>
       <c r="F25" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G25" s="15">
         <v>167000</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J25" s="23">
+        <v>1235</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M25" s="23">
+        <v>485</v>
+      </c>
+      <c r="N25" s="23">
+        <v>280</v>
+      </c>
+      <c r="O25" s="23">
+        <v>15000</v>
       </c>
       <c r="P25">
-        <v>1</v>
-      </c>
-      <c r="Q25">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>47673</v>
       </c>
       <c r="R25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>2048</v>
       </c>
-      <c r="B26" s="15">
-        <v>1760000</v>
+      <c r="B26" s="23">
+        <v>2024431</v>
       </c>
       <c r="C26" s="15">
         <v>57100000</v>
@@ -4592,79 +4648,79 @@
       <c r="D26" s="15">
         <v>58100000</v>
       </c>
-      <c r="E26" s="15">
-        <v>960000</v>
+      <c r="E26" s="23">
+        <v>860748</v>
       </c>
       <c r="F26" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G26" s="15">
         <v>167000</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J26" s="23">
+        <v>1235</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M26" s="23">
+        <v>485</v>
+      </c>
+      <c r="N26" s="23">
+        <v>280</v>
+      </c>
+      <c r="O26" s="23">
+        <v>15000</v>
       </c>
       <c r="P26">
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="23">
+        <v>47673</v>
       </c>
       <c r="R26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>2049</v>
       </c>
-      <c r="B27" s="15">
-        <v>1760000</v>
+      <c r="B27" s="23">
+        <v>2024431</v>
       </c>
       <c r="C27" s="15">
         <v>57100000</v>
@@ -4672,79 +4728,79 @@
       <c r="D27" s="15">
         <v>58100000</v>
       </c>
-      <c r="E27" s="15">
-        <v>960000</v>
+      <c r="E27" s="23">
+        <v>860748</v>
       </c>
       <c r="F27" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G27" s="15">
         <v>167000</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J27" s="23">
+        <v>1235</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M27" s="23">
+        <v>485</v>
+      </c>
+      <c r="N27" s="23">
+        <v>280</v>
+      </c>
+      <c r="O27" s="23">
+        <v>15000</v>
       </c>
       <c r="P27">
-        <v>1</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="23">
+        <v>47673</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>2050</v>
       </c>
-      <c r="B28" s="15">
-        <v>1760000</v>
+      <c r="B28" s="23">
+        <v>2024431</v>
       </c>
       <c r="C28" s="15">
         <v>57100000</v>
@@ -4752,71 +4808,71 @@
       <c r="D28" s="15">
         <v>58100000</v>
       </c>
-      <c r="E28" s="15">
-        <v>960000</v>
+      <c r="E28" s="23">
+        <v>860748</v>
       </c>
       <c r="F28" s="15">
-        <v>1961</v>
+        <v>2064.0329999999999</v>
       </c>
       <c r="G28" s="15">
         <v>167000</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
+        <v>999999999</v>
+      </c>
+      <c r="J28" s="23">
+        <v>1235</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-      <c r="O28">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M28" s="23">
+        <v>485</v>
+      </c>
+      <c r="N28" s="23">
+        <v>280</v>
+      </c>
+      <c r="O28" s="23">
+        <v>15000</v>
       </c>
       <c r="P28">
-        <v>1</v>
-      </c>
-      <c r="Q28">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="23">
+        <v>47673</v>
       </c>
       <c r="R28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="Y28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9414,22 +9470,22 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C2">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F2">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G2">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -9438,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -9447,19 +9503,19 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O2">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P2">
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -9494,22 +9550,22 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C3">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F3">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G3">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -9518,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -9527,19 +9583,19 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P3">
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -9574,22 +9630,22 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C4">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F4">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G4">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -9598,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -9607,19 +9663,19 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P4">
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -9654,22 +9710,22 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C5">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F5">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G5">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -9678,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -9687,19 +9743,19 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P5">
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -9734,22 +9790,22 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C6">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F6">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G6">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -9758,7 +9814,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -9767,19 +9823,19 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P6">
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -9814,22 +9870,22 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C7">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F7">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G7">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -9838,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -9847,19 +9903,19 @@
         <v>1</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P7">
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -9894,22 +9950,22 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C8">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F8">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G8">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -9918,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -9927,19 +9983,19 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -9974,22 +10030,22 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C9">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F9">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G9">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -9998,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -10007,19 +10063,19 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P9">
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -10054,22 +10110,22 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C10">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F10">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G10">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -10078,7 +10134,7 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -10087,19 +10143,19 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O10">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P10">
         <v>1</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -10134,22 +10190,22 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C11">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F11">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G11">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -10158,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -10167,19 +10223,19 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P11">
         <v>1</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -10214,22 +10270,22 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C12">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F12">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G12">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -10238,7 +10294,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -10247,19 +10303,19 @@
         <v>1</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P12">
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -10294,22 +10350,22 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C13">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F13">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G13">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -10318,7 +10374,7 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -10327,19 +10383,19 @@
         <v>1</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P13">
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -10374,22 +10430,22 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C14">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F14">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G14">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -10398,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -10407,19 +10463,19 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P14">
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -10454,22 +10510,22 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C15">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F15">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G15">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -10478,7 +10534,7 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -10487,19 +10543,19 @@
         <v>1</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P15">
         <v>1</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -10534,22 +10590,22 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C16">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F16">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G16">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -10558,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -10567,19 +10623,19 @@
         <v>1</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P16">
         <v>1</v>
       </c>
       <c r="Q16">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -10614,22 +10670,22 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C17">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F17">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G17">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -10638,7 +10694,7 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -10647,19 +10703,19 @@
         <v>1</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O17">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P17">
         <v>1</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -10694,22 +10750,22 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C18">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F18">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G18">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -10718,7 +10774,7 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -10727,19 +10783,19 @@
         <v>1</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P18">
         <v>1</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -10774,22 +10830,22 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C19">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F19">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G19">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -10798,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -10807,19 +10863,19 @@
         <v>1</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P19">
         <v>1</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -10854,22 +10910,22 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C20">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F20">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G20">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -10878,7 +10934,7 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -10887,19 +10943,19 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O20">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P20">
         <v>1</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -10934,22 +10990,22 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C21">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F21">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G21">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -10958,7 +11014,7 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -10967,19 +11023,19 @@
         <v>1</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P21">
         <v>1</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -11014,22 +11070,22 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C22">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F22">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G22">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -11038,7 +11094,7 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -11047,19 +11103,19 @@
         <v>1</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P22">
         <v>1</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -11094,22 +11150,22 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C23">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F23">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G23">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -11118,7 +11174,7 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -11127,19 +11183,19 @@
         <v>1</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P23">
         <v>1</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -11174,22 +11230,22 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C24">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F24">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G24">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -11198,7 +11254,7 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -11207,19 +11263,19 @@
         <v>1</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P24">
         <v>1</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -11254,22 +11310,22 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C25">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F25">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G25">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -11278,7 +11334,7 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -11287,19 +11343,19 @@
         <v>1</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P25">
         <v>1</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -11334,22 +11390,22 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C26">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F26">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G26">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -11358,7 +11414,7 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -11367,19 +11423,19 @@
         <v>1</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O26">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P26">
         <v>1</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -11414,22 +11470,22 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C27">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F27">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G27">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -11438,7 +11494,7 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -11447,19 +11503,19 @@
         <v>1</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P27">
         <v>1</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -11494,22 +11550,22 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>0.25</v>
+        <v>3.1422977119900275E-2</v>
       </c>
       <c r="C28">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>6.5000000000000002E-2</v>
+        <v>3.5137850036208979E-2</v>
       </c>
       <c r="F28">
-        <v>0.25</v>
+        <v>3.8659213057142858E-2</v>
       </c>
       <c r="G28">
-        <v>0.06</v>
+        <v>0.14503283901238367</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -11518,7 +11574,7 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>8.7983756844890182E-3</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -11527,19 +11583,19 @@
         <v>1</v>
       </c>
       <c r="M28">
-        <v>1</v>
+        <v>4.2719999999999998E-3</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>7.9640718562874246E-2</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>1.0031552557202004E-2</v>
       </c>
       <c r="P28">
         <v>1</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>1.2865132125632679E-2</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -11664,22 +11720,22 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -11744,22 +11800,22 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -11824,22 +11880,22 @@
         <v>2026</v>
       </c>
       <c r="B4">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -11904,22 +11960,22 @@
         <v>2027</v>
       </c>
       <c r="B5">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -11984,22 +12040,22 @@
         <v>2028</v>
       </c>
       <c r="B6">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -12064,22 +12120,22 @@
         <v>2029</v>
       </c>
       <c r="B7">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -12144,22 +12200,22 @@
         <v>2030</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -12224,22 +12280,22 @@
         <v>2031</v>
       </c>
       <c r="B9">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -12304,22 +12360,22 @@
         <v>2032</v>
       </c>
       <c r="B10">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -12384,22 +12440,22 @@
         <v>2033</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -12464,22 +12520,22 @@
         <v>2034</v>
       </c>
       <c r="B12">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -12544,22 +12600,22 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -12624,22 +12680,22 @@
         <v>2036</v>
       </c>
       <c r="B14">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -12704,22 +12760,22 @@
         <v>2037</v>
       </c>
       <c r="B15">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -12784,22 +12840,22 @@
         <v>2038</v>
       </c>
       <c r="B16">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -12864,22 +12920,22 @@
         <v>2039</v>
       </c>
       <c r="B17">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -12944,22 +13000,22 @@
         <v>2040</v>
       </c>
       <c r="B18">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -13024,22 +13080,22 @@
         <v>2041</v>
       </c>
       <c r="B19">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -13104,22 +13160,22 @@
         <v>2042</v>
       </c>
       <c r="B20">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -13184,22 +13240,22 @@
         <v>2043</v>
       </c>
       <c r="B21">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -13264,22 +13320,22 @@
         <v>2044</v>
       </c>
       <c r="B22">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -13344,22 +13400,22 @@
         <v>2045</v>
       </c>
       <c r="B23">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -13424,22 +13480,22 @@
         <v>2046</v>
       </c>
       <c r="B24">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -13504,22 +13560,22 @@
         <v>2047</v>
       </c>
       <c r="B25">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -13584,22 +13640,22 @@
         <v>2048</v>
       </c>
       <c r="B26">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -13664,22 +13720,22 @@
         <v>2049</v>
       </c>
       <c r="B27">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -13744,22 +13800,22 @@
         <v>2050</v>
       </c>
       <c r="B28">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>6.5000000000000002E-2</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -27521,6 +27577,26 @@
   </sheetData>
   <autoFilter ref="B1:B109" xr:uid="{DB5FB19D-A699-4685-BD4E-A72E73D671DD}"/>
   <mergeCells count="27">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A82:A85"/>
@@ -27528,26 +27604,6 @@
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input_urbsextensionv1.xlsx
+++ b/Input_urbsextensionv1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1155" documentId="13_ncr:1_{A1CEE875-B6E7-4616-ADB8-CAA4FD821F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{898C7E9C-83DA-4DD8-8EF3-751FB916CEA0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="10" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="8" xr2:uid="{81864710-3A67-40FC-ABA1-4EF02E4F8A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">gas_block!$B$1:$B$109</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -920,11 +919,11 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -2719,7 +2718,7 @@
       <c r="A2" s="14">
         <v>2024</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="22">
         <v>2024431</v>
       </c>
       <c r="C2" s="15">
@@ -2728,7 +2727,7 @@
       <c r="D2" s="15">
         <v>58100000</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="22">
         <v>860748</v>
       </c>
       <c r="F2" s="15">
@@ -2743,7 +2742,7 @@
       <c r="I2">
         <v>999999999</v>
       </c>
-      <c r="J2" s="23">
+      <c r="J2" s="22">
         <v>1235</v>
       </c>
       <c r="K2">
@@ -2752,19 +2751,19 @@
       <c r="L2">
         <v>0</v>
       </c>
-      <c r="M2" s="23">
+      <c r="M2" s="22">
         <v>485</v>
       </c>
-      <c r="N2" s="23">
+      <c r="N2" s="22">
         <v>280</v>
       </c>
-      <c r="O2" s="23">
+      <c r="O2" s="22">
         <v>15000</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
-      <c r="Q2" s="23">
+      <c r="Q2" s="22">
         <v>47673</v>
       </c>
       <c r="R2">
@@ -2799,7 +2798,7 @@
       <c r="A3" s="14">
         <v>2025</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>2024431</v>
       </c>
       <c r="C3" s="15">
@@ -2808,7 +2807,7 @@
       <c r="D3" s="15">
         <v>58100000</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="22">
         <v>860748</v>
       </c>
       <c r="F3" s="15">
@@ -2823,7 +2822,7 @@
       <c r="I3">
         <v>999999999</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="22">
         <v>1235</v>
       </c>
       <c r="K3">
@@ -2832,19 +2831,19 @@
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="22">
         <v>485</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="22">
         <v>280</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="22">
         <v>15000</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="22">
         <v>47673</v>
       </c>
       <c r="R3">
@@ -2879,7 +2878,7 @@
       <c r="A4" s="14">
         <v>2026</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="22">
         <v>2024431</v>
       </c>
       <c r="C4" s="15">
@@ -2888,7 +2887,7 @@
       <c r="D4" s="15">
         <v>58100000</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="22">
         <v>860748</v>
       </c>
       <c r="F4" s="15">
@@ -2903,7 +2902,7 @@
       <c r="I4">
         <v>999999999</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="22">
         <v>1235</v>
       </c>
       <c r="K4">
@@ -2912,19 +2911,19 @@
       <c r="L4">
         <v>0</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="22">
         <v>485</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="22">
         <v>280</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="22">
         <v>15000</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
-      <c r="Q4" s="23">
+      <c r="Q4" s="22">
         <v>47673</v>
       </c>
       <c r="R4">
@@ -2959,7 +2958,7 @@
       <c r="A5" s="14">
         <v>2027</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <v>2024431</v>
       </c>
       <c r="C5" s="15">
@@ -2968,7 +2967,7 @@
       <c r="D5" s="15">
         <v>58100000</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="22">
         <v>860748</v>
       </c>
       <c r="F5" s="15">
@@ -2983,7 +2982,7 @@
       <c r="I5">
         <v>999999999</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="22">
         <v>1235</v>
       </c>
       <c r="K5">
@@ -2992,19 +2991,19 @@
       <c r="L5">
         <v>0</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="22">
         <v>485</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="22">
         <v>280</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="22">
         <v>15000</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="22">
         <v>47673</v>
       </c>
       <c r="R5">
@@ -3039,7 +3038,7 @@
       <c r="A6" s="14">
         <v>2028</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="22">
         <v>2024431</v>
       </c>
       <c r="C6" s="15">
@@ -3048,7 +3047,7 @@
       <c r="D6" s="15">
         <v>58100000</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <v>860748</v>
       </c>
       <c r="F6" s="15">
@@ -3063,7 +3062,7 @@
       <c r="I6">
         <v>999999999</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="22">
         <v>1235</v>
       </c>
       <c r="K6">
@@ -3072,19 +3071,19 @@
       <c r="L6">
         <v>0</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="22">
         <v>485</v>
       </c>
-      <c r="N6" s="23">
+      <c r="N6" s="22">
         <v>280</v>
       </c>
-      <c r="O6" s="23">
+      <c r="O6" s="22">
         <v>15000</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="22">
         <v>47673</v>
       </c>
       <c r="R6">
@@ -3119,7 +3118,7 @@
       <c r="A7" s="14">
         <v>2029</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="22">
         <v>2024431</v>
       </c>
       <c r="C7" s="15">
@@ -3128,7 +3127,7 @@
       <c r="D7" s="15">
         <v>58100000</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>860748</v>
       </c>
       <c r="F7" s="15">
@@ -3143,7 +3142,7 @@
       <c r="I7">
         <v>999999999</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="22">
         <v>1235</v>
       </c>
       <c r="K7">
@@ -3152,19 +3151,19 @@
       <c r="L7">
         <v>0</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="22">
         <v>485</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="22">
         <v>280</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="22">
         <v>15000</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="22">
         <v>47673</v>
       </c>
       <c r="R7">
@@ -3199,7 +3198,7 @@
       <c r="A8" s="14">
         <v>2030</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <v>2024431</v>
       </c>
       <c r="C8" s="15">
@@ -3208,7 +3207,7 @@
       <c r="D8" s="15">
         <v>58100000</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <v>860748</v>
       </c>
       <c r="F8" s="15">
@@ -3223,7 +3222,7 @@
       <c r="I8">
         <v>999999999</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="22">
         <v>1235</v>
       </c>
       <c r="K8">
@@ -3232,19 +3231,19 @@
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="22">
         <v>485</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="22">
         <v>280</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="22">
         <v>15000</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="22">
         <v>47673</v>
       </c>
       <c r="R8">
@@ -3279,7 +3278,7 @@
       <c r="A9" s="14">
         <v>2031</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="22">
         <v>2024431</v>
       </c>
       <c r="C9" s="15">
@@ -3288,7 +3287,7 @@
       <c r="D9" s="15">
         <v>58100000</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="22">
         <v>860748</v>
       </c>
       <c r="F9" s="15">
@@ -3303,7 +3302,7 @@
       <c r="I9">
         <v>999999999</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="22">
         <v>1235</v>
       </c>
       <c r="K9">
@@ -3312,19 +3311,19 @@
       <c r="L9">
         <v>0</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="22">
         <v>485</v>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="22">
         <v>280</v>
       </c>
-      <c r="O9" s="23">
+      <c r="O9" s="22">
         <v>15000</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
-      <c r="Q9" s="23">
+      <c r="Q9" s="22">
         <v>47673</v>
       </c>
       <c r="R9">
@@ -3359,7 +3358,7 @@
       <c r="A10" s="14">
         <v>2032</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="22">
         <v>2024431</v>
       </c>
       <c r="C10" s="15">
@@ -3368,7 +3367,7 @@
       <c r="D10" s="15">
         <v>58100000</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <v>860748</v>
       </c>
       <c r="F10" s="15">
@@ -3383,7 +3382,7 @@
       <c r="I10">
         <v>999999999</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="22">
         <v>1235</v>
       </c>
       <c r="K10">
@@ -3392,19 +3391,19 @@
       <c r="L10">
         <v>0</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="22">
         <v>485</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="22">
         <v>280</v>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="22">
         <v>15000</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
-      <c r="Q10" s="23">
+      <c r="Q10" s="22">
         <v>47673</v>
       </c>
       <c r="R10">
@@ -3439,7 +3438,7 @@
       <c r="A11" s="14">
         <v>2033</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="22">
         <v>2024431</v>
       </c>
       <c r="C11" s="15">
@@ -3448,7 +3447,7 @@
       <c r="D11" s="15">
         <v>58100000</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="22">
         <v>860748</v>
       </c>
       <c r="F11" s="15">
@@ -3463,7 +3462,7 @@
       <c r="I11">
         <v>999999999</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="22">
         <v>1235</v>
       </c>
       <c r="K11">
@@ -3472,19 +3471,19 @@
       <c r="L11">
         <v>0</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="22">
         <v>485</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="22">
         <v>280</v>
       </c>
-      <c r="O11" s="23">
+      <c r="O11" s="22">
         <v>15000</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="Q11" s="22">
         <v>47673</v>
       </c>
       <c r="R11">
@@ -3519,7 +3518,7 @@
       <c r="A12" s="14">
         <v>2034</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="22">
         <v>2024431</v>
       </c>
       <c r="C12" s="15">
@@ -3528,7 +3527,7 @@
       <c r="D12" s="15">
         <v>58100000</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="22">
         <v>860748</v>
       </c>
       <c r="F12" s="15">
@@ -3543,7 +3542,7 @@
       <c r="I12">
         <v>999999999</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="22">
         <v>1235</v>
       </c>
       <c r="K12">
@@ -3552,19 +3551,19 @@
       <c r="L12">
         <v>0</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="22">
         <v>485</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="22">
         <v>280</v>
       </c>
-      <c r="O12" s="23">
+      <c r="O12" s="22">
         <v>15000</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
-      <c r="Q12" s="23">
+      <c r="Q12" s="22">
         <v>47673</v>
       </c>
       <c r="R12">
@@ -3599,7 +3598,7 @@
       <c r="A13" s="14">
         <v>2035</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="22">
         <v>2024431</v>
       </c>
       <c r="C13" s="15">
@@ -3608,7 +3607,7 @@
       <c r="D13" s="15">
         <v>58100000</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="22">
         <v>860748</v>
       </c>
       <c r="F13" s="15">
@@ -3623,7 +3622,7 @@
       <c r="I13">
         <v>999999999</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="22">
         <v>1235</v>
       </c>
       <c r="K13">
@@ -3632,19 +3631,19 @@
       <c r="L13">
         <v>0</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="22">
         <v>485</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="22">
         <v>280</v>
       </c>
-      <c r="O13" s="23">
+      <c r="O13" s="22">
         <v>15000</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
-      <c r="Q13" s="23">
+      <c r="Q13" s="22">
         <v>47673</v>
       </c>
       <c r="R13">
@@ -3679,7 +3678,7 @@
       <c r="A14" s="14">
         <v>2036</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="22">
         <v>2024431</v>
       </c>
       <c r="C14" s="15">
@@ -3688,7 +3687,7 @@
       <c r="D14" s="15">
         <v>58100000</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="22">
         <v>860748</v>
       </c>
       <c r="F14" s="15">
@@ -3703,7 +3702,7 @@
       <c r="I14">
         <v>999999999</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="22">
         <v>1235</v>
       </c>
       <c r="K14">
@@ -3712,19 +3711,19 @@
       <c r="L14">
         <v>0</v>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="22">
         <v>485</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="22">
         <v>280</v>
       </c>
-      <c r="O14" s="23">
+      <c r="O14" s="22">
         <v>15000</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
-      <c r="Q14" s="23">
+      <c r="Q14" s="22">
         <v>47673</v>
       </c>
       <c r="R14">
@@ -3759,7 +3758,7 @@
       <c r="A15" s="14">
         <v>2037</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="22">
         <v>2024431</v>
       </c>
       <c r="C15" s="15">
@@ -3768,7 +3767,7 @@
       <c r="D15" s="15">
         <v>58100000</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="22">
         <v>860748</v>
       </c>
       <c r="F15" s="15">
@@ -3783,7 +3782,7 @@
       <c r="I15">
         <v>999999999</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="22">
         <v>1235</v>
       </c>
       <c r="K15">
@@ -3792,19 +3791,19 @@
       <c r="L15">
         <v>0</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="22">
         <v>485</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="22">
         <v>280</v>
       </c>
-      <c r="O15" s="23">
+      <c r="O15" s="22">
         <v>15000</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
-      <c r="Q15" s="23">
+      <c r="Q15" s="22">
         <v>47673</v>
       </c>
       <c r="R15">
@@ -3839,7 +3838,7 @@
       <c r="A16" s="14">
         <v>2038</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="22">
         <v>2024431</v>
       </c>
       <c r="C16" s="15">
@@ -3848,7 +3847,7 @@
       <c r="D16" s="15">
         <v>58100000</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="22">
         <v>860748</v>
       </c>
       <c r="F16" s="15">
@@ -3863,7 +3862,7 @@
       <c r="I16">
         <v>999999999</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="22">
         <v>1235</v>
       </c>
       <c r="K16">
@@ -3872,19 +3871,19 @@
       <c r="L16">
         <v>0</v>
       </c>
-      <c r="M16" s="23">
+      <c r="M16" s="22">
         <v>485</v>
       </c>
-      <c r="N16" s="23">
+      <c r="N16" s="22">
         <v>280</v>
       </c>
-      <c r="O16" s="23">
+      <c r="O16" s="22">
         <v>15000</v>
       </c>
       <c r="P16">
         <v>0</v>
       </c>
-      <c r="Q16" s="23">
+      <c r="Q16" s="22">
         <v>47673</v>
       </c>
       <c r="R16">
@@ -3919,7 +3918,7 @@
       <c r="A17" s="14">
         <v>2039</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="22">
         <v>2024431</v>
       </c>
       <c r="C17" s="15">
@@ -3928,7 +3927,7 @@
       <c r="D17" s="15">
         <v>58100000</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="22">
         <v>860748</v>
       </c>
       <c r="F17" s="15">
@@ -3943,7 +3942,7 @@
       <c r="I17">
         <v>999999999</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="22">
         <v>1235</v>
       </c>
       <c r="K17">
@@ -3952,19 +3951,19 @@
       <c r="L17">
         <v>0</v>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="22">
         <v>485</v>
       </c>
-      <c r="N17" s="23">
+      <c r="N17" s="22">
         <v>280</v>
       </c>
-      <c r="O17" s="23">
+      <c r="O17" s="22">
         <v>15000</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
-      <c r="Q17" s="23">
+      <c r="Q17" s="22">
         <v>47673</v>
       </c>
       <c r="R17">
@@ -3999,7 +3998,7 @@
       <c r="A18" s="14">
         <v>2040</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="22">
         <v>2024431</v>
       </c>
       <c r="C18" s="15">
@@ -4008,7 +4007,7 @@
       <c r="D18" s="15">
         <v>58100000</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="22">
         <v>860748</v>
       </c>
       <c r="F18" s="15">
@@ -4023,7 +4022,7 @@
       <c r="I18">
         <v>999999999</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="22">
         <v>1235</v>
       </c>
       <c r="K18">
@@ -4032,19 +4031,19 @@
       <c r="L18">
         <v>0</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="22">
         <v>485</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="22">
         <v>280</v>
       </c>
-      <c r="O18" s="23">
+      <c r="O18" s="22">
         <v>15000</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
-      <c r="Q18" s="23">
+      <c r="Q18" s="22">
         <v>47673</v>
       </c>
       <c r="R18">
@@ -4079,7 +4078,7 @@
       <c r="A19" s="14">
         <v>2041</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="22">
         <v>2024431</v>
       </c>
       <c r="C19" s="15">
@@ -4088,7 +4087,7 @@
       <c r="D19" s="15">
         <v>58100000</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="22">
         <v>860748</v>
       </c>
       <c r="F19" s="15">
@@ -4103,7 +4102,7 @@
       <c r="I19">
         <v>999999999</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="22">
         <v>1235</v>
       </c>
       <c r="K19">
@@ -4112,19 +4111,19 @@
       <c r="L19">
         <v>0</v>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="22">
         <v>485</v>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="22">
         <v>280</v>
       </c>
-      <c r="O19" s="23">
+      <c r="O19" s="22">
         <v>15000</v>
       </c>
       <c r="P19">
         <v>0</v>
       </c>
-      <c r="Q19" s="23">
+      <c r="Q19" s="22">
         <v>47673</v>
       </c>
       <c r="R19">
@@ -4159,7 +4158,7 @@
       <c r="A20" s="14">
         <v>2042</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="22">
         <v>2024431</v>
       </c>
       <c r="C20" s="15">
@@ -4168,7 +4167,7 @@
       <c r="D20" s="15">
         <v>58100000</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="22">
         <v>860748</v>
       </c>
       <c r="F20" s="15">
@@ -4183,7 +4182,7 @@
       <c r="I20">
         <v>999999999</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="22">
         <v>1235</v>
       </c>
       <c r="K20">
@@ -4192,19 +4191,19 @@
       <c r="L20">
         <v>0</v>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="22">
         <v>485</v>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="22">
         <v>280</v>
       </c>
-      <c r="O20" s="23">
+      <c r="O20" s="22">
         <v>15000</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
-      <c r="Q20" s="23">
+      <c r="Q20" s="22">
         <v>47673</v>
       </c>
       <c r="R20">
@@ -4239,7 +4238,7 @@
       <c r="A21" s="14">
         <v>2043</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="22">
         <v>2024431</v>
       </c>
       <c r="C21" s="15">
@@ -4248,7 +4247,7 @@
       <c r="D21" s="15">
         <v>58100000</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="22">
         <v>860748</v>
       </c>
       <c r="F21" s="15">
@@ -4263,7 +4262,7 @@
       <c r="I21">
         <v>999999999</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="22">
         <v>1235</v>
       </c>
       <c r="K21">
@@ -4272,19 +4271,19 @@
       <c r="L21">
         <v>0</v>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="22">
         <v>485</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="22">
         <v>280</v>
       </c>
-      <c r="O21" s="23">
+      <c r="O21" s="22">
         <v>15000</v>
       </c>
       <c r="P21">
         <v>0</v>
       </c>
-      <c r="Q21" s="23">
+      <c r="Q21" s="22">
         <v>47673</v>
       </c>
       <c r="R21">
@@ -4319,7 +4318,7 @@
       <c r="A22" s="14">
         <v>2044</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B22" s="22">
         <v>2024431</v>
       </c>
       <c r="C22" s="15">
@@ -4328,7 +4327,7 @@
       <c r="D22" s="15">
         <v>58100000</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="22">
         <v>860748</v>
       </c>
       <c r="F22" s="15">
@@ -4343,7 +4342,7 @@
       <c r="I22">
         <v>999999999</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="22">
         <v>1235</v>
       </c>
       <c r="K22">
@@ -4352,19 +4351,19 @@
       <c r="L22">
         <v>0</v>
       </c>
-      <c r="M22" s="23">
+      <c r="M22" s="22">
         <v>485</v>
       </c>
-      <c r="N22" s="23">
+      <c r="N22" s="22">
         <v>280</v>
       </c>
-      <c r="O22" s="23">
+      <c r="O22" s="22">
         <v>15000</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
-      <c r="Q22" s="23">
+      <c r="Q22" s="22">
         <v>47673</v>
       </c>
       <c r="R22">
@@ -4399,7 +4398,7 @@
       <c r="A23" s="14">
         <v>2045</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="22">
         <v>2024431</v>
       </c>
       <c r="C23" s="15">
@@ -4408,7 +4407,7 @@
       <c r="D23" s="15">
         <v>58